--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -4114,7 +4114,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5050,7 +5050,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5463,7 +5463,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5502,7 +5502,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5986,7 +5986,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6430,7 +6430,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7528,7 +7528,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8763,7 +8763,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -9710,7 +9710,7 @@
     <col min="3" max="3" width="80.7109375" customWidth="1"/>
     <col min="4" max="5" width="20.7109375" customWidth="1"/>
     <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -148,6 +148,9 @@
     <t>Poster ID</t>
   </si>
   <si>
+    <t>Indico ID</t>
+  </si>
+  <si>
     <t>Screen ID</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t>Affiliation</t>
-  </si>
-  <si>
-    <t>Indico ID</t>
   </si>
   <si>
     <t>45</t>
@@ -4111,10 +4111,9 @@
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4144,51 +4143,51 @@
       <c r="A2" t="s">
         <v>1032</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166462</v>
+      </c>
+      <c r="D2" t="s">
         <v>1077</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>1122</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1141</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>124</v>
-      </c>
-      <c r="G2">
-        <v>166462</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>1033</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166486</v>
+      </c>
+      <c r="D3" t="s">
         <v>1078</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>1123</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1142</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>1177</v>
-      </c>
-      <c r="G3">
-        <v>166486</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>1034</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166515</v>
+      </c>
+      <c r="D4" t="s">
         <v>1079</v>
-      </c>
-      <c r="D4" t="s">
-        <v>189</v>
       </c>
       <c r="E4" t="s">
         <v>189</v>
@@ -4196,119 +4195,119 @@
       <c r="F4" t="s">
         <v>189</v>
       </c>
-      <c r="G4">
-        <v>166515</v>
+      <c r="G4" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>1035</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166545</v>
+      </c>
+      <c r="D5" t="s">
         <v>1080</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>1124</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1143</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>124</v>
-      </c>
-      <c r="G5">
-        <v>166545</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>1036</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166557</v>
+      </c>
+      <c r="D6" t="s">
         <v>1081</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>1125</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1144</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1178</v>
-      </c>
-      <c r="G6">
-        <v>166557</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>1037</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166566</v>
+      </c>
+      <c r="D7" t="s">
         <v>1082</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>95</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1145</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>124</v>
-      </c>
-      <c r="G7">
-        <v>166566</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>1038</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166600</v>
+      </c>
+      <c r="D8" t="s">
         <v>1083</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>660</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>1146</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>124</v>
-      </c>
-      <c r="G8">
-        <v>166600</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>1039</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166603</v>
+      </c>
+      <c r="D9" t="s">
         <v>1084</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>1126</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>1147</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>124</v>
-      </c>
-      <c r="G9">
-        <v>166603</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>1040</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166626</v>
+      </c>
+      <c r="D10" t="s">
         <v>1085</v>
-      </c>
-      <c r="D10" t="s">
-        <v>189</v>
       </c>
       <c r="E10" t="s">
         <v>189</v>
@@ -4316,636 +4315,636 @@
       <c r="F10" t="s">
         <v>189</v>
       </c>
-      <c r="G10">
-        <v>166626</v>
+      <c r="G10" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>1041</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166624</v>
+      </c>
+      <c r="D11" t="s">
         <v>1086</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>688</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1148</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>1027</v>
-      </c>
-      <c r="G11">
-        <v>166624</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>1042</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166628</v>
+      </c>
+      <c r="D12" t="s">
         <v>1087</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>90</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>1149</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>124</v>
-      </c>
-      <c r="G12">
-        <v>166628</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>1043</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166636</v>
+      </c>
+      <c r="D13" t="s">
         <v>1088</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1127</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1150</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>124</v>
-      </c>
-      <c r="G13">
-        <v>166636</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>1044</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166640</v>
+      </c>
+      <c r="D14" t="s">
         <v>1089</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>687</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1151</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>1179</v>
-      </c>
-      <c r="G14">
-        <v>166640</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>1045</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166668</v>
+      </c>
+      <c r="D15" t="s">
         <v>1090</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>884</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1152</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>124</v>
-      </c>
-      <c r="G15">
-        <v>166668</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>1046</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166682</v>
+      </c>
+      <c r="D16" t="s">
         <v>1091</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>289</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1153</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>124</v>
-      </c>
-      <c r="G16">
-        <v>166682</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>1047</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166705</v>
+      </c>
+      <c r="D17" t="s">
         <v>1092</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1128</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1154</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>124</v>
-      </c>
-      <c r="G17">
-        <v>166705</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>1048</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166716</v>
+      </c>
+      <c r="D18" t="s">
         <v>1093</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1129</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1155</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>1178</v>
-      </c>
-      <c r="G18">
-        <v>166716</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>1049</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166743</v>
+      </c>
+      <c r="D19" t="s">
         <v>1094</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>90</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1156</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>124</v>
-      </c>
-      <c r="G19">
-        <v>166743</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>1050</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166814</v>
+      </c>
+      <c r="D20" t="s">
         <v>1095</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1130</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1157</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>316</v>
-      </c>
-      <c r="G20">
-        <v>166814</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>1051</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166497</v>
+      </c>
+      <c r="D21" t="s">
         <v>1096</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>88</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1158</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>124</v>
-      </c>
-      <c r="G21">
-        <v>166497</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>1052</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166733</v>
+      </c>
+      <c r="D22" t="s">
         <v>1097</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>675</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1159</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>1180</v>
-      </c>
-      <c r="G22">
-        <v>166733</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>1053</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>166496</v>
+      </c>
+      <c r="D23" t="s">
         <v>1098</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>1131</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>1160</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>124</v>
-      </c>
-      <c r="G23">
-        <v>166496</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>1054</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>166783</v>
+      </c>
+      <c r="D24" t="s">
         <v>1099</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>286</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1161</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>124</v>
-      </c>
-      <c r="G24">
-        <v>166783</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>1055</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B25">
+        <v>166468</v>
+      </c>
+      <c r="D25" t="s">
         <v>1100</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>85</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>1162</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>124</v>
-      </c>
-      <c r="G25">
-        <v>166468</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>1056</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B26">
+        <v>166494</v>
+      </c>
+      <c r="D26" t="s">
         <v>1101</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>1127</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>1163</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>1181</v>
-      </c>
-      <c r="G26">
-        <v>166494</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>1057</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B27">
+        <v>166509</v>
+      </c>
+      <c r="D27" t="s">
         <v>1102</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>1132</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>1164</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>1182</v>
-      </c>
-      <c r="G27">
-        <v>166509</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>1058</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B28">
+        <v>166531</v>
+      </c>
+      <c r="D28" t="s">
         <v>1103</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>1133</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>1165</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>1183</v>
-      </c>
-      <c r="G28">
-        <v>166531</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>1059</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B29">
+        <v>166532</v>
+      </c>
+      <c r="D29" t="s">
         <v>1104</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>193</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>1166</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>124</v>
-      </c>
-      <c r="G29">
-        <v>166532</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>1060</v>
       </c>
-      <c r="C30" t="s">
+      <c r="B30">
+        <v>166559</v>
+      </c>
+      <c r="D30" t="s">
         <v>1105</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>196</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>1167</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>1184</v>
-      </c>
-      <c r="G30">
-        <v>166559</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>1061</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31">
+        <v>166564</v>
+      </c>
+      <c r="D31" t="s">
         <v>1106</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>90</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>1156</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>124</v>
-      </c>
-      <c r="G31">
-        <v>166564</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>1062</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32">
+        <v>166565</v>
+      </c>
+      <c r="D32" t="s">
         <v>1107</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>1134</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>1168</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>1185</v>
-      </c>
-      <c r="G32">
-        <v>166565</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>1063</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33">
+        <v>166606</v>
+      </c>
+      <c r="D33" t="s">
         <v>1108</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>1135</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>1169</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>124</v>
-      </c>
-      <c r="G33">
-        <v>166606</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>1064</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34">
+        <v>166658</v>
+      </c>
+      <c r="D34" t="s">
         <v>1109</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>1136</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>1170</v>
-      </c>
-      <c r="G34">
-        <v>166658</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>1065</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35">
+        <v>166667</v>
+      </c>
+      <c r="D35" t="s">
         <v>1110</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>90</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>1156</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>124</v>
-      </c>
-      <c r="G35">
-        <v>166667</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>1066</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36">
+        <v>166671</v>
+      </c>
+      <c r="D36" t="s">
         <v>1111</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>90</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>1171</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>124</v>
-      </c>
-      <c r="G36">
-        <v>166671</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>1067</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37">
+        <v>166684</v>
+      </c>
+      <c r="D37" t="s">
         <v>1112</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>678</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>1172</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>1186</v>
-      </c>
-      <c r="G37">
-        <v>166684</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>1068</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38">
+        <v>166730</v>
+      </c>
+      <c r="D38" t="s">
         <v>1113</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>445</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>741</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>124</v>
-      </c>
-      <c r="G38">
-        <v>166730</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>1069</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B39">
+        <v>166736</v>
+      </c>
+      <c r="D39" t="s">
         <v>1114</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>1137</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>1173</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>124</v>
-      </c>
-      <c r="G39">
-        <v>166736</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>1070</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40">
+        <v>166739</v>
+      </c>
+      <c r="D40" t="s">
         <v>1115</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>1138</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>1174</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>1187</v>
-      </c>
-      <c r="G40">
-        <v>166739</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>1071</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B41">
+        <v>166749</v>
+      </c>
+      <c r="D41" t="s">
         <v>1116</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>1139</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>1175</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>1188</v>
-      </c>
-      <c r="G41">
-        <v>166749</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>1072</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42">
+        <v>166766</v>
+      </c>
+      <c r="D42" t="s">
         <v>1117</v>
-      </c>
-      <c r="D42" t="s">
-        <v>189</v>
       </c>
       <c r="E42" t="s">
         <v>189</v>
@@ -4953,19 +4952,19 @@
       <c r="F42" t="s">
         <v>189</v>
       </c>
-      <c r="G42">
-        <v>166766</v>
+      <c r="G42" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>1073</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43">
+        <v>166778</v>
+      </c>
+      <c r="D43" t="s">
         <v>1118</v>
-      </c>
-      <c r="D43" t="s">
-        <v>189</v>
       </c>
       <c r="E43" t="s">
         <v>189</v>
@@ -4973,59 +4972,59 @@
       <c r="F43" t="s">
         <v>189</v>
       </c>
-      <c r="G43">
-        <v>166778</v>
+      <c r="G43" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>1074</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44">
+        <v>167683</v>
+      </c>
+      <c r="D44" t="s">
         <v>1119</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>87</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>106</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>1189</v>
-      </c>
-      <c r="G44">
-        <v>167683</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>1075</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45">
+        <v>167825</v>
+      </c>
+      <c r="D45" t="s">
         <v>1120</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>1140</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>1176</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>1190</v>
-      </c>
-      <c r="G45">
-        <v>167825</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>1076</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46">
+        <v>167830</v>
+      </c>
+      <c r="D46" t="s">
         <v>1121</v>
-      </c>
-      <c r="D46" t="s">
-        <v>189</v>
       </c>
       <c r="E46" t="s">
         <v>189</v>
@@ -5033,8 +5032,8 @@
       <c r="F46" t="s">
         <v>189</v>
       </c>
-      <c r="G46">
-        <v>167830</v>
+      <c r="G46" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -5047,10 +5046,9 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5080,374 +5078,374 @@
       <c r="A2" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166492</v>
+      </c>
+      <c r="D2" t="s">
         <v>66</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>85</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>104</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>123</v>
-      </c>
-      <c r="G2">
-        <v>166492</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166625</v>
+      </c>
+      <c r="D3" t="s">
         <v>67</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>86</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>105</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>124</v>
-      </c>
-      <c r="G3">
-        <v>166625</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>49</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166635</v>
+      </c>
+      <c r="D4" t="s">
         <v>68</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>87</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>106</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>124</v>
-      </c>
-      <c r="G4">
-        <v>166635</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>50</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166698</v>
+      </c>
+      <c r="D5" t="s">
         <v>69</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>88</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>107</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>124</v>
-      </c>
-      <c r="G5">
-        <v>166698</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>167674</v>
+      </c>
+      <c r="D6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>89</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>108</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>125</v>
-      </c>
-      <c r="G6">
-        <v>167674</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>52</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166697</v>
+      </c>
+      <c r="D7" t="s">
         <v>71</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>90</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>109</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>124</v>
-      </c>
-      <c r="G7">
-        <v>166697</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166811</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>91</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>110</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>126</v>
-      </c>
-      <c r="G8">
-        <v>166811</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>54</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166470</v>
+      </c>
+      <c r="D9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>92</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>111</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>124</v>
-      </c>
-      <c r="G9">
-        <v>166470</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166666</v>
+      </c>
+      <c r="D10" t="s">
         <v>74</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>93</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>112</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="G10">
-        <v>166666</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>56</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166501</v>
+      </c>
+      <c r="D11" t="s">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>94</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>113</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>127</v>
-      </c>
-      <c r="G11">
-        <v>166501</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>57</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166533</v>
+      </c>
+      <c r="D12" t="s">
         <v>76</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>95</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>114</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>128</v>
-      </c>
-      <c r="G12">
-        <v>166533</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>58</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166534</v>
+      </c>
+      <c r="D13" t="s">
         <v>77</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>96</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>115</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>129</v>
-      </c>
-      <c r="G13">
-        <v>166534</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166683</v>
+      </c>
+      <c r="D14" t="s">
         <v>78</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>97</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>116</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>124</v>
-      </c>
-      <c r="G14">
-        <v>166683</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>60</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166735</v>
+      </c>
+      <c r="D15" t="s">
         <v>79</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>117</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>130</v>
-      </c>
-      <c r="G15">
-        <v>166735</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166741</v>
+      </c>
+      <c r="D16" t="s">
         <v>80</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>99</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>118</v>
-      </c>
-      <c r="G16">
-        <v>166741</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166790</v>
+      </c>
+      <c r="D17" t="s">
         <v>81</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>100</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>119</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>131</v>
-      </c>
-      <c r="G17">
-        <v>166790</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>63</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166793</v>
+      </c>
+      <c r="D18" t="s">
         <v>82</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>101</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>120</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>132</v>
-      </c>
-      <c r="G18">
-        <v>166793</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>64</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166822</v>
+      </c>
+      <c r="D19" t="s">
         <v>83</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>102</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>121</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>133</v>
-      </c>
-      <c r="G19">
-        <v>166822</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>167676</v>
+      </c>
+      <c r="D20" t="s">
         <v>84</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>103</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>122</v>
-      </c>
-      <c r="G20">
-        <v>167676</v>
       </c>
     </row>
   </sheetData>
@@ -5460,10 +5458,9 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5499,10 +5496,9 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5532,239 +5528,239 @@
       <c r="A2" t="s">
         <v>134</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166466</v>
+      </c>
+      <c r="D2" t="s">
         <v>157</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>85</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>200</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>221</v>
-      </c>
-      <c r="G2">
-        <v>166466</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>135</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166467</v>
+      </c>
+      <c r="D3" t="s">
         <v>158</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>180</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>201</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>222</v>
-      </c>
-      <c r="G3">
-        <v>166467</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>136</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166519</v>
+      </c>
+      <c r="D4" t="s">
         <v>159</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>181</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>202</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>124</v>
-      </c>
-      <c r="G4">
-        <v>166519</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>137</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166550</v>
+      </c>
+      <c r="D5" t="s">
         <v>160</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>182</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>203</v>
-      </c>
-      <c r="G5">
-        <v>166550</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>138</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166645</v>
+      </c>
+      <c r="D6" t="s">
         <v>161</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>204</v>
-      </c>
-      <c r="G6">
-        <v>166645</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>139</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166643</v>
+      </c>
+      <c r="D7" t="s">
         <v>162</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>183</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>205</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>223</v>
-      </c>
-      <c r="G7">
-        <v>166643</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>140</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166685</v>
+      </c>
+      <c r="D8" t="s">
         <v>163</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>184</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>206</v>
-      </c>
-      <c r="G8">
-        <v>166685</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>141</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166810</v>
+      </c>
+      <c r="D9" t="s">
         <v>164</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>185</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>207</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>224</v>
-      </c>
-      <c r="G9">
-        <v>166810</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>142</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166740</v>
+      </c>
+      <c r="D10" t="s">
         <v>165</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>98</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>117</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>225</v>
-      </c>
-      <c r="G10">
-        <v>166740</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>143</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166754</v>
+      </c>
+      <c r="D11" t="s">
         <v>166</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>186</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>208</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>124</v>
-      </c>
-      <c r="G11">
-        <v>166754</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>144</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166775</v>
+      </c>
+      <c r="D12" t="s">
         <v>167</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>187</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>209</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>124</v>
-      </c>
-      <c r="G12">
-        <v>166775</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>145</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166475</v>
+      </c>
+      <c r="D13" t="s">
         <v>168</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>188</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>210</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>226</v>
-      </c>
-      <c r="G13">
-        <v>166475</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>146</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166476</v>
+      </c>
+      <c r="D14" t="s">
         <v>169</v>
-      </c>
-      <c r="D14" t="s">
-        <v>189</v>
       </c>
       <c r="E14" t="s">
         <v>189</v>
@@ -5772,205 +5768,205 @@
       <c r="F14" t="s">
         <v>189</v>
       </c>
-      <c r="G14">
-        <v>166476</v>
+      <c r="G14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>147</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166511</v>
+      </c>
+      <c r="D15" t="s">
         <v>170</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>190</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>211</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>227</v>
-      </c>
-      <c r="G15">
-        <v>166511</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>148</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166518</v>
+      </c>
+      <c r="D16" t="s">
         <v>171</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>191</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>212</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>124</v>
-      </c>
-      <c r="G16">
-        <v>166518</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>149</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166524</v>
+      </c>
+      <c r="D17" t="s">
         <v>172</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>192</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>213</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>228</v>
-      </c>
-      <c r="G17">
-        <v>166524</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>150</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166525</v>
+      </c>
+      <c r="D18" t="s">
         <v>173</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>193</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>214</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>124</v>
-      </c>
-      <c r="G18">
-        <v>166525</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>151</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166563</v>
+      </c>
+      <c r="D19" t="s">
         <v>174</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>194</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>215</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>229</v>
-      </c>
-      <c r="G19">
-        <v>166563</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>152</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166608</v>
+      </c>
+      <c r="D20" t="s">
         <v>175</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>195</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>216</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>230</v>
-      </c>
-      <c r="G20">
-        <v>166608</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>153</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166659</v>
+      </c>
+      <c r="D21" t="s">
         <v>176</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>196</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>217</v>
-      </c>
-      <c r="G21">
-        <v>166659</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>154</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166664</v>
+      </c>
+      <c r="D22" t="s">
         <v>177</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>197</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>218</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>124</v>
-      </c>
-      <c r="G22">
-        <v>166664</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>155</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>166727</v>
+      </c>
+      <c r="D23" t="s">
         <v>178</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>198</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>219</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>231</v>
-      </c>
-      <c r="G23">
-        <v>166727</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>156</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>166738</v>
+      </c>
+      <c r="D24" t="s">
         <v>179</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>199</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>220</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>124</v>
-      </c>
-      <c r="G24">
-        <v>166738</v>
       </c>
     </row>
   </sheetData>
@@ -5983,10 +5979,9 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6016,268 +6011,268 @@
       <c r="A2" t="s">
         <v>232</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166463</v>
+      </c>
+      <c r="D2" t="s">
         <v>253</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>274</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>293</v>
-      </c>
-      <c r="G2">
-        <v>166463</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>233</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166513</v>
+      </c>
+      <c r="D3" t="s">
         <v>254</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>275</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>294</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>229</v>
-      </c>
-      <c r="G3">
-        <v>166513</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>234</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166553</v>
+      </c>
+      <c r="D4" t="s">
         <v>255</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>276</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>295</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>124</v>
-      </c>
-      <c r="G4">
-        <v>166553</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>235</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166712</v>
+      </c>
+      <c r="D5" t="s">
         <v>256</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>180</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>296</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>124</v>
-      </c>
-      <c r="G5">
-        <v>166712</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>236</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166723</v>
+      </c>
+      <c r="D6" t="s">
         <v>257</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>277</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>297</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>313</v>
-      </c>
-      <c r="G6">
-        <v>166723</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>237</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166728</v>
+      </c>
+      <c r="D7" t="s">
         <v>258</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>278</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>298</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>124</v>
-      </c>
-      <c r="G7">
-        <v>166728</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>238</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166758</v>
+      </c>
+      <c r="D8" t="s">
         <v>259</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>279</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>299</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>314</v>
-      </c>
-      <c r="G8">
-        <v>166758</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>239</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166483</v>
+      </c>
+      <c r="D9" t="s">
         <v>260</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>280</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>300</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>315</v>
-      </c>
-      <c r="G9">
-        <v>166483</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>240</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166568</v>
+      </c>
+      <c r="D10" t="s">
         <v>261</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>281</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>301</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>316</v>
-      </c>
-      <c r="G10">
-        <v>166568</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166785</v>
+      </c>
+      <c r="D11" t="s">
         <v>262</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>282</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>302</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>317</v>
-      </c>
-      <c r="G11">
-        <v>166785</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>242</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166759</v>
+      </c>
+      <c r="D12" t="s">
         <v>263</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>283</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>303</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>318</v>
-      </c>
-      <c r="G12">
-        <v>166759</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>243</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166481</v>
+      </c>
+      <c r="D13" t="s">
         <v>264</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>284</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>304</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>124</v>
-      </c>
-      <c r="G13">
-        <v>166481</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>244</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166473</v>
+      </c>
+      <c r="D14" t="s">
         <v>265</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>285</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>305</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>319</v>
-      </c>
-      <c r="G14">
-        <v>166473</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>245</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166499</v>
+      </c>
+      <c r="D15" t="s">
         <v>266</v>
-      </c>
-      <c r="D15" t="s">
-        <v>189</v>
       </c>
       <c r="E15" t="s">
         <v>189</v>
@@ -6285,136 +6280,136 @@
       <c r="F15" t="s">
         <v>189</v>
       </c>
-      <c r="G15">
-        <v>166499</v>
+      <c r="G15" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>246</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166498</v>
+      </c>
+      <c r="D16" t="s">
         <v>267</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>286</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>306</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>124</v>
-      </c>
-      <c r="G16">
-        <v>166498</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>247</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166517</v>
+      </c>
+      <c r="D17" t="s">
         <v>268</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>287</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>307</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>320</v>
-      </c>
-      <c r="G17">
-        <v>166517</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>248</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166584</v>
+      </c>
+      <c r="D18" t="s">
         <v>269</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>288</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>308</v>
-      </c>
-      <c r="G18">
-        <v>166584</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>249</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166644</v>
+      </c>
+      <c r="D19" t="s">
         <v>270</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>289</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>309</v>
-      </c>
-      <c r="G19">
-        <v>166644</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>250</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166653</v>
+      </c>
+      <c r="D20" t="s">
         <v>271</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>290</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>310</v>
-      </c>
-      <c r="G20">
-        <v>166653</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>251</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166655</v>
+      </c>
+      <c r="D21" t="s">
         <v>272</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>291</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>311</v>
-      </c>
-      <c r="G21">
-        <v>166655</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>252</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166788</v>
+      </c>
+      <c r="D22" t="s">
         <v>273</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>292</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>312</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>321</v>
-      </c>
-      <c r="G22">
-        <v>166788</v>
       </c>
     </row>
   </sheetData>
@@ -6427,10 +6422,9 @@
   <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6460,242 +6454,242 @@
       <c r="A2" t="s">
         <v>322</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166500</v>
+      </c>
+      <c r="D2" t="s">
         <v>376</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>430</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>470</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>515</v>
-      </c>
-      <c r="G2">
-        <v>166500</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>323</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166535</v>
+      </c>
+      <c r="D3" t="s">
         <v>377</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>279</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>471</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>229</v>
-      </c>
-      <c r="G3">
-        <v>166535</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>324</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166543</v>
+      </c>
+      <c r="D4" t="s">
         <v>378</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>431</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>472</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>316</v>
-      </c>
-      <c r="G4">
-        <v>166543</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>325</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166549</v>
+      </c>
+      <c r="D5" t="s">
         <v>379</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>432</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>473</v>
-      </c>
-      <c r="G5">
-        <v>166549</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>326</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166616</v>
+      </c>
+      <c r="D6" t="s">
         <v>380</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>90</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>474</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>516</v>
-      </c>
-      <c r="G6">
-        <v>166616</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>327</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166693</v>
+      </c>
+      <c r="D7" t="s">
         <v>381</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>433</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>475</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>517</v>
-      </c>
-      <c r="G7">
-        <v>166693</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>328</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166706</v>
+      </c>
+      <c r="D8" t="s">
         <v>382</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>434</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>476</v>
-      </c>
-      <c r="G8">
-        <v>166706</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>329</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166721</v>
+      </c>
+      <c r="D9" t="s">
         <v>383</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>435</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>477</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>518</v>
-      </c>
-      <c r="G9">
-        <v>166721</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>330</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166724</v>
+      </c>
+      <c r="D10" t="s">
         <v>384</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>436</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>478</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="G10">
-        <v>166724</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>331</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166768</v>
+      </c>
+      <c r="D11" t="s">
         <v>385</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>437</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>479</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>124</v>
-      </c>
-      <c r="G11">
-        <v>166768</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>332</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166764</v>
+      </c>
+      <c r="D12" t="s">
         <v>386</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>438</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>480</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>124</v>
-      </c>
-      <c r="G12">
-        <v>166764</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>333</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166805</v>
+      </c>
+      <c r="D13" t="s">
         <v>387</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>439</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>481</v>
-      </c>
-      <c r="G13">
-        <v>166805</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>334</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166813</v>
+      </c>
+      <c r="D14" t="s">
         <v>388</v>
-      </c>
-      <c r="D14" t="s">
-        <v>189</v>
       </c>
       <c r="E14" t="s">
         <v>189</v>
@@ -6703,19 +6697,19 @@
       <c r="F14" t="s">
         <v>189</v>
       </c>
-      <c r="G14">
-        <v>166813</v>
+      <c r="G14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>335</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166821</v>
+      </c>
+      <c r="D15" t="s">
         <v>389</v>
-      </c>
-      <c r="D15" t="s">
-        <v>189</v>
       </c>
       <c r="E15" t="s">
         <v>189</v>
@@ -6723,119 +6717,119 @@
       <c r="F15" t="s">
         <v>189</v>
       </c>
-      <c r="G15">
-        <v>166821</v>
+      <c r="G15" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>336</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>167802</v>
+      </c>
+      <c r="D16" t="s">
         <v>390</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>197</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>482</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>519</v>
-      </c>
-      <c r="G16">
-        <v>167802</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>337</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>167855</v>
+      </c>
+      <c r="D17" t="s">
         <v>391</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>440</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>483</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>229</v>
-      </c>
-      <c r="G17">
-        <v>167855</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>338</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166537</v>
+      </c>
+      <c r="D18" t="s">
         <v>392</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>441</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>484</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>124</v>
-      </c>
-      <c r="G18">
-        <v>166537</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>339</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166548</v>
+      </c>
+      <c r="D19" t="s">
         <v>393</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>442</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>485</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>229</v>
-      </c>
-      <c r="G19">
-        <v>166548</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>340</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166588</v>
+      </c>
+      <c r="D20" t="s">
         <v>394</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>443</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>486</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>520</v>
-      </c>
-      <c r="G20">
-        <v>166588</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>341</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166611</v>
+      </c>
+      <c r="D21" t="s">
         <v>395</v>
-      </c>
-      <c r="D21" t="s">
-        <v>189</v>
       </c>
       <c r="E21" t="s">
         <v>189</v>
@@ -6843,119 +6837,119 @@
       <c r="F21" t="s">
         <v>189</v>
       </c>
-      <c r="G21">
-        <v>166611</v>
+      <c r="G21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>342</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166642</v>
+      </c>
+      <c r="D22" t="s">
         <v>396</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>444</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>487</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>229</v>
-      </c>
-      <c r="G22">
-        <v>166642</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>343</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>166665</v>
+      </c>
+      <c r="D23" t="s">
         <v>397</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>93</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>112</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>124</v>
-      </c>
-      <c r="G23">
-        <v>166665</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>344</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>166688</v>
+      </c>
+      <c r="D24" t="s">
         <v>398</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>445</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>488</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>124</v>
-      </c>
-      <c r="G24">
-        <v>166688</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>345</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B25">
+        <v>166722</v>
+      </c>
+      <c r="D25" t="s">
         <v>399</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>446</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>489</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>521</v>
-      </c>
-      <c r="G25">
-        <v>166722</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>346</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B26">
+        <v>166769</v>
+      </c>
+      <c r="D26" t="s">
         <v>400</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>443</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>490</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>124</v>
-      </c>
-      <c r="G26">
-        <v>166769</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>347</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B27">
+        <v>166471</v>
+      </c>
+      <c r="D27" t="s">
         <v>401</v>
-      </c>
-      <c r="D27" t="s">
-        <v>189</v>
       </c>
       <c r="E27" t="s">
         <v>189</v>
@@ -6963,36 +6957,36 @@
       <c r="F27" t="s">
         <v>189</v>
       </c>
-      <c r="G27">
-        <v>166471</v>
+      <c r="G27" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>348</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B28">
+        <v>166465</v>
+      </c>
+      <c r="D28" t="s">
         <v>402</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>447</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>491</v>
-      </c>
-      <c r="G28">
-        <v>166465</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>349</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B29">
+        <v>166490</v>
+      </c>
+      <c r="D29" t="s">
         <v>403</v>
-      </c>
-      <c r="D29" t="s">
-        <v>189</v>
       </c>
       <c r="E29" t="s">
         <v>189</v>
@@ -7000,233 +6994,233 @@
       <c r="F29" t="s">
         <v>189</v>
       </c>
-      <c r="G29">
-        <v>166490</v>
+      <c r="G29" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>350</v>
       </c>
-      <c r="C30" t="s">
+      <c r="B30">
+        <v>166491</v>
+      </c>
+      <c r="D30" t="s">
         <v>404</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>448</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>492</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>124</v>
-      </c>
-      <c r="G30">
-        <v>166491</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>351</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31">
+        <v>166547</v>
+      </c>
+      <c r="D31" t="s">
         <v>405</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>449</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>493</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>522</v>
-      </c>
-      <c r="G31">
-        <v>166547</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>352</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32">
+        <v>166554</v>
+      </c>
+      <c r="D32" t="s">
         <v>406</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>450</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>494</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>523</v>
-      </c>
-      <c r="G32">
-        <v>166554</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>353</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33">
+        <v>166787</v>
+      </c>
+      <c r="D33" t="s">
         <v>407</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>451</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>495</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>524</v>
-      </c>
-      <c r="G33">
-        <v>166787</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>354</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34">
+        <v>166536</v>
+      </c>
+      <c r="D34" t="s">
         <v>408</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>452</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>496</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>229</v>
-      </c>
-      <c r="G34">
-        <v>166536</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>355</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35">
+        <v>166725</v>
+      </c>
+      <c r="D35" t="s">
         <v>409</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>453</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>497</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>124</v>
-      </c>
-      <c r="G35">
-        <v>166725</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>356</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36">
+        <v>166464</v>
+      </c>
+      <c r="D36" t="s">
         <v>410</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>454</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>498</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>525</v>
-      </c>
-      <c r="G36">
-        <v>166464</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>357</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37">
+        <v>166555</v>
+      </c>
+      <c r="D37" t="s">
         <v>411</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>455</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>499</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>526</v>
-      </c>
-      <c r="G37">
-        <v>166555</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>358</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38">
+        <v>166556</v>
+      </c>
+      <c r="D38" t="s">
         <v>412</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>456</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>500</v>
-      </c>
-      <c r="G38">
-        <v>166556</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>359</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B39">
+        <v>166562</v>
+      </c>
+      <c r="D39" t="s">
         <v>413</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>457</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>501</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>527</v>
-      </c>
-      <c r="G39">
-        <v>166562</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>360</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40">
+        <v>166586</v>
+      </c>
+      <c r="D40" t="s">
         <v>414</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>458</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>502</v>
-      </c>
-      <c r="G40">
-        <v>166586</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>361</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B41">
+        <v>166613</v>
+      </c>
+      <c r="D41" t="s">
         <v>415</v>
-      </c>
-      <c r="D41" t="s">
-        <v>189</v>
       </c>
       <c r="E41" t="s">
         <v>189</v>
@@ -7234,196 +7228,196 @@
       <c r="F41" t="s">
         <v>189</v>
       </c>
-      <c r="G41">
-        <v>166613</v>
+      <c r="G41" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>362</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42">
+        <v>166617</v>
+      </c>
+      <c r="D42" t="s">
         <v>416</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>459</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>503</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>124</v>
-      </c>
-      <c r="G42">
-        <v>166617</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>363</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43">
+        <v>166634</v>
+      </c>
+      <c r="D43" t="s">
         <v>417</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>284</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>504</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>124</v>
-      </c>
-      <c r="G43">
-        <v>166634</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>364</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44">
+        <v>166639</v>
+      </c>
+      <c r="D44" t="s">
         <v>418</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>460</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>505</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>124</v>
-      </c>
-      <c r="G44">
-        <v>166639</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>365</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45">
+        <v>166647</v>
+      </c>
+      <c r="D45" t="s">
         <v>419</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>461</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>506</v>
-      </c>
-      <c r="G45">
-        <v>166647</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>366</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46">
+        <v>166670</v>
+      </c>
+      <c r="D46" t="s">
         <v>420</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>462</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>507</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>528</v>
-      </c>
-      <c r="G46">
-        <v>166670</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>367</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47">
+        <v>166686</v>
+      </c>
+      <c r="D47" t="s">
         <v>421</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>463</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>508</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>527</v>
-      </c>
-      <c r="G47">
-        <v>166686</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>368</v>
       </c>
-      <c r="C48" t="s">
+      <c r="B48">
+        <v>166689</v>
+      </c>
+      <c r="D48" t="s">
         <v>422</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>464</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>509</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>529</v>
-      </c>
-      <c r="G48">
-        <v>166689</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>369</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B49">
+        <v>166690</v>
+      </c>
+      <c r="D49" t="s">
         <v>423</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>465</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>510</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>530</v>
-      </c>
-      <c r="G49">
-        <v>166690</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>370</v>
       </c>
-      <c r="C50" t="s">
+      <c r="B50">
+        <v>166695</v>
+      </c>
+      <c r="D50" t="s">
         <v>424</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>466</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>511</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>531</v>
-      </c>
-      <c r="G50">
-        <v>166695</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>371</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B51">
+        <v>166704</v>
+      </c>
+      <c r="D51" t="s">
         <v>425</v>
-      </c>
-      <c r="D51" t="s">
-        <v>189</v>
       </c>
       <c r="E51" t="s">
         <v>189</v>
@@ -7431,79 +7425,79 @@
       <c r="F51" t="s">
         <v>189</v>
       </c>
-      <c r="G51">
-        <v>166704</v>
+      <c r="G51" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>372</v>
       </c>
-      <c r="C52" t="s">
+      <c r="B52">
+        <v>166726</v>
+      </c>
+      <c r="D52" t="s">
         <v>426</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>467</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>512</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>532</v>
-      </c>
-      <c r="G52">
-        <v>166726</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>373</v>
       </c>
-      <c r="C53" t="s">
+      <c r="B53">
+        <v>166812</v>
+      </c>
+      <c r="D53" t="s">
         <v>427</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>468</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>513</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>124</v>
-      </c>
-      <c r="G53">
-        <v>166812</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>374</v>
       </c>
-      <c r="C54" t="s">
+      <c r="B54">
+        <v>166820</v>
+      </c>
+      <c r="D54" t="s">
         <v>428</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>469</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>514</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>533</v>
-      </c>
-      <c r="G54">
-        <v>166820</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>375</v>
       </c>
-      <c r="C55" t="s">
+      <c r="B55">
+        <v>167673</v>
+      </c>
+      <c r="D55" t="s">
         <v>429</v>
-      </c>
-      <c r="D55" t="s">
-        <v>189</v>
       </c>
       <c r="E55" t="s">
         <v>189</v>
@@ -7511,8 +7505,8 @@
       <c r="F55" t="s">
         <v>189</v>
       </c>
-      <c r="G55">
-        <v>167673</v>
+      <c r="G55" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -7525,10 +7519,9 @@
   <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7558,188 +7551,188 @@
       <c r="A2" t="s">
         <v>534</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166461</v>
+      </c>
+      <c r="D2" t="s">
         <v>595</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>656</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>696</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>748</v>
-      </c>
-      <c r="G2">
-        <v>166461</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>535</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166479</v>
+      </c>
+      <c r="D3" t="s">
         <v>596</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>657</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>697</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>749</v>
-      </c>
-      <c r="G3">
-        <v>166479</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>536</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166522</v>
+      </c>
+      <c r="D4" t="s">
         <v>597</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>658</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>698</v>
-      </c>
-      <c r="G4">
-        <v>166522</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>537</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166488</v>
+      </c>
+      <c r="D5" t="s">
         <v>598</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>659</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>699</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>750</v>
-      </c>
-      <c r="G5">
-        <v>166488</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>538</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166495</v>
+      </c>
+      <c r="D6" t="s">
         <v>599</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>660</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>700</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>124</v>
-      </c>
-      <c r="G6">
-        <v>166495</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>539</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166520</v>
+      </c>
+      <c r="D7" t="s">
         <v>600</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>661</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>701</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>751</v>
-      </c>
-      <c r="G7">
-        <v>166520</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>540</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166528</v>
+      </c>
+      <c r="D8" t="s">
         <v>601</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>197</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>702</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>124</v>
-      </c>
-      <c r="G8">
-        <v>166528</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>541</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166523</v>
+      </c>
+      <c r="D9" t="s">
         <v>602</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>662</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>703</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>752</v>
-      </c>
-      <c r="G9">
-        <v>166523</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>542</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166570</v>
+      </c>
+      <c r="D10" t="s">
         <v>603</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>663</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>704</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="G10">
-        <v>166570</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>543</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166578</v>
+      </c>
+      <c r="D11" t="s">
         <v>604</v>
-      </c>
-      <c r="D11" t="s">
-        <v>189</v>
       </c>
       <c r="E11" t="s">
         <v>189</v>
@@ -7747,39 +7740,39 @@
       <c r="F11" t="s">
         <v>189</v>
       </c>
-      <c r="G11">
-        <v>166578</v>
+      <c r="G11" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>544</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166569</v>
+      </c>
+      <c r="D12" t="s">
         <v>605</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>664</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>705</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>753</v>
-      </c>
-      <c r="G12">
-        <v>166569</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>545</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166609</v>
+      </c>
+      <c r="D13" t="s">
         <v>606</v>
-      </c>
-      <c r="D13" t="s">
-        <v>189</v>
       </c>
       <c r="E13" t="s">
         <v>189</v>
@@ -7787,36 +7780,36 @@
       <c r="F13" t="s">
         <v>189</v>
       </c>
-      <c r="G13">
-        <v>166609</v>
+      <c r="G13" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>546</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166734</v>
+      </c>
+      <c r="D14" t="s">
         <v>607</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>180</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>706</v>
-      </c>
-      <c r="G14">
-        <v>166734</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>547</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166806</v>
+      </c>
+      <c r="D15" t="s">
         <v>608</v>
-      </c>
-      <c r="D15" t="s">
-        <v>189</v>
       </c>
       <c r="E15" t="s">
         <v>189</v>
@@ -7824,199 +7817,199 @@
       <c r="F15" t="s">
         <v>189</v>
       </c>
-      <c r="G15">
-        <v>166806</v>
+      <c r="G15" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>548</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166637</v>
+      </c>
+      <c r="D16" t="s">
         <v>609</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>665</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>707</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>124</v>
-      </c>
-      <c r="G16">
-        <v>166637</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>549</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166648</v>
+      </c>
+      <c r="D17" t="s">
         <v>610</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>468</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>708</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>222</v>
-      </c>
-      <c r="G17">
-        <v>166648</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>550</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166676</v>
+      </c>
+      <c r="D18" t="s">
         <v>611</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>666</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>709</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>754</v>
-      </c>
-      <c r="G18">
-        <v>166676</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>551</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166715</v>
+      </c>
+      <c r="D19" t="s">
         <v>612</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>667</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>710</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>755</v>
-      </c>
-      <c r="G19">
-        <v>166715</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>552</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166692</v>
+      </c>
+      <c r="D20" t="s">
         <v>613</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>668</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>711</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>124</v>
-      </c>
-      <c r="G20">
-        <v>166692</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>553</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166694</v>
+      </c>
+      <c r="D21" t="s">
         <v>614</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>90</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>712</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>124</v>
-      </c>
-      <c r="G21">
-        <v>166694</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>554</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166709</v>
+      </c>
+      <c r="D22" t="s">
         <v>615</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>669</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>713</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>756</v>
-      </c>
-      <c r="G22">
-        <v>166709</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>555</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>166717</v>
+      </c>
+      <c r="D23" t="s">
         <v>616</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>670</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>714</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>757</v>
-      </c>
-      <c r="G23">
-        <v>166717</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>556</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>166751</v>
+      </c>
+      <c r="D24" t="s">
         <v>617</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>453</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>715</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>758</v>
-      </c>
-      <c r="G24">
-        <v>166751</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>557</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B25">
+        <v>166763</v>
+      </c>
+      <c r="D25" t="s">
         <v>618</v>
-      </c>
-      <c r="D25" t="s">
-        <v>189</v>
       </c>
       <c r="E25" t="s">
         <v>189</v>
@@ -8024,39 +8017,39 @@
       <c r="F25" t="s">
         <v>189</v>
       </c>
-      <c r="G25">
-        <v>166763</v>
+      <c r="G25" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>558</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B26">
+        <v>166777</v>
+      </c>
+      <c r="D26" t="s">
         <v>619</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>445</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>716</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>759</v>
-      </c>
-      <c r="G26">
-        <v>166777</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>559</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B27">
+        <v>166789</v>
+      </c>
+      <c r="D27" t="s">
         <v>620</v>
-      </c>
-      <c r="D27" t="s">
-        <v>189</v>
       </c>
       <c r="E27" t="s">
         <v>189</v>
@@ -8064,404 +8057,404 @@
       <c r="F27" t="s">
         <v>189</v>
       </c>
-      <c r="G27">
-        <v>166789</v>
+      <c r="G27" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>560</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B28">
+        <v>166791</v>
+      </c>
+      <c r="D28" t="s">
         <v>621</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>671</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>119</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>760</v>
-      </c>
-      <c r="G28">
-        <v>166791</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>561</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B29">
+        <v>166819</v>
+      </c>
+      <c r="D29" t="s">
         <v>622</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>672</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>717</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>124</v>
-      </c>
-      <c r="G29">
-        <v>166819</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>562</v>
       </c>
-      <c r="C30" t="s">
+      <c r="B30">
+        <v>166527</v>
+      </c>
+      <c r="D30" t="s">
         <v>623</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>673</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>718</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>761</v>
-      </c>
-      <c r="G30">
-        <v>166527</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>563</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31">
+        <v>166610</v>
+      </c>
+      <c r="D31" t="s">
         <v>624</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>674</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>719</v>
-      </c>
-      <c r="G31">
-        <v>166610</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>564</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32">
+        <v>166512</v>
+      </c>
+      <c r="D32" t="s">
         <v>625</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>453</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>720</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>124</v>
-      </c>
-      <c r="G32">
-        <v>166512</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>565</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33">
+        <v>166526</v>
+      </c>
+      <c r="D33" t="s">
         <v>626</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>675</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>721</v>
-      </c>
-      <c r="G33">
-        <v>166526</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>566</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34">
+        <v>166530</v>
+      </c>
+      <c r="D34" t="s">
         <v>627</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>676</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>722</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>124</v>
-      </c>
-      <c r="G34">
-        <v>166530</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>567</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35">
+        <v>166539</v>
+      </c>
+      <c r="D35" t="s">
         <v>628</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>677</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>723</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>762</v>
-      </c>
-      <c r="G35">
-        <v>166539</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>568</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36">
+        <v>166602</v>
+      </c>
+      <c r="D36" t="s">
         <v>629</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>672</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>724</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>124</v>
-      </c>
-      <c r="G36">
-        <v>166602</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>569</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37">
+        <v>166605</v>
+      </c>
+      <c r="D37" t="s">
         <v>630</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>678</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>725</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>124</v>
-      </c>
-      <c r="G37">
-        <v>166605</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>570</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38">
+        <v>166614</v>
+      </c>
+      <c r="D38" t="s">
         <v>631</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>679</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>726</v>
-      </c>
-      <c r="G38">
-        <v>166614</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>571</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B39">
+        <v>166618</v>
+      </c>
+      <c r="D39" t="s">
         <v>632</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>676</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>727</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>124</v>
-      </c>
-      <c r="G39">
-        <v>166618</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>572</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40">
+        <v>166620</v>
+      </c>
+      <c r="D40" t="s">
         <v>633</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>95</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>728</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>763</v>
-      </c>
-      <c r="G40">
-        <v>166620</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>573</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B41">
+        <v>166621</v>
+      </c>
+      <c r="D41" t="s">
         <v>634</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>680</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>729</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>764</v>
-      </c>
-      <c r="G41">
-        <v>166621</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>574</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42">
+        <v>166632</v>
+      </c>
+      <c r="D42" t="s">
         <v>635</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>681</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>730</v>
-      </c>
-      <c r="G42">
-        <v>166632</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>575</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43">
+        <v>166649</v>
+      </c>
+      <c r="D43" t="s">
         <v>636</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>682</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>731</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>124</v>
-      </c>
-      <c r="G43">
-        <v>166649</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>576</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44">
+        <v>166652</v>
+      </c>
+      <c r="D44" t="s">
         <v>637</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>683</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>732</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>124</v>
-      </c>
-      <c r="G44">
-        <v>166652</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>577</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45">
+        <v>166672</v>
+      </c>
+      <c r="D45" t="s">
         <v>638</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>684</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>733</v>
-      </c>
-      <c r="G45">
-        <v>166672</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>578</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46">
+        <v>166677</v>
+      </c>
+      <c r="D46" t="s">
         <v>639</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>675</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>734</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>765</v>
-      </c>
-      <c r="G46">
-        <v>166677</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>579</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47">
+        <v>166680</v>
+      </c>
+      <c r="D47" t="s">
         <v>640</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>685</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>735</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>766</v>
-      </c>
-      <c r="G47">
-        <v>166680</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>580</v>
       </c>
-      <c r="C48" t="s">
+      <c r="B48">
+        <v>166681</v>
+      </c>
+      <c r="D48" t="s">
         <v>641</v>
-      </c>
-      <c r="D48" t="s">
-        <v>189</v>
       </c>
       <c r="E48" t="s">
         <v>189</v>
@@ -8469,39 +8462,39 @@
       <c r="F48" t="s">
         <v>189</v>
       </c>
-      <c r="G48">
-        <v>166681</v>
+      <c r="G48" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>581</v>
       </c>
-      <c r="C49" t="s">
+      <c r="B49">
+        <v>166718</v>
+      </c>
+      <c r="D49" t="s">
         <v>642</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>686</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>736</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>767</v>
-      </c>
-      <c r="G49">
-        <v>166718</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>582</v>
       </c>
-      <c r="C50" t="s">
+      <c r="B50">
+        <v>166720</v>
+      </c>
+      <c r="D50" t="s">
         <v>643</v>
-      </c>
-      <c r="D50" t="s">
-        <v>189</v>
       </c>
       <c r="E50" t="s">
         <v>189</v>
@@ -8509,245 +8502,245 @@
       <c r="F50" t="s">
         <v>189</v>
       </c>
-      <c r="G50">
-        <v>166720</v>
+      <c r="G50" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>583</v>
       </c>
-      <c r="C51" t="s">
+      <c r="B51">
+        <v>166742</v>
+      </c>
+      <c r="D51" t="s">
         <v>644</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>687</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>737</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>124</v>
-      </c>
-      <c r="G51">
-        <v>166742</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>584</v>
       </c>
-      <c r="C52" t="s">
+      <c r="B52">
+        <v>166752</v>
+      </c>
+      <c r="D52" t="s">
         <v>645</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>688</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>738</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>124</v>
-      </c>
-      <c r="G52">
-        <v>166752</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>585</v>
       </c>
-      <c r="C53" t="s">
+      <c r="B53">
+        <v>166761</v>
+      </c>
+      <c r="D53" t="s">
         <v>646</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>689</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>739</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>768</v>
-      </c>
-      <c r="G53">
-        <v>166761</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>586</v>
       </c>
-      <c r="C54" t="s">
+      <c r="B54">
+        <v>166772</v>
+      </c>
+      <c r="D54" t="s">
         <v>647</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>690</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>740</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>769</v>
-      </c>
-      <c r="G54">
-        <v>166772</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>587</v>
       </c>
-      <c r="C55" t="s">
+      <c r="B55">
+        <v>166786</v>
+      </c>
+      <c r="D55" t="s">
         <v>648</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>445</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>741</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>124</v>
-      </c>
-      <c r="G55">
-        <v>166786</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>588</v>
       </c>
-      <c r="C56" t="s">
+      <c r="B56">
+        <v>166815</v>
+      </c>
+      <c r="D56" t="s">
         <v>649</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>433</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>742</v>
-      </c>
-      <c r="G56">
-        <v>166815</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>589</v>
       </c>
-      <c r="C57" t="s">
+      <c r="B57">
+        <v>166816</v>
+      </c>
+      <c r="D57" t="s">
         <v>650</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>691</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>743</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>124</v>
-      </c>
-      <c r="G57">
-        <v>166816</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>590</v>
       </c>
-      <c r="C58" t="s">
+      <c r="B58">
+        <v>166817</v>
+      </c>
+      <c r="D58" t="s">
         <v>651</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>692</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>744</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>124</v>
-      </c>
-      <c r="G58">
-        <v>166817</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>591</v>
       </c>
-      <c r="C59" t="s">
+      <c r="B59">
+        <v>167826</v>
+      </c>
+      <c r="D59" t="s">
         <v>652</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>693</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>745</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>770</v>
-      </c>
-      <c r="G59">
-        <v>167826</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>592</v>
       </c>
-      <c r="C60" t="s">
+      <c r="B60">
+        <v>167837</v>
+      </c>
+      <c r="D60" t="s">
         <v>653</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>694</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>746</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>771</v>
-      </c>
-      <c r="G60">
-        <v>167837</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>593</v>
       </c>
-      <c r="C61" t="s">
+      <c r="B61">
+        <v>170164</v>
+      </c>
+      <c r="D61" t="s">
         <v>654</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>662</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>747</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>124</v>
-      </c>
-      <c r="G61">
-        <v>170164</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>594</v>
       </c>
-      <c r="C62" t="s">
+      <c r="B62">
+        <v>170518</v>
+      </c>
+      <c r="D62" t="s">
         <v>655</v>
-      </c>
-      <c r="D62" t="s">
-        <v>695</v>
       </c>
       <c r="E62" t="s">
         <v>695</v>
       </c>
       <c r="F62" t="s">
+        <v>695</v>
+      </c>
+      <c r="G62" t="s">
         <v>772</v>
-      </c>
-      <c r="G62">
-        <v>170518</v>
       </c>
     </row>
   </sheetData>
@@ -8760,10 +8753,9 @@
   <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -8793,251 +8785,251 @@
       <c r="A2" t="s">
         <v>773</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166521</v>
+      </c>
+      <c r="D2" t="s">
         <v>819</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>865</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>893</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>124</v>
-      </c>
-      <c r="G2">
-        <v>166521</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>774</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166516</v>
+      </c>
+      <c r="D3" t="s">
         <v>820</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>865</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>894</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>929</v>
-      </c>
-      <c r="G3">
-        <v>166516</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>775</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166508</v>
+      </c>
+      <c r="D4" t="s">
         <v>821</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>866</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>895</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>124</v>
-      </c>
-      <c r="G4">
-        <v>166508</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>776</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166540</v>
+      </c>
+      <c r="D5" t="s">
         <v>822</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>867</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>896</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>930</v>
-      </c>
-      <c r="G5">
-        <v>166540</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>777</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166541</v>
+      </c>
+      <c r="D6" t="s">
         <v>823</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>868</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>897</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>931</v>
-      </c>
-      <c r="G6">
-        <v>166541</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>778</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166561</v>
+      </c>
+      <c r="D7" t="s">
         <v>824</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>869</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>496</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>932</v>
-      </c>
-      <c r="G7">
-        <v>166561</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>779</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166619</v>
+      </c>
+      <c r="D8" t="s">
         <v>825</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>870</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>898</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>933</v>
-      </c>
-      <c r="G8">
-        <v>166619</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>780</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>166623</v>
+      </c>
+      <c r="D9" t="s">
         <v>826</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>871</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>899</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>124</v>
-      </c>
-      <c r="G9">
-        <v>166623</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>781</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166630</v>
+      </c>
+      <c r="D10" t="s">
         <v>827</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>871</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>899</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="G10">
-        <v>166630</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>782</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166663</v>
+      </c>
+      <c r="D11" t="s">
         <v>828</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>872</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>900</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>934</v>
-      </c>
-      <c r="G11">
-        <v>166663</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>783</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166673</v>
+      </c>
+      <c r="D12" t="s">
         <v>829</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>873</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>901</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>935</v>
-      </c>
-      <c r="G12">
-        <v>166673</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>784</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166675</v>
+      </c>
+      <c r="D13" t="s">
         <v>830</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>873</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>901</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>935</v>
-      </c>
-      <c r="G13">
-        <v>166675</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>785</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166710</v>
+      </c>
+      <c r="D14" t="s">
         <v>831</v>
-      </c>
-      <c r="D14" t="s">
-        <v>189</v>
       </c>
       <c r="E14" t="s">
         <v>189</v>
@@ -9045,353 +9037,353 @@
       <c r="F14" t="s">
         <v>189</v>
       </c>
-      <c r="G14">
-        <v>166710</v>
+      <c r="G14" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>786</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166711</v>
+      </c>
+      <c r="D15" t="s">
         <v>832</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>874</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>902</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>936</v>
-      </c>
-      <c r="G15">
-        <v>166711</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>787</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166731</v>
+      </c>
+      <c r="D16" t="s">
         <v>833</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>875</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>897</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>937</v>
-      </c>
-      <c r="G16">
-        <v>166731</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>788</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166755</v>
+      </c>
+      <c r="D17" t="s">
         <v>834</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>95</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>903</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>124</v>
-      </c>
-      <c r="G17">
-        <v>166755</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>789</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166757</v>
+      </c>
+      <c r="D18" t="s">
         <v>835</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>876</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>904</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>938</v>
-      </c>
-      <c r="G18">
-        <v>166757</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>790</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166771</v>
+      </c>
+      <c r="D19" t="s">
         <v>836</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>877</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>905</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>124</v>
-      </c>
-      <c r="G19">
-        <v>166771</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>791</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>167481</v>
+      </c>
+      <c r="D20" t="s">
         <v>837</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>661</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>906</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>229</v>
-      </c>
-      <c r="G20">
-        <v>167481</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>792</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>167793</v>
+      </c>
+      <c r="D21" t="s">
         <v>838</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>85</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>907</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>124</v>
-      </c>
-      <c r="G21">
-        <v>167793</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>793</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>168287</v>
+      </c>
+      <c r="D22" t="s">
         <v>839</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>878</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>908</v>
-      </c>
-      <c r="G22">
-        <v>168287</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>794</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>166567</v>
+      </c>
+      <c r="D23" t="s">
         <v>840</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>879</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>909</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>939</v>
-      </c>
-      <c r="G23">
-        <v>166567</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>795</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>166538</v>
+      </c>
+      <c r="D24" t="s">
         <v>841</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>880</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>910</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>940</v>
-      </c>
-      <c r="G24">
-        <v>166538</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>796</v>
       </c>
-      <c r="C25" t="s">
+      <c r="B25">
+        <v>166678</v>
+      </c>
+      <c r="D25" t="s">
         <v>842</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>881</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>911</v>
-      </c>
-      <c r="G25">
-        <v>166678</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>797</v>
       </c>
-      <c r="C26" t="s">
+      <c r="B26">
+        <v>167682</v>
+      </c>
+      <c r="D26" t="s">
         <v>843</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>468</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>708</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>222</v>
-      </c>
-      <c r="G26">
-        <v>167682</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>798</v>
       </c>
-      <c r="C27" t="s">
+      <c r="B27">
+        <v>166529</v>
+      </c>
+      <c r="D27" t="s">
         <v>844</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>882</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>912</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>941</v>
-      </c>
-      <c r="G27">
-        <v>166529</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>799</v>
       </c>
-      <c r="C28" t="s">
+      <c r="B28">
+        <v>166472</v>
+      </c>
+      <c r="D28" t="s">
         <v>845</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>687</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>913</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>942</v>
-      </c>
-      <c r="G28">
-        <v>166472</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>800</v>
       </c>
-      <c r="C29" t="s">
+      <c r="B29">
+        <v>166571</v>
+      </c>
+      <c r="D29" t="s">
         <v>846</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>883</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>914</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>943</v>
-      </c>
-      <c r="G29">
-        <v>166571</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>801</v>
       </c>
-      <c r="C30" t="s">
+      <c r="B30">
+        <v>166575</v>
+      </c>
+      <c r="D30" t="s">
         <v>847</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>884</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>915</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>124</v>
-      </c>
-      <c r="G30">
-        <v>166575</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>802</v>
       </c>
-      <c r="C31" t="s">
+      <c r="B31">
+        <v>166590</v>
+      </c>
+      <c r="D31" t="s">
         <v>848</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>885</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>916</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>944</v>
-      </c>
-      <c r="G31">
-        <v>166590</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>803</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32">
+        <v>166595</v>
+      </c>
+      <c r="D32" t="s">
         <v>849</v>
-      </c>
-      <c r="D32" t="s">
-        <v>189</v>
       </c>
       <c r="E32" t="s">
         <v>189</v>
@@ -9399,56 +9391,56 @@
       <c r="F32" t="s">
         <v>189</v>
       </c>
-      <c r="G32">
-        <v>166595</v>
+      <c r="G32" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>804</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33">
+        <v>166598</v>
+      </c>
+      <c r="D33" t="s">
         <v>850</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>866</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>917</v>
-      </c>
-      <c r="G33">
-        <v>166598</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>805</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34">
+        <v>166629</v>
+      </c>
+      <c r="D34" t="s">
         <v>851</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>871</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>899</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>124</v>
-      </c>
-      <c r="G34">
-        <v>166629</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>806</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35">
+        <v>166650</v>
+      </c>
+      <c r="D35" t="s">
         <v>852</v>
-      </c>
-      <c r="D35" t="s">
-        <v>189</v>
       </c>
       <c r="E35" t="s">
         <v>189</v>
@@ -9456,245 +9448,245 @@
       <c r="F35" t="s">
         <v>189</v>
       </c>
-      <c r="G35">
-        <v>166650</v>
+      <c r="G35" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>807</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36">
+        <v>166657</v>
+      </c>
+      <c r="D36" t="s">
         <v>853</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>886</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>918</v>
-      </c>
-      <c r="G36">
-        <v>166657</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>808</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37">
+        <v>166687</v>
+      </c>
+      <c r="D37" t="s">
         <v>854</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>887</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>919</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>945</v>
-      </c>
-      <c r="G37">
-        <v>166687</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>809</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38">
+        <v>166691</v>
+      </c>
+      <c r="D38" t="s">
         <v>855</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>464</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>509</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>529</v>
-      </c>
-      <c r="G38">
-        <v>166691</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>810</v>
       </c>
-      <c r="C39" t="s">
+      <c r="B39">
+        <v>166708</v>
+      </c>
+      <c r="D39" t="s">
         <v>856</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>888</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>920</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>124</v>
-      </c>
-      <c r="G39">
-        <v>166708</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>811</v>
       </c>
-      <c r="C40" t="s">
+      <c r="B40">
+        <v>166719</v>
+      </c>
+      <c r="D40" t="s">
         <v>857</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>889</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>921</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>767</v>
-      </c>
-      <c r="G40">
-        <v>166719</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>812</v>
       </c>
-      <c r="C41" t="s">
+      <c r="B41">
+        <v>166744</v>
+      </c>
+      <c r="D41" t="s">
         <v>858</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>448</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>922</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>124</v>
-      </c>
-      <c r="G41">
-        <v>166744</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>813</v>
       </c>
-      <c r="C42" t="s">
+      <c r="B42">
+        <v>166746</v>
+      </c>
+      <c r="D42" t="s">
         <v>859</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>692</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>923</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>946</v>
-      </c>
-      <c r="G42">
-        <v>166746</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>814</v>
       </c>
-      <c r="C43" t="s">
+      <c r="B43">
+        <v>166753</v>
+      </c>
+      <c r="D43" t="s">
         <v>860</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>197</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>924</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>947</v>
-      </c>
-      <c r="G43">
-        <v>166753</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>815</v>
       </c>
-      <c r="C44" t="s">
+      <c r="B44">
+        <v>166779</v>
+      </c>
+      <c r="D44" t="s">
         <v>861</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>890</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>925</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>124</v>
-      </c>
-      <c r="G44">
-        <v>166779</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>816</v>
       </c>
-      <c r="C45" t="s">
+      <c r="B45">
+        <v>166818</v>
+      </c>
+      <c r="D45" t="s">
         <v>862</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>891</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>926</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>948</v>
-      </c>
-      <c r="G45">
-        <v>166818</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>817</v>
       </c>
-      <c r="C46" t="s">
+      <c r="B46">
+        <v>167482</v>
+      </c>
+      <c r="D46" t="s">
         <v>863</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>892</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>927</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>124</v>
-      </c>
-      <c r="G46">
-        <v>167482</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>818</v>
       </c>
-      <c r="C47" t="s">
+      <c r="B47">
+        <v>167812</v>
+      </c>
+      <c r="D47" t="s">
         <v>864</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>453</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>928</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>124</v>
-      </c>
-      <c r="G47">
-        <v>167812</v>
       </c>
     </row>
   </sheetData>
@@ -9707,10 +9699,9 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="80.7109375" customWidth="1"/>
-    <col min="4" max="5" width="20.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" customWidth="1"/>
+    <col min="5" max="6" width="20.7109375" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -9740,131 +9731,131 @@
       <c r="A2" t="s">
         <v>949</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B2">
+        <v>166631</v>
+      </c>
+      <c r="D2" t="s">
         <v>972</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>995</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>1007</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>124</v>
-      </c>
-      <c r="G2">
-        <v>166631</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>950</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B3">
+        <v>166646</v>
+      </c>
+      <c r="D3" t="s">
         <v>973</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>996</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1008</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>124</v>
-      </c>
-      <c r="G3">
-        <v>166646</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>951</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4">
+        <v>166660</v>
+      </c>
+      <c r="D4" t="s">
         <v>974</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>997</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>1009</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>761</v>
-      </c>
-      <c r="G4">
-        <v>166660</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>952</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B5">
+        <v>166661</v>
+      </c>
+      <c r="D5" t="s">
         <v>975</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>430</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>1010</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>766</v>
-      </c>
-      <c r="G5">
-        <v>166661</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>953</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B6">
+        <v>166699</v>
+      </c>
+      <c r="D6" t="s">
         <v>976</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>998</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>1011</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>1026</v>
-      </c>
-      <c r="G6">
-        <v>166699</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>954</v>
       </c>
-      <c r="C7" t="s">
+      <c r="B7">
+        <v>166701</v>
+      </c>
+      <c r="D7" t="s">
         <v>977</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>999</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>1012</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>1027</v>
-      </c>
-      <c r="G7">
-        <v>166701</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>955</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8">
+        <v>166784</v>
+      </c>
+      <c r="D8" t="s">
         <v>978</v>
-      </c>
-      <c r="D8" t="s">
-        <v>189</v>
       </c>
       <c r="E8" t="s">
         <v>189</v>
@@ -9872,19 +9863,19 @@
       <c r="F8" t="s">
         <v>189</v>
       </c>
-      <c r="G8">
-        <v>166784</v>
+      <c r="G8" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>956</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B9">
+        <v>167801</v>
+      </c>
+      <c r="D9" t="s">
         <v>979</v>
-      </c>
-      <c r="D9" t="s">
-        <v>189</v>
       </c>
       <c r="E9" t="s">
         <v>189</v>
@@ -9892,59 +9883,59 @@
       <c r="F9" t="s">
         <v>189</v>
       </c>
-      <c r="G9">
-        <v>167801</v>
+      <c r="G9" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>957</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B10">
+        <v>166747</v>
+      </c>
+      <c r="D10" t="s">
         <v>980</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>1000</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>1013</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>124</v>
-      </c>
-      <c r="G10">
-        <v>166747</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>958</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B11">
+        <v>166487</v>
+      </c>
+      <c r="D11" t="s">
         <v>981</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>1001</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1014</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>1028</v>
-      </c>
-      <c r="G11">
-        <v>166487</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>959</v>
       </c>
-      <c r="C12" t="s">
+      <c r="B12">
+        <v>166560</v>
+      </c>
+      <c r="D12" t="s">
         <v>982</v>
-      </c>
-      <c r="D12" t="s">
-        <v>189</v>
       </c>
       <c r="E12" t="s">
         <v>189</v>
@@ -9952,176 +9943,176 @@
       <c r="F12" t="s">
         <v>189</v>
       </c>
-      <c r="G12">
-        <v>166560</v>
+      <c r="G12" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>960</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B13">
+        <v>166587</v>
+      </c>
+      <c r="D13" t="s">
         <v>983</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1002</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1015</v>
-      </c>
-      <c r="G13">
-        <v>166587</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>961</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14">
+        <v>166597</v>
+      </c>
+      <c r="D14" t="s">
         <v>984</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>90</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1016</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>124</v>
-      </c>
-      <c r="G14">
-        <v>166597</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>962</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15">
+        <v>166604</v>
+      </c>
+      <c r="D15" t="s">
         <v>985</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>1003</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1017</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>229</v>
-      </c>
-      <c r="G15">
-        <v>166604</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>963</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B16">
+        <v>166607</v>
+      </c>
+      <c r="D16" t="s">
         <v>986</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>884</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1018</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>124</v>
-      </c>
-      <c r="G16">
-        <v>166607</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>964</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B17">
+        <v>166612</v>
+      </c>
+      <c r="D17" t="s">
         <v>987</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>85</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1019</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>124</v>
-      </c>
-      <c r="G17">
-        <v>166612</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>965</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B18">
+        <v>166627</v>
+      </c>
+      <c r="D18" t="s">
         <v>988</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1004</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1020</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>124</v>
-      </c>
-      <c r="G18">
-        <v>166627</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>966</v>
       </c>
-      <c r="C19" t="s">
+      <c r="B19">
+        <v>166729</v>
+      </c>
+      <c r="D19" t="s">
         <v>989</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>1005</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1021</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>124</v>
-      </c>
-      <c r="G19">
-        <v>166729</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>967</v>
       </c>
-      <c r="C20" t="s">
+      <c r="B20">
+        <v>166737</v>
+      </c>
+      <c r="D20" t="s">
         <v>990</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>661</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1022</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>1029</v>
-      </c>
-      <c r="G20">
-        <v>166737</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>968</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B21">
+        <v>166750</v>
+      </c>
+      <c r="D21" t="s">
         <v>991</v>
-      </c>
-      <c r="D21" t="s">
-        <v>189</v>
       </c>
       <c r="E21" t="s">
         <v>189</v>
@@ -10129,68 +10120,68 @@
       <c r="F21" t="s">
         <v>189</v>
       </c>
-      <c r="G21">
-        <v>166750</v>
+      <c r="G21" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>969</v>
       </c>
-      <c r="C22" t="s">
+      <c r="B22">
+        <v>166796</v>
+      </c>
+      <c r="D22" t="s">
         <v>992</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>436</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1023</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>124</v>
-      </c>
-      <c r="G22">
-        <v>166796</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>970</v>
       </c>
-      <c r="C23" t="s">
+      <c r="B23">
+        <v>167817</v>
+      </c>
+      <c r="D23" t="s">
         <v>993</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>197</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>1024</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>1030</v>
-      </c>
-      <c r="G23">
-        <v>167817</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>971</v>
       </c>
-      <c r="C24" t="s">
+      <c r="B24">
+        <v>171014</v>
+      </c>
+      <c r="D24" t="s">
         <v>994</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>1006</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>1025</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>1031</v>
-      </c>
-      <c r="G24">
-        <v>171014</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -145,10 +145,10 @@
     <t>27/05/2022 19:15</t>
   </si>
   <si>
-    <t>Poster ID</t>
-  </si>
-  <si>
-    <t>Indico ID</t>
+    <t>Friendly ID</t>
+  </si>
+  <si>
+    <t>DB ID</t>
   </si>
   <si>
     <t>Screen ID</t>
@@ -3956,7 +3956,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="2" width="100.7109375" customWidth="1"/>
     <col min="3" max="4" width="20.7109375" customWidth="1"/>
   </cols>
@@ -4111,6 +4111,7 @@
   <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -5345,6 +5346,7 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -5788,6 +5790,7 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -6200,6 +6203,7 @@
   <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -7297,6 +7301,7 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -7792,6 +7797,7 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -8275,6 +8281,7 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -8313,6 +8320,7 @@
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>
@@ -9248,6 +9256,7 @@
   <dimension ref="A1:G47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="100.7109375" customWidth="1"/>
     <col min="5" max="6" width="20.7109375" customWidth="1"/>
     <col min="7" max="7" width="60.7109375" customWidth="1"/>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Detector Systems and Future accelerators</t>
   </si>
   <si>
-    <t xml:space="preserve">23/05/2021 10:20</t>
+    <t xml:space="preserve">23/05/2022 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2022 12:40</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Photo Detectors and PID</t>
   </si>
   <si>
-    <t xml:space="preserve">23/05/2021 15:30</t>
+    <t xml:space="preserve">23/05/2022 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2022 18:50</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Gas Detectors</t>
   </si>
   <si>
-    <t xml:space="preserve">27/05/2022 08:30</t>
+    <t xml:space="preserve">27/05/2021 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">27/05/2022 12:10</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Front End, Trigger, DAQ and Data Mangement</t>
   </si>
   <si>
-    <t xml:space="preserve">27/05/2022 15:30</t>
+    <t xml:space="preserve">27/05/2021 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">27/05/2022 19:15</t>
@@ -3719,7 +3719,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100.71"/>
@@ -3883,7 +3883,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G62"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5127,7 +5127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5580,7 +5580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -6002,7 +6002,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7109,7 +7109,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7614,7 +7614,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8107,7 +8107,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8155,7 +8155,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -9100,7 +9100,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Solid State Detectors</t>
   </si>
   <si>
-    <t xml:space="preserve">24/05/2022 08:30</t>
+    <t xml:space="preserve">24/05/2021 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">24/05/2022 12:15</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Application to life sciences and other societal challanges</t>
   </si>
   <si>
-    <t xml:space="preserve">24/05/2022 15:30</t>
+    <t xml:space="preserve">24/05/2021 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">24/05/2022 19:10</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">Gas Detectors</t>
   </si>
   <si>
-    <t xml:space="preserve">27/05/2021 08:30</t>
+    <t xml:space="preserve">27/05/2022 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">27/05/2022 12:10</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">Front End, Trigger, DAQ and Data Mangement</t>
   </si>
   <si>
-    <t xml:space="preserve">27/05/2021 15:30</t>
+    <t xml:space="preserve">27/05/2022 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">27/05/2022 19:15</t>
@@ -3719,7 +3719,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100.71"/>
@@ -3883,7 +3883,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G62"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5127,7 +5127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5580,7 +5580,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -6002,7 +6002,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7109,7 +7109,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7614,7 +7614,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8107,7 +8107,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8155,7 +8155,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -9100,7 +9100,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -49,7 +49,7 @@
     <t xml:space="preserve">Detector Systems and Future accelerators</t>
   </si>
   <si>
-    <t xml:space="preserve">23/05/2022 10:20</t>
+    <t xml:space="preserve">23/05/2021 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2022 12:40</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">Photo Detectors and PID</t>
   </si>
   <si>
-    <t xml:space="preserve">23/05/2022 15:30</t>
+    <t xml:space="preserve">23/05/2021 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">23/05/2022 18:50</t>
@@ -73,7 +73,7 @@
     <t xml:space="preserve">Solid State Detectors</t>
   </si>
   <si>
-    <t xml:space="preserve">24/05/2021 08:30</t>
+    <t xml:space="preserve">24/05/2022 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">24/05/2022 12:15</t>
@@ -85,7 +85,7 @@
     <t xml:space="preserve">Application to life sciences and other societal challanges</t>
   </si>
   <si>
-    <t xml:space="preserve">24/05/2021 15:30</t>
+    <t xml:space="preserve">24/05/2022 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">24/05/2022 19:10</t>
@@ -3719,7 +3719,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100.71"/>
@@ -3868,8 +3868,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -3883,7 +3883,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G62"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5112,8 +5112,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5127,7 +5127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5165,6 +5165,9 @@
       <c r="B2" s="0" t="n">
         <v>166463</v>
       </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="D2" s="0" t="s">
         <v>48</v>
       </c>
@@ -5182,6 +5185,9 @@
       <c r="B3" s="0" t="n">
         <v>166513</v>
       </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="D3" s="0" t="s">
         <v>52</v>
       </c>
@@ -5202,6 +5208,9 @@
       <c r="B4" s="0" t="n">
         <v>166553</v>
       </c>
+      <c r="C4" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="D4" s="0" t="s">
         <v>57</v>
       </c>
@@ -5222,6 +5231,9 @@
       <c r="B5" s="0" t="n">
         <v>166712</v>
       </c>
+      <c r="C5" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="D5" s="0" t="s">
         <v>62</v>
       </c>
@@ -5565,8 +5577,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5580,7 +5592,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -5987,8 +5999,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6002,7 +6014,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G55"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7094,8 +7106,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7109,7 +7121,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -7599,8 +7611,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -7614,7 +7626,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8092,8 +8104,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8107,7 +8119,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -8140,8 +8152,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -8155,7 +8167,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G46"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -9085,8 +9097,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -9100,7 +9112,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultColWidth="8.70703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="12.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="100.71"/>
@@ -10041,8 +10053,8 @@
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1202">
   <si>
     <t>Session ID</t>
   </si>
@@ -418,6 +418,9 @@
     <t>Viaux</t>
   </si>
   <si>
+    <t>University of California Irvine</t>
+  </si>
+  <si>
     <t>CERN</t>
   </si>
   <si>
@@ -454,6 +457,9 @@
     <t>Institute of Space Science</t>
   </si>
   <si>
+    <t>University of Mainz</t>
+  </si>
+  <si>
     <t>UTFSM</t>
   </si>
   <si>
@@ -700,6 +706,9 @@
     <t>University of Manchester</t>
   </si>
   <si>
+    <t>Jozef Stefan Institute</t>
+  </si>
+  <si>
     <t>57</t>
   </si>
   <si>
@@ -1246,18 +1255,27 @@
     <t>IFJ PAN</t>
   </si>
   <si>
+    <t>University of Iowa</t>
+  </si>
+  <si>
     <t>Université de Genève</t>
   </si>
   <si>
     <t>University of Cambridge (GB)</t>
   </si>
   <si>
+    <t>University of California Santa Cruz</t>
+  </si>
+  <si>
     <t>UNAM</t>
   </si>
   <si>
     <t>University and INFN Perugia</t>
   </si>
   <si>
+    <t>IFCA</t>
+  </si>
+  <si>
     <t>Fondazione Bruno Kessler</t>
   </si>
   <si>
@@ -1267,6 +1285,9 @@
     <t>Universidade de Santiago de Compostela</t>
   </si>
   <si>
+    <t>ETH Zürich</t>
+  </si>
+  <si>
     <t>Institute of Physics of the Czech Academy of Sciences</t>
   </si>
   <si>
@@ -1285,6 +1306,9 @@
     <t>DESY</t>
   </si>
   <si>
+    <t>University of Torino</t>
+  </si>
+  <si>
     <t>INFN Pisa / Belle II</t>
   </si>
   <si>
@@ -1786,12 +1810,18 @@
     <t>INFN</t>
   </si>
   <si>
+    <t>Charles University</t>
+  </si>
+  <si>
     <t>Princeton University</t>
   </si>
   <si>
     <t>University of Tsukuba - Faculty - Graduate School of Pure and Applied Sciences, Tsukuba, Japan</t>
   </si>
   <si>
+    <t>University of Tokyo</t>
+  </si>
+  <si>
     <t>University of Science and Technology of China</t>
   </si>
   <si>
@@ -1810,6 +1840,9 @@
     <t>CEA</t>
   </si>
   <si>
+    <t>Ludwig Maximilians University München</t>
+  </si>
+  <si>
     <t>the University of Tokyo</t>
   </si>
   <si>
@@ -1933,6 +1966,9 @@
     <t>SRON Leiden</t>
   </si>
   <si>
+    <t>University Milano Bicocca</t>
+  </si>
+  <si>
     <t>GE</t>
   </si>
   <si>
@@ -2680,6 +2716,9 @@
     <t>Federica</t>
   </si>
   <si>
+    <t>Brunella</t>
+  </si>
+  <si>
     <t>Saikat</t>
   </si>
   <si>
@@ -2761,6 +2800,9 @@
     <t>Cuna</t>
   </si>
   <si>
+    <t>D'Anzi</t>
+  </si>
+  <si>
     <t>Biswas</t>
   </si>
   <si>
@@ -2881,6 +2923,9 @@
     <t>Physics Department - University of Coimbra</t>
   </si>
   <si>
+    <t>University of Coimbra</t>
+  </si>
+  <si>
     <t>Departamento de Física Universidade de Coimbra and LIP</t>
   </si>
   <si>
@@ -3505,6 +3550,9 @@
     <t>CPPM - - CNRS - IN2P3</t>
   </si>
   <si>
+    <t>University of Heidelberg</t>
+  </si>
+  <si>
     <t>Nanjing University</t>
   </si>
   <si>
@@ -3517,6 +3565,9 @@
     <t>University of West Bohemia</t>
   </si>
   <si>
+    <t>Instituto Nazionale di Fisica Nucleare</t>
+  </si>
+  <si>
     <t>University of Torino and Istituto Nazionale di Fisica Nucleare</t>
   </si>
   <si>
@@ -3541,12 +3592,24 @@
     <t>Max-Planck-Institut für Physik</t>
   </si>
   <si>
+    <t>Technische Universität Dortmund</t>
+  </si>
+  <si>
+    <t>Imperial College</t>
+  </si>
+  <si>
     <t>INFN - Lecce</t>
   </si>
   <si>
     <t>OMEGA Microelectronics</t>
   </si>
   <si>
+    <t>FNAL</t>
+  </si>
+  <si>
+    <t>University of Zürich</t>
+  </si>
+  <si>
     <t>University of Pisa and INFN-Pisa</t>
   </si>
   <si>
@@ -3554,6 +3617,9 @@
   </si>
   <si>
     <t>HSE University</t>
+  </si>
+  <si>
+    <t>University of Frankfurt</t>
   </si>
   <si>
     <t>HSE, JINR</t>
@@ -4109,1118 +4175,1142 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="B2">
         <v>166461</v>
       </c>
       <c r="D2" t="s">
-        <v>1022</v>
+        <v>1037</v>
       </c>
       <c r="E2" t="s">
-        <v>1079</v>
+        <v>1094</v>
       </c>
       <c r="F2" t="s">
-        <v>1109</v>
+        <v>1124</v>
       </c>
       <c r="G2" t="s">
-        <v>1158</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="B3">
         <v>166479</v>
       </c>
       <c r="D3" t="s">
-        <v>1023</v>
+        <v>1038</v>
       </c>
       <c r="E3" t="s">
-        <v>1080</v>
+        <v>1095</v>
       </c>
       <c r="F3" t="s">
-        <v>1110</v>
+        <v>1125</v>
       </c>
       <c r="G3" t="s">
-        <v>1159</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="B4">
         <v>166522</v>
       </c>
       <c r="D4" t="s">
-        <v>1024</v>
+        <v>1039</v>
       </c>
       <c r="E4" t="s">
-        <v>1081</v>
+        <v>1096</v>
       </c>
       <c r="F4" t="s">
-        <v>1111</v>
+        <v>1126</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1175</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="B5">
         <v>166488</v>
       </c>
       <c r="D5" t="s">
-        <v>1025</v>
+        <v>1040</v>
       </c>
       <c r="E5" t="s">
-        <v>1082</v>
+        <v>1097</v>
       </c>
       <c r="F5" t="s">
-        <v>1112</v>
+        <v>1127</v>
       </c>
       <c r="G5" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="B6">
         <v>166495</v>
       </c>
       <c r="D6" t="s">
-        <v>1026</v>
+        <v>1041</v>
       </c>
       <c r="E6" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="F6" t="s">
-        <v>1113</v>
+        <v>1128</v>
       </c>
       <c r="G6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="B7">
         <v>166520</v>
       </c>
       <c r="D7" t="s">
-        <v>1027</v>
+        <v>1042</v>
       </c>
       <c r="E7" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="F7" t="s">
-        <v>1114</v>
+        <v>1129</v>
       </c>
       <c r="G7" t="s">
-        <v>1161</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="B8">
         <v>166528</v>
       </c>
       <c r="D8" t="s">
-        <v>1028</v>
+        <v>1043</v>
       </c>
       <c r="E8" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F8" t="s">
-        <v>1115</v>
+        <v>1130</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="B9">
         <v>166523</v>
       </c>
       <c r="D9" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
       <c r="E9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F9" t="s">
-        <v>1116</v>
+        <v>1131</v>
       </c>
       <c r="G9" t="s">
-        <v>1162</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
       <c r="B10">
         <v>166570</v>
       </c>
       <c r="D10" t="s">
-        <v>1030</v>
+        <v>1045</v>
       </c>
       <c r="E10" t="s">
-        <v>1083</v>
+        <v>1098</v>
       </c>
       <c r="F10" t="s">
-        <v>1117</v>
+        <v>1132</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>974</v>
+        <v>989</v>
       </c>
       <c r="B11">
         <v>166578</v>
       </c>
       <c r="D11" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
       <c r="E11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>975</v>
+        <v>990</v>
       </c>
       <c r="B12">
         <v>166569</v>
       </c>
       <c r="D12" t="s">
-        <v>1032</v>
+        <v>1047</v>
       </c>
       <c r="E12" t="s">
-        <v>1084</v>
+        <v>1099</v>
       </c>
       <c r="F12" t="s">
-        <v>1118</v>
+        <v>1133</v>
       </c>
       <c r="G12" t="s">
-        <v>1163</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>976</v>
+        <v>991</v>
       </c>
       <c r="B13">
         <v>166734</v>
       </c>
       <c r="D13" t="s">
-        <v>1033</v>
+        <v>1048</v>
       </c>
       <c r="E13" t="s">
         <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>1119</v>
+        <v>1134</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>977</v>
+        <v>992</v>
       </c>
       <c r="B14">
         <v>166806</v>
       </c>
       <c r="D14" t="s">
-        <v>1034</v>
+        <v>1049</v>
       </c>
       <c r="E14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>978</v>
+        <v>993</v>
       </c>
       <c r="B15">
         <v>166637</v>
       </c>
       <c r="D15" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="E15" t="s">
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="F15" t="s">
-        <v>1120</v>
+        <v>1135</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>979</v>
+        <v>994</v>
       </c>
       <c r="B16">
         <v>166648</v>
       </c>
       <c r="D16" t="s">
-        <v>1036</v>
+        <v>1051</v>
       </c>
       <c r="E16" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F16" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="G16" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>980</v>
+        <v>995</v>
       </c>
       <c r="B17">
         <v>166676</v>
       </c>
       <c r="D17" t="s">
-        <v>1037</v>
+        <v>1052</v>
       </c>
       <c r="E17" t="s">
-        <v>1086</v>
+        <v>1101</v>
       </c>
       <c r="F17" t="s">
-        <v>1121</v>
+        <v>1136</v>
       </c>
       <c r="G17" t="s">
-        <v>1164</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>981</v>
+        <v>996</v>
       </c>
       <c r="B18">
         <v>166715</v>
       </c>
       <c r="D18" t="s">
-        <v>1038</v>
+        <v>1053</v>
       </c>
       <c r="E18" t="s">
-        <v>1087</v>
+        <v>1102</v>
       </c>
       <c r="F18" t="s">
-        <v>1122</v>
+        <v>1137</v>
       </c>
       <c r="G18" t="s">
-        <v>1165</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>982</v>
+        <v>997</v>
       </c>
       <c r="B19">
         <v>166692</v>
       </c>
       <c r="D19" t="s">
-        <v>1039</v>
+        <v>1054</v>
       </c>
       <c r="E19" t="s">
-        <v>1088</v>
+        <v>1103</v>
       </c>
       <c r="F19" t="s">
-        <v>1123</v>
+        <v>1138</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>983</v>
+        <v>998</v>
       </c>
       <c r="B20">
         <v>166694</v>
       </c>
       <c r="D20" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="E20" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F20" t="s">
-        <v>1124</v>
+        <v>1139</v>
       </c>
       <c r="G20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>984</v>
+        <v>999</v>
       </c>
       <c r="B21">
         <v>166709</v>
       </c>
       <c r="D21" t="s">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="E21" t="s">
-        <v>1089</v>
+        <v>1104</v>
       </c>
       <c r="F21" t="s">
-        <v>1125</v>
+        <v>1140</v>
       </c>
       <c r="G21" t="s">
-        <v>1166</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>985</v>
+        <v>1000</v>
       </c>
       <c r="B22">
         <v>166717</v>
       </c>
       <c r="D22" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="E22" t="s">
-        <v>1090</v>
+        <v>1105</v>
       </c>
       <c r="F22" t="s">
-        <v>1126</v>
+        <v>1141</v>
       </c>
       <c r="G22" t="s">
-        <v>1167</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>986</v>
+        <v>1001</v>
       </c>
       <c r="B23">
         <v>166751</v>
       </c>
       <c r="D23" t="s">
-        <v>1043</v>
+        <v>1058</v>
       </c>
       <c r="E23" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F23" t="s">
-        <v>1127</v>
+        <v>1142</v>
       </c>
       <c r="G23" t="s">
-        <v>1168</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>987</v>
+        <v>1002</v>
       </c>
       <c r="B24">
         <v>166777</v>
       </c>
       <c r="D24" t="s">
-        <v>1044</v>
+        <v>1059</v>
       </c>
       <c r="E24" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F24" t="s">
-        <v>1128</v>
+        <v>1143</v>
       </c>
       <c r="G24" t="s">
-        <v>1169</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>988</v>
+        <v>1003</v>
       </c>
       <c r="B25">
         <v>166789</v>
       </c>
       <c r="D25" t="s">
-        <v>1045</v>
+        <v>1060</v>
       </c>
       <c r="E25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G25" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>989</v>
+        <v>1004</v>
       </c>
       <c r="B26">
         <v>166791</v>
       </c>
       <c r="D26" t="s">
-        <v>1046</v>
+        <v>1061</v>
       </c>
       <c r="E26" t="s">
-        <v>1091</v>
+        <v>1106</v>
       </c>
       <c r="F26" t="s">
-        <v>1129</v>
+        <v>1144</v>
       </c>
       <c r="G26" t="s">
-        <v>1170</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>990</v>
+        <v>1005</v>
       </c>
       <c r="B27">
         <v>166819</v>
       </c>
       <c r="D27" t="s">
-        <v>1047</v>
+        <v>1062</v>
       </c>
       <c r="E27" t="s">
         <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="G27" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="B28">
         <v>166527</v>
       </c>
       <c r="D28" t="s">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="E28" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="F28" t="s">
-        <v>1130</v>
+        <v>1145</v>
       </c>
       <c r="G28" t="s">
-        <v>1171</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="B29">
         <v>166610</v>
       </c>
       <c r="D29" t="s">
-        <v>1049</v>
+        <v>1064</v>
       </c>
       <c r="E29" t="s">
-        <v>1092</v>
+        <v>1107</v>
       </c>
       <c r="F29" t="s">
-        <v>1131</v>
+        <v>1146</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="B30">
         <v>166512</v>
       </c>
       <c r="D30" t="s">
-        <v>1050</v>
+        <v>1065</v>
       </c>
       <c r="E30" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F30" t="s">
-        <v>1132</v>
+        <v>1147</v>
       </c>
       <c r="G30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="B31">
         <v>166526</v>
       </c>
       <c r="D31" t="s">
-        <v>1051</v>
+        <v>1066</v>
       </c>
       <c r="E31" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F31" t="s">
-        <v>1133</v>
+        <v>1148</v>
+      </c>
+      <c r="G31" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="B32">
         <v>166530</v>
       </c>
       <c r="D32" t="s">
-        <v>1052</v>
+        <v>1067</v>
       </c>
       <c r="E32" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
       <c r="G32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="B33">
         <v>166602</v>
       </c>
       <c r="D33" t="s">
-        <v>1053</v>
+        <v>1068</v>
       </c>
       <c r="E33" t="s">
-        <v>1094</v>
+        <v>1109</v>
       </c>
       <c r="F33" t="s">
-        <v>1135</v>
+        <v>1150</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="B34">
         <v>166605</v>
       </c>
       <c r="D34" t="s">
-        <v>1054</v>
+        <v>1069</v>
       </c>
       <c r="E34" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F34" t="s">
-        <v>1136</v>
+        <v>1151</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>998</v>
+        <v>1013</v>
       </c>
       <c r="B35">
         <v>166614</v>
       </c>
       <c r="D35" t="s">
-        <v>1055</v>
+        <v>1070</v>
       </c>
       <c r="E35" t="s">
-        <v>1095</v>
+        <v>1110</v>
       </c>
       <c r="F35" t="s">
-        <v>1137</v>
+        <v>1152</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1190</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>999</v>
+        <v>1014</v>
       </c>
       <c r="B36">
         <v>166618</v>
       </c>
       <c r="D36" t="s">
-        <v>1056</v>
+        <v>1071</v>
       </c>
       <c r="E36" t="s">
-        <v>1093</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="s">
-        <v>1138</v>
+        <v>1153</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>1000</v>
+        <v>1015</v>
       </c>
       <c r="B37">
         <v>166620</v>
       </c>
       <c r="D37" t="s">
-        <v>1057</v>
+        <v>1072</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F37" t="s">
-        <v>1139</v>
+        <v>1154</v>
       </c>
       <c r="G37" t="s">
-        <v>1172</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>1001</v>
+        <v>1016</v>
       </c>
       <c r="B38">
         <v>166621</v>
       </c>
       <c r="D38" t="s">
-        <v>1058</v>
+        <v>1073</v>
       </c>
       <c r="E38" t="s">
-        <v>1096</v>
+        <v>1111</v>
       </c>
       <c r="F38" t="s">
-        <v>1140</v>
+        <v>1155</v>
       </c>
       <c r="G38" t="s">
-        <v>1173</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>1002</v>
+        <v>1017</v>
       </c>
       <c r="B39">
         <v>166632</v>
       </c>
       <c r="D39" t="s">
-        <v>1059</v>
+        <v>1074</v>
       </c>
       <c r="E39" t="s">
-        <v>1097</v>
+        <v>1112</v>
       </c>
       <c r="F39" t="s">
-        <v>1141</v>
+        <v>1156</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="B40">
         <v>166649</v>
       </c>
       <c r="D40" t="s">
-        <v>1060</v>
+        <v>1075</v>
       </c>
       <c r="E40" t="s">
-        <v>1098</v>
+        <v>1113</v>
       </c>
       <c r="F40" t="s">
-        <v>1142</v>
+        <v>1157</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
       <c r="B41">
         <v>166652</v>
       </c>
       <c r="D41" t="s">
-        <v>1061</v>
+        <v>1076</v>
       </c>
       <c r="E41" t="s">
-        <v>1099</v>
+        <v>1114</v>
       </c>
       <c r="F41" t="s">
-        <v>1143</v>
+        <v>1158</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>1005</v>
+        <v>1020</v>
       </c>
       <c r="B42">
         <v>166672</v>
       </c>
       <c r="D42" t="s">
-        <v>1062</v>
+        <v>1077</v>
       </c>
       <c r="E42" t="s">
-        <v>1100</v>
+        <v>1115</v>
       </c>
       <c r="F42" t="s">
-        <v>1144</v>
+        <v>1159</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>1006</v>
+        <v>1021</v>
       </c>
       <c r="B43">
         <v>166677</v>
       </c>
       <c r="D43" t="s">
-        <v>1063</v>
+        <v>1078</v>
       </c>
       <c r="E43" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F43" t="s">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="G43" t="s">
-        <v>1174</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>1007</v>
+        <v>1022</v>
       </c>
       <c r="B44">
         <v>166680</v>
       </c>
       <c r="D44" t="s">
-        <v>1064</v>
+        <v>1079</v>
       </c>
       <c r="E44" t="s">
-        <v>1101</v>
+        <v>1116</v>
       </c>
       <c r="F44" t="s">
-        <v>1146</v>
+        <v>1161</v>
       </c>
       <c r="G44" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>1008</v>
+        <v>1023</v>
       </c>
       <c r="B45">
         <v>166718</v>
       </c>
       <c r="D45" t="s">
-        <v>1065</v>
+        <v>1080</v>
       </c>
       <c r="E45" t="s">
-        <v>1102</v>
+        <v>1117</v>
       </c>
       <c r="F45" t="s">
-        <v>1147</v>
+        <v>1162</v>
       </c>
       <c r="G45" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>1009</v>
+        <v>1024</v>
       </c>
       <c r="B46">
         <v>166720</v>
       </c>
       <c r="D46" t="s">
-        <v>1066</v>
+        <v>1081</v>
       </c>
       <c r="E46" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F46" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G46" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>1010</v>
+        <v>1025</v>
       </c>
       <c r="B47">
         <v>166742</v>
       </c>
       <c r="D47" t="s">
-        <v>1067</v>
+        <v>1082</v>
       </c>
       <c r="E47" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F47" t="s">
-        <v>1148</v>
+        <v>1163</v>
       </c>
       <c r="G47" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>1011</v>
+        <v>1026</v>
       </c>
       <c r="B48">
         <v>166752</v>
       </c>
       <c r="D48" t="s">
-        <v>1068</v>
+        <v>1083</v>
       </c>
       <c r="E48" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F48" t="s">
-        <v>1149</v>
+        <v>1164</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>1012</v>
+        <v>1027</v>
       </c>
       <c r="B49">
         <v>166761</v>
       </c>
       <c r="D49" t="s">
-        <v>1069</v>
+        <v>1084</v>
       </c>
       <c r="E49" t="s">
-        <v>1103</v>
+        <v>1118</v>
       </c>
       <c r="F49" t="s">
-        <v>1150</v>
+        <v>1165</v>
       </c>
       <c r="G49" t="s">
-        <v>1175</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>1013</v>
+        <v>1028</v>
       </c>
       <c r="B50">
         <v>166772</v>
       </c>
       <c r="D50" t="s">
-        <v>1070</v>
+        <v>1085</v>
       </c>
       <c r="E50" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="F50" t="s">
-        <v>1151</v>
+        <v>1166</v>
       </c>
       <c r="G50" t="s">
-        <v>1176</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>1014</v>
+        <v>1029</v>
       </c>
       <c r="B51">
         <v>166786</v>
       </c>
       <c r="D51" t="s">
-        <v>1071</v>
+        <v>1086</v>
       </c>
       <c r="E51" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F51" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="G51" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="B52">
         <v>166815</v>
       </c>
       <c r="D52" t="s">
-        <v>1072</v>
+        <v>1087</v>
       </c>
       <c r="E52" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F52" t="s">
-        <v>1152</v>
+        <v>1167</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1198</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="B53">
         <v>166816</v>
       </c>
       <c r="D53" t="s">
-        <v>1073</v>
+        <v>1088</v>
       </c>
       <c r="E53" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="F53" t="s">
-        <v>1153</v>
+        <v>1168</v>
       </c>
       <c r="G53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>1017</v>
+        <v>1032</v>
       </c>
       <c r="B54">
         <v>166817</v>
       </c>
       <c r="D54" t="s">
-        <v>1074</v>
+        <v>1089</v>
       </c>
       <c r="E54" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="F54" t="s">
-        <v>1154</v>
+        <v>1169</v>
       </c>
       <c r="G54" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>1018</v>
+        <v>1033</v>
       </c>
       <c r="B55">
         <v>167826</v>
       </c>
       <c r="D55" t="s">
-        <v>1075</v>
+        <v>1090</v>
       </c>
       <c r="E55" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
       <c r="F55" t="s">
-        <v>1155</v>
+        <v>1170</v>
       </c>
       <c r="G55" t="s">
-        <v>1177</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>1019</v>
+        <v>1034</v>
       </c>
       <c r="B56">
         <v>167837</v>
       </c>
       <c r="D56" t="s">
-        <v>1076</v>
+        <v>1091</v>
       </c>
       <c r="E56" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="F56" t="s">
-        <v>1156</v>
+        <v>1171</v>
       </c>
       <c r="G56" t="s">
-        <v>1178</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>1020</v>
+        <v>1035</v>
       </c>
       <c r="B57">
         <v>170164</v>
       </c>
       <c r="D57" t="s">
-        <v>1077</v>
+        <v>1092</v>
       </c>
       <c r="E57" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F57" t="s">
-        <v>1157</v>
+        <v>1172</v>
       </c>
       <c r="G57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>1021</v>
+        <v>1036</v>
       </c>
       <c r="B58">
         <v>170518</v>
       </c>
       <c r="D58" t="s">
-        <v>1078</v>
+        <v>1093</v>
       </c>
       <c r="E58" t="s">
-        <v>1108</v>
+        <v>1123</v>
       </c>
       <c r="F58" t="s">
-        <v>1108</v>
+        <v>1123</v>
       </c>
       <c r="G58" t="s">
-        <v>1179</v>
+        <v>1201</v>
       </c>
     </row>
   </sheetData>
@@ -5278,6 +5368,9 @@
       <c r="F2" t="s">
         <v>110</v>
       </c>
+      <c r="G2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
@@ -5296,7 +5389,7 @@
         <v>111</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5316,7 +5409,7 @@
         <v>112</v>
       </c>
       <c r="G4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5336,7 +5429,7 @@
         <v>113</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -5356,7 +5449,7 @@
         <v>114</v>
       </c>
       <c r="G6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5376,7 +5469,7 @@
         <v>115</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -5396,7 +5489,7 @@
         <v>116</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -5416,7 +5509,7 @@
         <v>117</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5436,7 +5529,7 @@
         <v>118</v>
       </c>
       <c r="G10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5456,7 +5549,7 @@
         <v>119</v>
       </c>
       <c r="G11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5476,7 +5569,7 @@
         <v>120</v>
       </c>
       <c r="G12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5496,7 +5589,7 @@
         <v>121</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5516,7 +5609,7 @@
         <v>122</v>
       </c>
       <c r="G14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5536,7 +5629,7 @@
         <v>123</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5556,7 +5649,7 @@
         <v>124</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5576,7 +5669,7 @@
         <v>125</v>
       </c>
       <c r="G17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5595,6 +5688,9 @@
       <c r="F18" t="s">
         <v>126</v>
       </c>
+      <c r="G18" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
@@ -5612,6 +5708,9 @@
       <c r="F19" t="s">
         <v>127</v>
       </c>
+      <c r="G19" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
@@ -5629,6 +5728,9 @@
       <c r="F20" t="s">
         <v>128</v>
       </c>
+      <c r="G20" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
@@ -5646,6 +5748,9 @@
       <c r="F21" t="s">
         <v>129</v>
       </c>
+      <c r="G21" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
@@ -5664,7 +5769,7 @@
         <v>130</v>
       </c>
       <c r="G22" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -5708,356 +5813,362 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>166492</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B3">
         <v>166625</v>
       </c>
       <c r="D3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B4">
         <v>166635</v>
       </c>
       <c r="D4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5">
         <v>166698</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>167674</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B7">
         <v>166697</v>
       </c>
       <c r="D7" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E7" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8">
         <v>166811</v>
       </c>
       <c r="D8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B9">
         <v>166470</v>
       </c>
       <c r="D9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B10">
         <v>166666</v>
       </c>
       <c r="D10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B11">
         <v>166501</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B12">
         <v>166533</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B13">
         <v>166534</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G13" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B14">
         <v>166683</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B15">
         <v>166735</v>
       </c>
       <c r="D15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G15" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B16">
         <v>166741</v>
       </c>
       <c r="D16" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E16" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F16" t="s">
-        <v>212</v>
+        <v>214</v>
+      </c>
+      <c r="G16" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B17">
         <v>166793</v>
       </c>
       <c r="D17" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E17" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F17" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B18">
         <v>166822</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E18" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B19">
         <v>167676</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E19" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F19" t="s">
-        <v>215</v>
+        <v>217</v>
+      </c>
+      <c r="G19" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -6101,941 +6212,962 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B2">
         <v>166500</v>
       </c>
       <c r="D2" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B3">
         <v>166535</v>
       </c>
       <c r="D3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
         <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B4">
         <v>166543</v>
       </c>
       <c r="D4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B5">
         <v>166549</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F5" t="s">
-        <v>364</v>
+        <v>367</v>
+      </c>
+      <c r="G5" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B6">
         <v>166616</v>
       </c>
       <c r="D6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="G6" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B7">
         <v>166693</v>
       </c>
       <c r="D7" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G7" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B8">
         <v>166706</v>
       </c>
       <c r="D8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E8" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F8" t="s">
-        <v>367</v>
+        <v>370</v>
+      </c>
+      <c r="G8" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B9">
         <v>166721</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E9" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="F9" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G9" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B10">
         <v>166724</v>
       </c>
       <c r="D10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E10" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B11">
         <v>166768</v>
       </c>
       <c r="D11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E11" t="s">
         <v>91</v>
       </c>
       <c r="F11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B12">
         <v>166764</v>
       </c>
       <c r="D12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E12" t="s">
         <v>92</v>
       </c>
       <c r="F12" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G12" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B13">
         <v>166805</v>
       </c>
       <c r="D13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F13" t="s">
-        <v>372</v>
+        <v>375</v>
+      </c>
+      <c r="G13" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B14">
         <v>166813</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B15">
         <v>167802</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E15" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F15" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G15" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B16">
         <v>167855</v>
       </c>
       <c r="D16" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E16" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F16" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B17">
         <v>166537</v>
       </c>
       <c r="D17" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E17" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F17" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B18">
         <v>166548</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E18" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="F18" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B19">
         <v>166588</v>
       </c>
       <c r="D19" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G19" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B20">
         <v>166642</v>
       </c>
       <c r="D20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E20" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F20" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B21">
         <v>166665</v>
       </c>
       <c r="D21" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E21" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B22">
         <v>166688</v>
       </c>
       <c r="D22" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E22" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F22" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B23">
         <v>166722</v>
       </c>
       <c r="D23" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E23" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="G23" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B24">
         <v>166769</v>
       </c>
       <c r="D24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E24" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F24" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B25">
         <v>166471</v>
       </c>
       <c r="D25" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E25" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F25" t="s">
-        <v>382</v>
+        <v>385</v>
+      </c>
+      <c r="G25" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B26">
         <v>166465</v>
       </c>
       <c r="D26" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="E26" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F26" t="s">
-        <v>383</v>
+        <v>386</v>
+      </c>
+      <c r="G26" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B27">
         <v>166491</v>
       </c>
       <c r="D27" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E27" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F27" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="G27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B28">
         <v>166547</v>
       </c>
       <c r="D28" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E28" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="F28" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="G28" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B29">
         <v>166554</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E29" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="F29" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G29" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B30">
         <v>166787</v>
       </c>
       <c r="D30" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E30" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="F30" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G30" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B31">
         <v>166536</v>
       </c>
       <c r="D31" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E31" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F31" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B32">
         <v>166725</v>
       </c>
       <c r="D32" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E32" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F32" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B33">
         <v>166464</v>
       </c>
       <c r="D33" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E33" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="F33" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G33" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B34">
         <v>166555</v>
       </c>
       <c r="D34" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E34" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F34" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G34" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B35">
         <v>166562</v>
       </c>
       <c r="D35" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E35" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F35" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G35" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B36">
         <v>166586</v>
       </c>
       <c r="D36" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E36" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F36" t="s">
-        <v>393</v>
+        <v>396</v>
+      </c>
+      <c r="G36" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B37">
         <v>166613</v>
       </c>
       <c r="D37" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E37" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F37" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G37" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B38">
         <v>166617</v>
       </c>
       <c r="D38" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="E38" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="F38" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B39">
         <v>166634</v>
       </c>
       <c r="D39" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E39" t="s">
         <v>100</v>
       </c>
       <c r="F39" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B40">
         <v>166639</v>
       </c>
       <c r="D40" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E40" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F40" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B41">
         <v>166647</v>
       </c>
       <c r="D41" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="E41" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="F41" t="s">
-        <v>397</v>
+        <v>400</v>
+      </c>
+      <c r="G41" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B42">
         <v>166670</v>
       </c>
       <c r="D42" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E42" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F42" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="G42" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B43">
         <v>166686</v>
       </c>
       <c r="D43" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E43" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F43" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G43" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B44">
         <v>166689</v>
       </c>
       <c r="D44" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E44" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F44" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G44" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B45">
         <v>166690</v>
       </c>
       <c r="D45" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E45" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F45" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G45" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B46">
         <v>166695</v>
       </c>
       <c r="D46" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E46" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F46" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="G46" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B47">
         <v>166726</v>
       </c>
       <c r="D47" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E47" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="F47" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="G47" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B48">
         <v>166812</v>
       </c>
       <c r="D48" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E48" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F48" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B49">
         <v>167673</v>
       </c>
       <c r="D49" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="E49" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="F49" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -7079,402 +7211,402 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B2">
         <v>166631</v>
       </c>
       <c r="D2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="E2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="F2" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="B3">
         <v>166646</v>
       </c>
       <c r="D3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="E3" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F3" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="G3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B4">
         <v>166660</v>
       </c>
       <c r="D4" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="E4" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F4" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="G4" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B5">
         <v>166661</v>
       </c>
       <c r="D5" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="E5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="F5" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="G5" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="B6">
         <v>166699</v>
       </c>
       <c r="D6" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="E6" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F6" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="G6" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B7">
         <v>166701</v>
       </c>
       <c r="D7" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="E7" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="F7" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="G7" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="B8">
         <v>166784</v>
       </c>
       <c r="D8" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="E8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B9">
         <v>166747</v>
       </c>
       <c r="D9" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="E9" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="F9" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="B10">
         <v>166487</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E10" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="F10" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="G10" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="B11">
         <v>166560</v>
       </c>
       <c r="D11" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="G11" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B12">
         <v>166597</v>
       </c>
       <c r="D12" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B13">
         <v>166604</v>
       </c>
       <c r="D13" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="E13" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="F13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="G13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B14">
         <v>166607</v>
       </c>
       <c r="D14" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="E14" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="F14" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B15">
         <v>166612</v>
       </c>
       <c r="D15" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="E15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B16">
         <v>166627</v>
       </c>
       <c r="D16" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="E16" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="F16" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B17">
         <v>166729</v>
       </c>
       <c r="D17" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="E17" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="F17" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B18">
         <v>166750</v>
       </c>
       <c r="D18" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="E18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B19">
         <v>166796</v>
       </c>
       <c r="D19" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="E19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F19" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B20">
         <v>167817</v>
       </c>
       <c r="D20" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="E20" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F20" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="G20" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B21">
         <v>171014</v>
       </c>
       <c r="D21" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="E21" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="F21" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="G21" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -7518,433 +7650,442 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B2">
         <v>166466</v>
       </c>
       <c r="D2" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="E2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F2" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="G2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="B3">
         <v>166467</v>
       </c>
       <c r="D3" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E3" t="s">
         <v>92</v>
       </c>
       <c r="F3" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="G3" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B4">
         <v>166519</v>
       </c>
       <c r="D4" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c r="E4" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="F4" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="B5">
         <v>166550</v>
       </c>
       <c r="D5" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E5" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="F5" t="s">
-        <v>567</v>
+        <v>575</v>
+      </c>
+      <c r="G5" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B6">
         <v>166645</v>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E6" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="F6" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="G6" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B7">
         <v>166643</v>
       </c>
       <c r="D7" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E7" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="F7" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="G7" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B8">
         <v>166685</v>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="E8" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="F8" t="s">
-        <v>570</v>
+        <v>578</v>
+      </c>
+      <c r="G8" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B9">
         <v>166810</v>
       </c>
       <c r="D9" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E9" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
       <c r="F9" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="G9" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B10">
         <v>166740</v>
       </c>
       <c r="D10" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G10" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="B11">
         <v>166754</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E11" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="F11" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B12">
         <v>166775</v>
       </c>
       <c r="D12" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E12" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F12" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="B13">
         <v>166475</v>
       </c>
       <c r="D13" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="E13" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="F13" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="G13" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B14">
         <v>166511</v>
       </c>
       <c r="D14" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
       <c r="E14" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="F14" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="G14" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="B15">
         <v>166518</v>
       </c>
       <c r="D15" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="E15" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="F15" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B16">
         <v>166524</v>
       </c>
       <c r="D16" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="E16" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="F16" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="G16" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="B17">
         <v>166525</v>
       </c>
       <c r="D17" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="E17" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="F17" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B18">
         <v>166563</v>
       </c>
       <c r="D18" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E18" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="F18" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="B19">
         <v>166608</v>
       </c>
       <c r="D19" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="E19" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F19" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="G19" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B20">
         <v>166659</v>
       </c>
       <c r="D20" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E20" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="F20" t="s">
-        <v>581</v>
+        <v>589</v>
+      </c>
+      <c r="G20" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="B21">
         <v>166664</v>
       </c>
       <c r="D21" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="E21" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F21" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B22">
         <v>166727</v>
       </c>
       <c r="D22" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E22" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="F22" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="G22" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="B23">
         <v>166738</v>
       </c>
       <c r="D23" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="E23" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="F23" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -7988,199 +8129,202 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="B2">
         <v>166656</v>
       </c>
       <c r="D2" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B3">
         <v>166795</v>
       </c>
       <c r="D3" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="E3" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
       <c r="F3" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="G3" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="B4">
         <v>166674</v>
       </c>
       <c r="D4" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="E4" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="F4" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="B5">
         <v>166582</v>
       </c>
       <c r="D5" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="E5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F5" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="G5" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="B6">
         <v>166679</v>
       </c>
       <c r="D6" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="E6" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="F6" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="G6" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="B7">
         <v>166794</v>
       </c>
       <c r="D7" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="E7" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="F7" t="s">
-        <v>628</v>
+        <v>639</v>
+      </c>
+      <c r="G7" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="B8">
         <v>167882</v>
       </c>
       <c r="D8" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="B9">
         <v>166696</v>
       </c>
       <c r="D9" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="E9" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F9" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="G9" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="B10">
         <v>166700</v>
       </c>
       <c r="D10" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="E10" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="F10" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="G10" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="B11">
         <v>166792</v>
       </c>
       <c r="D11" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="E11" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="F11" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -8224,819 +8368,822 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="B2">
         <v>166462</v>
       </c>
       <c r="D2" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="E2" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="F2" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="B3">
         <v>166486</v>
       </c>
       <c r="D3" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="E3" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F3" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="G3" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="B4">
         <v>166545</v>
       </c>
       <c r="D4" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="E4" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="F4" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="B5">
         <v>166557</v>
       </c>
       <c r="D5" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="E5" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F5" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="G5" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="B6">
         <v>166566</v>
       </c>
       <c r="D6" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="E6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F6" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="G6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="B7">
         <v>166600</v>
       </c>
       <c r="D7" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="E7" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="F7" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="G7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="B8">
         <v>166603</v>
       </c>
       <c r="D8" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="E8" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="F8" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="B9">
         <v>166624</v>
       </c>
       <c r="D9" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="E9" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F9" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="G9" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="B10">
         <v>166628</v>
       </c>
       <c r="D10" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F10" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="B11">
         <v>166636</v>
       </c>
       <c r="D11" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="E11" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F11" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="G11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="B12">
         <v>166640</v>
       </c>
       <c r="D12" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="E12" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F12" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="G12" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="B13">
         <v>166668</v>
       </c>
       <c r="D13" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="E13" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="F13" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="G13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="B14">
         <v>166682</v>
       </c>
       <c r="D14" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="E14" t="s">
         <v>106</v>
       </c>
       <c r="F14" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="B15">
         <v>166705</v>
       </c>
       <c r="D15" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="E15" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="F15" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="B16">
         <v>166716</v>
       </c>
       <c r="D16" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="E16" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="F16" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="G16" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="B17">
         <v>166743</v>
       </c>
       <c r="D17" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="G17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="B18">
         <v>166814</v>
       </c>
       <c r="D18" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="E18" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="F18" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="B19">
         <v>166497</v>
       </c>
       <c r="D19" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="E19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F19" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="B20">
         <v>166733</v>
       </c>
       <c r="D20" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="E20" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F20" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="G20" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="B21">
         <v>166496</v>
       </c>
       <c r="D21" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="E21" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="F21" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="G21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="B22">
         <v>166783</v>
       </c>
       <c r="D22" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="E22" t="s">
         <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="G22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="B23">
         <v>166468</v>
       </c>
       <c r="D23" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E23" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F23" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="B24">
         <v>166494</v>
       </c>
       <c r="D24" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="E24" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F24" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="G24" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="B25">
         <v>166509</v>
       </c>
       <c r="D25" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="E25" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F25" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="G25" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="B26">
         <v>166531</v>
       </c>
       <c r="D26" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="E26" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="F26" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="G26" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="B27">
         <v>166532</v>
       </c>
       <c r="D27" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="E27" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="F27" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="G27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="B28">
         <v>166559</v>
       </c>
       <c r="D28" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="E28" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c r="F28" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="G28" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="B29">
         <v>166564</v>
       </c>
       <c r="D29" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="E29" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F29" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="B30">
         <v>166565</v>
       </c>
       <c r="D30" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="E30" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="F30" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="G30" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="B31">
         <v>166606</v>
       </c>
       <c r="D31" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="E31" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="F31" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="G31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="B32">
         <v>166658</v>
       </c>
       <c r="D32" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="E32" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="F32" t="s">
-        <v>769</v>
+        <v>781</v>
+      </c>
+      <c r="G32" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="B33">
         <v>166667</v>
       </c>
       <c r="D33" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="E33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F33" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="G33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="B34">
         <v>166671</v>
       </c>
       <c r="D34" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="E34" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="G34" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="B35">
         <v>166684</v>
       </c>
       <c r="D35" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="E35" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F35" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="G35" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="B36">
         <v>166730</v>
       </c>
       <c r="D36" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="E36" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F36" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B37">
         <v>166736</v>
       </c>
       <c r="D37" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="E37" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="F37" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="G37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="B38">
         <v>166739</v>
       </c>
       <c r="D38" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="E38" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="F38" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="G38" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="B39">
         <v>166749</v>
       </c>
       <c r="D39" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="E39" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="F39" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="G39" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="B40">
         <v>166766</v>
       </c>
       <c r="D40" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="E40" t="s">
         <v>106</v>
       </c>
       <c r="F40" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="G40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="B41">
         <v>167683</v>
       </c>
       <c r="D41" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="E41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F41" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="B42">
         <v>167825</v>
       </c>
       <c r="D42" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="E42" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="F42" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="G42" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -9080,870 +9227,882 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="B2">
         <v>166521</v>
       </c>
       <c r="D2" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="E2" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="F2" t="s">
-        <v>905</v>
+        <v>918</v>
       </c>
       <c r="G2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="B3">
         <v>166516</v>
       </c>
       <c r="D3" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="E3" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="F3" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="G3" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="B4">
         <v>166508</v>
       </c>
       <c r="D4" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="E4" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="F4" t="s">
-        <v>907</v>
+        <v>920</v>
       </c>
       <c r="G4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="B5">
         <v>166540</v>
       </c>
       <c r="D5" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="E5" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="F5" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="G5" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="B6">
         <v>166541</v>
       </c>
       <c r="D6" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="E6" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="F6" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="G6" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="B7">
         <v>166561</v>
       </c>
       <c r="D7" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="E7" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="F7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="G7" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="B8">
         <v>166619</v>
       </c>
       <c r="D8" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="E8" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="F8" t="s">
-        <v>910</v>
+        <v>923</v>
       </c>
       <c r="G8" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="B9">
         <v>166623</v>
       </c>
       <c r="D9" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="E9" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="F9" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="G9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="B10">
         <v>166630</v>
       </c>
       <c r="D10" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="E10" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="F10" t="s">
-        <v>911</v>
+        <v>925</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="B11">
         <v>166663</v>
       </c>
       <c r="D11" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="E11" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="F11" t="s">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="G11" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="B12">
         <v>166673</v>
       </c>
       <c r="D12" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="E12" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="F12" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="G12" t="s">
-        <v>949</v>
+        <v>963</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="B13">
         <v>166675</v>
       </c>
       <c r="D13" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="E13" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="F13" t="s">
-        <v>913</v>
+        <v>927</v>
       </c>
       <c r="G13" t="s">
-        <v>949</v>
+        <v>963</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="B14">
         <v>166710</v>
       </c>
       <c r="D14" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="E14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G14" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="B15">
         <v>166711</v>
       </c>
       <c r="D15" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="E15" t="s">
-        <v>887</v>
+        <v>900</v>
       </c>
       <c r="F15" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="G15" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="B16">
         <v>166755</v>
       </c>
       <c r="D16" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="E16" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F16" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="G16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="B17">
         <v>166757</v>
       </c>
       <c r="D17" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="E17" t="s">
-        <v>888</v>
+        <v>901</v>
       </c>
       <c r="F17" t="s">
-        <v>916</v>
+        <v>930</v>
       </c>
       <c r="G17" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="B18">
         <v>167481</v>
       </c>
       <c r="D18" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="E18" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="F18" t="s">
-        <v>917</v>
+        <v>931</v>
       </c>
       <c r="G18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="B19">
         <v>167793</v>
       </c>
       <c r="D19" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="E19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F19" t="s">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="B20">
         <v>168287</v>
       </c>
       <c r="D20" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="E20" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
       <c r="F20" t="s">
-        <v>919</v>
+        <v>933</v>
+      </c>
+      <c r="G20" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="B21">
         <v>166567</v>
       </c>
       <c r="D21" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="E21" t="s">
-        <v>891</v>
+        <v>904</v>
       </c>
       <c r="F21" t="s">
-        <v>920</v>
+        <v>934</v>
       </c>
       <c r="G21" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="B22">
         <v>166538</v>
       </c>
       <c r="D22" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="E22" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="F22" t="s">
-        <v>921</v>
+        <v>935</v>
       </c>
       <c r="G22" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="B23">
         <v>166678</v>
       </c>
       <c r="D23" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="E23" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="F23" t="s">
-        <v>922</v>
+        <v>936</v>
+      </c>
+      <c r="G23" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="B24">
         <v>167682</v>
       </c>
       <c r="D24" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
       <c r="E24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F24" t="s">
-        <v>923</v>
+        <v>937</v>
       </c>
       <c r="G24" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="B25">
         <v>166529</v>
       </c>
       <c r="D25" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="E25" t="s">
-        <v>894</v>
+        <v>907</v>
       </c>
       <c r="F25" t="s">
-        <v>924</v>
+        <v>938</v>
       </c>
       <c r="G25" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="B26">
         <v>166472</v>
       </c>
       <c r="D26" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="E26" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F26" t="s">
-        <v>925</v>
+        <v>939</v>
       </c>
       <c r="G26" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="B27">
         <v>166571</v>
       </c>
       <c r="D27" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="E27" t="s">
-        <v>895</v>
+        <v>908</v>
       </c>
       <c r="F27" t="s">
-        <v>926</v>
+        <v>940</v>
       </c>
       <c r="G27" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="B28">
         <v>166575</v>
       </c>
       <c r="D28" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="E28" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="F28" t="s">
-        <v>927</v>
+        <v>941</v>
       </c>
       <c r="G28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="B29">
         <v>166590</v>
       </c>
       <c r="D29" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
       <c r="E29" t="s">
-        <v>896</v>
+        <v>909</v>
       </c>
       <c r="F29" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="G29" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="B30">
         <v>166598</v>
       </c>
       <c r="D30" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
       <c r="E30" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="F30" t="s">
-        <v>929</v>
+        <v>943</v>
+      </c>
+      <c r="G30" t="s">
+        <v>966</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="B31">
         <v>166629</v>
       </c>
       <c r="D31" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
       <c r="E31" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="F31" t="s">
-        <v>911</v>
+        <v>924</v>
       </c>
       <c r="G31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="B32">
         <v>166650</v>
       </c>
       <c r="D32" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="E32" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F32" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
       <c r="G32" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="B33">
         <v>166657</v>
       </c>
       <c r="D33" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="E33" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="F33" t="s">
-        <v>931</v>
+        <v>945</v>
+      </c>
+      <c r="G33" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="B34">
         <v>166687</v>
       </c>
       <c r="D34" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
       <c r="E34" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="F34" t="s">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="G34" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="B35">
         <v>166691</v>
       </c>
       <c r="D35" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="E35" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F35" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G35" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="B36">
         <v>166708</v>
       </c>
       <c r="D36" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="E36" t="s">
-        <v>899</v>
+        <v>912</v>
       </c>
       <c r="F36" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="B37">
         <v>166719</v>
       </c>
       <c r="D37" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="E37" t="s">
-        <v>900</v>
+        <v>913</v>
       </c>
       <c r="F37" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="G37" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="B38">
         <v>166744</v>
       </c>
       <c r="D38" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="E38" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F38" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="G38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="B39">
         <v>166746</v>
       </c>
       <c r="D39" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
       <c r="E39" t="s">
-        <v>901</v>
+        <v>914</v>
       </c>
       <c r="F39" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="G39" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="B40">
         <v>166753</v>
       </c>
       <c r="D40" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="E40" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F40" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
       <c r="G40" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="B41">
         <v>166779</v>
       </c>
       <c r="D41" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
       <c r="E41" t="s">
-        <v>902</v>
+        <v>915</v>
       </c>
       <c r="F41" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="G41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="B42">
         <v>166818</v>
       </c>
       <c r="D42" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
       <c r="E42" t="s">
         <v>102</v>
       </c>
       <c r="F42" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
       <c r="G42" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="B43">
         <v>167482</v>
       </c>
       <c r="D43" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
       <c r="E43" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="F43" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
       <c r="G43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="B44">
         <v>167812</v>
       </c>
       <c r="D44" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="E44" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F44" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="G44" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="B45">
         <v>171332</v>
       </c>
       <c r="D45" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="E45" t="s">
-        <v>904</v>
+        <v>917</v>
       </c>
       <c r="F45" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="G45" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10410"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE25D24-F3E7-DF40-8610-DC764D9C75FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -18,12 +24,12 @@
     <sheet name="26959" sheetId="9" r:id="rId9"/>
     <sheet name="26960" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="1184">
   <si>
     <t>Session ID</t>
   </si>
@@ -89,60 +95,6 @@
   </si>
   <si>
     <t>Front End, Trigger, DAQ and Data Mangement</t>
-  </si>
-  <si>
-    <t>23/05/2022 10:20</t>
-  </si>
-  <si>
-    <t>23/05/2022 15:30</t>
-  </si>
-  <si>
-    <t>24/05/2022 08:30</t>
-  </si>
-  <si>
-    <t>24/05/2022 15:30</t>
-  </si>
-  <si>
-    <t>25/05/2022 08:30</t>
-  </si>
-  <si>
-    <t>26/05/2022 08:30</t>
-  </si>
-  <si>
-    <t>26/05/2022 15:30</t>
-  </si>
-  <si>
-    <t>27/05/2022 08:30</t>
-  </si>
-  <si>
-    <t>27/05/2022 15:30</t>
-  </si>
-  <si>
-    <t>23/05/2022 12:40</t>
-  </si>
-  <si>
-    <t>23/05/2022 18:50</t>
-  </si>
-  <si>
-    <t>24/05/2022 12:15</t>
-  </si>
-  <si>
-    <t>24/05/2022 19:10</t>
-  </si>
-  <si>
-    <t>25/05/2022 11:30</t>
-  </si>
-  <si>
-    <t>26/05/2022 11:05</t>
-  </si>
-  <si>
-    <t>26/05/2022 18:50</t>
-  </si>
-  <si>
-    <t>27/05/2022 12:10</t>
-  </si>
-  <si>
-    <t>27/05/2022 19:15</t>
   </si>
   <si>
     <t>Friendly ID</t>
@@ -3634,8 +3586,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3687,17 +3639,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3744,7 +3705,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3776,9 +3737,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3810,6 +3789,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3985,16 +3982,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4008,130 +4005,130 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="C2" s="2">
+        <v>44704.208333333336</v>
+      </c>
+      <c r="D2" s="2">
+        <v>44704.958333333336</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="C3" s="2">
+        <v>44704.208333333336</v>
+      </c>
+      <c r="D3" s="2">
+        <v>44704.958333333336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="C4" s="2">
+        <v>44705.208333333336</v>
+      </c>
+      <c r="D4" s="2">
+        <v>44705.958333333336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="C5" s="2">
+        <v>44705.208333333336</v>
+      </c>
+      <c r="D5" s="2">
+        <v>44705.958333333336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="2">
+        <v>44706.208333333336</v>
+      </c>
+      <c r="D6" s="2">
+        <v>44706.958333333336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="C7" s="2">
+        <v>44707.208333333336</v>
+      </c>
+      <c r="D7" s="2">
+        <v>44707.958333333336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="C8" s="2">
+        <v>44707.208333333336</v>
+      </c>
+      <c r="D8" s="2">
+        <v>44707.958333333336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="C9" s="2">
+        <v>44708.208333333336</v>
+      </c>
+      <c r="D9" s="2">
+        <v>44708.958333333336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
+      <c r="C10" s="2">
+        <v>44708.208333333336</v>
+      </c>
+      <c r="D10" s="2">
+        <v>44708.958333333336</v>
       </c>
     </row>
   </sheetData>
@@ -4140,1177 +4137,1315 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>980</v>
+        <v>962</v>
       </c>
       <c r="B2">
         <v>166461</v>
       </c>
       <c r="D2" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="E2" t="s">
-        <v>1094</v>
+        <v>1076</v>
       </c>
       <c r="F2" t="s">
-        <v>1124</v>
+        <v>1106</v>
       </c>
       <c r="G2" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="B3">
         <v>166479</v>
       </c>
       <c r="D3" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="E3" t="s">
-        <v>1095</v>
+        <v>1077</v>
       </c>
       <c r="F3" t="s">
-        <v>1125</v>
+        <v>1107</v>
       </c>
       <c r="G3" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="B4">
         <v>166522</v>
       </c>
       <c r="D4" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="E4" t="s">
-        <v>1096</v>
+        <v>1078</v>
       </c>
       <c r="F4" t="s">
-        <v>1126</v>
+        <v>1108</v>
       </c>
       <c r="G4" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="B5">
         <v>166488</v>
       </c>
       <c r="D5" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="E5" t="s">
-        <v>1097</v>
+        <v>1079</v>
       </c>
       <c r="F5" t="s">
-        <v>1127</v>
+        <v>1109</v>
       </c>
       <c r="G5" t="s">
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="B6">
         <v>166495</v>
       </c>
       <c r="D6" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="E6" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="F6" t="s">
-        <v>1128</v>
+        <v>1110</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>985</v>
+        <v>967</v>
       </c>
       <c r="B7">
         <v>166520</v>
       </c>
       <c r="D7" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
       <c r="E7" t="s">
-        <v>902</v>
+        <v>884</v>
       </c>
       <c r="F7" t="s">
-        <v>1129</v>
+        <v>1111</v>
       </c>
       <c r="G7" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
       <c r="B8">
         <v>166528</v>
       </c>
       <c r="D8" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="E8" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>1130</v>
+        <v>1112</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="B9">
         <v>166523</v>
       </c>
       <c r="D9" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F9" t="s">
-        <v>1131</v>
+        <v>1113</v>
       </c>
       <c r="G9" t="s">
-        <v>1178</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>988</v>
+        <v>970</v>
       </c>
       <c r="B10">
         <v>166570</v>
       </c>
       <c r="D10" t="s">
-        <v>1045</v>
+        <v>1027</v>
       </c>
       <c r="E10" t="s">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="F10" t="s">
-        <v>1132</v>
+        <v>1114</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="B11">
         <v>166578</v>
       </c>
       <c r="D11" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="E11" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F11" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G11" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>990</v>
+        <v>972</v>
       </c>
       <c r="B12">
         <v>166569</v>
       </c>
       <c r="D12" t="s">
-        <v>1047</v>
+        <v>1029</v>
       </c>
       <c r="E12" t="s">
-        <v>1099</v>
+        <v>1081</v>
       </c>
       <c r="F12" t="s">
-        <v>1133</v>
+        <v>1115</v>
       </c>
       <c r="G12" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="B13">
         <v>166734</v>
       </c>
+      <c r="C13">
+        <v>10</v>
+      </c>
       <c r="D13" t="s">
-        <v>1048</v>
+        <v>1030</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1134</v>
+        <v>1116</v>
       </c>
       <c r="G13" t="s">
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="B14">
         <v>166806</v>
       </c>
+      <c r="C14">
+        <v>11</v>
+      </c>
       <c r="D14" t="s">
-        <v>1049</v>
+        <v>1031</v>
       </c>
       <c r="E14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="B15">
         <v>166637</v>
       </c>
+      <c r="C15">
+        <v>12</v>
+      </c>
       <c r="D15" t="s">
-        <v>1050</v>
+        <v>1032</v>
       </c>
       <c r="E15" t="s">
-        <v>1100</v>
+        <v>1082</v>
       </c>
       <c r="F15" t="s">
-        <v>1135</v>
+        <v>1117</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
       <c r="B16">
         <v>166648</v>
       </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
       <c r="D16" t="s">
-        <v>1051</v>
+        <v>1033</v>
       </c>
       <c r="E16" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="F16" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="G16" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="B17">
         <v>166676</v>
       </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
       <c r="D17" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="E17" t="s">
-        <v>1101</v>
+        <v>1083</v>
       </c>
       <c r="F17" t="s">
-        <v>1136</v>
+        <v>1118</v>
       </c>
       <c r="G17" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="B18">
         <v>166715</v>
       </c>
+      <c r="C18">
+        <v>15</v>
+      </c>
       <c r="D18" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
       <c r="E18" t="s">
-        <v>1102</v>
+        <v>1084</v>
       </c>
       <c r="F18" t="s">
-        <v>1137</v>
+        <v>1119</v>
       </c>
       <c r="G18" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>997</v>
+        <v>979</v>
       </c>
       <c r="B19">
         <v>166692</v>
       </c>
+      <c r="C19">
+        <v>16</v>
+      </c>
       <c r="D19" t="s">
-        <v>1054</v>
+        <v>1036</v>
       </c>
       <c r="E19" t="s">
-        <v>1103</v>
+        <v>1085</v>
       </c>
       <c r="F19" t="s">
-        <v>1138</v>
+        <v>1120</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>998</v>
+        <v>980</v>
       </c>
       <c r="B20">
         <v>166694</v>
       </c>
+      <c r="C20">
+        <v>17</v>
+      </c>
       <c r="D20" t="s">
-        <v>1055</v>
+        <v>1037</v>
       </c>
       <c r="E20" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>1139</v>
+        <v>1121</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="B21">
         <v>166709</v>
       </c>
+      <c r="C21">
+        <v>18</v>
+      </c>
       <c r="D21" t="s">
-        <v>1056</v>
+        <v>1038</v>
       </c>
       <c r="E21" t="s">
-        <v>1104</v>
+        <v>1086</v>
       </c>
       <c r="F21" t="s">
-        <v>1140</v>
+        <v>1122</v>
       </c>
       <c r="G21" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="B22">
         <v>166717</v>
       </c>
+      <c r="C22">
+        <v>19</v>
+      </c>
       <c r="D22" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="E22" t="s">
-        <v>1105</v>
+        <v>1087</v>
       </c>
       <c r="F22" t="s">
-        <v>1141</v>
+        <v>1123</v>
       </c>
       <c r="G22" t="s">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="B23">
         <v>166751</v>
       </c>
+      <c r="C23">
+        <v>20</v>
+      </c>
       <c r="D23" t="s">
-        <v>1058</v>
+        <v>1040</v>
       </c>
       <c r="E23" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="F23" t="s">
-        <v>1142</v>
+        <v>1124</v>
       </c>
       <c r="G23" t="s">
-        <v>1185</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="B24">
         <v>166777</v>
       </c>
+      <c r="C24">
+        <v>10</v>
+      </c>
       <c r="D24" t="s">
-        <v>1059</v>
+        <v>1041</v>
       </c>
       <c r="E24" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="F24" t="s">
-        <v>1143</v>
+        <v>1125</v>
       </c>
       <c r="G24" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="B25">
         <v>166789</v>
       </c>
+      <c r="C25">
+        <v>11</v>
+      </c>
       <c r="D25" t="s">
-        <v>1060</v>
+        <v>1042</v>
       </c>
       <c r="E25" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F25" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G25" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="B26">
         <v>166791</v>
       </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
       <c r="D26" t="s">
-        <v>1061</v>
+        <v>1043</v>
       </c>
       <c r="E26" t="s">
-        <v>1106</v>
+        <v>1088</v>
       </c>
       <c r="F26" t="s">
-        <v>1144</v>
+        <v>1126</v>
       </c>
       <c r="G26" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
       <c r="B27">
         <v>166819</v>
       </c>
+      <c r="C27">
+        <v>13</v>
+      </c>
       <c r="D27" t="s">
-        <v>1062</v>
+        <v>1044</v>
       </c>
       <c r="E27" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>953</v>
+        <v>935</v>
       </c>
       <c r="G27" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="B28">
         <v>166527</v>
       </c>
+      <c r="C28">
+        <v>14</v>
+      </c>
       <c r="D28" t="s">
-        <v>1063</v>
+        <v>1045</v>
       </c>
       <c r="E28" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="F28" t="s">
-        <v>1145</v>
+        <v>1127</v>
       </c>
       <c r="G28" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>1007</v>
+        <v>989</v>
       </c>
       <c r="B29">
         <v>166610</v>
       </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
       <c r="D29" t="s">
-        <v>1064</v>
+        <v>1046</v>
       </c>
       <c r="E29" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
       <c r="F29" t="s">
-        <v>1146</v>
+        <v>1128</v>
       </c>
       <c r="G29" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>1008</v>
+        <v>990</v>
       </c>
       <c r="B30">
         <v>166512</v>
       </c>
+      <c r="C30">
+        <v>16</v>
+      </c>
       <c r="D30" t="s">
-        <v>1065</v>
+        <v>1047</v>
       </c>
       <c r="E30" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="F30" t="s">
-        <v>1147</v>
+        <v>1129</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>1009</v>
+        <v>991</v>
       </c>
       <c r="B31">
         <v>166526</v>
       </c>
+      <c r="C31">
+        <v>17</v>
+      </c>
       <c r="D31" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="E31" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="F31" t="s">
-        <v>1148</v>
+        <v>1130</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>1010</v>
+        <v>992</v>
       </c>
       <c r="B32">
         <v>166530</v>
       </c>
+      <c r="C32">
+        <v>18</v>
+      </c>
       <c r="D32" t="s">
-        <v>1067</v>
+        <v>1049</v>
       </c>
       <c r="E32" t="s">
-        <v>1108</v>
+        <v>1090</v>
       </c>
       <c r="F32" t="s">
-        <v>1149</v>
+        <v>1131</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>1011</v>
+        <v>993</v>
       </c>
       <c r="B33">
         <v>166602</v>
       </c>
+      <c r="C33">
+        <v>19</v>
+      </c>
       <c r="D33" t="s">
-        <v>1068</v>
+        <v>1050</v>
       </c>
       <c r="E33" t="s">
-        <v>1109</v>
+        <v>1091</v>
       </c>
       <c r="F33" t="s">
-        <v>1150</v>
+        <v>1132</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>1012</v>
+        <v>994</v>
       </c>
       <c r="B34">
         <v>166605</v>
       </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
       <c r="D34" t="s">
-        <v>1069</v>
+        <v>1051</v>
       </c>
       <c r="E34" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="F34" t="s">
-        <v>1151</v>
+        <v>1133</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>1013</v>
+        <v>995</v>
       </c>
       <c r="B35">
         <v>166614</v>
       </c>
+      <c r="C35">
+        <v>10</v>
+      </c>
       <c r="D35" t="s">
-        <v>1070</v>
+        <v>1052</v>
       </c>
       <c r="E35" t="s">
-        <v>1110</v>
+        <v>1092</v>
       </c>
       <c r="F35" t="s">
-        <v>1152</v>
+        <v>1134</v>
       </c>
       <c r="G35" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>1014</v>
+        <v>996</v>
       </c>
       <c r="B36">
         <v>166618</v>
       </c>
+      <c r="C36">
+        <v>11</v>
+      </c>
       <c r="D36" t="s">
-        <v>1071</v>
+        <v>1053</v>
       </c>
       <c r="E36" t="s">
-        <v>1108</v>
+        <v>1090</v>
       </c>
       <c r="F36" t="s">
-        <v>1153</v>
+        <v>1135</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>1015</v>
+        <v>997</v>
       </c>
       <c r="B37">
         <v>166620</v>
       </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
       <c r="D37" t="s">
-        <v>1072</v>
+        <v>1054</v>
       </c>
       <c r="E37" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>1154</v>
+        <v>1136</v>
       </c>
       <c r="G37" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>1016</v>
+        <v>998</v>
       </c>
       <c r="B38">
         <v>166621</v>
       </c>
+      <c r="C38">
+        <v>13</v>
+      </c>
       <c r="D38" t="s">
-        <v>1073</v>
+        <v>1055</v>
       </c>
       <c r="E38" t="s">
-        <v>1111</v>
+        <v>1093</v>
       </c>
       <c r="F38" t="s">
-        <v>1155</v>
+        <v>1137</v>
       </c>
       <c r="G38" t="s">
-        <v>1192</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>1017</v>
+        <v>999</v>
       </c>
       <c r="B39">
         <v>166632</v>
       </c>
+      <c r="C39">
+        <v>14</v>
+      </c>
       <c r="D39" t="s">
-        <v>1074</v>
+        <v>1056</v>
       </c>
       <c r="E39" t="s">
-        <v>1112</v>
+        <v>1094</v>
       </c>
       <c r="F39" t="s">
-        <v>1156</v>
+        <v>1138</v>
       </c>
       <c r="G39" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1018</v>
+        <v>1000</v>
       </c>
       <c r="B40">
         <v>166649</v>
       </c>
+      <c r="C40">
+        <v>15</v>
+      </c>
       <c r="D40" t="s">
-        <v>1075</v>
+        <v>1057</v>
       </c>
       <c r="E40" t="s">
-        <v>1113</v>
+        <v>1095</v>
       </c>
       <c r="F40" t="s">
-        <v>1157</v>
+        <v>1139</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1019</v>
+        <v>1001</v>
       </c>
       <c r="B41">
         <v>166652</v>
       </c>
+      <c r="C41">
+        <v>16</v>
+      </c>
       <c r="D41" t="s">
-        <v>1076</v>
+        <v>1058</v>
       </c>
       <c r="E41" t="s">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="F41" t="s">
-        <v>1158</v>
+        <v>1140</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1020</v>
+        <v>1002</v>
       </c>
       <c r="B42">
         <v>166672</v>
       </c>
+      <c r="C42">
+        <v>17</v>
+      </c>
       <c r="D42" t="s">
-        <v>1077</v>
+        <v>1059</v>
       </c>
       <c r="E42" t="s">
-        <v>1115</v>
+        <v>1097</v>
       </c>
       <c r="F42" t="s">
-        <v>1159</v>
+        <v>1141</v>
       </c>
       <c r="G42" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="B43">
         <v>166677</v>
       </c>
+      <c r="C43">
+        <v>18</v>
+      </c>
       <c r="D43" t="s">
-        <v>1078</v>
+        <v>1060</v>
       </c>
       <c r="E43" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="F43" t="s">
-        <v>1160</v>
+        <v>1142</v>
       </c>
       <c r="G43" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="B44">
         <v>166680</v>
       </c>
+      <c r="C44">
+        <v>19</v>
+      </c>
       <c r="D44" t="s">
-        <v>1079</v>
+        <v>1061</v>
       </c>
       <c r="E44" t="s">
-        <v>1116</v>
+        <v>1098</v>
       </c>
       <c r="F44" t="s">
-        <v>1161</v>
+        <v>1143</v>
       </c>
       <c r="G44" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1023</v>
+        <v>1005</v>
       </c>
       <c r="B45">
         <v>166718</v>
       </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
       <c r="D45" t="s">
-        <v>1080</v>
+        <v>1062</v>
       </c>
       <c r="E45" t="s">
-        <v>1117</v>
+        <v>1099</v>
       </c>
       <c r="F45" t="s">
-        <v>1162</v>
+        <v>1144</v>
       </c>
       <c r="G45" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="B46">
         <v>166720</v>
       </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
       <c r="D46" t="s">
-        <v>1081</v>
+        <v>1063</v>
       </c>
       <c r="E46" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F46" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G46" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1025</v>
+        <v>1007</v>
       </c>
       <c r="B47">
         <v>166742</v>
       </c>
+      <c r="C47">
+        <v>11</v>
+      </c>
       <c r="D47" t="s">
-        <v>1082</v>
+        <v>1064</v>
       </c>
       <c r="E47" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="F47" t="s">
-        <v>1163</v>
+        <v>1145</v>
       </c>
       <c r="G47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>1026</v>
+        <v>1008</v>
       </c>
       <c r="B48">
         <v>166752</v>
       </c>
+      <c r="C48">
+        <v>12</v>
+      </c>
       <c r="D48" t="s">
-        <v>1083</v>
+        <v>1065</v>
       </c>
       <c r="E48" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="F48" t="s">
-        <v>1164</v>
+        <v>1146</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1027</v>
+        <v>1009</v>
       </c>
       <c r="B49">
         <v>166761</v>
       </c>
+      <c r="C49">
+        <v>13</v>
+      </c>
       <c r="D49" t="s">
-        <v>1084</v>
+        <v>1066</v>
       </c>
       <c r="E49" t="s">
-        <v>1118</v>
+        <v>1100</v>
       </c>
       <c r="F49" t="s">
-        <v>1165</v>
+        <v>1147</v>
       </c>
       <c r="G49" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1028</v>
+        <v>1010</v>
       </c>
       <c r="B50">
         <v>166772</v>
       </c>
+      <c r="C50">
+        <v>14</v>
+      </c>
       <c r="D50" t="s">
-        <v>1085</v>
+        <v>1067</v>
       </c>
       <c r="E50" t="s">
-        <v>1119</v>
+        <v>1101</v>
       </c>
       <c r="F50" t="s">
-        <v>1166</v>
+        <v>1148</v>
       </c>
       <c r="G50" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1029</v>
+        <v>1011</v>
       </c>
       <c r="B51">
         <v>166786</v>
       </c>
+      <c r="C51">
+        <v>15</v>
+      </c>
       <c r="D51" t="s">
-        <v>1086</v>
+        <v>1068</v>
       </c>
       <c r="E51" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="F51" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="G51" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="B52">
         <v>166815</v>
       </c>
+      <c r="C52">
+        <v>16</v>
+      </c>
       <c r="D52" t="s">
-        <v>1087</v>
+        <v>1069</v>
       </c>
       <c r="E52" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="F52" t="s">
-        <v>1167</v>
+        <v>1149</v>
       </c>
       <c r="G52" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="B53">
         <v>166816</v>
       </c>
+      <c r="C53">
+        <v>17</v>
+      </c>
       <c r="D53" t="s">
-        <v>1088</v>
+        <v>1070</v>
       </c>
       <c r="E53" t="s">
-        <v>1120</v>
+        <v>1102</v>
       </c>
       <c r="F53" t="s">
-        <v>1168</v>
+        <v>1150</v>
       </c>
       <c r="G53" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
       <c r="B54">
         <v>166817</v>
       </c>
+      <c r="C54">
+        <v>18</v>
+      </c>
       <c r="D54" t="s">
-        <v>1089</v>
+        <v>1071</v>
       </c>
       <c r="E54" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="F54" t="s">
-        <v>1169</v>
+        <v>1151</v>
       </c>
       <c r="G54" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="B55">
         <v>167826</v>
       </c>
+      <c r="C55">
+        <v>19</v>
+      </c>
       <c r="D55" t="s">
-        <v>1090</v>
+        <v>1072</v>
       </c>
       <c r="E55" t="s">
-        <v>1121</v>
+        <v>1103</v>
       </c>
       <c r="F55" t="s">
-        <v>1170</v>
+        <v>1152</v>
       </c>
       <c r="G55" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1034</v>
+        <v>1016</v>
       </c>
       <c r="B56">
         <v>167837</v>
       </c>
+      <c r="C56">
+        <v>20</v>
+      </c>
       <c r="D56" t="s">
-        <v>1091</v>
+        <v>1073</v>
       </c>
       <c r="E56" t="s">
-        <v>1122</v>
+        <v>1104</v>
       </c>
       <c r="F56" t="s">
-        <v>1171</v>
+        <v>1153</v>
       </c>
       <c r="G56" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="B57">
         <v>170164</v>
       </c>
+      <c r="C57">
+        <v>10</v>
+      </c>
       <c r="D57" t="s">
-        <v>1092</v>
+        <v>1074</v>
       </c>
       <c r="E57" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F57" t="s">
-        <v>1172</v>
+        <v>1154</v>
       </c>
       <c r="G57" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="B58">
         <v>170518</v>
       </c>
+      <c r="C58">
+        <v>11</v>
+      </c>
       <c r="D58" t="s">
-        <v>1093</v>
+        <v>1075</v>
       </c>
       <c r="E58" t="s">
-        <v>1123</v>
+        <v>1105</v>
       </c>
       <c r="F58" t="s">
-        <v>1123</v>
+        <v>1105</v>
       </c>
       <c r="G58" t="s">
-        <v>1201</v>
+        <v>1183</v>
       </c>
     </row>
   </sheetData>
@@ -5319,457 +5454,520 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>166463</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>166513</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>166553</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>166712</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>166723</v>
       </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="G6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>166728</v>
       </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>166758</v>
       </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>166483</v>
       </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>166568</v>
       </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G10" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>166785</v>
       </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>166759</v>
       </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="G12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>166481</v>
       </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>166473</v>
       </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B15">
         <v>166499</v>
       </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B16">
         <v>166498</v>
       </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F16" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B17">
         <v>166517</v>
       </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F17" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" t="s">
         <v>125</v>
       </c>
-      <c r="G17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="B18">
         <v>166584</v>
       </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B19">
         <v>166644</v>
       </c>
+      <c r="C19">
+        <v>7</v>
+      </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E19" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F19" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="B20">
         <v>166653</v>
       </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F20" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B21">
         <v>166655</v>
       </c>
+      <c r="C21">
+        <v>9</v>
+      </c>
       <c r="D21" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G21" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B22">
         <v>166788</v>
       </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
       <c r="D22" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -5778,397 +5976,451 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B2">
         <v>166492</v>
       </c>
+      <c r="C2">
+        <v>12</v>
+      </c>
       <c r="D2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E2" t="s">
         <v>164</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>182</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>200</v>
       </c>
-      <c r="G2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B3">
         <v>166625</v>
       </c>
+      <c r="C3">
+        <v>13</v>
+      </c>
       <c r="D3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E3" t="s">
         <v>165</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>183</v>
       </c>
-      <c r="F3" t="s">
-        <v>201</v>
-      </c>
       <c r="G3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="B4">
         <v>166635</v>
       </c>
+      <c r="C4">
+        <v>14</v>
+      </c>
       <c r="D4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E4" t="s">
         <v>166</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>184</v>
       </c>
-      <c r="F4" t="s">
-        <v>202</v>
-      </c>
       <c r="G4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B5">
         <v>166698</v>
       </c>
+      <c r="C5">
+        <v>15</v>
+      </c>
       <c r="D5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5" t="s">
         <v>167</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>185</v>
       </c>
-      <c r="F5" t="s">
-        <v>203</v>
-      </c>
       <c r="G5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B6">
         <v>167674</v>
       </c>
+      <c r="C6">
+        <v>16</v>
+      </c>
       <c r="D6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
         <v>168</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>186</v>
       </c>
-      <c r="F6" t="s">
-        <v>204</v>
-      </c>
       <c r="G6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B7">
         <v>166697</v>
       </c>
+      <c r="C7">
+        <v>17</v>
+      </c>
       <c r="D7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" t="s">
         <v>169</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>187</v>
       </c>
-      <c r="F7" t="s">
-        <v>205</v>
-      </c>
       <c r="G7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B8">
         <v>166811</v>
       </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
       <c r="D8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" t="s">
         <v>170</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>188</v>
       </c>
-      <c r="F8" t="s">
-        <v>206</v>
-      </c>
       <c r="G8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="B9">
         <v>166470</v>
       </c>
+      <c r="C9">
+        <v>19</v>
+      </c>
       <c r="D9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E9" t="s">
         <v>171</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>189</v>
       </c>
-      <c r="F9" t="s">
-        <v>207</v>
-      </c>
       <c r="G9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>154</v>
       </c>
       <c r="B10">
         <v>166666</v>
       </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
       <c r="D10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" t="s">
         <v>172</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>190</v>
       </c>
-      <c r="F10" t="s">
-        <v>208</v>
-      </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="B11">
         <v>166501</v>
       </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
       <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" t="s">
         <v>173</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>191</v>
       </c>
-      <c r="F11" t="s">
-        <v>209</v>
-      </c>
       <c r="G11" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="B12">
         <v>166533</v>
       </c>
+      <c r="C12">
+        <v>13</v>
+      </c>
       <c r="D12" t="s">
+        <v>156</v>
+      </c>
+      <c r="E12" t="s">
         <v>174</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>192</v>
       </c>
-      <c r="F12" t="s">
-        <v>210</v>
-      </c>
       <c r="G12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="B13">
         <v>166534</v>
       </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
       <c r="D13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" t="s">
         <v>175</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>193</v>
       </c>
-      <c r="F13" t="s">
-        <v>211</v>
-      </c>
       <c r="G13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="B14">
         <v>166683</v>
       </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
       <c r="D14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" t="s">
         <v>176</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>194</v>
       </c>
-      <c r="F14" t="s">
-        <v>212</v>
-      </c>
       <c r="G14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="B15">
         <v>166735</v>
       </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
       <c r="D15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E15" t="s">
         <v>177</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>195</v>
       </c>
-      <c r="F15" t="s">
-        <v>213</v>
-      </c>
       <c r="G15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B16">
         <v>166741</v>
       </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
       <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16" t="s">
         <v>178</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>196</v>
       </c>
-      <c r="F16" t="s">
-        <v>214</v>
-      </c>
       <c r="G16" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B17">
         <v>166793</v>
       </c>
+      <c r="C17">
+        <v>18</v>
+      </c>
       <c r="D17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" t="s">
         <v>179</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>197</v>
       </c>
-      <c r="F17" t="s">
-        <v>215</v>
-      </c>
       <c r="G17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="B18">
         <v>166822</v>
       </c>
+      <c r="C18">
+        <v>19</v>
+      </c>
       <c r="D18" t="s">
+        <v>162</v>
+      </c>
+      <c r="E18" t="s">
         <v>180</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>198</v>
       </c>
-      <c r="F18" t="s">
-        <v>216</v>
-      </c>
       <c r="G18" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="B19">
         <v>167676</v>
       </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
       <c r="D19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E19" t="s">
         <v>181</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>199</v>
       </c>
-      <c r="F19" t="s">
-        <v>217</v>
-      </c>
       <c r="G19" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -6177,997 +6429,1141 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="B2">
         <v>166500</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="E2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="F2" t="s">
-        <v>364</v>
+        <v>346</v>
       </c>
       <c r="G2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B3">
         <v>166535</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>365</v>
+        <v>347</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="B4">
         <v>166543</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
       <c r="D4" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="E4" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="F4" t="s">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="G4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="B5">
         <v>166549</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="F5" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="G5" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="B6">
         <v>166616</v>
       </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="E6" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F6" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="G6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="B7">
         <v>166693</v>
       </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E7" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="F7" t="s">
-        <v>369</v>
+        <v>351</v>
       </c>
       <c r="G7" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="B8">
         <v>166706</v>
       </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
       <c r="D8" t="s">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="E8" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="F8" t="s">
-        <v>370</v>
+        <v>352</v>
       </c>
       <c r="G8" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="B9">
         <v>166721</v>
       </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
       <c r="D9" t="s">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="E9" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="F9" t="s">
-        <v>371</v>
+        <v>353</v>
       </c>
       <c r="G9" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="B10">
         <v>166724</v>
       </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
       <c r="D10" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="E10" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="F10" t="s">
-        <v>372</v>
+        <v>354</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="B11">
         <v>166768</v>
       </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
       <c r="D11" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>373</v>
+        <v>355</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="B12">
         <v>166764</v>
       </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
       <c r="D12" t="s">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="E12" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="G12" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="B13">
         <v>166805</v>
       </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
       <c r="D13" t="s">
-        <v>287</v>
+        <v>269</v>
       </c>
       <c r="E13" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="F13" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="G13" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="B14">
         <v>166813</v>
       </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="B15">
         <v>167802</v>
       </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>271</v>
       </c>
       <c r="E15" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="G15" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B16">
         <v>167855</v>
       </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="F16" t="s">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B17">
         <v>166537</v>
       </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
       <c r="D17" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="E17" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="F17" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="B18">
         <v>166548</v>
       </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
       <c r="D18" t="s">
-        <v>292</v>
+        <v>274</v>
       </c>
       <c r="E18" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="F18" t="s">
-        <v>379</v>
+        <v>361</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B19">
         <v>166588</v>
       </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
       <c r="D19" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="E19" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="F19" t="s">
-        <v>380</v>
+        <v>362</v>
       </c>
       <c r="G19" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="B20">
         <v>166642</v>
       </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
       <c r="D20" t="s">
-        <v>294</v>
+        <v>276</v>
       </c>
       <c r="E20" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="F20" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
       <c r="G20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="B21">
         <v>166665</v>
       </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
       <c r="D21" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
+        <v>172</v>
+      </c>
+      <c r="F21" t="s">
         <v>190</v>
       </c>
-      <c r="F21" t="s">
-        <v>208</v>
-      </c>
       <c r="G21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B22">
         <v>166688</v>
       </c>
+      <c r="C22">
+        <v>7</v>
+      </c>
       <c r="D22" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="E22" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="F22" t="s">
-        <v>382</v>
+        <v>364</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B23">
         <v>166722</v>
       </c>
+      <c r="C23">
+        <v>8</v>
+      </c>
       <c r="D23" t="s">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="E23" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="F23" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="G23" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="B24">
         <v>166769</v>
       </c>
+      <c r="C24">
+        <v>9</v>
+      </c>
       <c r="D24" t="s">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="E24" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="F24" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="G24" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="B25">
         <v>166471</v>
       </c>
+      <c r="C25">
+        <v>10</v>
+      </c>
       <c r="D25" t="s">
-        <v>299</v>
+        <v>281</v>
       </c>
       <c r="E25" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="F25" t="s">
-        <v>385</v>
+        <v>367</v>
       </c>
       <c r="G25" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B26">
         <v>166465</v>
       </c>
+      <c r="C26">
+        <v>11</v>
+      </c>
       <c r="D26" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="E26" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="F26" t="s">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="G26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="B27">
         <v>166491</v>
       </c>
+      <c r="C27">
+        <v>12</v>
+      </c>
       <c r="D27" t="s">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="E27" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="F27" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>236</v>
       </c>
       <c r="B28">
         <v>166547</v>
       </c>
+      <c r="C28">
+        <v>13</v>
+      </c>
       <c r="D28" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="E28" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="F28" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="G28" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="B29">
         <v>166554</v>
       </c>
+      <c r="C29">
+        <v>14</v>
+      </c>
       <c r="D29" t="s">
-        <v>303</v>
+        <v>285</v>
       </c>
       <c r="E29" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="F29" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="G29" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="B30">
         <v>166787</v>
       </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
       <c r="D30" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="F30" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="G30" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="B31">
         <v>166536</v>
       </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
       <c r="D31" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="E31" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="F31" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="G31" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="B32">
         <v>166725</v>
       </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
       <c r="D32" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="F32" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="G32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="B33">
         <v>166464</v>
       </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
       <c r="D33" t="s">
-        <v>307</v>
+        <v>289</v>
       </c>
       <c r="E33" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="F33" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="G33" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="B34">
         <v>166555</v>
       </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
       <c r="D34" t="s">
-        <v>308</v>
+        <v>290</v>
       </c>
       <c r="E34" t="s">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="F34" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="G34" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="B35">
         <v>166562</v>
       </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
       <c r="D35" t="s">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="E35" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="F35" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="G35" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="B36">
         <v>166586</v>
       </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
       <c r="D36" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="E36" t="s">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="F36" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="G36" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B37">
         <v>166613</v>
       </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
       <c r="D37" t="s">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="E37" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F37" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G37" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="B38">
         <v>166617</v>
       </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
       <c r="D38" t="s">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="E38" t="s">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="F38" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>265</v>
+        <v>247</v>
       </c>
       <c r="B39">
         <v>166634</v>
       </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
       <c r="D39" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="B40">
         <v>166639</v>
       </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
       <c r="D40" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="E40" t="s">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="F40" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>267</v>
+        <v>249</v>
       </c>
       <c r="B41">
         <v>166647</v>
       </c>
+      <c r="C41">
+        <v>12</v>
+      </c>
       <c r="D41" t="s">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="E41" t="s">
-        <v>355</v>
+        <v>337</v>
       </c>
       <c r="F41" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="G41" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="B42">
         <v>166670</v>
       </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
       <c r="D42" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="E42" t="s">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="G42" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="B43">
         <v>166686</v>
       </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
       <c r="D43" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="E43" t="s">
-        <v>357</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="G43" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="B44">
         <v>166689</v>
       </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
       <c r="D44" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="E44" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="F44" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="G44" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B45">
         <v>166690</v>
       </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
       <c r="D45" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="E45" t="s">
-        <v>359</v>
+        <v>341</v>
       </c>
       <c r="F45" t="s">
-        <v>404</v>
+        <v>386</v>
       </c>
       <c r="G45" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="B46">
         <v>166695</v>
       </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
       <c r="D46" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
       <c r="E46" t="s">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="F46" t="s">
-        <v>405</v>
+        <v>387</v>
       </c>
       <c r="G46" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="B47">
         <v>166726</v>
       </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
       <c r="D47" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="E47" t="s">
-        <v>361</v>
+        <v>343</v>
       </c>
       <c r="F47" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="G47" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B48">
         <v>166812</v>
       </c>
+      <c r="C48">
+        <v>5</v>
+      </c>
       <c r="D48" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="E48" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="F48" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="G48" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="B49">
         <v>167673</v>
       </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
       <c r="D49" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="E49" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="F49" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="G49" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -7176,437 +7572,497 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="B2">
         <v>166631</v>
       </c>
+      <c r="C2">
+        <v>15</v>
+      </c>
       <c r="D2" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="E2" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="F2" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="B3">
         <v>166646</v>
       </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
       <c r="D3" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="E3" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="F3" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="G3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="B4">
         <v>166660</v>
       </c>
+      <c r="C4">
+        <v>17</v>
+      </c>
       <c r="D4" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E4" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="F4" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
       <c r="G4" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>436</v>
+        <v>418</v>
       </c>
       <c r="B5">
         <v>166661</v>
       </c>
+      <c r="C5">
+        <v>18</v>
+      </c>
       <c r="D5" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="E5" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="F5" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="G5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="B6">
         <v>166699</v>
       </c>
+      <c r="C6">
+        <v>19</v>
+      </c>
       <c r="D6" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E6" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="F6" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="G6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B7">
         <v>166701</v>
       </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
       <c r="D7" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="F7" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="G7" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="B8">
         <v>166784</v>
       </c>
+      <c r="C8">
+        <v>15</v>
+      </c>
       <c r="D8" t="s">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F8" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="B9">
         <v>166747</v>
       </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
       <c r="D9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E9" t="s">
         <v>460</v>
       </c>
-      <c r="E9" t="s">
-        <v>478</v>
-      </c>
       <c r="F9" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="B10">
         <v>166487</v>
       </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
       <c r="D10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" t="s">
         <v>461</v>
       </c>
-      <c r="E10" t="s">
-        <v>479</v>
-      </c>
       <c r="F10" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="G10" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>442</v>
+        <v>424</v>
       </c>
       <c r="B11">
         <v>166560</v>
       </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
       <c r="D11" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="F11" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="G11" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="B12">
         <v>166597</v>
       </c>
+      <c r="C12">
+        <v>19</v>
+      </c>
       <c r="D12" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="B13">
         <v>166604</v>
       </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
       <c r="D13" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="F13" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="G13" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="B14">
         <v>166607</v>
       </c>
+      <c r="C14">
+        <v>15</v>
+      </c>
       <c r="D14" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="E14" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F14" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>446</v>
+        <v>428</v>
       </c>
       <c r="B15">
         <v>166612</v>
       </c>
+      <c r="C15">
+        <v>16</v>
+      </c>
       <c r="D15" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F15" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="B16">
         <v>166627</v>
       </c>
+      <c r="C16">
+        <v>17</v>
+      </c>
       <c r="D16" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E16" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="B17">
         <v>166729</v>
       </c>
+      <c r="C17">
+        <v>18</v>
+      </c>
       <c r="D17" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="E17" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="F17" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>449</v>
+        <v>431</v>
       </c>
       <c r="B18">
         <v>166750</v>
       </c>
+      <c r="C18">
+        <v>19</v>
+      </c>
       <c r="D18" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="E18" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F18" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G18" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>450</v>
+        <v>432</v>
       </c>
       <c r="B19">
         <v>166796</v>
       </c>
+      <c r="C19">
+        <v>20</v>
+      </c>
       <c r="D19" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
       <c r="E19" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="F19" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="B20">
         <v>167817</v>
       </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
       <c r="D20" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="E20" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F20" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="G20" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B21">
         <v>171014</v>
       </c>
+      <c r="C21">
+        <v>16</v>
+      </c>
       <c r="D21" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="E21" t="s">
+        <v>466</v>
+      </c>
+      <c r="F21" t="s">
         <v>484</v>
       </c>
-      <c r="F21" t="s">
-        <v>502</v>
-      </c>
       <c r="G21" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -7615,477 +8071,543 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="B2">
         <v>166466</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="E2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F2" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="G2" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B3">
         <v>166467</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="G3" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="B4">
         <v>166519</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
       <c r="D4" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="E4" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="F4" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="B5">
         <v>166550</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="E5" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="F5" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="G5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="B6">
         <v>166645</v>
       </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="E6" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="F6" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="G6" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="B7">
         <v>166643</v>
       </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
       <c r="D7" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
       <c r="E7" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="F7" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="G7" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="B8">
         <v>166685</v>
       </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
       <c r="D8" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="E8" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="F8" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="G8" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B9">
         <v>166810</v>
       </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
       <c r="D9" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="E9" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="F9" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="G9" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="B10">
         <v>166740</v>
       </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
       <c r="D10" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="E10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" t="s">
         <v>195</v>
       </c>
-      <c r="F10" t="s">
-        <v>213</v>
-      </c>
       <c r="G10" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="B11">
         <v>166754</v>
       </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
       <c r="D11" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="E11" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="F11" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="B12">
         <v>166775</v>
       </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
       <c r="D12" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="E12" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="F12" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="G12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="B13">
         <v>166475</v>
       </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
       <c r="D13" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="E13" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
       <c r="F13" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="G13" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="B14">
         <v>166511</v>
       </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
       <c r="D14" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="E14" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="F14" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="G14" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="B15">
         <v>166518</v>
       </c>
+      <c r="C15">
+        <v>14</v>
+      </c>
       <c r="D15" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="E15" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="F15" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="B16">
         <v>166524</v>
       </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
       <c r="D16" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E16" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="F16" t="s">
+        <v>567</v>
+      </c>
+      <c r="G16" t="s">
         <v>585</v>
       </c>
-      <c r="G16" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="B17">
         <v>166525</v>
       </c>
+      <c r="C17">
+        <v>16</v>
+      </c>
       <c r="D17" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
       <c r="E17" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="F17" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="B18">
         <v>166563</v>
       </c>
+      <c r="C18">
+        <v>17</v>
+      </c>
       <c r="D18" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="E18" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="F18" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
       <c r="B19">
         <v>166608</v>
       </c>
+      <c r="C19">
+        <v>18</v>
+      </c>
       <c r="D19" t="s">
+        <v>532</v>
+      </c>
+      <c r="E19" t="s">
         <v>550</v>
       </c>
-      <c r="E19" t="s">
-        <v>568</v>
-      </c>
       <c r="F19" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="G19" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="B20">
         <v>166659</v>
       </c>
+      <c r="C20">
+        <v>19</v>
+      </c>
       <c r="D20" t="s">
+        <v>533</v>
+      </c>
+      <c r="E20" t="s">
         <v>551</v>
       </c>
-      <c r="E20" t="s">
-        <v>569</v>
-      </c>
       <c r="F20" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="G20" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="B21">
         <v>166664</v>
       </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
       <c r="D21" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="E21" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F21" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="B22">
         <v>166727</v>
       </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
       <c r="D22" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
       <c r="E22" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="F22" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="G22" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="B23">
         <v>166738</v>
       </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
       <c r="D23" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="E23" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="F23" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -8094,237 +8616,267 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="B2">
         <v>166656</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>634</v>
+        <v>616</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="B3">
         <v>166795</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
-        <v>618</v>
+        <v>600</v>
       </c>
       <c r="E3" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F3" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="G3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="B4">
         <v>166674</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
       <c r="D4" t="s">
-        <v>619</v>
+        <v>601</v>
       </c>
       <c r="E4" t="s">
-        <v>628</v>
+        <v>610</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>618</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
       <c r="B5">
         <v>166582</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>620</v>
+        <v>602</v>
       </c>
       <c r="E5" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="G5" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="B6">
         <v>166679</v>
       </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
       <c r="D6" t="s">
-        <v>621</v>
+        <v>603</v>
       </c>
       <c r="E6" t="s">
-        <v>629</v>
+        <v>611</v>
       </c>
       <c r="F6" t="s">
-        <v>638</v>
+        <v>620</v>
       </c>
       <c r="G6" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="B7">
         <v>166794</v>
       </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
       <c r="D7" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="E7" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="F7" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="G7" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="B8">
         <v>167882</v>
       </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
       <c r="D8" t="s">
-        <v>623</v>
+        <v>605</v>
       </c>
       <c r="E8" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="B9">
         <v>166696</v>
       </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
       <c r="D9" t="s">
-        <v>624</v>
+        <v>606</v>
       </c>
       <c r="E9" t="s">
-        <v>631</v>
+        <v>613</v>
       </c>
       <c r="F9" t="s">
-        <v>641</v>
+        <v>623</v>
       </c>
       <c r="G9" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="B10">
         <v>166700</v>
       </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
       <c r="D10" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="E10" t="s">
-        <v>632</v>
+        <v>614</v>
       </c>
       <c r="F10" t="s">
-        <v>642</v>
+        <v>624</v>
       </c>
       <c r="G10" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="B11">
         <v>166792</v>
       </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
       <c r="D11" t="s">
-        <v>626</v>
+        <v>608</v>
       </c>
       <c r="E11" t="s">
-        <v>633</v>
+        <v>615</v>
       </c>
       <c r="F11" t="s">
-        <v>643</v>
+        <v>625</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -8333,857 +8885,980 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>650</v>
+        <v>632</v>
       </c>
       <c r="B2">
         <v>166462</v>
       </c>
+      <c r="C2">
+        <v>5</v>
+      </c>
       <c r="D2" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="E2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>633</v>
-      </c>
-      <c r="F2" t="s">
-        <v>643</v>
-      </c>
-      <c r="G2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>651</v>
       </c>
       <c r="B3">
         <v>166486</v>
       </c>
+      <c r="C3">
+        <v>6</v>
+      </c>
       <c r="D3" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="E3" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="F3" t="s">
-        <v>754</v>
+        <v>736</v>
       </c>
       <c r="G3" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>652</v>
+        <v>634</v>
       </c>
       <c r="B4">
         <v>166545</v>
       </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
       <c r="D4" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="E4" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="F4" t="s">
-        <v>755</v>
+        <v>737</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>653</v>
+        <v>635</v>
       </c>
       <c r="B5">
         <v>166557</v>
       </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
       <c r="D5" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="E5" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="F5" t="s">
-        <v>756</v>
+        <v>738</v>
       </c>
       <c r="G5" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>654</v>
+        <v>636</v>
       </c>
       <c r="B6">
         <v>166566</v>
       </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
       <c r="D6" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>757</v>
+        <v>739</v>
       </c>
       <c r="G6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>655</v>
+        <v>637</v>
       </c>
       <c r="B7">
         <v>166600</v>
       </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
       <c r="D7" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="E7" t="s">
-        <v>630</v>
+        <v>612</v>
       </c>
       <c r="F7" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="G7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>656</v>
+        <v>638</v>
       </c>
       <c r="B8">
         <v>166603</v>
       </c>
+      <c r="C8">
+        <v>11</v>
+      </c>
       <c r="D8" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="E8" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="F8" t="s">
-        <v>759</v>
+        <v>741</v>
       </c>
       <c r="G8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>657</v>
+        <v>639</v>
       </c>
       <c r="B9">
         <v>166624</v>
       </c>
+      <c r="C9">
+        <v>12</v>
+      </c>
       <c r="D9" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="E9" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="F9" t="s">
-        <v>760</v>
+        <v>742</v>
       </c>
       <c r="G9" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>658</v>
+        <v>640</v>
       </c>
       <c r="B10">
         <v>166628</v>
       </c>
+      <c r="C10">
+        <v>13</v>
+      </c>
       <c r="D10" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>640</v>
+        <v>622</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>659</v>
+        <v>641</v>
       </c>
       <c r="B11">
         <v>166636</v>
       </c>
+      <c r="C11">
+        <v>14</v>
+      </c>
       <c r="D11" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="E11" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="F11" t="s">
-        <v>761</v>
+        <v>743</v>
       </c>
       <c r="G11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>660</v>
+        <v>642</v>
       </c>
       <c r="B12">
         <v>166640</v>
       </c>
+      <c r="C12">
+        <v>15</v>
+      </c>
       <c r="D12" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="E12" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="F12" t="s">
-        <v>762</v>
+        <v>744</v>
       </c>
       <c r="G12" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="B13">
         <v>166668</v>
       </c>
+      <c r="C13">
+        <v>16</v>
+      </c>
       <c r="D13" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="E13" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F13" t="s">
-        <v>763</v>
+        <v>745</v>
       </c>
       <c r="G13" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>662</v>
+        <v>644</v>
       </c>
       <c r="B14">
         <v>166682</v>
       </c>
+      <c r="C14">
+        <v>17</v>
+      </c>
       <c r="D14" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="E14" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="G14" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="B15">
         <v>166705</v>
       </c>
+      <c r="C15">
+        <v>18</v>
+      </c>
       <c r="D15" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="E15" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
       <c r="F15" t="s">
-        <v>765</v>
+        <v>747</v>
       </c>
       <c r="G15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="B16">
         <v>166716</v>
       </c>
+      <c r="C16">
+        <v>19</v>
+      </c>
       <c r="D16" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="E16" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
       <c r="F16" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="G16" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="B17">
         <v>166743</v>
       </c>
+      <c r="C17">
+        <v>20</v>
+      </c>
       <c r="D17" t="s">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="G17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="B18">
         <v>166814</v>
       </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
       <c r="D18" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="E18" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
       <c r="F18" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="G18" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="B19">
         <v>166497</v>
       </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
       <c r="D19" t="s">
-        <v>708</v>
+        <v>690</v>
       </c>
       <c r="E19" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>769</v>
+        <v>751</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="B20">
         <v>166733</v>
       </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
       <c r="D20" t="s">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="E20" t="s">
-        <v>742</v>
+        <v>724</v>
       </c>
       <c r="F20" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="G20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="B21">
         <v>166496</v>
       </c>
+      <c r="C21">
+        <v>8</v>
+      </c>
       <c r="D21" t="s">
-        <v>710</v>
+        <v>692</v>
       </c>
       <c r="E21" t="s">
-        <v>743</v>
+        <v>725</v>
       </c>
       <c r="F21" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="G21" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="B22">
         <v>166783</v>
       </c>
+      <c r="C22">
+        <v>9</v>
+      </c>
       <c r="D22" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="G22" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="B23">
         <v>166468</v>
       </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
       <c r="D23" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="E23" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="G23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="B24">
         <v>166494</v>
       </c>
+      <c r="C24">
+        <v>11</v>
+      </c>
       <c r="D24" t="s">
-        <v>713</v>
+        <v>695</v>
       </c>
       <c r="E24" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="F24" t="s">
+        <v>756</v>
+      </c>
+      <c r="G24" t="s">
         <v>774</v>
       </c>
-      <c r="G24" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="B25">
         <v>166509</v>
       </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
       <c r="D25" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="E25" t="s">
-        <v>744</v>
+        <v>726</v>
       </c>
       <c r="F25" t="s">
+        <v>757</v>
+      </c>
+      <c r="G25" t="s">
         <v>775</v>
       </c>
-      <c r="G25" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="B26">
         <v>166531</v>
       </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
       <c r="D26" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
       <c r="E26" t="s">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="F26" t="s">
+        <v>758</v>
+      </c>
+      <c r="G26" t="s">
         <v>776</v>
       </c>
-      <c r="G26" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="B27">
         <v>166532</v>
       </c>
+      <c r="C27">
+        <v>14</v>
+      </c>
       <c r="D27" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
       <c r="E27" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="F27" t="s">
-        <v>777</v>
+        <v>759</v>
       </c>
       <c r="G27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="B28">
         <v>166559</v>
       </c>
+      <c r="C28">
+        <v>15</v>
+      </c>
       <c r="D28" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="E28" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="F28" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="G28" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="B29">
         <v>166564</v>
       </c>
+      <c r="C29">
+        <v>16</v>
+      </c>
       <c r="D29" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="E29" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="B30">
         <v>166565</v>
       </c>
+      <c r="C30">
+        <v>17</v>
+      </c>
       <c r="D30" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
       <c r="E30" t="s">
-        <v>746</v>
+        <v>728</v>
       </c>
       <c r="F30" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="G30" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="B31">
         <v>166606</v>
       </c>
+      <c r="C31">
+        <v>18</v>
+      </c>
       <c r="D31" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
       <c r="E31" t="s">
-        <v>747</v>
+        <v>729</v>
       </c>
       <c r="F31" t="s">
-        <v>780</v>
+        <v>762</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="B32">
         <v>166658</v>
       </c>
+      <c r="C32">
+        <v>19</v>
+      </c>
       <c r="D32" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
       <c r="E32" t="s">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="F32" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="G32" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="B33">
         <v>166667</v>
       </c>
+      <c r="C33">
+        <v>20</v>
+      </c>
       <c r="D33" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
       <c r="E33" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>767</v>
+        <v>749</v>
       </c>
       <c r="G33" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="B34">
         <v>166671</v>
       </c>
+      <c r="C34">
+        <v>5</v>
+      </c>
       <c r="D34" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="G34" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="B35">
         <v>166684</v>
       </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
       <c r="D35" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="E35" t="s">
-        <v>749</v>
+        <v>731</v>
       </c>
       <c r="F35" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="G35" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="B36">
         <v>166730</v>
       </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
       <c r="D36" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="E36" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="F36" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="B37">
         <v>166736</v>
       </c>
+      <c r="C37">
+        <v>8</v>
+      </c>
       <c r="D37" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
       <c r="E37" t="s">
-        <v>750</v>
+        <v>732</v>
       </c>
       <c r="F37" t="s">
-        <v>785</v>
+        <v>767</v>
       </c>
       <c r="G37" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="B38">
         <v>166739</v>
       </c>
+      <c r="C38">
+        <v>9</v>
+      </c>
       <c r="D38" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
       <c r="E38" t="s">
-        <v>751</v>
+        <v>733</v>
       </c>
       <c r="F38" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="G38" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="B39">
         <v>166749</v>
       </c>
+      <c r="C39">
+        <v>10</v>
+      </c>
       <c r="D39" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
       <c r="E39" t="s">
-        <v>752</v>
+        <v>734</v>
       </c>
       <c r="F39" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="G39" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="B40">
         <v>166766</v>
       </c>
+      <c r="C40">
+        <v>11</v>
+      </c>
       <c r="D40" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="B41">
         <v>167683</v>
       </c>
+      <c r="C41">
+        <v>12</v>
+      </c>
       <c r="D41" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
       <c r="E41" t="s">
+        <v>166</v>
+      </c>
+      <c r="F41" t="s">
         <v>184</v>
       </c>
-      <c r="F41" t="s">
-        <v>202</v>
-      </c>
       <c r="G41" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B42">
         <v>167825</v>
       </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
       <c r="D42" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
       <c r="E42" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="F42" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="G42" t="s">
-        <v>801</v>
+        <v>783</v>
       </c>
     </row>
   </sheetData>
@@ -9192,917 +9867,1049 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>802</v>
+        <v>784</v>
       </c>
       <c r="B2">
         <v>166521</v>
       </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
       <c r="D2" t="s">
-        <v>846</v>
+        <v>828</v>
       </c>
       <c r="E2" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
       <c r="F2" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="G2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="B3">
         <v>166516</v>
       </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
       <c r="D3" t="s">
-        <v>847</v>
+        <v>829</v>
       </c>
       <c r="E3" t="s">
-        <v>890</v>
+        <v>872</v>
       </c>
       <c r="F3" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="G3" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>804</v>
+        <v>786</v>
       </c>
       <c r="B4">
         <v>166508</v>
       </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
       <c r="D4" t="s">
-        <v>848</v>
+        <v>830</v>
       </c>
       <c r="E4" t="s">
-        <v>891</v>
+        <v>873</v>
       </c>
       <c r="F4" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>805</v>
+        <v>787</v>
       </c>
       <c r="B5">
         <v>166540</v>
       </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
       <c r="D5" t="s">
-        <v>849</v>
+        <v>831</v>
       </c>
       <c r="E5" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="F5" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="G5" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>806</v>
+        <v>788</v>
       </c>
       <c r="B6">
         <v>166541</v>
       </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
       <c r="D6" t="s">
-        <v>850</v>
+        <v>832</v>
       </c>
       <c r="E6" t="s">
-        <v>893</v>
+        <v>875</v>
       </c>
       <c r="F6" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="G6" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="B7">
         <v>166561</v>
       </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
       <c r="D7" t="s">
-        <v>851</v>
+        <v>833</v>
       </c>
       <c r="E7" t="s">
-        <v>894</v>
+        <v>876</v>
       </c>
       <c r="F7" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="G7" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="B8">
         <v>166619</v>
       </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
       <c r="D8" t="s">
-        <v>852</v>
+        <v>834</v>
       </c>
       <c r="E8" t="s">
-        <v>895</v>
+        <v>877</v>
       </c>
       <c r="F8" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="G8" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
       <c r="B9">
         <v>166623</v>
       </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
       <c r="D9" t="s">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="E9" t="s">
-        <v>896</v>
+        <v>878</v>
       </c>
       <c r="F9" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>810</v>
+        <v>792</v>
       </c>
       <c r="B10">
         <v>166630</v>
       </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
       <c r="D10" t="s">
-        <v>854</v>
+        <v>836</v>
       </c>
       <c r="E10" t="s">
-        <v>897</v>
+        <v>879</v>
       </c>
       <c r="F10" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="B11">
         <v>166663</v>
       </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
-        <v>855</v>
+        <v>837</v>
       </c>
       <c r="E11" t="s">
-        <v>898</v>
+        <v>880</v>
       </c>
       <c r="F11" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="G11" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="B12">
         <v>166673</v>
       </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
       <c r="D12" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
       <c r="E12" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="F12" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="G12" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="B13">
         <v>166675</v>
       </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
       <c r="D13" t="s">
-        <v>857</v>
+        <v>839</v>
       </c>
       <c r="E13" t="s">
-        <v>899</v>
+        <v>881</v>
       </c>
       <c r="F13" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="G13" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>814</v>
+        <v>796</v>
       </c>
       <c r="B14">
         <v>166710</v>
       </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
       <c r="D14" t="s">
-        <v>858</v>
+        <v>840</v>
       </c>
       <c r="E14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="F14" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G14" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>815</v>
+        <v>797</v>
       </c>
       <c r="B15">
         <v>166711</v>
       </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
       <c r="D15" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
       <c r="E15" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="F15" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="G15" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
       <c r="B16">
         <v>166755</v>
       </c>
+      <c r="C16">
+        <v>6</v>
+      </c>
       <c r="D16" t="s">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="F16" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="G16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>817</v>
+        <v>799</v>
       </c>
       <c r="B17">
         <v>166757</v>
       </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
       <c r="D17" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="E17" t="s">
-        <v>901</v>
+        <v>883</v>
       </c>
       <c r="F17" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="G17" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="B18">
         <v>167481</v>
       </c>
+      <c r="C18">
+        <v>8</v>
+      </c>
       <c r="D18" t="s">
-        <v>862</v>
+        <v>844</v>
       </c>
       <c r="E18" t="s">
-        <v>902</v>
+        <v>884</v>
       </c>
       <c r="F18" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="G18" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>819</v>
+        <v>801</v>
       </c>
       <c r="B19">
         <v>167793</v>
       </c>
+      <c r="C19">
+        <v>9</v>
+      </c>
       <c r="D19" t="s">
-        <v>863</v>
+        <v>845</v>
       </c>
       <c r="E19" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>820</v>
+        <v>802</v>
       </c>
       <c r="B20">
         <v>168287</v>
       </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
       <c r="D20" t="s">
-        <v>864</v>
+        <v>846</v>
       </c>
       <c r="E20" t="s">
-        <v>903</v>
+        <v>885</v>
       </c>
       <c r="F20" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="G20" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>821</v>
+        <v>803</v>
       </c>
       <c r="B21">
         <v>166567</v>
       </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
       <c r="D21" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
       <c r="E21" t="s">
-        <v>904</v>
+        <v>886</v>
       </c>
       <c r="F21" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
       <c r="G21" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>822</v>
+        <v>804</v>
       </c>
       <c r="B22">
         <v>166538</v>
       </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
       <c r="D22" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
       <c r="E22" t="s">
-        <v>905</v>
+        <v>887</v>
       </c>
       <c r="F22" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="G22" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="B23">
         <v>166678</v>
       </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
       <c r="D23" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
       <c r="E23" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
       <c r="F23" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="G23" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>824</v>
+        <v>806</v>
       </c>
       <c r="B24">
         <v>167682</v>
       </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
       <c r="D24" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="E24" t="s">
-        <v>362</v>
+        <v>344</v>
       </c>
       <c r="F24" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="G24" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>825</v>
+        <v>807</v>
       </c>
       <c r="B25">
         <v>166529</v>
       </c>
+      <c r="C25">
+        <v>6</v>
+      </c>
       <c r="D25" t="s">
-        <v>869</v>
+        <v>851</v>
       </c>
       <c r="E25" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="F25" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="G25" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>826</v>
+        <v>808</v>
       </c>
       <c r="B26">
         <v>166472</v>
       </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
       <c r="D26" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="E26" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
       <c r="F26" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
       <c r="G26" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="B27">
         <v>166571</v>
       </c>
+      <c r="C27">
+        <v>8</v>
+      </c>
       <c r="D27" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
       <c r="E27" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="F27" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="G27" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
       <c r="B28">
         <v>166575</v>
       </c>
+      <c r="C28">
+        <v>9</v>
+      </c>
       <c r="D28" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="E28" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="F28" t="s">
-        <v>941</v>
+        <v>923</v>
       </c>
       <c r="G28" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>829</v>
+        <v>811</v>
       </c>
       <c r="B29">
         <v>166590</v>
       </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
       <c r="D29" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="E29" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="F29" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="G29" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>830</v>
+        <v>812</v>
       </c>
       <c r="B30">
         <v>166598</v>
       </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
       <c r="D30" t="s">
-        <v>874</v>
+        <v>856</v>
       </c>
       <c r="E30" t="s">
-        <v>891</v>
+        <v>873</v>
       </c>
       <c r="F30" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
       <c r="G30" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>831</v>
+        <v>813</v>
       </c>
       <c r="B31">
         <v>166629</v>
       </c>
+      <c r="C31">
+        <v>3</v>
+      </c>
       <c r="D31" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="E31" t="s">
-        <v>896</v>
+        <v>878</v>
       </c>
       <c r="F31" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="G31" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>832</v>
+        <v>814</v>
       </c>
       <c r="B32">
         <v>166650</v>
       </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
       <c r="D32" t="s">
-        <v>876</v>
+        <v>858</v>
       </c>
       <c r="E32" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="F32" t="s">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="G32" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="B33">
         <v>166657</v>
       </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
       <c r="D33" t="s">
-        <v>877</v>
+        <v>859</v>
       </c>
       <c r="E33" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="F33" t="s">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="G33" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>834</v>
+        <v>816</v>
       </c>
       <c r="B34">
         <v>166687</v>
       </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
       <c r="D34" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="E34" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="F34" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="G34" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>835</v>
+        <v>817</v>
       </c>
       <c r="B35">
         <v>166691</v>
       </c>
+      <c r="C35">
+        <v>7</v>
+      </c>
       <c r="D35" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="E35" t="s">
-        <v>358</v>
+        <v>340</v>
       </c>
       <c r="F35" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="G35" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>836</v>
+        <v>818</v>
       </c>
       <c r="B36">
         <v>166708</v>
       </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
       <c r="D36" t="s">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="E36" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="F36" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
       <c r="G36" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
       <c r="B37">
         <v>166719</v>
       </c>
+      <c r="C37">
+        <v>9</v>
+      </c>
       <c r="D37" t="s">
-        <v>881</v>
+        <v>863</v>
       </c>
       <c r="E37" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F37" t="s">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="G37" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="B38">
         <v>166744</v>
       </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
       <c r="D38" t="s">
-        <v>882</v>
+        <v>864</v>
       </c>
       <c r="E38" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="F38" t="s">
-        <v>949</v>
+        <v>931</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="B39">
         <v>166746</v>
       </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
       <c r="D39" t="s">
-        <v>883</v>
+        <v>865</v>
       </c>
       <c r="E39" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="F39" t="s">
-        <v>950</v>
+        <v>932</v>
       </c>
       <c r="G39" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>840</v>
+        <v>822</v>
       </c>
       <c r="B40">
         <v>166753</v>
       </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
       <c r="D40" t="s">
-        <v>884</v>
+        <v>866</v>
       </c>
       <c r="E40" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="F40" t="s">
-        <v>951</v>
+        <v>933</v>
       </c>
       <c r="G40" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="B41">
         <v>166779</v>
       </c>
+      <c r="C41">
+        <v>4</v>
+      </c>
       <c r="D41" t="s">
-        <v>885</v>
+        <v>867</v>
       </c>
       <c r="E41" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="F41" t="s">
-        <v>952</v>
+        <v>934</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="B42">
         <v>166818</v>
       </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
       <c r="D42" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="E42" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>953</v>
+        <v>935</v>
       </c>
       <c r="G42" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="B43">
         <v>167482</v>
       </c>
+      <c r="C43">
+        <v>6</v>
+      </c>
       <c r="D43" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
       <c r="E43" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="F43" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="G43" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="B44">
         <v>167812</v>
       </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
       <c r="D44" t="s">
-        <v>888</v>
+        <v>870</v>
       </c>
       <c r="E44" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="F44" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
       <c r="G44" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>845</v>
+        <v>827</v>
       </c>
       <c r="B45">
         <v>171332</v>
       </c>
+      <c r="C45">
+        <v>8</v>
+      </c>
       <c r="D45" t="s">
-        <v>889</v>
+        <v>871</v>
       </c>
       <c r="E45" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="F45" t="s">
-        <v>956</v>
+        <v>938</v>
       </c>
       <c r="G45" t="s">
-        <v>979</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE25D24-F3E7-DF40-8610-DC764D9C75FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B718B10-E89A-D645-A20C-3A3398FF4786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B718B10-E89A-D645-A20C-3A3398FF4786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F2CDB-704C-354C-9E03-A9EE769BD09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1194">
   <si>
     <t>Session ID</t>
   </si>
@@ -3581,13 +3581,43 @@
   </si>
   <si>
     <t>Jagiellonian University</t>
+  </si>
+  <si>
+    <t>23/05/22 5:00</t>
+  </si>
+  <si>
+    <t>24/05/22 5:00</t>
+  </si>
+  <si>
+    <t>25/05/22 5:00</t>
+  </si>
+  <si>
+    <t>26/05/22 5:00</t>
+  </si>
+  <si>
+    <t>27/05/22 5:00</t>
+  </si>
+  <si>
+    <t>23/05/22 23:00</t>
+  </si>
+  <si>
+    <t>24/05/22 23:00</t>
+  </si>
+  <si>
+    <t>25/05/22 23:00</t>
+  </si>
+  <si>
+    <t>26/05/22 23:00</t>
+  </si>
+  <si>
+    <t>27/05/22 23:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3599,6 +3629,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3644,7 +3680,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4012,11 +4048,11 @@
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2">
-        <v>44704.208333333336</v>
-      </c>
-      <c r="D2" s="2">
-        <v>44704.958333333336</v>
+      <c r="C2" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4026,11 +4062,11 @@
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2">
-        <v>44704.208333333336</v>
-      </c>
-      <c r="D3" s="2">
-        <v>44704.958333333336</v>
+      <c r="C3" s="2" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4040,11 +4076,11 @@
       <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2">
-        <v>44705.208333333336</v>
-      </c>
-      <c r="D4" s="2">
-        <v>44705.958333333336</v>
+      <c r="C4" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>1190</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4054,11 +4090,11 @@
       <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2">
-        <v>44705.208333333336</v>
-      </c>
-      <c r="D5" s="2">
-        <v>44705.958333333336</v>
+      <c r="C5" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1190</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4068,11 +4104,11 @@
       <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2">
-        <v>44706.208333333336</v>
-      </c>
-      <c r="D6" s="2">
-        <v>44706.958333333336</v>
+      <c r="C6" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4082,11 +4118,11 @@
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="2">
-        <v>44707.208333333336</v>
-      </c>
-      <c r="D7" s="2">
-        <v>44707.958333333336</v>
+      <c r="C7" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>1192</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4096,11 +4132,11 @@
       <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="2">
-        <v>44707.208333333336</v>
-      </c>
-      <c r="D8" s="2">
-        <v>44707.958333333336</v>
+      <c r="C8" s="2" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>1192</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4110,11 +4146,11 @@
       <c r="B9" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2">
-        <v>44708.208333333336</v>
-      </c>
-      <c r="D9" s="2">
-        <v>44708.958333333336</v>
+      <c r="C9" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1193</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4124,14 +4160,15 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="2">
-        <v>44708.208333333336</v>
-      </c>
-      <c r="D10" s="2">
-        <v>44708.958333333336</v>
+      <c r="C10" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>1193</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4177,6 +4214,9 @@
       <c r="B2">
         <v>166461</v>
       </c>
+      <c r="C2">
+        <v>10</v>
+      </c>
       <c r="D2" t="s">
         <v>1019</v>
       </c>
@@ -4197,6 +4237,9 @@
       <c r="B3">
         <v>166479</v>
       </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
       <c r="D3" t="s">
         <v>1020</v>
       </c>
@@ -4217,6 +4260,9 @@
       <c r="B4">
         <v>166522</v>
       </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
       <c r="D4" t="s">
         <v>1021</v>
       </c>
@@ -4237,6 +4283,9 @@
       <c r="B5">
         <v>166488</v>
       </c>
+      <c r="C5">
+        <v>13</v>
+      </c>
       <c r="D5" t="s">
         <v>1022</v>
       </c>
@@ -4257,6 +4306,9 @@
       <c r="B6">
         <v>166495</v>
       </c>
+      <c r="C6">
+        <v>14</v>
+      </c>
       <c r="D6" t="s">
         <v>1023</v>
       </c>
@@ -4277,6 +4329,9 @@
       <c r="B7">
         <v>166520</v>
       </c>
+      <c r="C7">
+        <v>15</v>
+      </c>
       <c r="D7" t="s">
         <v>1024</v>
       </c>
@@ -4297,6 +4352,9 @@
       <c r="B8">
         <v>166528</v>
       </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
       <c r="D8" t="s">
         <v>1025</v>
       </c>
@@ -4317,6 +4375,9 @@
       <c r="B9">
         <v>166523</v>
       </c>
+      <c r="C9">
+        <v>17</v>
+      </c>
       <c r="D9" t="s">
         <v>1026</v>
       </c>
@@ -4337,6 +4398,9 @@
       <c r="B10">
         <v>166570</v>
       </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
       <c r="D10" t="s">
         <v>1027</v>
       </c>
@@ -4357,6 +4421,9 @@
       <c r="B11">
         <v>166578</v>
       </c>
+      <c r="C11">
+        <v>19</v>
+      </c>
       <c r="D11" t="s">
         <v>1028</v>
       </c>
@@ -4376,6 +4443,9 @@
       </c>
       <c r="B12">
         <v>166569</v>
+      </c>
+      <c r="C12">
+        <v>20</v>
       </c>
       <c r="D12" t="s">
         <v>1029</v>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F2CDB-704C-354C-9E03-A9EE769BD09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E86944-7FF7-7A48-B832-75DE85369EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3583,34 +3583,34 @@
     <t>Jagiellonian University</t>
   </si>
   <si>
-    <t>23/05/22 5:00</t>
-  </si>
-  <si>
-    <t>24/05/22 5:00</t>
-  </si>
-  <si>
-    <t>25/05/22 5:00</t>
-  </si>
-  <si>
-    <t>26/05/22 5:00</t>
-  </si>
-  <si>
-    <t>27/05/22 5:00</t>
-  </si>
-  <si>
-    <t>23/05/22 23:00</t>
-  </si>
-  <si>
-    <t>24/05/22 23:00</t>
-  </si>
-  <si>
-    <t>25/05/22 23:00</t>
-  </si>
-  <si>
-    <t>26/05/22 23:00</t>
-  </si>
-  <si>
-    <t>27/05/22 23:00</t>
+    <t>23/05/2022 5:00</t>
+  </si>
+  <si>
+    <t>24/05/2022 5:00</t>
+  </si>
+  <si>
+    <t>25/05/2022 5:00</t>
+  </si>
+  <si>
+    <t>26/05/2022 5:00</t>
+  </si>
+  <si>
+    <t>27/05/2022 5:00</t>
+  </si>
+  <si>
+    <t>23/05/2022 23:00</t>
+  </si>
+  <si>
+    <t>24/05/2022 23:00</t>
+  </si>
+  <si>
+    <t>25/05/2022 23:00</t>
+  </si>
+  <si>
+    <t>26/05/2022 23:00</t>
+  </si>
+  <si>
+    <t>27/05/2022 23:00</t>
   </si>
 </sst>
 </file>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E86944-7FF7-7A48-B832-75DE85369EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AD497D-7E90-DB4E-BDEB-5299BF241BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1193">
   <si>
     <t>Session ID</t>
   </si>
@@ -1015,9 +1015,6 @@
     <t>Panagiotis</t>
   </si>
   <si>
-    <t>Oscar Augusto</t>
-  </si>
-  <si>
     <t>Abhishek</t>
   </si>
   <si>
@@ -1147,9 +1144,6 @@
     <t>Assiouras</t>
   </si>
   <si>
-    <t>de Aguiar Francisco</t>
-  </si>
-  <si>
     <t>Sharma</t>
   </si>
   <si>
@@ -3611,6 +3605,9 @@
   </si>
   <si>
     <t>27/05/2022 23:00</t>
+  </si>
+  <si>
+    <t>Zunica</t>
   </si>
 </sst>
 </file>
@@ -4049,10 +4046,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4063,10 +4060,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4077,10 +4074,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4091,10 +4088,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4105,10 +4102,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4119,10 +4116,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4133,10 +4130,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4147,10 +4144,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4161,10 +4158,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
     </row>
   </sheetData>
@@ -4209,7 +4206,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4218,21 +4215,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="F2" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G2" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4241,21 +4238,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E3" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F3" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G3" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4264,21 +4261,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F4" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G4" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4287,21 +4284,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E5" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="F5" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G5" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4310,13 +4307,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="E6" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F6" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4324,7 +4321,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4333,21 +4330,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E7" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="F7" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G7" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4356,13 +4353,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E8" t="s">
         <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4370,7 +4367,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4379,21 +4376,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F9" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G9" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4402,13 +4399,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E10" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F10" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4416,7 +4413,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4425,7 +4422,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="E11" t="s">
         <v>314</v>
@@ -4439,7 +4436,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4448,21 +4445,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E12" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="F12" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G12" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4471,21 +4468,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G13" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4494,7 +4491,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="E14" t="s">
         <v>314</v>
@@ -4508,7 +4505,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4517,13 +4514,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E15" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F15" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4531,7 +4528,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4540,21 +4537,21 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F16" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G16" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4563,21 +4560,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="E17" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="F17" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G17" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4586,21 +4583,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E18" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="F18" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G18" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4609,13 +4606,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E19" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="F19" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4623,7 +4620,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4632,13 +4629,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E20" t="s">
         <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4646,7 +4643,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4655,21 +4652,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E21" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="F21" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G21" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4678,21 +4675,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E22" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="F22" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G22" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4701,21 +4698,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F23" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G23" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4724,21 +4721,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E24" t="s">
         <v>321</v>
       </c>
       <c r="F24" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="G24" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4747,7 +4744,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E25" t="s">
         <v>314</v>
@@ -4761,7 +4758,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4770,21 +4767,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E26" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="F26" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="G26" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4793,21 +4790,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G27" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4816,21 +4813,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E28" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F28" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="G28" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4839,21 +4836,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E29" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="F29" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="G29" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4862,13 +4859,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="E30" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F30" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4876,7 +4873,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4885,13 +4882,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="E31" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F31" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4899,7 +4896,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4908,13 +4905,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="E32" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F32" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4922,7 +4919,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4931,13 +4928,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E33" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="F33" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4945,7 +4942,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4954,13 +4951,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="E34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F34" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4968,7 +4965,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4977,21 +4974,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E35" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="F35" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G35" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -5000,13 +4997,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E36" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="F36" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5014,7 +5011,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5023,21 +5020,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E37" t="s">
         <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="G37" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5046,21 +5043,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E38" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F38" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G38" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5069,21 +5066,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E39" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="F39" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G39" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5092,13 +5089,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E40" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="F40" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5106,7 +5103,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5115,13 +5112,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="E41" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="F41" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5129,7 +5126,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5138,21 +5135,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E42" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="F42" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G42" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5161,21 +5158,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E43" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F43" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G43" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5184,21 +5181,21 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E44" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="F44" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G44" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5207,21 +5204,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E45" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F45" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G45" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5230,7 +5227,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E46" t="s">
         <v>314</v>
@@ -5244,7 +5241,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5253,13 +5250,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E47" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F47" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5267,7 +5264,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5276,13 +5273,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="E48" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F48" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5290,7 +5287,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5299,21 +5296,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="E49" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="F49" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G49" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5322,21 +5319,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E50" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="F50" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G50" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5345,13 +5342,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="E51" t="s">
         <v>321</v>
       </c>
       <c r="F51" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5359,7 +5356,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5368,21 +5365,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E52" t="s">
         <v>309</v>
       </c>
       <c r="F52" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G52" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5391,13 +5388,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="E53" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="F53" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5405,7 +5402,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5414,13 +5411,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="E54" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F54" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5428,7 +5425,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5437,21 +5434,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="E55" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F55" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="G55" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5460,21 +5457,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="E56" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="F56" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="G56" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5483,13 +5480,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="E57" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5497,7 +5494,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5506,16 +5503,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="E58" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F58" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G58" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -6549,10 +6546,10 @@
         <v>306</v>
       </c>
       <c r="F2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -6572,7 +6569,7 @@
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G3" t="s">
         <v>114</v>
@@ -6595,7 +6592,7 @@
         <v>307</v>
       </c>
       <c r="F4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -6618,10 +6615,10 @@
         <v>308</v>
       </c>
       <c r="F5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G5" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -6641,10 +6638,10 @@
         <v>169</v>
       </c>
       <c r="F6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -6664,10 +6661,10 @@
         <v>309</v>
       </c>
       <c r="F7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -6687,10 +6684,10 @@
         <v>310</v>
       </c>
       <c r="F8" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -6710,10 +6707,10 @@
         <v>311</v>
       </c>
       <c r="F9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -6733,7 +6730,7 @@
         <v>312</v>
       </c>
       <c r="F10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -6756,7 +6753,7 @@
         <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -6779,10 +6776,10 @@
         <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G12" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -6802,10 +6799,10 @@
         <v>313</v>
       </c>
       <c r="F13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -6848,10 +6845,10 @@
         <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G15" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -6871,7 +6868,7 @@
         <v>316</v>
       </c>
       <c r="F16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G16" t="s">
         <v>114</v>
@@ -6894,7 +6891,7 @@
         <v>317</v>
       </c>
       <c r="F17" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -6917,7 +6914,7 @@
         <v>318</v>
       </c>
       <c r="F18" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -6940,10 +6937,10 @@
         <v>319</v>
       </c>
       <c r="F19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -6963,7 +6960,7 @@
         <v>320</v>
       </c>
       <c r="F20" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G20" t="s">
         <v>114</v>
@@ -7009,7 +7006,7 @@
         <v>321</v>
       </c>
       <c r="F22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -7032,10 +7029,10 @@
         <v>322</v>
       </c>
       <c r="F23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G23" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -7055,7 +7052,7 @@
         <v>319</v>
       </c>
       <c r="F24" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G24" t="s">
         <v>118</v>
@@ -7078,10 +7075,10 @@
         <v>323</v>
       </c>
       <c r="F25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G25" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -7101,7 +7098,7 @@
         <v>324</v>
       </c>
       <c r="F26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G26" t="s">
         <v>114</v>
@@ -7124,7 +7121,7 @@
         <v>325</v>
       </c>
       <c r="F27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -7147,10 +7144,10 @@
         <v>326</v>
       </c>
       <c r="F28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G28" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -7170,10 +7167,10 @@
         <v>327</v>
       </c>
       <c r="F29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G29" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -7190,13 +7187,13 @@
         <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>328</v>
+        <v>890</v>
       </c>
       <c r="F30" t="s">
-        <v>372</v>
+        <v>1192</v>
       </c>
       <c r="G30" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -7213,10 +7210,10 @@
         <v>287</v>
       </c>
       <c r="E31" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F31" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
         <v>114</v>
@@ -7236,10 +7233,10 @@
         <v>288</v>
       </c>
       <c r="E32" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F32" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -7259,13 +7256,13 @@
         <v>289</v>
       </c>
       <c r="E33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F33" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G33" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
@@ -7282,13 +7279,13 @@
         <v>290</v>
       </c>
       <c r="E34" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F34" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G34" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -7305,13 +7302,13 @@
         <v>291</v>
       </c>
       <c r="E35" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G35" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -7328,10 +7325,10 @@
         <v>292</v>
       </c>
       <c r="E36" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F36" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G36" t="s">
         <v>208</v>
@@ -7374,10 +7371,10 @@
         <v>294</v>
       </c>
       <c r="E38" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F38" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G38" t="s">
         <v>118</v>
@@ -7400,7 +7397,7 @@
         <v>82</v>
       </c>
       <c r="F39" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G39" t="s">
         <v>118</v>
@@ -7420,10 +7417,10 @@
         <v>296</v>
       </c>
       <c r="E40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F40" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -7443,13 +7440,13 @@
         <v>297</v>
       </c>
       <c r="E41" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F41" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G41" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -7466,13 +7463,13 @@
         <v>298</v>
       </c>
       <c r="E42" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F42" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G42" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -7489,13 +7486,13 @@
         <v>299</v>
       </c>
       <c r="E43" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F43" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G43" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -7512,13 +7509,13 @@
         <v>300</v>
       </c>
       <c r="E44" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F44" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G44" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -7535,13 +7532,13 @@
         <v>301</v>
       </c>
       <c r="E45" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F45" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G45" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -7558,13 +7555,13 @@
         <v>302</v>
       </c>
       <c r="E46" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F46" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G46" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -7581,13 +7578,13 @@
         <v>303</v>
       </c>
       <c r="E47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F47" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G47" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -7604,10 +7601,10 @@
         <v>304</v>
       </c>
       <c r="E48" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F48" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -7627,10 +7624,10 @@
         <v>305</v>
       </c>
       <c r="E49" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F49" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G49" t="s">
         <v>118</v>
@@ -7677,7 +7674,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B2">
         <v>166631</v>
@@ -7686,13 +7683,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B3">
         <v>166646</v>
@@ -7709,13 +7706,13 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G3" t="s">
         <v>118</v>
@@ -7723,7 +7720,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B4">
         <v>166660</v>
@@ -7732,21 +7729,21 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F4" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B5">
         <v>166661</v>
@@ -7755,21 +7752,21 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E5" t="s">
         <v>306</v>
       </c>
       <c r="F5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B6">
         <v>166699</v>
@@ -7778,21 +7775,21 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B7">
         <v>166701</v>
@@ -7801,21 +7798,21 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E7" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B8">
         <v>166784</v>
@@ -7824,7 +7821,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E8" t="s">
         <v>314</v>
@@ -7838,7 +7835,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B9">
         <v>166747</v>
@@ -7847,13 +7844,13 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F9" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -7861,7 +7858,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B10">
         <v>166487</v>
@@ -7870,21 +7867,21 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E10" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F10" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G10" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B11">
         <v>166560</v>
@@ -7893,21 +7890,21 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E11" t="s">
         <v>166</v>
       </c>
       <c r="F11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B12">
         <v>166597</v>
@@ -7916,13 +7913,13 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -7930,7 +7927,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B13">
         <v>166604</v>
@@ -7939,13 +7936,13 @@
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G13" t="s">
         <v>114</v>
@@ -7953,7 +7950,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B14">
         <v>166607</v>
@@ -7962,13 +7959,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F14" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -7976,7 +7973,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B15">
         <v>166612</v>
@@ -7985,13 +7982,13 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
         <v>164</v>
       </c>
       <c r="F15" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -7999,7 +7996,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B16">
         <v>166627</v>
@@ -8008,13 +8005,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E16" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F16" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
@@ -8022,7 +8019,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B17">
         <v>166729</v>
@@ -8031,13 +8028,13 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E17" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8045,7 +8042,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B18">
         <v>166750</v>
@@ -8054,7 +8051,7 @@
         <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E18" t="s">
         <v>314</v>
@@ -8068,7 +8065,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B19">
         <v>166796</v>
@@ -8077,13 +8074,13 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E19" t="s">
         <v>312</v>
       </c>
       <c r="F19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -8091,7 +8088,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B20">
         <v>167817</v>
@@ -8100,21 +8097,21 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E20" t="s">
         <v>315</v>
       </c>
       <c r="F20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B21">
         <v>171014</v>
@@ -8123,16 +8120,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E21" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="G21" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -8176,7 +8173,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -8185,21 +8182,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E2" t="s">
         <v>164</v>
       </c>
       <c r="F2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -8208,21 +8205,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E3" t="s">
         <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="G3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -8231,13 +8228,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E4" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8245,7 +8242,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8254,21 +8251,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B6">
         <v>166645</v>
@@ -8277,21 +8274,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B7">
         <v>166643</v>
@@ -8300,21 +8297,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E7" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G7" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B8">
         <v>166685</v>
@@ -8323,21 +8320,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E8" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F8" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G8" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B9">
         <v>166810</v>
@@ -8346,21 +8343,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E9" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F9" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G9" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B10">
         <v>166740</v>
@@ -8369,7 +8366,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E10" t="s">
         <v>177</v>
@@ -8378,12 +8375,12 @@
         <v>195</v>
       </c>
       <c r="G10" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B11">
         <v>166754</v>
@@ -8392,13 +8389,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E11" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F11" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8406,7 +8403,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B12">
         <v>166775</v>
@@ -8415,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E12" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -8429,7 +8426,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B13">
         <v>166475</v>
@@ -8438,21 +8435,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E13" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F13" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G13" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B14">
         <v>166511</v>
@@ -8461,21 +8458,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F14" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G14" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B15">
         <v>166518</v>
@@ -8484,13 +8481,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E15" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F15" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -8498,7 +8495,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B16">
         <v>166524</v>
@@ -8507,21 +8504,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E16" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G16" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B17">
         <v>166525</v>
@@ -8530,13 +8527,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E17" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F17" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8544,7 +8541,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B18">
         <v>166563</v>
@@ -8553,13 +8550,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F18" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -8567,7 +8564,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B19">
         <v>166608</v>
@@ -8576,21 +8573,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E19" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F19" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="G19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B20">
         <v>166659</v>
@@ -8599,21 +8596,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E20" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F20" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G20" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B21">
         <v>166664</v>
@@ -8622,13 +8619,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E21" t="s">
         <v>315</v>
       </c>
       <c r="F21" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -8636,7 +8633,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B22">
         <v>166727</v>
@@ -8645,21 +8642,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E22" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F22" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="G22" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B23">
         <v>166738</v>
@@ -8668,13 +8665,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E23" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F23" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -8721,7 +8718,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8730,13 +8727,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E2" t="s">
         <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8744,7 +8741,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8753,21 +8750,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8776,13 +8773,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F4" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8790,7 +8787,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8799,21 +8796,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E5" t="s">
         <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8822,21 +8819,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F6" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B7">
         <v>166794</v>
@@ -8845,21 +8842,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F7" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G7" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B8">
         <v>167882</v>
@@ -8868,13 +8865,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E8" t="s">
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -8882,7 +8879,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B9">
         <v>166696</v>
@@ -8891,21 +8888,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E9" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F9" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B10">
         <v>166700</v>
@@ -8914,21 +8911,21 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F10" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B11">
         <v>166792</v>
@@ -8937,13 +8934,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E11" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F11" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8990,7 +8987,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8999,13 +8996,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9013,7 +9010,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9022,21 +9019,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F3" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9045,13 +9042,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E4" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9059,7 +9056,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9068,21 +9065,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E5" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F5" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G5" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9091,13 +9088,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E6" t="s">
         <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9105,7 +9102,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9114,13 +9111,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E7" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F7" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9128,7 +9125,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9137,13 +9134,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E8" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F8" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9151,7 +9148,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9160,21 +9157,21 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E9" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F9" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G9" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9183,13 +9180,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E10" t="s">
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9197,7 +9194,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9206,13 +9203,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E11" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F11" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9220,7 +9217,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9229,21 +9226,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E12" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F12" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G12" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9252,13 +9249,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9266,7 +9263,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9275,13 +9272,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E14" t="s">
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9289,7 +9286,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9298,13 +9295,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E15" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="F15" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9312,7 +9309,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9321,21 +9318,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E16" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F16" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G16" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9344,13 +9341,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E17" t="s">
         <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9358,7 +9355,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9367,13 +9364,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E18" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="F18" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9381,7 +9378,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9390,13 +9387,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E19" t="s">
         <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9404,7 +9401,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9413,13 +9410,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E20" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F20" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9427,7 +9424,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9436,13 +9433,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E21" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F21" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9450,7 +9447,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9459,13 +9456,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9473,7 +9470,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9482,13 +9479,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9496,7 +9493,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9505,21 +9502,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E24" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G24" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9528,21 +9525,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E25" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F25" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G25" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9551,21 +9548,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E26" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="F26" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G26" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9574,13 +9571,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E27" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9588,7 +9585,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9597,21 +9594,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E28" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F28" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G28" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9620,13 +9617,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="E29" t="s">
         <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9634,7 +9631,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9643,21 +9640,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E30" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F30" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G30" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9666,13 +9663,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E31" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F31" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9680,7 +9677,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9689,21 +9686,21 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E32" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F32" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G32" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9712,13 +9709,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E33" t="s">
         <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9726,7 +9723,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9735,13 +9732,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9749,7 +9746,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9758,21 +9755,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E35" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F35" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G35" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9781,13 +9778,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E36" t="s">
         <v>321</v>
       </c>
       <c r="F36" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9795,7 +9792,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9804,13 +9801,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E37" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F37" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9818,7 +9815,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9827,21 +9824,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E38" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F38" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G38" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9850,21 +9847,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E39" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F39" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G39" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9873,13 +9870,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9887,7 +9884,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9896,7 +9893,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E41" t="s">
         <v>166</v>
@@ -9905,12 +9902,12 @@
         <v>184</v>
       </c>
       <c r="G41" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9919,16 +9916,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E42" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="F42" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G42" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -9972,7 +9969,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9981,13 +9978,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F2" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9995,7 +9992,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10004,21 +10001,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G3" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10027,13 +10024,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10041,7 +10038,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10050,21 +10047,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E5" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="F5" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G5" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10073,21 +10070,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E6" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="F6" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G6" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10096,21 +10093,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E7" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="F7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G7" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10119,21 +10116,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E8" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F8" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G8" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10142,13 +10139,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E9" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F9" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10156,7 +10153,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10165,13 +10162,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E10" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="F10" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10179,7 +10176,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B11">
         <v>166663</v>
@@ -10188,21 +10185,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="F11" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G11" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B12">
         <v>166673</v>
@@ -10211,21 +10208,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="F12" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G12" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B13">
         <v>166675</v>
@@ -10234,21 +10231,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E13" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="F13" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G13" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B14">
         <v>166710</v>
@@ -10257,7 +10254,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E14" t="s">
         <v>314</v>
@@ -10271,7 +10268,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B15">
         <v>166711</v>
@@ -10280,21 +10277,21 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E15" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="F15" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="G15" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B16">
         <v>166755</v>
@@ -10303,13 +10300,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E16" t="s">
         <v>174</v>
       </c>
       <c r="F16" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
@@ -10317,7 +10314,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B17">
         <v>166757</v>
@@ -10326,21 +10323,21 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E17" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="F17" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G17" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B18">
         <v>167481</v>
@@ -10349,13 +10346,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E18" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="F18" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -10363,7 +10360,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B19">
         <v>167793</v>
@@ -10372,13 +10369,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -10386,7 +10383,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B20">
         <v>168287</v>
@@ -10395,21 +10392,21 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E20" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="F20" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G20" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B21">
         <v>166567</v>
@@ -10418,21 +10415,21 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E21" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="F21" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="G21" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B22">
         <v>166538</v>
@@ -10441,21 +10438,21 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E22" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="F22" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G22" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B23">
         <v>166678</v>
@@ -10464,21 +10461,21 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E23" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F23" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G23" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B24">
         <v>167682</v>
@@ -10487,21 +10484,21 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E24" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F24" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G24" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="B25">
         <v>166529</v>
@@ -10510,21 +10507,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E25" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="F25" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G25" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B26">
         <v>166472</v>
@@ -10533,21 +10530,21 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E26" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F26" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G26" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B27">
         <v>166571</v>
@@ -10556,21 +10553,21 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E27" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="F27" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="G27" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B28">
         <v>166575</v>
@@ -10579,13 +10576,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E28" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F28" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G28" t="s">
         <v>118</v>
@@ -10593,7 +10590,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B29">
         <v>166590</v>
@@ -10602,21 +10599,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E29" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="F29" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="G29" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B30">
         <v>166598</v>
@@ -10625,21 +10622,21 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E30" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F30" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="G30" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B31">
         <v>166629</v>
@@ -10648,13 +10645,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E31" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="F31" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -10662,7 +10659,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B32">
         <v>166650</v>
@@ -10671,21 +10668,21 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E32" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F32" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G32" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B33">
         <v>166657</v>
@@ -10694,13 +10691,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E33" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="F33" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="G33" t="s">
         <v>114</v>
@@ -10708,7 +10705,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B34">
         <v>166687</v>
@@ -10717,21 +10714,21 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E34" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="F34" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="G34" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B35">
         <v>166691</v>
@@ -10740,21 +10737,21 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F35" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G35" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B36">
         <v>166708</v>
@@ -10763,13 +10760,13 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E36" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="F36" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -10777,7 +10774,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B37">
         <v>166719</v>
@@ -10786,21 +10783,21 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E37" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="F37" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="G37" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B38">
         <v>166744</v>
@@ -10809,13 +10806,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E38" t="s">
         <v>325</v>
       </c>
       <c r="F38" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="G38" t="s">
         <v>118</v>
@@ -10823,7 +10820,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B39">
         <v>166746</v>
@@ -10832,21 +10829,21 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E39" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="F39" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G39" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B40">
         <v>166753</v>
@@ -10855,21 +10852,21 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E40" t="s">
         <v>315</v>
       </c>
       <c r="F40" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G40" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B41">
         <v>166779</v>
@@ -10878,13 +10875,13 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E41" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="F41" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -10892,7 +10889,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B42">
         <v>166818</v>
@@ -10901,21 +10898,21 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E42" t="s">
         <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="G42" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B43">
         <v>167482</v>
@@ -10924,13 +10921,13 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E43" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="F43" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10938,7 +10935,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B44">
         <v>167812</v>
@@ -10947,13 +10944,13 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F44" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="G44" t="s">
         <v>118</v>
@@ -10961,7 +10958,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B45">
         <v>171332</v>
@@ -10970,16 +10967,16 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E45" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="F45" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="G45" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AD497D-7E90-DB4E-BDEB-5299BF241BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F6E511-5B5B-8343-A033-BC0F7989285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6497,7 +6497,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7221,160 +7221,160 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B32">
-        <v>166725</v>
+        <v>166464</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E32" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>404</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B33">
-        <v>166464</v>
+        <v>166555</v>
       </c>
       <c r="C33">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F33" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G33" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B34">
-        <v>166555</v>
+        <v>166562</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E34" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F34" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G34" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B35">
-        <v>166562</v>
+        <v>166586</v>
       </c>
       <c r="C35">
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E35" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F35" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G35" t="s">
-        <v>406</v>
+        <v>208</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B36">
-        <v>166586</v>
+        <v>166613</v>
       </c>
       <c r="C36">
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E36" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="F36" t="s">
-        <v>376</v>
+        <v>314</v>
       </c>
       <c r="G36" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B37">
-        <v>166613</v>
+        <v>166617</v>
       </c>
       <c r="C37">
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="F37" t="s">
-        <v>314</v>
+        <v>377</v>
       </c>
       <c r="G37" t="s">
-        <v>314</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B38">
-        <v>166617</v>
+        <v>166634</v>
       </c>
       <c r="C38">
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E38" t="s">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="F38" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G38" t="s">
         <v>118</v>
@@ -7382,22 +7382,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B39">
-        <v>166634</v>
+        <v>166639</v>
       </c>
       <c r="C39">
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E39" t="s">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="F39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G39" t="s">
         <v>118</v>
@@ -7405,231 +7405,208 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B40">
-        <v>166639</v>
+        <v>166647</v>
       </c>
       <c r="C40">
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E40" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F40" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G40" t="s">
-        <v>118</v>
+        <v>407</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B41">
-        <v>166647</v>
+        <v>166670</v>
       </c>
       <c r="C41">
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E41" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F41" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G41" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B42">
-        <v>166670</v>
+        <v>166686</v>
       </c>
       <c r="C42">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E42" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F42" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G42" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B43">
-        <v>166686</v>
+        <v>166689</v>
       </c>
       <c r="C43">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E43" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F43" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G43" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B44">
-        <v>166689</v>
+        <v>166690</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E44" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F44" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G44" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B45">
-        <v>166690</v>
+        <v>166695</v>
       </c>
       <c r="C45">
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E45" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F45" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G45" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B46">
-        <v>166695</v>
+        <v>166726</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E46" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F46" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G46" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B47">
-        <v>166726</v>
+        <v>166812</v>
       </c>
       <c r="C47">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E47" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F47" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G47" t="s">
-        <v>412</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B48">
-        <v>166812</v>
+        <v>167673</v>
       </c>
       <c r="C48">
         <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E48" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F48" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>257</v>
-      </c>
-      <c r="B49">
-        <v>167673</v>
-      </c>
-      <c r="C49">
-        <v>6</v>
-      </c>
-      <c r="D49" t="s">
-        <v>305</v>
-      </c>
-      <c r="E49" t="s">
-        <v>344</v>
-      </c>
-      <c r="F49" t="s">
-        <v>388</v>
-      </c>
-      <c r="G49" t="s">
         <v>118</v>
       </c>
     </row>
@@ -8953,7 +8930,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -9926,6 +9903,29 @@
       </c>
       <c r="G42" t="s">
         <v>781</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>240</v>
+      </c>
+      <c r="B43">
+        <v>166725</v>
+      </c>
+      <c r="C43">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>288</v>
+      </c>
+      <c r="E43" t="s">
+        <v>329</v>
+      </c>
+      <c r="F43" t="s">
+        <v>372</v>
+      </c>
+      <c r="G43" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F6E511-5B5B-8343-A033-BC0F7989285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D78DB9-BC47-4B40-9AFD-F06C462A442E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1197">
   <si>
     <t>Session ID</t>
   </si>
@@ -3608,6 +3608,18 @@
   </si>
   <si>
     <t>Zunica</t>
+  </si>
+  <si>
+    <t>ORIGIN, an EU project targeting real-time 3D dose imaging and source localization in brachytherapy: commissioning and first results of a 16-sensor prototype.</t>
+  </si>
+  <si>
+    <t>Agnese</t>
+  </si>
+  <si>
+    <t>Giaz</t>
+  </si>
+  <si>
+    <t>Università degli studi dell'Insubria</t>
   </si>
 </sst>
 </file>
@@ -7617,7 +7629,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -8107,6 +8119,29 @@
       </c>
       <c r="G21" t="s">
         <v>490</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>400</v>
+      </c>
+      <c r="B22">
+        <v>171701</v>
+      </c>
+      <c r="C22">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1196</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7D78DB9-BC47-4B40-9AFD-F06C462A442E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C38D547-E91A-7544-9F56-D1804DB5D30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1501,9 +1501,6 @@
     <t>Paul Scherrer Institut - ETH Zürich</t>
   </si>
   <si>
-    <t>TTA Techtra</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -3620,6 +3617,9 @@
   </si>
   <si>
     <t>Università degli studi dell'Insubria</t>
+  </si>
+  <si>
+    <t>Wroclaw University of Science and Technology</t>
   </si>
 </sst>
 </file>
@@ -4058,10 +4058,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,10 +4072,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4086,10 +4086,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4100,10 +4100,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4114,10 +4114,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4128,10 +4128,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4142,10 +4142,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4156,10 +4156,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4170,10 +4170,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
   </sheetData>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4227,21 +4227,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4250,21 +4250,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4273,21 +4273,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F4" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G4" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4296,21 +4296,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G5" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4319,13 +4319,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F6" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4342,21 +4342,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F7" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G7" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4365,13 +4365,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E8" t="s">
         <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4388,21 +4388,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E9" t="s">
         <v>344</v>
       </c>
       <c r="F9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4411,13 +4411,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E10" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F10" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4425,7 +4425,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4434,7 +4434,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E11" t="s">
         <v>314</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4457,21 +4457,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E12" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F12" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G12" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4480,21 +4480,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G13" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E14" t="s">
         <v>314</v>
@@ -4517,7 +4517,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4526,13 +4526,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E15" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F15" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4540,7 +4540,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4549,21 +4549,21 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E16" t="s">
         <v>343</v>
       </c>
       <c r="F16" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G16" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4572,21 +4572,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E17" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F17" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G17" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4595,21 +4595,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E18" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F18" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G18" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4618,13 +4618,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E19" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F19" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4632,7 +4632,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4641,13 +4641,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E20" t="s">
         <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4664,21 +4664,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E21" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F21" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G21" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4687,21 +4687,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E22" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F22" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G22" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4710,21 +4710,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E23" t="s">
         <v>329</v>
       </c>
       <c r="F23" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G23" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4733,21 +4733,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E24" t="s">
         <v>321</v>
       </c>
       <c r="F24" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G24" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4756,7 +4756,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E25" t="s">
         <v>314</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4779,21 +4779,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E26" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F26" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G26" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4802,21 +4802,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G27" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4825,21 +4825,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E28" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F28" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G28" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4848,21 +4848,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E29" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F29" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G29" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4871,13 +4871,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E30" t="s">
         <v>329</v>
       </c>
       <c r="F30" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4894,13 +4894,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E31" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F31" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4908,7 +4908,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4917,13 +4917,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E32" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F32" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4931,7 +4931,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4940,13 +4940,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E33" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F33" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4954,7 +4954,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4963,13 +4963,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E34" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4986,21 +4986,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E35" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F35" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G35" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -5009,13 +5009,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E36" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F36" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5032,21 +5032,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E37" t="s">
         <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G37" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5055,21 +5055,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E38" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F38" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G38" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5078,21 +5078,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E39" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F39" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G39" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5101,13 +5101,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E40" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F40" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5124,13 +5124,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E41" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F41" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5147,21 +5147,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E42" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F42" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G42" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5170,21 +5170,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E43" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F43" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G43" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5193,13 +5193,13 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E44" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F44" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G44" t="s">
         <v>484</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5216,21 +5216,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E45" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F45" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G45" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5239,7 +5239,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E46" t="s">
         <v>314</v>
@@ -5253,7 +5253,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5262,13 +5262,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E47" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F47" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5285,13 +5285,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E48" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F48" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5299,7 +5299,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5308,21 +5308,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E49" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F49" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G49" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5331,21 +5331,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E50" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F50" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G50" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5354,13 +5354,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="E51" t="s">
         <v>321</v>
       </c>
       <c r="F51" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5368,7 +5368,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5377,21 +5377,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E52" t="s">
         <v>309</v>
       </c>
       <c r="F52" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G52" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5400,13 +5400,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E53" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F53" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5423,13 +5423,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E54" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F54" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5446,21 +5446,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E55" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F55" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G55" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5469,21 +5469,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="E56" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F56" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G56" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5492,13 +5492,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E57" t="s">
         <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5506,7 +5506,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5515,16 +5515,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E58" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F58" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G58" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
   </sheetData>
@@ -7199,10 +7199,10 @@
         <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F30" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G30" t="s">
         <v>403</v>
@@ -8118,7 +8118,7 @@
         <v>482</v>
       </c>
       <c r="G21" t="s">
-        <v>490</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8132,16 +8132,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E22" t="s">
         <v>1193</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1194</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>1195</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1196</v>
       </c>
     </row>
   </sheetData>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -8194,21 +8194,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E2" t="s">
         <v>164</v>
       </c>
       <c r="F2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -8217,21 +8217,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E3" t="s">
         <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -8240,13 +8240,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8254,7 +8254,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8263,21 +8263,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F5" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G5" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B6">
         <v>166645</v>
@@ -8286,21 +8286,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B7">
         <v>166643</v>
@@ -8309,21 +8309,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E7" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F7" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B8">
         <v>166685</v>
@@ -8332,21 +8332,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E8" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F8" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G8" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9">
         <v>166810</v>
@@ -8355,21 +8355,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10">
         <v>166740</v>
@@ -8378,7 +8378,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E10" t="s">
         <v>177</v>
@@ -8387,12 +8387,12 @@
         <v>195</v>
       </c>
       <c r="G10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B11">
         <v>166754</v>
@@ -8401,13 +8401,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E11" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F11" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8415,7 +8415,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B12">
         <v>166775</v>
@@ -8424,13 +8424,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B13">
         <v>166475</v>
@@ -8447,21 +8447,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F13" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G13" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B14">
         <v>166511</v>
@@ -8470,21 +8470,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G14" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B15">
         <v>166518</v>
@@ -8493,13 +8493,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E15" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F15" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -8507,7 +8507,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B16">
         <v>166524</v>
@@ -8516,21 +8516,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E16" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F16" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G16" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B17">
         <v>166525</v>
@@ -8539,13 +8539,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E17" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F17" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8553,7 +8553,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B18">
         <v>166563</v>
@@ -8562,13 +8562,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E18" t="s">
         <v>455</v>
       </c>
       <c r="F18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -8576,7 +8576,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B19">
         <v>166608</v>
@@ -8585,21 +8585,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E19" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F19" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G19" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B20">
         <v>166659</v>
@@ -8608,21 +8608,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E20" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F20" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G20" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B21">
         <v>166664</v>
@@ -8631,13 +8631,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E21" t="s">
         <v>315</v>
       </c>
       <c r="F21" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B22">
         <v>166727</v>
@@ -8654,21 +8654,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E22" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="F22" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B23">
         <v>166738</v>
@@ -8677,13 +8677,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="F23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -8730,7 +8730,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8739,13 +8739,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E2" t="s">
         <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8753,7 +8753,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8762,21 +8762,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8785,13 +8785,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8808,21 +8808,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E5" t="s">
         <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G5" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8831,21 +8831,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G6" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B7">
         <v>166794</v>
@@ -8854,21 +8854,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F7" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B8">
         <v>167882</v>
@@ -8877,13 +8877,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E8" t="s">
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -8891,7 +8891,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B9">
         <v>166696</v>
@@ -8900,21 +8900,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B10">
         <v>166700</v>
@@ -8923,21 +8923,21 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B11">
         <v>166792</v>
@@ -8946,13 +8946,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8999,7 +8999,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -9008,13 +9008,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9022,7 +9022,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9031,21 +9031,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9054,13 +9054,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9077,21 +9077,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F5" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9100,13 +9100,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E6" t="s">
         <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9114,7 +9114,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9123,13 +9123,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E7" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F7" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9137,7 +9137,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9146,13 +9146,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F8" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9160,7 +9160,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9169,13 +9169,13 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G9" t="s">
         <v>486</v>
@@ -9183,7 +9183,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9192,13 +9192,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E10" t="s">
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9206,7 +9206,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9215,13 +9215,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F11" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9229,7 +9229,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9238,21 +9238,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9261,13 +9261,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E13" t="s">
         <v>461</v>
       </c>
       <c r="F13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9275,7 +9275,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9284,13 +9284,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E14" t="s">
         <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9307,13 +9307,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E15" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F15" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9321,7 +9321,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9330,21 +9330,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E16" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F16" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G16" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9353,13 +9353,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E17" t="s">
         <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9367,7 +9367,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9376,13 +9376,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E18" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9399,13 +9399,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E19" t="s">
         <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9413,7 +9413,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9422,13 +9422,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E20" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F20" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9436,7 +9436,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9445,13 +9445,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E21" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F21" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9459,7 +9459,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9468,13 +9468,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9482,7 +9482,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9491,13 +9491,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9505,7 +9505,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9514,21 +9514,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E24" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F24" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G24" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9537,21 +9537,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E25" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F25" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G25" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9560,21 +9560,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E26" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F26" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G26" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9583,13 +9583,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E27" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F27" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9597,7 +9597,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9606,21 +9606,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E28" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F28" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G28" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9629,13 +9629,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E29" t="s">
         <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9643,7 +9643,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9652,21 +9652,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E30" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F30" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G30" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9675,13 +9675,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E31" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F31" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9689,7 +9689,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9698,13 +9698,13 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E32" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F32" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G32" t="s">
         <v>406</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9721,13 +9721,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E33" t="s">
         <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9735,7 +9735,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9744,13 +9744,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9767,21 +9767,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E35" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F35" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G35" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9790,13 +9790,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E36" t="s">
         <v>321</v>
       </c>
       <c r="F36" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9804,7 +9804,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9813,13 +9813,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E37" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F37" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9827,7 +9827,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9836,21 +9836,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E38" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F38" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G38" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9859,21 +9859,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E39" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F39" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G39" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9882,13 +9882,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9896,7 +9896,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9905,7 +9905,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E41" t="s">
         <v>166</v>
@@ -9914,12 +9914,12 @@
         <v>184</v>
       </c>
       <c r="G41" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9928,16 +9928,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E42" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="F42" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G42" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -10004,7 +10004,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -10013,13 +10013,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -10027,7 +10027,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10036,21 +10036,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10059,13 +10059,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10073,7 +10073,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10082,21 +10082,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10105,21 +10105,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E6" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F6" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G6" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10128,21 +10128,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E7" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F7" t="s">
         <v>371</v>
       </c>
       <c r="G7" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10151,21 +10151,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E8" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F8" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G8" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10174,13 +10174,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10197,13 +10197,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E10" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F10" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10211,7 +10211,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B11">
         <v>166663</v>
@@ -10220,21 +10220,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F11" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G11" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B12">
         <v>166673</v>
@@ -10243,21 +10243,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F12" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G12" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B13">
         <v>166675</v>
@@ -10266,21 +10266,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E13" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F13" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G13" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B14">
         <v>166710</v>
@@ -10289,7 +10289,7 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E14" t="s">
         <v>314</v>
@@ -10303,7 +10303,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B15">
         <v>166711</v>
@@ -10312,21 +10312,21 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E15" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F15" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G15" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B16">
         <v>166755</v>
@@ -10335,13 +10335,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E16" t="s">
         <v>174</v>
       </c>
       <c r="F16" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
@@ -10349,7 +10349,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B17">
         <v>166757</v>
@@ -10358,21 +10358,21 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E17" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F17" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G17" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B18">
         <v>167481</v>
@@ -10381,13 +10381,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E18" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F18" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -10395,7 +10395,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B19">
         <v>167793</v>
@@ -10404,13 +10404,13 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E19" t="s">
         <v>164</v>
       </c>
       <c r="F19" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B20">
         <v>168287</v>
@@ -10427,21 +10427,21 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E20" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G20" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B21">
         <v>166567</v>
@@ -10450,21 +10450,21 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E21" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F21" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G21" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B22">
         <v>166538</v>
@@ -10473,21 +10473,21 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E22" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F22" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G22" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B23">
         <v>166678</v>
@@ -10496,21 +10496,21 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E23" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G23" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B24">
         <v>167682</v>
@@ -10519,21 +10519,21 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E24" t="s">
         <v>343</v>
       </c>
       <c r="F24" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B25">
         <v>166529</v>
@@ -10542,21 +10542,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E25" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F25" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G25" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B26">
         <v>166472</v>
@@ -10565,21 +10565,21 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E26" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F26" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G26" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B27">
         <v>166571</v>
@@ -10588,21 +10588,21 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E27" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F27" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G27" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B28">
         <v>166575</v>
@@ -10611,13 +10611,13 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E28" t="s">
         <v>461</v>
       </c>
       <c r="F28" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G28" t="s">
         <v>118</v>
@@ -10625,7 +10625,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B29">
         <v>166590</v>
@@ -10634,21 +10634,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E29" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F29" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G29" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B30">
         <v>166598</v>
@@ -10657,21 +10657,21 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E30" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F30" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G30" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B31">
         <v>166629</v>
@@ -10680,13 +10680,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E31" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F31" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -10694,7 +10694,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B32">
         <v>166650</v>
@@ -10703,21 +10703,21 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E32" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F32" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G32" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B33">
         <v>166657</v>
@@ -10726,13 +10726,13 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E33" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F33" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G33" t="s">
         <v>114</v>
@@ -10740,7 +10740,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B34">
         <v>166687</v>
@@ -10749,21 +10749,21 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E34" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F34" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G34" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B35">
         <v>166691</v>
@@ -10772,7 +10772,7 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E35" t="s">
         <v>339</v>
@@ -10786,7 +10786,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B36">
         <v>166708</v>
@@ -10795,13 +10795,13 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E36" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F36" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -10809,7 +10809,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B37">
         <v>166719</v>
@@ -10818,21 +10818,21 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E37" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F37" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G37" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B38">
         <v>166744</v>
@@ -10841,13 +10841,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E38" t="s">
         <v>325</v>
       </c>
       <c r="F38" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G38" t="s">
         <v>118</v>
@@ -10855,7 +10855,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B39">
         <v>166746</v>
@@ -10864,21 +10864,21 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E39" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F39" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G39" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B40">
         <v>166753</v>
@@ -10887,21 +10887,21 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E40" t="s">
         <v>315</v>
       </c>
       <c r="F40" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G40" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B41">
         <v>166779</v>
@@ -10910,13 +10910,13 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E41" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F41" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -10924,7 +10924,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B42">
         <v>166818</v>
@@ -10933,21 +10933,21 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E42" t="s">
         <v>84</v>
       </c>
       <c r="F42" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G42" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B43">
         <v>167482</v>
@@ -10956,13 +10956,13 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E43" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F43" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B44">
         <v>167812</v>
@@ -10979,13 +10979,13 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E44" t="s">
         <v>329</v>
       </c>
       <c r="F44" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G44" t="s">
         <v>118</v>
@@ -10993,7 +10993,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B45">
         <v>171332</v>
@@ -11002,16 +11002,16 @@
         <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E45" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F45" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G45" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C38D547-E91A-7544-9F56-D1804DB5D30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DA1D85-328B-1346-994F-29985118C988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -3298,9 +3298,6 @@
     <t>Fabio</t>
   </si>
   <si>
-    <t>Kirika</t>
-  </si>
-  <si>
     <t>José David</t>
   </si>
   <si>
@@ -3424,9 +3421,6 @@
     <t>Gaioni</t>
   </si>
   <si>
-    <t>Uchida</t>
-  </si>
-  <si>
     <t>Carniti</t>
   </si>
   <si>
@@ -3620,6 +3614,12 @@
   </si>
   <si>
     <t>Wroclaw University of Science and Technology</t>
+  </si>
+  <si>
+    <t>Geoff</t>
+  </si>
+  <si>
+    <t>Hall</t>
   </si>
 </sst>
 </file>
@@ -4058,10 +4058,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,10 +4072,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4086,10 +4086,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4100,10 +4100,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4114,10 +4114,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4128,10 +4128,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4142,10 +4142,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4156,10 +4156,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4170,10 +4170,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
@@ -4233,10 +4233,10 @@
         <v>1073</v>
       </c>
       <c r="F2" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G2" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -4256,10 +4256,10 @@
         <v>1074</v>
       </c>
       <c r="F3" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G3" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -4279,10 +4279,10 @@
         <v>1075</v>
       </c>
       <c r="F4" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G4" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -4302,10 +4302,10 @@
         <v>1076</v>
       </c>
       <c r="F5" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G5" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -4325,7 +4325,7 @@
         <v>609</v>
       </c>
       <c r="F6" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4348,10 +4348,10 @@
         <v>881</v>
       </c>
       <c r="F7" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G7" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -4371,7 +4371,7 @@
         <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4394,10 +4394,10 @@
         <v>344</v>
       </c>
       <c r="F9" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G9" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -4417,7 +4417,7 @@
         <v>1077</v>
       </c>
       <c r="F10" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4463,10 +4463,10 @@
         <v>1078</v>
       </c>
       <c r="F12" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G12" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -4486,10 +4486,10 @@
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G13" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -4532,7 +4532,7 @@
         <v>1079</v>
       </c>
       <c r="F15" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4578,10 +4578,10 @@
         <v>1080</v>
       </c>
       <c r="F17" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G17" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -4601,10 +4601,10 @@
         <v>1081</v>
       </c>
       <c r="F18" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G18" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -4624,7 +4624,7 @@
         <v>1082</v>
       </c>
       <c r="F19" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4647,7 +4647,7 @@
         <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4670,10 +4670,10 @@
         <v>1083</v>
       </c>
       <c r="F21" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G21" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -4693,10 +4693,10 @@
         <v>1084</v>
       </c>
       <c r="F22" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G22" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -4716,10 +4716,10 @@
         <v>329</v>
       </c>
       <c r="F23" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G23" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -4739,10 +4739,10 @@
         <v>321</v>
       </c>
       <c r="F24" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G24" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -4785,10 +4785,10 @@
         <v>1085</v>
       </c>
       <c r="F26" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G26" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -4831,10 +4831,10 @@
         <v>608</v>
       </c>
       <c r="F28" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G28" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -4854,10 +4854,10 @@
         <v>1086</v>
       </c>
       <c r="F29" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G29" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -4877,7 +4877,7 @@
         <v>329</v>
       </c>
       <c r="F30" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4900,7 +4900,7 @@
         <v>721</v>
       </c>
       <c r="F31" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4923,7 +4923,7 @@
         <v>1087</v>
       </c>
       <c r="F32" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4946,7 +4946,7 @@
         <v>1088</v>
       </c>
       <c r="F33" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4969,7 +4969,7 @@
         <v>728</v>
       </c>
       <c r="F34" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4989,13 +4989,13 @@
         <v>1049</v>
       </c>
       <c r="E35" t="s">
-        <v>1089</v>
+        <v>1195</v>
       </c>
       <c r="F35" t="s">
-        <v>1131</v>
+        <v>1196</v>
       </c>
       <c r="G35" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -5015,7 +5015,7 @@
         <v>1087</v>
       </c>
       <c r="F36" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5038,10 +5038,10 @@
         <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="G37" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -5058,13 +5058,13 @@
         <v>1052</v>
       </c>
       <c r="E38" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F38" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="G38" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -5081,13 +5081,13 @@
         <v>1053</v>
       </c>
       <c r="E39" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F39" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="G39" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -5104,10 +5104,10 @@
         <v>1054</v>
       </c>
       <c r="E40" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F40" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5127,10 +5127,10 @@
         <v>1055</v>
       </c>
       <c r="E41" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="F41" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5150,13 +5150,13 @@
         <v>1056</v>
       </c>
       <c r="E42" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="F42" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="G42" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -5176,10 +5176,10 @@
         <v>721</v>
       </c>
       <c r="F43" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="G43" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -5196,10 +5196,10 @@
         <v>1058</v>
       </c>
       <c r="E44" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F44" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="G44" t="s">
         <v>484</v>
@@ -5219,10 +5219,10 @@
         <v>1059</v>
       </c>
       <c r="E45" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F45" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="G45" t="s">
         <v>954</v>
@@ -5268,7 +5268,7 @@
         <v>717</v>
       </c>
       <c r="F47" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5291,7 +5291,7 @@
         <v>715</v>
       </c>
       <c r="F48" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5311,13 +5311,13 @@
         <v>1063</v>
       </c>
       <c r="E49" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="F49" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G49" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -5334,13 +5334,13 @@
         <v>1064</v>
       </c>
       <c r="E50" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F50" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G50" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -5383,10 +5383,10 @@
         <v>309</v>
       </c>
       <c r="F52" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G52" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -5403,10 +5403,10 @@
         <v>1067</v>
       </c>
       <c r="E53" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F53" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5429,7 +5429,7 @@
         <v>893</v>
       </c>
       <c r="F54" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5449,13 +5449,13 @@
         <v>1069</v>
       </c>
       <c r="E55" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="F55" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="G55" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -5472,13 +5472,13 @@
         <v>1070</v>
       </c>
       <c r="E56" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F56" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="G56" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -5498,7 +5498,7 @@
         <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5518,13 +5518,13 @@
         <v>1072</v>
       </c>
       <c r="E58" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="F58" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G58" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -7202,7 +7202,7 @@
         <v>889</v>
       </c>
       <c r="F30" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G30" t="s">
         <v>403</v>
@@ -8118,7 +8118,7 @@
         <v>482</v>
       </c>
       <c r="G21" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8132,16 +8132,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F22" t="s">
         <v>1192</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>1193</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1194</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1195</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DA1D85-328B-1346-994F-29985118C988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553328CD-09E0-8F44-9F51-5E74BD5AAF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="1195">
   <si>
     <t>Session ID</t>
   </si>
@@ -1783,9 +1783,6 @@
     <t>CEA</t>
   </si>
   <si>
-    <t>Ludwig Maximilians University München</t>
-  </si>
-  <si>
     <t>the University of Tokyo</t>
   </si>
   <si>
@@ -2401,9 +2398,6 @@
     <t>211</t>
   </si>
   <si>
-    <t>256</t>
-  </si>
-  <si>
     <t>265</t>
   </si>
   <si>
@@ -2533,9 +2527,6 @@
     <t>Particle identification with the cluster counting technique for the IDEA drift chamber</t>
   </si>
   <si>
-    <t>Visual investigation of possible degradation in GEM foils under test</t>
-  </si>
-  <si>
     <t>Study of ageing of the Straw Tube detectors</t>
   </si>
   <si>
@@ -2662,9 +2653,6 @@
     <t>Brunella</t>
   </si>
   <si>
-    <t>Saikat</t>
-  </si>
-  <si>
     <t>ARINDAM</t>
   </si>
   <si>
@@ -2746,9 +2734,6 @@
     <t>D'Anzi</t>
   </si>
   <si>
-    <t>Biswas</t>
-  </si>
-  <si>
     <t>SEN</t>
   </si>
   <si>
@@ -2857,9 +2842,6 @@
     <t>Bose Institute</t>
   </si>
   <si>
-    <t>BOSE INSTITUTE</t>
-  </si>
-  <si>
     <t>Temple University</t>
   </si>
   <si>
@@ -3334,9 +3316,6 @@
     <t>Vitaly</t>
   </si>
   <si>
-    <t>Shivani</t>
-  </si>
-  <si>
     <t>Ritt</t>
   </si>
   <si>
@@ -3620,6 +3599,21 @@
   </si>
   <si>
     <t>Hall</t>
+  </si>
+  <si>
+    <t>Max Planck Institut für Physik</t>
+  </si>
+  <si>
+    <t>Piero</t>
+  </si>
+  <si>
+    <t>Chessa</t>
+  </si>
+  <si>
+    <t>Kapłon</t>
+  </si>
+  <si>
+    <t>Łukasz</t>
   </si>
 </sst>
 </file>
@@ -4058,10 +4052,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4072,10 +4066,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1179</v>
+        <v>1172</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4086,10 +4080,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4100,10 +4094,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4114,10 +4108,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1181</v>
+        <v>1174</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4128,10 +4122,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4142,10 +4136,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4156,10 +4150,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4170,10 +4164,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
     </row>
   </sheetData>
@@ -4218,7 +4212,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4227,21 +4221,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="E2" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="F2" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="G2" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4250,21 +4244,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="E3" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="F3" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="G3" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4273,21 +4267,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="E4" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="F4" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="G4" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4296,21 +4290,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="E5" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="F5" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
       <c r="G5" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4319,13 +4313,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="E6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F6" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4333,7 +4327,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4342,21 +4336,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="E7" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="F7" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
       <c r="G7" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4365,13 +4359,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="E8" t="s">
         <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4379,7 +4373,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4388,21 +4382,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="E9" t="s">
         <v>344</v>
       </c>
       <c r="F9" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="G9" t="s">
-        <v>1155</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4411,13 +4405,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="E10" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="F10" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4425,7 +4419,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4434,7 +4428,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="E11" t="s">
         <v>314</v>
@@ -4448,7 +4442,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4457,21 +4451,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="E12" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="F12" t="s">
-        <v>1111</v>
+        <v>1104</v>
       </c>
       <c r="G12" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4480,21 +4474,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="G13" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4503,7 +4497,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="E14" t="s">
         <v>314</v>
@@ -4517,7 +4511,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4526,13 +4520,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="E15" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="F15" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4540,7 +4534,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4549,13 +4543,13 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="E16" t="s">
         <v>343</v>
       </c>
       <c r="F16" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="G16" t="s">
         <v>573</v>
@@ -4563,7 +4557,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4572,21 +4566,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="E17" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F17" t="s">
-        <v>1114</v>
+        <v>1107</v>
       </c>
       <c r="G17" t="s">
-        <v>1158</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4595,21 +4589,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="E18" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="F18" t="s">
-        <v>1115</v>
+        <v>1108</v>
       </c>
       <c r="G18" t="s">
-        <v>1159</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4618,13 +4612,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="E19" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="F19" t="s">
-        <v>1116</v>
+        <v>1109</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4632,7 +4626,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4641,13 +4635,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="E20" t="s">
         <v>169</v>
       </c>
       <c r="F20" t="s">
-        <v>1117</v>
+        <v>1110</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4655,7 +4649,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4664,21 +4658,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
       <c r="E21" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="F21" t="s">
-        <v>1118</v>
+        <v>1111</v>
       </c>
       <c r="G21" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4687,21 +4681,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="E22" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
       <c r="F22" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="G22" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4710,21 +4704,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="E23" t="s">
         <v>329</v>
       </c>
       <c r="F23" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="G23" t="s">
-        <v>1162</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4733,21 +4727,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="E24" t="s">
         <v>321</v>
       </c>
       <c r="F24" t="s">
-        <v>1121</v>
+        <v>1114</v>
       </c>
       <c r="G24" t="s">
-        <v>1163</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4756,7 +4750,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="E25" t="s">
         <v>314</v>
@@ -4770,7 +4764,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4779,21 +4773,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
       <c r="E26" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="F26" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G26" t="s">
-        <v>1164</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4802,21 +4796,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="G27" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4825,21 +4819,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="E28" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F28" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="G28" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4848,21 +4842,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="E29" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="F29" t="s">
-        <v>1124</v>
+        <v>1117</v>
       </c>
       <c r="G29" t="s">
-        <v>1166</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4871,13 +4865,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="E30" t="s">
         <v>329</v>
       </c>
       <c r="F30" t="s">
-        <v>1125</v>
+        <v>1118</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4885,7 +4879,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4894,13 +4888,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="E31" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F31" t="s">
-        <v>1126</v>
+        <v>1119</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4908,7 +4902,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4917,13 +4911,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="E32" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="F32" t="s">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4931,7 +4925,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4940,13 +4934,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="E33" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="F33" t="s">
-        <v>1128</v>
+        <v>1121</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4954,7 +4948,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4963,13 +4957,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="E34" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F34" t="s">
-        <v>1129</v>
+        <v>1122</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4977,7 +4971,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4986,21 +4980,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="E35" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="F35" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="G35" t="s">
-        <v>1167</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -5009,13 +5003,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="E36" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="F36" t="s">
-        <v>1130</v>
+        <v>1123</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5023,7 +5017,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5032,21 +5026,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="E37" t="s">
         <v>174</v>
       </c>
       <c r="F37" t="s">
-        <v>1131</v>
+        <v>1124</v>
       </c>
       <c r="G37" t="s">
-        <v>1168</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5055,21 +5049,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="E38" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="F38" t="s">
-        <v>1132</v>
+        <v>1125</v>
       </c>
       <c r="G38" t="s">
-        <v>1169</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5078,21 +5072,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="E39" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="F39" t="s">
-        <v>1133</v>
+        <v>1126</v>
       </c>
       <c r="G39" t="s">
-        <v>1170</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5101,13 +5095,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="E40" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="F40" t="s">
-        <v>1134</v>
+        <v>1127</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5115,7 +5109,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5124,13 +5118,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="E41" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="F41" t="s">
-        <v>1135</v>
+        <v>1128</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5138,7 +5132,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5147,21 +5141,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="E42" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F42" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="G42" t="s">
-        <v>1171</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5170,21 +5164,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="E43" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F43" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="G43" t="s">
-        <v>1172</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5193,13 +5187,13 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="E44" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="F44" t="s">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="G44" t="s">
         <v>484</v>
@@ -5207,7 +5201,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5216,21 +5210,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="E45" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="F45" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G45" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5239,7 +5233,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="E46" t="s">
         <v>314</v>
@@ -5253,7 +5247,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5262,13 +5256,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="E47" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F47" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5276,7 +5270,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5285,13 +5279,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="E48" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F48" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5299,7 +5293,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5308,21 +5302,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="E49" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="F49" t="s">
-        <v>1142</v>
+        <v>1135</v>
       </c>
       <c r="G49" t="s">
-        <v>1173</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5331,21 +5325,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="E50" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="F50" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="G50" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5354,13 +5348,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="E51" t="s">
         <v>321</v>
       </c>
       <c r="F51" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5368,7 +5362,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5377,21 +5371,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="E52" t="s">
         <v>309</v>
       </c>
       <c r="F52" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="G52" t="s">
-        <v>1175</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5400,13 +5394,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="E53" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F53" t="s">
-        <v>1145</v>
+        <v>1138</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5414,7 +5408,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5423,13 +5417,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="E54" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="F54" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5437,7 +5431,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5446,21 +5440,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="E55" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="F55" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="G55" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5469,21 +5463,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="E56" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="F56" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="G56" t="s">
-        <v>1177</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5492,13 +5486,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="E57" t="s">
         <v>344</v>
       </c>
       <c r="F57" t="s">
-        <v>1149</v>
+        <v>1142</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5506,7 +5500,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5515,16 +5509,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="E58" t="s">
-        <v>1101</v>
+        <v>1194</v>
       </c>
       <c r="F58" t="s">
-        <v>1101</v>
+        <v>1193</v>
       </c>
       <c r="G58" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
     </row>
   </sheetData>
@@ -7199,10 +7193,10 @@
         <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="F30" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="G30" t="s">
         <v>403</v>
@@ -8118,7 +8112,7 @@
         <v>482</v>
       </c>
       <c r="G21" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8132,16 +8126,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
       <c r="E22" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="F22" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="G22" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
     </row>
   </sheetData>
@@ -8617,7 +8611,7 @@
         <v>568</v>
       </c>
       <c r="G20" t="s">
-        <v>584</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -8663,7 +8657,7 @@
         <v>570</v>
       </c>
       <c r="G22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -8730,7 +8724,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8739,13 +8733,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E2" t="s">
         <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8753,7 +8747,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8762,21 +8756,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8785,13 +8779,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E4" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8799,7 +8793,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8808,21 +8802,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E5" t="s">
         <v>174</v>
       </c>
       <c r="F5" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8831,21 +8825,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B7">
         <v>166794</v>
@@ -8854,21 +8848,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="G7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B8">
         <v>167882</v>
@@ -8877,13 +8871,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E8" t="s">
         <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -8891,7 +8885,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B9">
         <v>166696</v>
@@ -8900,21 +8894,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="G9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B10">
         <v>166700</v>
@@ -8923,21 +8917,21 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="G10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B11">
         <v>166792</v>
@@ -8946,13 +8940,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8999,7 +8993,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -9008,13 +9002,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9022,7 +9016,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9031,21 +9025,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E3" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9054,13 +9048,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9068,7 +9062,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9077,21 +9071,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E5" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9100,13 +9094,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E6" t="s">
         <v>174</v>
       </c>
       <c r="F6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9114,7 +9108,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9123,13 +9117,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E7" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F7" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9137,7 +9131,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9146,13 +9140,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9160,7 +9154,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9169,13 +9163,13 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G9" t="s">
         <v>486</v>
@@ -9183,7 +9177,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9192,13 +9186,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E10" t="s">
         <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9206,7 +9200,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9215,13 +9209,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F11" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9229,7 +9223,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9238,21 +9232,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E12" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F12" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G12" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9261,13 +9255,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E13" t="s">
         <v>461</v>
       </c>
       <c r="F13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9275,7 +9269,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9284,13 +9278,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>1191</v>
       </c>
       <c r="F14" t="s">
-        <v>743</v>
+        <v>1192</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9298,7 +9292,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9307,13 +9301,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E15" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F15" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9321,7 +9315,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9330,21 +9324,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E16" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F16" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G16" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9353,13 +9347,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E17" t="s">
         <v>169</v>
       </c>
       <c r="F17" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9367,7 +9361,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9376,13 +9370,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E18" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F18" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9390,7 +9384,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9399,13 +9393,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E19" t="s">
         <v>167</v>
       </c>
       <c r="F19" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9413,7 +9407,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9422,13 +9416,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E20" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F20" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9436,7 +9430,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9445,13 +9439,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E21" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F21" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9459,7 +9453,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9468,13 +9462,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9482,7 +9476,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9491,13 +9485,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E23" t="s">
         <v>164</v>
       </c>
       <c r="F23" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9505,7 +9499,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9514,21 +9508,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E24" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F24" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G24" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9537,21 +9531,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F25" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G25" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9560,21 +9554,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E26" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F26" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G26" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9583,13 +9577,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E27" t="s">
         <v>546</v>
       </c>
       <c r="F27" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9597,7 +9591,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9606,21 +9600,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E28" t="s">
         <v>548</v>
       </c>
       <c r="F28" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G28" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9629,13 +9623,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E29" t="s">
         <v>169</v>
       </c>
       <c r="F29" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9643,7 +9637,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9652,21 +9646,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="F30" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G30" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9675,13 +9669,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E31" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F31" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9689,7 +9683,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9698,13 +9692,13 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E32" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="F32" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G32" t="s">
         <v>406</v>
@@ -9712,7 +9706,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9721,13 +9715,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E33" t="s">
         <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9735,7 +9729,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9744,13 +9738,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E34" t="s">
         <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9758,7 +9752,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9767,21 +9761,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E35" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F35" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G35" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9790,13 +9784,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E36" t="s">
         <v>321</v>
       </c>
       <c r="F36" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9804,7 +9798,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9813,13 +9807,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E37" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="F37" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9827,7 +9821,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9836,21 +9830,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E38" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F38" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G38" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9859,21 +9853,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E39" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="F39" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G39" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9882,13 +9876,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9896,7 +9890,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9905,7 +9899,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E41" t="s">
         <v>166</v>
@@ -9914,12 +9908,12 @@
         <v>184</v>
       </c>
       <c r="G41" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9928,16 +9922,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E42" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="F42" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G42" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -9970,7 +9964,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -10004,7 +9998,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -10013,13 +10007,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E2" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -10027,7 +10021,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10036,21 +10030,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F3" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G3" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10059,13 +10053,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E4" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="F4" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10073,7 +10067,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10082,21 +10076,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E5" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="F5" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G5" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10105,21 +10099,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E6" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F6" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="G6" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10128,21 +10122,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E7" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F7" t="s">
         <v>371</v>
       </c>
       <c r="G7" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10151,21 +10145,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E8" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="F8" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="G8" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10174,13 +10168,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E9" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F9" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10188,7 +10182,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10197,13 +10191,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E10" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F10" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10211,758 +10205,758 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B11">
-        <v>166663</v>
+        <v>166673</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E11" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F11" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G11" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B12">
-        <v>166673</v>
+        <v>166675</v>
       </c>
       <c r="C12">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E12" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F12" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="G12" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B13">
-        <v>166675</v>
+        <v>166710</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E13" t="s">
-        <v>878</v>
+        <v>314</v>
       </c>
       <c r="F13" t="s">
-        <v>906</v>
+        <v>314</v>
       </c>
       <c r="G13" t="s">
-        <v>942</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B14">
-        <v>166710</v>
+        <v>166711</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>875</v>
       </c>
       <c r="F14" t="s">
-        <v>314</v>
+        <v>902</v>
       </c>
       <c r="G14" t="s">
-        <v>314</v>
+        <v>937</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B15">
-        <v>166711</v>
+        <v>166755</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E15" t="s">
-        <v>879</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G15" t="s">
-        <v>943</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B16">
-        <v>166755</v>
+        <v>166757</v>
       </c>
       <c r="C16">
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E16" t="s">
-        <v>174</v>
+        <v>876</v>
       </c>
       <c r="F16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B17">
-        <v>166757</v>
+        <v>167481</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E17" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="F17" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G17" t="s">
-        <v>944</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B18">
-        <v>167481</v>
+        <v>167793</v>
       </c>
       <c r="C18">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E18" t="s">
-        <v>881</v>
+        <v>164</v>
       </c>
       <c r="F18" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B19">
-        <v>167793</v>
+        <v>168287</v>
       </c>
       <c r="C19">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E19" t="s">
-        <v>164</v>
+        <v>878</v>
       </c>
       <c r="F19" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G19" t="s">
-        <v>118</v>
+        <v>939</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B20">
-        <v>168287</v>
+        <v>166567</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E20" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="F20" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G20" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B21">
-        <v>166567</v>
+        <v>166538</v>
       </c>
       <c r="C21">
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E21" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="F21" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G21" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B22">
-        <v>166538</v>
+        <v>166678</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E22" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="F22" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="G22" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B23">
-        <v>166678</v>
+        <v>167682</v>
       </c>
       <c r="C23">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E23" t="s">
-        <v>885</v>
+        <v>343</v>
       </c>
       <c r="F23" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G23" t="s">
-        <v>941</v>
+        <v>573</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B24">
-        <v>167682</v>
+        <v>166529</v>
       </c>
       <c r="C24">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E24" t="s">
-        <v>343</v>
+        <v>882</v>
       </c>
       <c r="F24" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="G24" t="s">
-        <v>573</v>
+        <v>942</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B25">
-        <v>166529</v>
+        <v>166472</v>
       </c>
       <c r="C25">
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E25" t="s">
-        <v>886</v>
+        <v>716</v>
       </c>
       <c r="F25" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G25" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B26">
-        <v>166472</v>
+        <v>166571</v>
       </c>
       <c r="C26">
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E26" t="s">
-        <v>717</v>
+        <v>883</v>
       </c>
       <c r="F26" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="G26" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B27">
-        <v>166571</v>
+        <v>166575</v>
       </c>
       <c r="C27">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E27" t="s">
-        <v>887</v>
+        <v>461</v>
       </c>
       <c r="F27" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G27" t="s">
-        <v>950</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B28">
-        <v>166575</v>
+        <v>166590</v>
       </c>
       <c r="C28">
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E28" t="s">
-        <v>461</v>
+        <v>884</v>
       </c>
       <c r="F28" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="G28" t="s">
-        <v>118</v>
+        <v>945</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B29">
-        <v>166590</v>
+        <v>166598</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E29" t="s">
-        <v>888</v>
+        <v>867</v>
       </c>
       <c r="F29" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G29" t="s">
-        <v>951</v>
+        <v>939</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B30">
-        <v>166598</v>
+        <v>166629</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E30" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="F30" t="s">
-        <v>922</v>
+        <v>899</v>
       </c>
       <c r="G30" t="s">
-        <v>945</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B31">
-        <v>166629</v>
+        <v>166650</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E31" t="s">
-        <v>875</v>
+        <v>714</v>
       </c>
       <c r="F31" t="s">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="G31" t="s">
-        <v>118</v>
+        <v>946</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B32">
-        <v>166650</v>
+        <v>166657</v>
       </c>
       <c r="C32">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E32" t="s">
-        <v>715</v>
+        <v>885</v>
       </c>
       <c r="F32" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G32" t="s">
-        <v>952</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B33">
-        <v>166657</v>
+        <v>166687</v>
       </c>
       <c r="C33">
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E33" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F33" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>947</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B34">
-        <v>166687</v>
+        <v>166691</v>
       </c>
       <c r="C34">
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E34" t="s">
-        <v>890</v>
+        <v>339</v>
       </c>
       <c r="F34" t="s">
-        <v>925</v>
+        <v>383</v>
       </c>
       <c r="G34" t="s">
-        <v>953</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B35">
-        <v>166691</v>
+        <v>166708</v>
       </c>
       <c r="C35">
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E35" t="s">
-        <v>339</v>
+        <v>887</v>
       </c>
       <c r="F35" t="s">
-        <v>383</v>
+        <v>921</v>
       </c>
       <c r="G35" t="s">
-        <v>409</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B36">
-        <v>166708</v>
+        <v>166719</v>
       </c>
       <c r="C36">
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E36" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="F36" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="G36" t="s">
-        <v>118</v>
+        <v>948</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B37">
-        <v>166719</v>
+        <v>166744</v>
       </c>
       <c r="C37">
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="E37" t="s">
-        <v>892</v>
+        <v>325</v>
       </c>
       <c r="F37" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G37" t="s">
-        <v>954</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B38">
-        <v>166744</v>
+        <v>166746</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E38" t="s">
-        <v>325</v>
+        <v>889</v>
       </c>
       <c r="F38" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="G38" t="s">
-        <v>118</v>
+        <v>949</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B39">
-        <v>166746</v>
+        <v>166753</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E39" t="s">
-        <v>893</v>
+        <v>315</v>
       </c>
       <c r="F39" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="G39" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B40">
-        <v>166753</v>
+        <v>166779</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E40" t="s">
-        <v>315</v>
+        <v>890</v>
       </c>
       <c r="F40" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="G40" t="s">
-        <v>956</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B41">
-        <v>166779</v>
+        <v>166818</v>
       </c>
       <c r="C41">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E41" t="s">
-        <v>894</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="G41" t="s">
-        <v>118</v>
+        <v>951</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B42">
-        <v>166818</v>
+        <v>167482</v>
       </c>
       <c r="C42">
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>891</v>
       </c>
       <c r="F42" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="G42" t="s">
-        <v>957</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B43">
-        <v>167482</v>
+        <v>167812</v>
       </c>
       <c r="C43">
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E43" t="s">
-        <v>895</v>
+        <v>329</v>
       </c>
       <c r="F43" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10970,48 +10964,25 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B44">
-        <v>167812</v>
+        <v>171332</v>
       </c>
       <c r="C44">
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E44" t="s">
-        <v>329</v>
+        <v>892</v>
       </c>
       <c r="F44" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="G44" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>824</v>
-      </c>
-      <c r="B45">
-        <v>171332</v>
-      </c>
-      <c r="C45">
-        <v>8</v>
-      </c>
-      <c r="D45" t="s">
-        <v>868</v>
-      </c>
-      <c r="E45" t="s">
-        <v>896</v>
-      </c>
-      <c r="F45" t="s">
-        <v>935</v>
-      </c>
-      <c r="G45" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553328CD-09E0-8F44-9F51-5E74BD5AAF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82872C31-8345-6849-A36D-D8732F57186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1193">
   <si>
     <t>Session ID</t>
   </si>
@@ -430,9 +430,6 @@
     <t>249</t>
   </si>
   <si>
-    <t>297</t>
-  </si>
-  <si>
     <t>433</t>
   </si>
   <si>
@@ -484,9 +481,6 @@
     <t>Development of Single-Photon Avalanche Diode Array for Particle Physics and Medical Imaging</t>
   </si>
   <si>
-    <t>Ultra-Stable and Robust Response to X-Rays in 2D Layered Perovskite Micro-Crystalline Films Directly Deposited on Flexible Substrate</t>
-  </si>
-  <si>
     <t>Development of MCP-PMT and test of LAPPDs for Nuclear Physics Programs</t>
   </si>
   <si>
@@ -592,9 +586,6 @@
     <t>Vachon</t>
   </si>
   <si>
-    <t>Verdi</t>
-  </si>
-  <si>
     <t>Xie</t>
   </si>
   <si>
@@ -3614,6 +3605,9 @@
   </si>
   <si>
     <t>Łukasz</t>
+  </si>
+  <si>
+    <t>The DAQ and clock distribution system of CMS MIP Timing Detector</t>
   </si>
 </sst>
 </file>
@@ -4052,10 +4046,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4066,10 +4060,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4080,10 +4074,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4094,10 +4088,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4108,10 +4102,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4122,10 +4116,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4136,10 +4130,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4150,10 +4144,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4164,10 +4158,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -4178,7 +4172,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -4212,7 +4206,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4221,21 +4215,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F2" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="G2" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4244,21 +4238,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E3" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="F3" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="G3" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4267,21 +4261,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="E4" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F4" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="G4" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4290,21 +4284,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="E5" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F5" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="G5" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4313,13 +4307,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="E6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F6" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4327,7 +4321,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4336,21 +4330,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E7" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F7" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="G7" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4359,13 +4353,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F8" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4373,7 +4367,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4382,21 +4376,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F9" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="G9" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4405,13 +4399,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E10" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F10" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4419,7 +4413,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4428,21 +4422,21 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4451,21 +4445,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E12" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F12" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="G12" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4474,21 +4468,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="G13" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4497,21 +4491,21 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4520,13 +4514,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E15" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="F15" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4534,7 +4528,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4543,21 +4537,21 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E16" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F16" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="G16" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4566,21 +4560,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E17" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="F17" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G17" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4589,21 +4583,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E18" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F18" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="G18" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4612,13 +4606,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E19" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="F19" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4626,7 +4620,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4635,13 +4629,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4649,7 +4643,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4658,21 +4652,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E21" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F21" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="G21" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4681,21 +4675,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E22" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="F22" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G22" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4704,21 +4698,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E23" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F23" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="G23" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4727,21 +4721,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="E24" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F24" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="G24" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4750,21 +4744,21 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G25" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4773,21 +4767,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="E26" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="F26" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="G26" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4796,21 +4790,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="G27" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4819,21 +4813,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E28" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F28" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="G28" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4842,21 +4836,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E29" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="F29" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="G29" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4865,13 +4859,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E30" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F30" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4879,7 +4873,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4888,13 +4882,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E31" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F31" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4902,7 +4896,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4911,13 +4905,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E32" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F32" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4925,7 +4919,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4934,13 +4928,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="E33" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="F33" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4948,7 +4942,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4957,13 +4951,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E34" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F34" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4971,7 +4965,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4980,21 +4974,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E35" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="F35" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="G35" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -5003,13 +4997,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E36" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F36" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5017,7 +5011,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5026,21 +5020,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E37" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="G37" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5049,21 +5043,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E38" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="F38" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="G38" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5072,21 +5066,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E39" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F39" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G39" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5095,13 +5089,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="E40" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="F40" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5109,7 +5103,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5118,13 +5112,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E41" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="F41" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5132,7 +5126,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5141,21 +5135,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="E42" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="F42" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="G42" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5164,21 +5158,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="E43" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F43" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="G43" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5187,21 +5181,21 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E44" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="F44" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="G44" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5210,21 +5204,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E45" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="F45" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="G45" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5233,21 +5227,21 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E46" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F46" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G46" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5256,13 +5250,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E47" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F47" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5270,7 +5264,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5279,13 +5273,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E48" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F48" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5293,7 +5287,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5302,21 +5296,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E49" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F49" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="G49" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5325,21 +5319,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="E50" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="F50" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="G50" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5348,13 +5342,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="E51" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F51" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5362,7 +5356,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5371,21 +5365,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E52" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F52" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="G52" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5394,13 +5388,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="E53" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="F53" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5408,7 +5402,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5417,13 +5411,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E54" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F54" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5431,7 +5425,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5440,21 +5434,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E55" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="F55" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
       <c r="G55" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5463,21 +5457,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="E56" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="F56" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="G56" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5486,13 +5480,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E57" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F57" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5500,7 +5494,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5509,16 +5503,39 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="E58" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="F58" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="G58" t="s">
-        <v>1171</v>
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>182</v>
+      </c>
+      <c r="B59">
+        <v>171826</v>
+      </c>
+      <c r="C59">
+        <v>12</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E59" t="s">
+        <v>544</v>
+      </c>
+      <c r="F59" t="s">
+        <v>564</v>
+      </c>
+      <c r="G59" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -6050,7 +6067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -6093,16 +6110,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -6116,13 +6133,13 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G3" t="s">
         <v>118</v>
@@ -6139,13 +6156,13 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -6162,13 +6179,13 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G5" t="s">
         <v>118</v>
@@ -6185,16 +6202,16 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -6202,22 +6219,22 @@
         <v>133</v>
       </c>
       <c r="B7">
-        <v>166697</v>
+        <v>166811</v>
       </c>
       <c r="C7">
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G7" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -6225,22 +6242,22 @@
         <v>134</v>
       </c>
       <c r="B8">
-        <v>166811</v>
+        <v>166470</v>
       </c>
       <c r="C8">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F8" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G8" t="s">
-        <v>202</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -6248,19 +6265,19 @@
         <v>135</v>
       </c>
       <c r="B9">
-        <v>166470</v>
+        <v>166666</v>
       </c>
       <c r="C9">
         <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -6271,22 +6288,22 @@
         <v>136</v>
       </c>
       <c r="B10">
-        <v>166666</v>
+        <v>166501</v>
       </c>
       <c r="C10">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G10" t="s">
-        <v>118</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -6294,22 +6311,22 @@
         <v>137</v>
       </c>
       <c r="B11">
-        <v>166501</v>
+        <v>166533</v>
       </c>
       <c r="C11">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6317,22 +6334,22 @@
         <v>138</v>
       </c>
       <c r="B12">
-        <v>166533</v>
+        <v>166534</v>
       </c>
       <c r="C12">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -6340,22 +6357,22 @@
         <v>139</v>
       </c>
       <c r="B13">
-        <v>166534</v>
+        <v>166683</v>
       </c>
       <c r="C13">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -6363,22 +6380,22 @@
         <v>140</v>
       </c>
       <c r="B14">
-        <v>166683</v>
+        <v>166735</v>
       </c>
       <c r="C14">
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F14" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G14" t="s">
-        <v>118</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -6386,22 +6403,22 @@
         <v>141</v>
       </c>
       <c r="B15">
-        <v>166735</v>
+        <v>166741</v>
       </c>
       <c r="C15">
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G15" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -6409,22 +6426,22 @@
         <v>142</v>
       </c>
       <c r="B16">
-        <v>166741</v>
+        <v>166793</v>
       </c>
       <c r="C16">
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G16" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -6432,22 +6449,22 @@
         <v>143</v>
       </c>
       <c r="B17">
-        <v>166793</v>
+        <v>166822</v>
       </c>
       <c r="C17">
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -6455,45 +6472,22 @@
         <v>144</v>
       </c>
       <c r="B18">
-        <v>166822</v>
+        <v>167676</v>
       </c>
       <c r="C18">
         <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F18" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G18" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B19">
-        <v>167676</v>
-      </c>
-      <c r="C19">
-        <v>20</v>
-      </c>
-      <c r="D19" t="s">
-        <v>163</v>
-      </c>
-      <c r="E19" t="s">
-        <v>181</v>
-      </c>
-      <c r="F19" t="s">
-        <v>199</v>
-      </c>
-      <c r="G19" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -6537,7 +6531,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B2">
         <v>166500</v>
@@ -6546,21 +6540,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B3">
         <v>166535</v>
@@ -6569,13 +6563,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
         <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G3" t="s">
         <v>114</v>
@@ -6583,7 +6577,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B4">
         <v>166543</v>
@@ -6592,13 +6586,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -6606,7 +6600,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B5">
         <v>166549</v>
@@ -6615,21 +6609,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B6">
         <v>166616</v>
@@ -6638,21 +6632,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F6" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="G6" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B7">
         <v>166693</v>
@@ -6661,21 +6655,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B8">
         <v>166706</v>
@@ -6684,21 +6678,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F8" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B9">
         <v>166721</v>
@@ -6707,21 +6701,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B10">
         <v>166724</v>
@@ -6730,13 +6724,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -6744,7 +6738,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B11">
         <v>166768</v>
@@ -6753,13 +6747,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
         <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -6767,7 +6761,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B12">
         <v>166764</v>
@@ -6776,21 +6770,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
         <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G12" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B13">
         <v>166805</v>
@@ -6799,21 +6793,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F13" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B14">
         <v>166813</v>
@@ -6822,21 +6816,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G14" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B15">
         <v>167802</v>
@@ -6845,21 +6839,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F15" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G15" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B16">
         <v>167855</v>
@@ -6868,13 +6862,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F16" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G16" t="s">
         <v>114</v>
@@ -6882,7 +6876,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B17">
         <v>166537</v>
@@ -6891,13 +6885,13 @@
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E17" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F17" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -6905,7 +6899,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B18">
         <v>166548</v>
@@ -6914,13 +6908,13 @@
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E18" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F18" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -6928,7 +6922,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B19">
         <v>166588</v>
@@ -6937,21 +6931,21 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F19" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G19" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B20">
         <v>166642</v>
@@ -6960,13 +6954,13 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E20" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F20" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G20" t="s">
         <v>114</v>
@@ -6974,7 +6968,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B21">
         <v>166665</v>
@@ -6983,13 +6977,13 @@
         <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E21" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -6997,7 +6991,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B22">
         <v>166688</v>
@@ -7006,13 +7000,13 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F22" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -7020,7 +7014,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B23">
         <v>166722</v>
@@ -7029,21 +7023,21 @@
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E23" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F23" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G23" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B24">
         <v>166769</v>
@@ -7052,13 +7046,13 @@
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F24" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G24" t="s">
         <v>118</v>
@@ -7066,7 +7060,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B25">
         <v>166471</v>
@@ -7075,21 +7069,21 @@
         <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F25" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G25" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B26">
         <v>166465</v>
@@ -7098,13 +7092,13 @@
         <v>11</v>
       </c>
       <c r="D26" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E26" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G26" t="s">
         <v>114</v>
@@ -7112,7 +7106,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B27">
         <v>166491</v>
@@ -7121,13 +7115,13 @@
         <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E27" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F27" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -7135,7 +7129,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B28">
         <v>166547</v>
@@ -7144,21 +7138,21 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E28" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F28" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G28" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B29">
         <v>166554</v>
@@ -7167,21 +7161,21 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E29" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F29" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G29" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B30">
         <v>166787</v>
@@ -7190,21 +7184,21 @@
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E30" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="F30" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="G30" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B31">
         <v>166536</v>
@@ -7213,13 +7207,13 @@
         <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E31" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F31" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G31" t="s">
         <v>114</v>
@@ -7227,7 +7221,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B32">
         <v>166464</v>
@@ -7236,21 +7230,21 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E32" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F32" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G32" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B33">
         <v>166555</v>
@@ -7259,21 +7253,21 @@
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E33" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F33" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G33" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B34">
         <v>166562</v>
@@ -7282,21 +7276,21 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F34" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="G34" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B35">
         <v>166586</v>
@@ -7305,21 +7299,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E35" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F35" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G35" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B36">
         <v>166613</v>
@@ -7328,21 +7322,21 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E36" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F36" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G36" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B37">
         <v>166617</v>
@@ -7351,13 +7345,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E37" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F37" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -7365,7 +7359,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B38">
         <v>166634</v>
@@ -7374,13 +7368,13 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E38" t="s">
         <v>82</v>
       </c>
       <c r="F38" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="G38" t="s">
         <v>118</v>
@@ -7388,7 +7382,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B39">
         <v>166639</v>
@@ -7397,13 +7391,13 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F39" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="G39" t="s">
         <v>118</v>
@@ -7411,7 +7405,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B40">
         <v>166647</v>
@@ -7420,21 +7414,21 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E40" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F40" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G40" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B41">
         <v>166670</v>
@@ -7443,21 +7437,21 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E41" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F41" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G41" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B42">
         <v>166686</v>
@@ -7466,21 +7460,21 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E42" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F42" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="G42" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B43">
         <v>166689</v>
@@ -7489,21 +7483,21 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E43" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F43" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G43" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B44">
         <v>166690</v>
@@ -7512,21 +7506,21 @@
         <v>1</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E44" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F44" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G44" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B45">
         <v>166695</v>
@@ -7535,21 +7529,21 @@
         <v>2</v>
       </c>
       <c r="D45" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E45" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F45" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G45" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B46">
         <v>166726</v>
@@ -7558,21 +7552,21 @@
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E46" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F46" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G46" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B47">
         <v>166812</v>
@@ -7581,13 +7575,13 @@
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E47" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F47" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -7595,7 +7589,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B48">
         <v>167673</v>
@@ -7604,13 +7598,13 @@
         <v>5</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E48" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F48" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -7657,7 +7651,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B2">
         <v>166631</v>
@@ -7666,13 +7660,13 @@
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -7680,7 +7674,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B3">
         <v>166646</v>
@@ -7689,13 +7683,13 @@
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G3" t="s">
         <v>118</v>
@@ -7703,7 +7697,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B4">
         <v>166660</v>
@@ -7712,21 +7706,21 @@
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B5">
         <v>166661</v>
@@ -7735,21 +7729,21 @@
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F5" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B6">
         <v>166699</v>
@@ -7758,21 +7752,21 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F6" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G6" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B7">
         <v>166701</v>
@@ -7781,21 +7775,21 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E7" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F7" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G7" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B8">
         <v>166784</v>
@@ -7804,21 +7798,21 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B9">
         <v>166747</v>
@@ -7827,13 +7821,13 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -7841,7 +7835,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B10">
         <v>166487</v>
@@ -7850,21 +7844,21 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E10" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F10" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G10" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B11">
         <v>166560</v>
@@ -7873,21 +7867,21 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G11" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B12">
         <v>166597</v>
@@ -7896,13 +7890,13 @@
         <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -7910,7 +7904,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B13">
         <v>166604</v>
@@ -7919,13 +7913,13 @@
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F13" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G13" t="s">
         <v>114</v>
@@ -7933,7 +7927,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B14">
         <v>166607</v>
@@ -7942,13 +7936,13 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F14" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -7956,7 +7950,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B15">
         <v>166612</v>
@@ -7965,13 +7959,13 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F15" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -7979,7 +7973,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B16">
         <v>166627</v>
@@ -7988,13 +7982,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E16" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F16" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
@@ -8002,7 +7996,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B17">
         <v>166729</v>
@@ -8011,13 +8005,13 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F17" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8025,7 +8019,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B18">
         <v>166750</v>
@@ -8034,21 +8028,21 @@
         <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G18" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B19">
         <v>166796</v>
@@ -8057,13 +8051,13 @@
         <v>20</v>
       </c>
       <c r="D19" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E19" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -8071,7 +8065,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B20">
         <v>167817</v>
@@ -8080,21 +8074,21 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E20" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F20" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="G20" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B21">
         <v>171014</v>
@@ -8103,16 +8097,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E21" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F21" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="G21" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8126,16 +8120,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G22" t="s">
         <v>1183</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1186</v>
       </c>
     </row>
   </sheetData>
@@ -8179,7 +8173,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -8188,21 +8182,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="G2" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -8211,21 +8205,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E3" t="s">
         <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G3" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -8234,13 +8228,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F4" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8248,7 +8242,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8257,21 +8251,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B6">
         <v>166645</v>
@@ -8280,21 +8274,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F6" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B7">
         <v>166643</v>
@@ -8303,21 +8297,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F7" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="G7" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B8">
         <v>166685</v>
@@ -8326,21 +8320,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E8" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F8" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="G8" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B9">
         <v>166810</v>
@@ -8349,21 +8343,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E9" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F9" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="G9" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B10">
         <v>166740</v>
@@ -8372,21 +8366,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G10" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B11">
         <v>166754</v>
@@ -8395,13 +8389,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E11" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F11" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8409,7 +8403,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B12">
         <v>166775</v>
@@ -8418,13 +8412,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E12" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="F12" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -8432,7 +8426,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B13">
         <v>166475</v>
@@ -8441,21 +8435,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E13" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F13" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="G13" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B14">
         <v>166511</v>
@@ -8464,21 +8458,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E14" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F14" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="G14" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B15">
         <v>166518</v>
@@ -8487,13 +8481,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E15" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F15" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -8501,7 +8495,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B16">
         <v>166524</v>
@@ -8510,21 +8504,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E16" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F16" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G16" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B17">
         <v>166525</v>
@@ -8533,13 +8527,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F17" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8547,7 +8541,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B18">
         <v>166563</v>
@@ -8556,13 +8550,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E18" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F18" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -8570,7 +8564,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B19">
         <v>166608</v>
@@ -8579,21 +8573,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E19" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="F19" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="G19" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B20">
         <v>166659</v>
@@ -8602,21 +8596,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E20" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F20" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G20" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B21">
         <v>166664</v>
@@ -8625,13 +8619,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F21" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -8639,7 +8633,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B22">
         <v>166727</v>
@@ -8648,21 +8642,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E22" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F22" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="G22" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B23">
         <v>166738</v>
@@ -8671,13 +8665,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E23" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F23" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -8724,7 +8718,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8733,13 +8727,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8747,7 +8741,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8756,21 +8750,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="G3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8779,13 +8773,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E4" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="F4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8793,7 +8787,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8802,21 +8796,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G5" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8825,21 +8819,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F6" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G6" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B7">
         <v>166794</v>
@@ -8848,21 +8842,21 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="E7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F7" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="G7" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="B8">
         <v>167882</v>
@@ -8871,13 +8865,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="E8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F8" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -8885,7 +8879,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B9">
         <v>166696</v>
@@ -8894,21 +8888,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E9" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="F9" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G9" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="B10">
         <v>166700</v>
@@ -8917,21 +8911,21 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="E10" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="F10" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="G10" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B11">
         <v>166792</v>
@@ -8940,13 +8934,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="E11" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F11" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8993,7 +8987,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -9002,13 +8996,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="F2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9016,7 +9010,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9025,21 +9019,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="E3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="F3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="G3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9048,13 +9042,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="E4" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F4" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9062,7 +9056,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9071,21 +9065,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E5" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F5" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G5" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9094,13 +9088,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9108,7 +9102,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9117,13 +9111,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="E7" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="F7" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9131,7 +9125,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9140,13 +9134,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E8" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F8" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9154,7 +9148,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9163,21 +9157,21 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="E9" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F9" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="G9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9186,13 +9180,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F10" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9200,7 +9194,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9209,13 +9203,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E11" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F11" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9223,7 +9217,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9232,21 +9226,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="E12" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F12" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="G12" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9255,13 +9249,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="E13" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F13" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9269,7 +9263,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9278,13 +9272,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E14" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="F14" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9292,7 +9286,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9301,13 +9295,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="E15" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F15" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9315,7 +9309,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9324,21 +9318,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E16" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F16" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G16" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9347,13 +9341,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9361,7 +9355,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9370,13 +9364,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E18" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F18" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9384,7 +9378,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9393,13 +9387,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9407,7 +9401,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9416,13 +9410,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E20" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F20" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9430,7 +9424,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9439,13 +9433,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E21" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="F21" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9453,7 +9447,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9462,13 +9456,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9476,7 +9470,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9485,13 +9479,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9499,7 +9493,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9508,21 +9502,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="E24" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F24" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="G24" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9531,21 +9525,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="E25" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="F25" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="G25" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9554,21 +9548,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E26" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F26" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="G26" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9577,13 +9571,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E27" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F27" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9591,7 +9585,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9600,21 +9594,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E28" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F28" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="G28" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9623,13 +9617,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9637,7 +9631,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9646,21 +9640,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E30" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F30" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="G30" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9669,13 +9663,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="E31" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="F31" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9683,7 +9677,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9692,21 +9686,21 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="E32" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="F32" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G32" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9715,13 +9709,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F33" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9729,7 +9723,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9738,13 +9732,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F34" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9752,7 +9746,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9761,21 +9755,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E35" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="F35" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G35" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9784,13 +9778,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E36" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F36" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9798,7 +9792,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9807,13 +9801,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E37" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="F37" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9821,7 +9815,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9830,21 +9824,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E38" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="F38" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G38" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9853,21 +9847,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E39" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="F39" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="G39" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9876,13 +9870,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9890,7 +9884,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9899,21 +9893,21 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G41" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9922,21 +9916,21 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E42" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F42" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="G42" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B43">
         <v>166725</v>
@@ -9945,13 +9939,13 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E43" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F43" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -9998,7 +9992,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -10007,13 +10001,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="E2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -10021,7 +10015,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10030,21 +10024,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10053,13 +10047,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E4" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="F4" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10067,7 +10061,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10076,21 +10070,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E5" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="F5" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G5" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10099,21 +10093,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="E6" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F6" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="G6" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10122,21 +10116,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="E7" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="F7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G7" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10145,21 +10139,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E8" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="F8" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="G8" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10168,13 +10162,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E9" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F9" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10182,7 +10176,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10191,13 +10185,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E10" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="F10" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10205,7 +10199,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B11">
         <v>166673</v>
@@ -10214,21 +10208,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E11" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="F11" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="G11" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B12">
         <v>166675</v>
@@ -10237,21 +10231,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E12" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="F12" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="G12" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B13">
         <v>166710</v>
@@ -10260,21 +10254,21 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B14">
         <v>166711</v>
@@ -10283,21 +10277,21 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E14" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="F14" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G14" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="B15">
         <v>166755</v>
@@ -10306,13 +10300,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -10320,7 +10314,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B16">
         <v>166757</v>
@@ -10329,21 +10323,21 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E16" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F16" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="G16" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B17">
         <v>167481</v>
@@ -10352,13 +10346,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E17" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="F17" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G17" t="s">
         <v>114</v>
@@ -10366,7 +10360,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="B18">
         <v>167793</v>
@@ -10375,13 +10369,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G18" t="s">
         <v>118</v>
@@ -10389,7 +10383,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="B19">
         <v>168287</v>
@@ -10398,21 +10392,21 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="E19" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="F19" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G19" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B20">
         <v>166567</v>
@@ -10421,21 +10415,21 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="E20" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="F20" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G20" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="B21">
         <v>166538</v>
@@ -10444,21 +10438,21 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E21" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="F21" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="G21" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="B22">
         <v>166678</v>
@@ -10467,21 +10461,21 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="E22" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F22" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="G22" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="B23">
         <v>167682</v>
@@ -10490,21 +10484,21 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="E23" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="G23" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="B24">
         <v>166529</v>
@@ -10513,21 +10507,21 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E24" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="F24" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="G24" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B25">
         <v>166472</v>
@@ -10536,21 +10530,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="E25" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F25" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="G25" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B26">
         <v>166571</v>
@@ -10559,21 +10553,21 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="E26" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="F26" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="G26" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B27">
         <v>166575</v>
@@ -10582,13 +10576,13 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="E27" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F27" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -10596,7 +10590,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="B28">
         <v>166590</v>
@@ -10605,21 +10599,21 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="E28" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="F28" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="G28" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B29">
         <v>166598</v>
@@ -10628,21 +10622,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="E29" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="F29" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="G29" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="B30">
         <v>166629</v>
@@ -10651,13 +10645,13 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="E30" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="F30" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -10665,7 +10659,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B31">
         <v>166650</v>
@@ -10674,21 +10668,21 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E31" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F31" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="G31" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="B32">
         <v>166657</v>
@@ -10697,13 +10691,13 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="E32" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="F32" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="G32" t="s">
         <v>114</v>
@@ -10711,7 +10705,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B33">
         <v>166687</v>
@@ -10720,21 +10714,21 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E33" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="F33" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G33" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="B34">
         <v>166691</v>
@@ -10743,21 +10737,21 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="E34" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F34" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G34" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B35">
         <v>166708</v>
@@ -10766,13 +10760,13 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E35" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="F35" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="G35" t="s">
         <v>118</v>
@@ -10780,7 +10774,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B36">
         <v>166719</v>
@@ -10789,21 +10783,21 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="E36" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="F36" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="G36" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B37">
         <v>166744</v>
@@ -10812,13 +10806,13 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -10826,7 +10820,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B38">
         <v>166746</v>
@@ -10835,21 +10829,21 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="E38" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="F38" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="G38" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B39">
         <v>166753</v>
@@ -10858,21 +10852,21 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F39" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="G39" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B40">
         <v>166779</v>
@@ -10881,13 +10875,13 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="E40" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="F40" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -10895,7 +10889,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B41">
         <v>166818</v>
@@ -10904,21 +10898,21 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E41" t="s">
         <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="G41" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="B42">
         <v>167482</v>
@@ -10927,13 +10921,13 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="E42" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="F42" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="G42" t="s">
         <v>118</v>
@@ -10941,7 +10935,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B43">
         <v>167812</v>
@@ -10950,13 +10944,13 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="E43" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F43" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10964,7 +10958,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B44">
         <v>171332</v>
@@ -10973,16 +10967,16 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="E44" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F44" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="G44" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82872C31-8345-6849-A36D-D8732F57186B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F9749A-8B12-3543-A1FB-EC5559C257D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="1190">
   <si>
     <t>Session ID</t>
   </si>
@@ -1792,9 +1792,6 @@
     <t>272</t>
   </si>
   <si>
-    <t>423</t>
-  </si>
-  <si>
     <t>204</t>
   </si>
   <si>
@@ -1822,9 +1819,6 @@
     <t>Background of X-ray TES micro-calorimeter arrays for elusive particle experiments</t>
   </si>
   <si>
-    <t>Response characterization of PVT scintillators to alpha and beta/gamma sources for low temperature applications</t>
-  </si>
-  <si>
     <t>Design and preliminary characterizations of traveling wave parametric amplifiers for DARTWARS</t>
   </si>
   <si>
@@ -1873,9 +1867,6 @@
     <t>Vaccaro</t>
   </si>
   <si>
-    <t>Gironi</t>
-  </si>
-  <si>
     <t>Borghesi</t>
   </si>
   <si>
@@ -1897,9 +1888,6 @@
     <t>SRON Leiden</t>
   </si>
   <si>
-    <t>University Milano Bicocca</t>
-  </si>
-  <si>
     <t>GE</t>
   </si>
   <si>
@@ -3608,6 +3596,9 @@
   </si>
   <si>
     <t>The DAQ and clock distribution system of CMS MIP Timing Detector</t>
+  </si>
+  <si>
+    <t>Operational results with the pixelated timing Counter (pTC) of the MEGII experiment during the first year of physics data taking</t>
   </si>
 </sst>
 </file>
@@ -4046,10 +4037,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4060,10 +4051,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4074,10 +4065,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4088,10 +4079,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4102,10 +4093,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4116,10 +4107,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4130,10 +4121,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4144,10 +4135,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4158,10 +4149,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
     </row>
   </sheetData>
@@ -4206,7 +4197,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4215,21 +4206,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="E2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="F2" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="G2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4238,21 +4229,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="E3" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F3" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="G3" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4261,21 +4252,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="E4" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="F4" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G4" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4284,21 +4275,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="E5" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="F5" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G5" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4307,13 +4298,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="E6" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F6" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4321,7 +4312,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4330,21 +4321,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="E7" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="F7" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="G7" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4353,13 +4344,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="E8" t="s">
         <v>312</v>
       </c>
       <c r="F8" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4367,7 +4358,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4376,21 +4367,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="E9" t="s">
         <v>341</v>
       </c>
       <c r="F9" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="G9" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4399,13 +4390,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="E10" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="F10" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4413,7 +4404,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4422,7 +4413,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="E11" t="s">
         <v>311</v>
@@ -4436,7 +4427,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4445,21 +4436,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="E12" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="F12" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="G12" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4468,21 +4459,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="G13" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4491,7 +4482,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="E14" t="s">
         <v>311</v>
@@ -4505,7 +4496,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4514,13 +4505,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="E15" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="F15" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4528,7 +4519,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4537,13 +4528,13 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="E16" t="s">
         <v>340</v>
       </c>
       <c r="F16" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G16" t="s">
         <v>570</v>
@@ -4551,7 +4542,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4560,21 +4551,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="E17" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="F17" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="G17" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4583,21 +4574,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="E18" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="F18" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="G18" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4606,13 +4597,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="E19" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="F19" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4620,7 +4611,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4629,13 +4620,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="E20" t="s">
         <v>167</v>
       </c>
       <c r="F20" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4643,7 +4634,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4652,21 +4643,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E21" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F21" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="G21" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4675,21 +4666,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="E22" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="F22" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="G22" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4698,21 +4689,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E23" t="s">
         <v>326</v>
       </c>
       <c r="F23" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="G23" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4721,21 +4712,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="E24" t="s">
         <v>318</v>
       </c>
       <c r="F24" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="G24" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4744,7 +4735,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E25" t="s">
         <v>311</v>
@@ -4758,7 +4749,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4767,21 +4758,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="E26" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="F26" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="G26" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4790,21 +4781,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="G27" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4813,21 +4804,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="E28" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F28" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="G28" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4836,21 +4827,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="E29" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="F29" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="G29" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4859,13 +4850,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E30" t="s">
         <v>326</v>
       </c>
       <c r="F30" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4873,7 +4864,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4882,13 +4873,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E31" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F31" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4896,7 +4887,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4905,13 +4896,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="E32" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F32" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4919,7 +4910,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4928,13 +4919,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="E33" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="F33" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4942,7 +4933,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4951,13 +4942,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="E34" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F34" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4965,7 +4956,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4974,21 +4965,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="E35" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="F35" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="G35" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -4997,13 +4988,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="E36" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F36" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5011,7 +5002,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5020,21 +5011,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="G37" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5043,21 +5034,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="E38" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="F38" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="G38" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5066,21 +5057,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="E39" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F39" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="G39" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5089,13 +5080,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="E40" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F40" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5103,7 +5094,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5112,13 +5103,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E41" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F41" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5126,7 +5117,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5135,21 +5126,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="E42" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="F42" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="G42" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5158,21 +5149,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="E43" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F43" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="G43" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5181,13 +5172,13 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E44" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="F44" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="G44" t="s">
         <v>481</v>
@@ -5195,7 +5186,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5204,21 +5195,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="E45" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="F45" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="G45" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5227,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="E46" t="s">
         <v>311</v>
@@ -5241,7 +5232,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5250,13 +5241,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E47" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F47" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5264,7 +5255,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5273,13 +5264,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="E48" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F48" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5287,7 +5278,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5296,21 +5287,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="E49" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="F49" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="G49" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5319,21 +5310,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="E50" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F50" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="G50" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5342,13 +5333,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E51" t="s">
         <v>318</v>
       </c>
       <c r="F51" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5356,7 +5347,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5365,21 +5356,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="E52" t="s">
         <v>306</v>
       </c>
       <c r="F52" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="G52" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5388,13 +5379,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="E53" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="F53" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5402,7 +5393,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5411,13 +5402,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="E54" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="F54" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5425,7 +5416,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5434,21 +5425,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="E55" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="F55" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="G55" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5457,21 +5448,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="E56" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="F56" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="G56" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5480,13 +5471,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="E57" t="s">
         <v>341</v>
       </c>
       <c r="F57" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5494,7 +5485,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5503,16 +5494,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="E58" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="F58" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="G58" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -5526,7 +5517,7 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="E59" t="s">
         <v>544</v>
@@ -6497,7 +6488,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7187,10 +7178,10 @@
         <v>283</v>
       </c>
       <c r="E30" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="F30" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="G30" t="s">
         <v>400</v>
@@ -7607,6 +7598,29 @@
         <v>385</v>
       </c>
       <c r="G48" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>184</v>
+      </c>
+      <c r="B49">
+        <v>171868</v>
+      </c>
+      <c r="C49">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E49" t="s">
+        <v>459</v>
+      </c>
+      <c r="F49" t="s">
+        <v>475</v>
+      </c>
+      <c r="G49" t="s">
         <v>118</v>
       </c>
     </row>
@@ -8106,7 +8120,7 @@
         <v>479</v>
       </c>
       <c r="G21" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8120,16 +8134,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E22" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="F22" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="G22" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
     </row>
   </sheetData>
@@ -8605,7 +8619,7 @@
         <v>565</v>
       </c>
       <c r="G20" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -8684,7 +8698,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -8727,13 +8741,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E2" t="s">
         <v>172</v>
       </c>
       <c r="F2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8750,16 +8764,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F3" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G3" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -8773,13 +8787,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8796,16 +8810,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E5" t="s">
         <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="G5" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -8819,16 +8833,16 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G6" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -8836,22 +8850,22 @@
         <v>587</v>
       </c>
       <c r="B7">
-        <v>166794</v>
+        <v>167882</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E7" t="s">
-        <v>605</v>
+        <v>167</v>
       </c>
       <c r="F7" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="G7" t="s">
-        <v>622</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -8859,22 +8873,22 @@
         <v>588</v>
       </c>
       <c r="B8">
-        <v>167882</v>
+        <v>166696</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>604</v>
       </c>
       <c r="F8" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G8" t="s">
-        <v>118</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -8882,22 +8896,22 @@
         <v>589</v>
       </c>
       <c r="B9">
-        <v>166696</v>
+        <v>166700</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="G9" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -8905,44 +8919,21 @@
         <v>590</v>
       </c>
       <c r="B10">
-        <v>166700</v>
+        <v>166792</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G10" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>591</v>
-      </c>
-      <c r="B11">
-        <v>166792</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>601</v>
-      </c>
-      <c r="E11" t="s">
-        <v>608</v>
-      </c>
-      <c r="F11" t="s">
-        <v>618</v>
-      </c>
-      <c r="G11" t="s">
         <v>118</v>
       </c>
     </row>
@@ -8987,7 +8978,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8996,13 +8987,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9010,7 +9001,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9019,21 +9010,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E3" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="F3" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G3" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9042,13 +9033,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E4" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="F4" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9056,7 +9047,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9065,21 +9056,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E5" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="F5" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G5" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9088,13 +9079,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E6" t="s">
         <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9102,7 +9093,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9111,13 +9102,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E7" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F7" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9125,7 +9116,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9134,13 +9125,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E8" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="F8" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9148,7 +9139,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9157,13 +9148,13 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="E9" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F9" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G9" t="s">
         <v>483</v>
@@ -9171,7 +9162,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9180,13 +9171,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E10" t="s">
         <v>167</v>
       </c>
       <c r="F10" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9194,7 +9185,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9203,13 +9194,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E11" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F11" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9217,7 +9208,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9226,21 +9217,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E12" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F12" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="G12" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9249,13 +9240,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E13" t="s">
         <v>458</v>
       </c>
       <c r="F13" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9263,7 +9254,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9272,13 +9263,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="E14" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="F14" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9286,7 +9277,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9295,13 +9286,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E15" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="F15" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9309,7 +9300,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9318,21 +9309,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E16" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="F16" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G16" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9341,13 +9332,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="E17" t="s">
         <v>167</v>
       </c>
       <c r="F17" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9355,7 +9346,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9364,13 +9355,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="E18" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="F18" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9378,7 +9369,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9387,13 +9378,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="E19" t="s">
         <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9401,7 +9392,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9410,13 +9401,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="E20" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="F20" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9424,7 +9415,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9433,13 +9424,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E21" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="F21" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9447,7 +9438,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9456,13 +9447,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9470,7 +9461,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9479,13 +9470,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9493,7 +9484,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9502,21 +9493,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="E24" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="F24" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="G24" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9525,21 +9516,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="E25" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="F25" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G25" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9548,21 +9539,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="E26" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="F26" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="G26" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9571,13 +9562,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="E27" t="s">
         <v>543</v>
       </c>
       <c r="F27" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9585,7 +9576,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9594,21 +9585,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="E28" t="s">
         <v>545</v>
       </c>
       <c r="F28" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G28" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9617,13 +9608,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="E29" t="s">
         <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9631,7 +9622,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9640,21 +9631,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="E30" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="F30" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G30" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9663,13 +9654,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="E31" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="F31" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9677,7 +9668,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9686,13 +9677,13 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="E32" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="F32" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G32" t="s">
         <v>403</v>
@@ -9700,7 +9691,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9709,13 +9700,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
       </c>
       <c r="F33" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9723,7 +9714,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9732,13 +9723,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
       </c>
       <c r="F34" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9746,7 +9737,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9755,21 +9746,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="E35" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="F35" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G35" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9778,13 +9769,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="E36" t="s">
         <v>318</v>
       </c>
       <c r="F36" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9792,7 +9783,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9801,13 +9792,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E37" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="F37" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9815,7 +9806,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9824,21 +9815,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="E38" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F38" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="G38" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9847,21 +9838,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="E39" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="F39" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G39" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9870,13 +9861,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9884,7 +9875,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9893,7 +9884,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9902,12 +9893,12 @@
         <v>182</v>
       </c>
       <c r="G41" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9916,16 +9907,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E42" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="F42" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="G42" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -9992,7 +9983,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -10001,13 +9992,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -10015,7 +10006,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10024,21 +10015,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E3" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F3" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="G3" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10047,13 +10038,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E4" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F4" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10061,7 +10052,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10070,21 +10061,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E5" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="F5" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="G5" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10093,21 +10084,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="E6" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F6" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="G6" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10116,21 +10107,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="E7" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F7" t="s">
         <v>368</v>
       </c>
       <c r="G7" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10139,21 +10130,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E8" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="F8" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="G8" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10162,13 +10153,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E9" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F9" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10176,7 +10167,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10185,13 +10176,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E10" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="F10" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10199,7 +10190,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B11">
         <v>166673</v>
@@ -10208,21 +10199,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E11" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="F11" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G11" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B12">
         <v>166675</v>
@@ -10231,21 +10222,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E12" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="F12" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="G12" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B13">
         <v>166710</v>
@@ -10254,7 +10245,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="E13" t="s">
         <v>311</v>
@@ -10268,7 +10259,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B14">
         <v>166711</v>
@@ -10277,21 +10268,21 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="E14" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="F14" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="G14" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B15">
         <v>166755</v>
@@ -10300,13 +10291,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="E15" t="s">
         <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -10314,7 +10305,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B16">
         <v>166757</v>
@@ -10323,21 +10314,21 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="E16" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F16" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="G16" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B17">
         <v>167481</v>
@@ -10346,13 +10337,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="E17" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="F17" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="G17" t="s">
         <v>114</v>
@@ -10360,7 +10351,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B18">
         <v>167793</v>
@@ -10369,13 +10360,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="E18" t="s">
         <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="G18" t="s">
         <v>118</v>
@@ -10383,7 +10374,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B19">
         <v>168287</v>
@@ -10392,21 +10383,21 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="E19" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="F19" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="G19" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B20">
         <v>166567</v>
@@ -10415,21 +10406,21 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="E20" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="F20" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="G20" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B21">
         <v>166538</v>
@@ -10438,21 +10429,21 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E21" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="F21" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="G21" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B22">
         <v>166678</v>
@@ -10461,21 +10452,21 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="E22" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F22" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="G22" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B23">
         <v>167682</v>
@@ -10484,13 +10475,13 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E23" t="s">
         <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="G23" t="s">
         <v>570</v>
@@ -10498,7 +10489,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B24">
         <v>166529</v>
@@ -10507,21 +10498,21 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="E24" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="F24" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="G24" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B25">
         <v>166472</v>
@@ -10530,21 +10521,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E25" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="F25" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="G25" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B26">
         <v>166571</v>
@@ -10553,21 +10544,21 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="E26" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F26" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="G26" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B27">
         <v>166575</v>
@@ -10576,13 +10567,13 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="E27" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -10590,7 +10581,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B28">
         <v>166590</v>
@@ -10599,21 +10590,21 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="E28" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="F28" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="G28" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B29">
         <v>166598</v>
@@ -10622,21 +10613,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E29" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="F29" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="G29" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B30">
         <v>166629</v>
@@ -10645,13 +10636,13 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E30" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="F30" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -10659,7 +10650,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B31">
         <v>166650</v>
@@ -10668,21 +10659,21 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="E31" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="F31" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="G31" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B32">
         <v>166657</v>
@@ -10691,13 +10682,13 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="E32" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="F32" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="G32" t="s">
         <v>114</v>
@@ -10705,7 +10696,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B33">
         <v>166687</v>
@@ -10714,21 +10705,21 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="E33" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F33" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G33" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B34">
         <v>166691</v>
@@ -10737,7 +10728,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="E34" t="s">
         <v>336</v>
@@ -10751,7 +10742,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B35">
         <v>166708</v>
@@ -10760,13 +10751,13 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="E35" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="F35" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="G35" t="s">
         <v>118</v>
@@ -10774,7 +10765,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B36">
         <v>166719</v>
@@ -10783,21 +10774,21 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="E36" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="F36" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="G36" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B37">
         <v>166744</v>
@@ -10806,13 +10797,13 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="E37" t="s">
         <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -10820,7 +10811,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B38">
         <v>166746</v>
@@ -10829,21 +10820,21 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="E38" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="F38" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="G38" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B39">
         <v>166753</v>
@@ -10852,21 +10843,21 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="E39" t="s">
         <v>312</v>
       </c>
       <c r="F39" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="G39" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B40">
         <v>166779</v>
@@ -10875,13 +10866,13 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="E40" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="F40" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -10889,7 +10880,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B41">
         <v>166818</v>
@@ -10898,21 +10889,21 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="E41" t="s">
         <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="G41" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B42">
         <v>167482</v>
@@ -10921,13 +10912,13 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="E42" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="F42" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G42" t="s">
         <v>118</v>
@@ -10935,7 +10926,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B43">
         <v>167812</v>
@@ -10944,13 +10935,13 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="E43" t="s">
         <v>326</v>
       </c>
       <c r="F43" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10958,7 +10949,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B44">
         <v>171332</v>
@@ -10967,16 +10958,16 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="E44" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="F44" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="G44" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F9749A-8B12-3543-A1FB-EC5559C257D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06519633-1D65-684B-9144-B42DF361114C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -1375,9 +1375,6 @@
     <t>Detection of inter-fraction morphological changes in particle therapy exploiting charged secondary fragments</t>
   </si>
   <si>
-    <t>The SciFi beam monitor</t>
-  </si>
-  <si>
     <t>The use of Low-Temperature Cofired Ceramics technology in Gas Electron Multiplier detectors</t>
   </si>
   <si>
@@ -3599,6 +3596,9 @@
   </si>
   <si>
     <t>Operational results with the pixelated timing Counter (pTC) of the MEGII experiment during the first year of physics data taking</t>
+  </si>
+  <si>
+    <t>Beam monitoring detectors for High Intensity Muon Beams</t>
   </si>
 </sst>
 </file>
@@ -4037,10 +4037,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4051,10 +4051,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4065,10 +4065,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4079,10 +4079,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4093,10 +4093,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4107,10 +4107,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4121,10 +4121,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4135,10 +4135,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4149,10 +4149,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4206,21 +4206,21 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4229,21 +4229,21 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G3" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4252,21 +4252,21 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F4" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G4" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4275,21 +4275,21 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E5" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F5" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G5" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4298,13 +4298,13 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F6" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -4312,7 +4312,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4321,21 +4321,21 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E7" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F7" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4344,13 +4344,13 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E8" t="s">
         <v>312</v>
       </c>
       <c r="F8" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4367,21 +4367,21 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E9" t="s">
         <v>341</v>
       </c>
       <c r="F9" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G9" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4390,13 +4390,13 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E10" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F10" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -4404,7 +4404,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4413,7 +4413,7 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E11" t="s">
         <v>311</v>
@@ -4427,7 +4427,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4436,21 +4436,21 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E12" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F12" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G12" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4459,21 +4459,21 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E13" t="s">
         <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G13" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B14">
         <v>166806</v>
@@ -4482,7 +4482,7 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E14" t="s">
         <v>311</v>
@@ -4496,7 +4496,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B15">
         <v>166637</v>
@@ -4505,13 +4505,13 @@
         <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E15" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F15" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B16">
         <v>166648</v>
@@ -4528,21 +4528,21 @@
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E16" t="s">
         <v>340</v>
       </c>
       <c r="F16" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G16" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B17">
         <v>166676</v>
@@ -4551,21 +4551,21 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E17" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F17" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G17" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B18">
         <v>166715</v>
@@ -4574,21 +4574,21 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E18" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F18" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G18" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B19">
         <v>166692</v>
@@ -4597,13 +4597,13 @@
         <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E19" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F19" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B20">
         <v>166694</v>
@@ -4620,13 +4620,13 @@
         <v>17</v>
       </c>
       <c r="D20" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E20" t="s">
         <v>167</v>
       </c>
       <c r="F20" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B21">
         <v>166709</v>
@@ -4643,21 +4643,21 @@
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E21" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F21" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G21" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B22">
         <v>166717</v>
@@ -4666,21 +4666,21 @@
         <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E22" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F22" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G22" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B23">
         <v>166751</v>
@@ -4689,21 +4689,21 @@
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E23" t="s">
         <v>326</v>
       </c>
       <c r="F23" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G23" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B24">
         <v>166777</v>
@@ -4712,21 +4712,21 @@
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E24" t="s">
         <v>318</v>
       </c>
       <c r="F24" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G24" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B25">
         <v>166789</v>
@@ -4735,7 +4735,7 @@
         <v>11</v>
       </c>
       <c r="D25" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E25" t="s">
         <v>311</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B26">
         <v>166791</v>
@@ -4758,21 +4758,21 @@
         <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E26" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F26" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G26" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B27">
         <v>166819</v>
@@ -4781,21 +4781,21 @@
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E27" t="s">
         <v>84</v>
       </c>
       <c r="F27" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G27" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B28">
         <v>166527</v>
@@ -4804,21 +4804,21 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E28" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F28" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G28" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B29">
         <v>166610</v>
@@ -4827,21 +4827,21 @@
         <v>15</v>
       </c>
       <c r="D29" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E29" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F29" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G29" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B30">
         <v>166512</v>
@@ -4850,13 +4850,13 @@
         <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E30" t="s">
         <v>326</v>
       </c>
       <c r="F30" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B31">
         <v>166526</v>
@@ -4873,13 +4873,13 @@
         <v>17</v>
       </c>
       <c r="D31" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E31" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F31" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4887,7 +4887,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B32">
         <v>166530</v>
@@ -4896,13 +4896,13 @@
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E32" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F32" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B33">
         <v>166602</v>
@@ -4919,13 +4919,13 @@
         <v>19</v>
       </c>
       <c r="D33" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E33" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F33" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4933,7 +4933,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B34">
         <v>166605</v>
@@ -4942,13 +4942,13 @@
         <v>20</v>
       </c>
       <c r="D34" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E34" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F34" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B35">
         <v>166614</v>
@@ -4965,21 +4965,21 @@
         <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E35" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F35" t="s">
         <v>1181</v>
       </c>
-      <c r="F35" t="s">
-        <v>1182</v>
-      </c>
       <c r="G35" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B36">
         <v>166618</v>
@@ -4988,13 +4988,13 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E36" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="F36" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5002,7 +5002,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B37">
         <v>166620</v>
@@ -5011,21 +5011,21 @@
         <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E37" t="s">
         <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G37" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B38">
         <v>166621</v>
@@ -5034,21 +5034,21 @@
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E38" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="F38" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G38" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B39">
         <v>166632</v>
@@ -5057,21 +5057,21 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E39" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F39" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G39" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B40">
         <v>166649</v>
@@ -5080,13 +5080,13 @@
         <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E40" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F40" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5094,7 +5094,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B41">
         <v>166652</v>
@@ -5103,13 +5103,13 @@
         <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E41" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F41" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B42">
         <v>166672</v>
@@ -5126,21 +5126,21 @@
         <v>17</v>
       </c>
       <c r="D42" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E42" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F42" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G42" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B43">
         <v>166677</v>
@@ -5149,21 +5149,21 @@
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E43" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F43" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G43" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B44">
         <v>166680</v>
@@ -5172,21 +5172,21 @@
         <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E44" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F44" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G44" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B45">
         <v>166718</v>
@@ -5195,21 +5195,21 @@
         <v>20</v>
       </c>
       <c r="D45" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E45" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F45" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G45" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B46">
         <v>166720</v>
@@ -5218,7 +5218,7 @@
         <v>10</v>
       </c>
       <c r="D46" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E46" t="s">
         <v>311</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B47">
         <v>166742</v>
@@ -5241,13 +5241,13 @@
         <v>11</v>
       </c>
       <c r="D47" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E47" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F47" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5255,7 +5255,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B48">
         <v>166752</v>
@@ -5264,13 +5264,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E48" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F48" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5278,7 +5278,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B49">
         <v>166761</v>
@@ -5287,21 +5287,21 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E49" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F49" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G49" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B50">
         <v>166772</v>
@@ -5310,21 +5310,21 @@
         <v>14</v>
       </c>
       <c r="D50" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E50" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F50" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G50" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B51">
         <v>166786</v>
@@ -5333,13 +5333,13 @@
         <v>15</v>
       </c>
       <c r="D51" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E51" t="s">
         <v>318</v>
       </c>
       <c r="F51" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G51" t="s">
         <v>118</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B52">
         <v>166815</v>
@@ -5356,21 +5356,21 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E52" t="s">
         <v>306</v>
       </c>
       <c r="F52" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G52" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B53">
         <v>166816</v>
@@ -5379,13 +5379,13 @@
         <v>17</v>
       </c>
       <c r="D53" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E53" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F53" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5393,7 +5393,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B54">
         <v>166817</v>
@@ -5402,13 +5402,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E54" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F54" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5416,7 +5416,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B55">
         <v>167826</v>
@@ -5425,21 +5425,21 @@
         <v>19</v>
       </c>
       <c r="D55" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E55" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="F55" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G55" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B56">
         <v>167837</v>
@@ -5448,21 +5448,21 @@
         <v>20</v>
       </c>
       <c r="D56" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E56" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F56" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G56" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B57">
         <v>170164</v>
@@ -5471,13 +5471,13 @@
         <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E57" t="s">
         <v>341</v>
       </c>
       <c r="F57" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B58">
         <v>170518</v>
@@ -5494,16 +5494,16 @@
         <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E58" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="F58" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G58" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -5517,16 +5517,16 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E59" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F59" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G59" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -7178,10 +7178,10 @@
         <v>283</v>
       </c>
       <c r="E30" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F30" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G30" t="s">
         <v>400</v>
@@ -7612,13 +7612,13 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E49" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F49" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G49" t="s">
         <v>118</v>
@@ -7677,10 +7677,10 @@
         <v>430</v>
       </c>
       <c r="E2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -7700,10 +7700,10 @@
         <v>431</v>
       </c>
       <c r="E3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G3" t="s">
         <v>118</v>
@@ -7723,13 +7723,13 @@
         <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -7749,10 +7749,10 @@
         <v>303</v>
       </c>
       <c r="F5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -7769,13 +7769,13 @@
         <v>434</v>
       </c>
       <c r="E6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -7792,13 +7792,13 @@
         <v>435</v>
       </c>
       <c r="E7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -7838,10 +7838,10 @@
         <v>437</v>
       </c>
       <c r="E9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -7861,13 +7861,13 @@
         <v>438</v>
       </c>
       <c r="E10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F10" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G10" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -7887,10 +7887,10 @@
         <v>164</v>
       </c>
       <c r="F11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G11" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7910,7 +7910,7 @@
         <v>167</v>
       </c>
       <c r="F12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -7930,10 +7930,10 @@
         <v>441</v>
       </c>
       <c r="E13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G13" t="s">
         <v>114</v>
@@ -7953,10 +7953,10 @@
         <v>442</v>
       </c>
       <c r="E14" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F14" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -7979,7 +7979,7 @@
         <v>162</v>
       </c>
       <c r="F15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -7999,10 +7999,10 @@
         <v>444</v>
       </c>
       <c r="E16" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F16" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G16" t="s">
         <v>118</v>
@@ -8022,10 +8022,10 @@
         <v>445</v>
       </c>
       <c r="E17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8071,7 +8071,7 @@
         <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -8088,16 +8088,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>448</v>
+        <v>1189</v>
       </c>
       <c r="E20" t="s">
         <v>312</v>
       </c>
       <c r="F20" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G20" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -8111,16 +8111,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F21" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G21" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8134,16 +8134,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E22" t="s">
         <v>1176</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>1177</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>1178</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1179</v>
       </c>
     </row>
   </sheetData>
@@ -8187,7 +8187,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -8196,21 +8196,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E2" t="s">
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -8219,21 +8219,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E3" t="s">
         <v>74</v>
       </c>
       <c r="F3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -8242,13 +8242,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8265,21 +8265,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B6">
         <v>166645</v>
@@ -8288,21 +8288,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B7">
         <v>166643</v>
@@ -8311,21 +8311,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F7" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B8">
         <v>166685</v>
@@ -8334,21 +8334,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E8" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F8" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G8" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B9">
         <v>166810</v>
@@ -8357,21 +8357,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B10">
         <v>166740</v>
@@ -8380,7 +8380,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E10" t="s">
         <v>175</v>
@@ -8389,12 +8389,12 @@
         <v>192</v>
       </c>
       <c r="G10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B11">
         <v>166754</v>
@@ -8403,13 +8403,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E11" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F11" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -8417,7 +8417,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B12">
         <v>166775</v>
@@ -8426,13 +8426,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E12" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F12" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G12" t="s">
         <v>118</v>
@@ -8440,7 +8440,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B13">
         <v>166475</v>
@@ -8449,21 +8449,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E13" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F13" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G13" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B14">
         <v>166511</v>
@@ -8472,21 +8472,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="E14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F14" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G14" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B15">
         <v>166518</v>
@@ -8495,13 +8495,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E15" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F15" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -8509,7 +8509,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B16">
         <v>166524</v>
@@ -8518,21 +8518,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E16" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="F16" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="G16" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B17">
         <v>166525</v>
@@ -8541,13 +8541,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E17" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F17" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -8555,7 +8555,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B18">
         <v>166563</v>
@@ -8564,13 +8564,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G18" t="s">
         <v>114</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B19">
         <v>166608</v>
@@ -8587,21 +8587,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E19" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F19" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G19" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B20">
         <v>166659</v>
@@ -8610,21 +8610,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E20" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F20" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B21">
         <v>166664</v>
@@ -8633,13 +8633,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E21" t="s">
         <v>312</v>
       </c>
       <c r="F21" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -8647,7 +8647,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B22">
         <v>166727</v>
@@ -8656,21 +8656,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E22" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F22" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G22" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B23">
         <v>166738</v>
@@ -8679,13 +8679,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E23" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8741,13 +8741,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E2" t="s">
         <v>172</v>
       </c>
       <c r="F2" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -8755,7 +8755,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8764,21 +8764,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="G3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8787,13 +8787,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -8801,7 +8801,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8810,21 +8810,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E5" t="s">
         <v>172</v>
       </c>
       <c r="F5" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="G5" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8833,21 +8833,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="G6" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B7">
         <v>167882</v>
@@ -8856,13 +8856,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E7" t="s">
         <v>167</v>
       </c>
       <c r="F7" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -8870,7 +8870,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B8">
         <v>166696</v>
@@ -8879,21 +8879,21 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B9">
         <v>166700</v>
@@ -8902,21 +8902,21 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="G9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B10">
         <v>166792</v>
@@ -8925,13 +8925,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E10" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8987,13 +8987,13 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E2" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F2" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -9010,21 +9010,21 @@
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -9033,13 +9033,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -9047,7 +9047,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -9056,21 +9056,21 @@
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E5" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F5" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G5" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -9079,13 +9079,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E6" t="s">
         <v>172</v>
       </c>
       <c r="F6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
@@ -9093,7 +9093,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -9102,13 +9102,13 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G7" t="s">
         <v>118</v>
@@ -9116,7 +9116,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -9125,13 +9125,13 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G8" t="s">
         <v>118</v>
@@ -9139,7 +9139,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -9148,21 +9148,21 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -9171,13 +9171,13 @@
         <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E10" t="s">
         <v>167</v>
       </c>
       <c r="F10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -9185,7 +9185,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -9194,13 +9194,13 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E11" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G11" t="s">
         <v>118</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -9217,21 +9217,21 @@
         <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E12" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -9240,13 +9240,13 @@
         <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F13" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G13" t="s">
         <v>118</v>
@@ -9254,7 +9254,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -9263,13 +9263,13 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E14" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F14" t="s">
         <v>1184</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1185</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>
@@ -9277,7 +9277,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -9286,13 +9286,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E15" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -9300,7 +9300,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B16">
         <v>166716</v>
@@ -9309,21 +9309,21 @@
         <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E16" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F16" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G16" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B17">
         <v>166743</v>
@@ -9332,13 +9332,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E17" t="s">
         <v>167</v>
       </c>
       <c r="F17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G17" t="s">
         <v>118</v>
@@ -9346,7 +9346,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B18">
         <v>166814</v>
@@ -9355,13 +9355,13 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E18" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F18" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9369,7 +9369,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B19">
         <v>166497</v>
@@ -9378,13 +9378,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E19" t="s">
         <v>165</v>
       </c>
       <c r="F19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G19" t="s">
         <v>118</v>
@@ -9392,7 +9392,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B20">
         <v>166733</v>
@@ -9401,13 +9401,13 @@
         <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E20" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F20" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G20" t="s">
         <v>118</v>
@@ -9415,7 +9415,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B21">
         <v>166496</v>
@@ -9424,13 +9424,13 @@
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E21" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F21" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G21" t="s">
         <v>118</v>
@@ -9438,7 +9438,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9447,13 +9447,13 @@
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E22" t="s">
         <v>85</v>
       </c>
       <c r="F22" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G22" t="s">
         <v>118</v>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9470,13 +9470,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G23" t="s">
         <v>118</v>
@@ -9484,7 +9484,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9493,21 +9493,21 @@
         <v>11</v>
       </c>
       <c r="D24" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E24" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9516,21 +9516,21 @@
         <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E25" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F25" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G25" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9539,21 +9539,21 @@
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E26" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="F26" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G26" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9562,13 +9562,13 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E27" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F27" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -9576,7 +9576,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9585,21 +9585,21 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E28" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F28" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9608,13 +9608,13 @@
         <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E29" t="s">
         <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G29" t="s">
         <v>118</v>
@@ -9622,7 +9622,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9631,21 +9631,21 @@
         <v>17</v>
       </c>
       <c r="D30" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E30" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="F30" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G30" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9654,13 +9654,13 @@
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E31" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="F31" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -9668,7 +9668,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9677,13 +9677,13 @@
         <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E32" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F32" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G32" t="s">
         <v>403</v>
@@ -9691,7 +9691,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9700,13 +9700,13 @@
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E33" t="s">
         <v>167</v>
       </c>
       <c r="F33" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9723,13 +9723,13 @@
         <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E34" t="s">
         <v>167</v>
       </c>
       <c r="F34" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -9737,7 +9737,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9746,21 +9746,21 @@
         <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E35" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F35" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G35" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9769,13 +9769,13 @@
         <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E36" t="s">
         <v>318</v>
       </c>
       <c r="F36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9792,13 +9792,13 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="F37" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -9806,7 +9806,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9815,21 +9815,21 @@
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E38" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F38" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G38" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9838,21 +9838,21 @@
         <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E39" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="F39" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G39" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9861,13 +9861,13 @@
         <v>11</v>
       </c>
       <c r="D40" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -9875,7 +9875,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9884,7 +9884,7 @@
         <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9893,12 +9893,12 @@
         <v>182</v>
       </c>
       <c r="G41" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9907,16 +9907,16 @@
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E42" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G42" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -9983,7 +9983,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9992,13 +9992,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G2" t="s">
         <v>118</v>
@@ -10006,7 +10006,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B3">
         <v>166516</v>
@@ -10015,21 +10015,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B4">
         <v>166508</v>
@@ -10038,13 +10038,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G4" t="s">
         <v>118</v>
@@ -10052,7 +10052,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B5">
         <v>166540</v>
@@ -10061,21 +10061,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F5" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G5" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B6">
         <v>166541</v>
@@ -10084,21 +10084,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E6" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F6" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G6" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B7">
         <v>166561</v>
@@ -10107,21 +10107,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F7" t="s">
         <v>368</v>
       </c>
       <c r="G7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B8">
         <v>166619</v>
@@ -10130,21 +10130,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F8" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G8" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B9">
         <v>166623</v>
@@ -10153,13 +10153,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F9" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G9" t="s">
         <v>118</v>
@@ -10167,7 +10167,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B10">
         <v>166630</v>
@@ -10176,13 +10176,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E10" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F10" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G10" t="s">
         <v>118</v>
@@ -10190,7 +10190,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B11">
         <v>166673</v>
@@ -10199,21 +10199,21 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B12">
         <v>166675</v>
@@ -10222,21 +10222,21 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E12" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F12" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G12" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B13">
         <v>166710</v>
@@ -10245,7 +10245,7 @@
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E13" t="s">
         <v>311</v>
@@ -10259,7 +10259,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B14">
         <v>166711</v>
@@ -10268,21 +10268,21 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E14" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F14" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G14" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B15">
         <v>166755</v>
@@ -10291,13 +10291,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E15" t="s">
         <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G15" t="s">
         <v>118</v>
@@ -10305,7 +10305,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B16">
         <v>166757</v>
@@ -10314,21 +10314,21 @@
         <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E16" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F16" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G16" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B17">
         <v>167481</v>
@@ -10337,13 +10337,13 @@
         <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E17" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F17" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G17" t="s">
         <v>114</v>
@@ -10351,7 +10351,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B18">
         <v>167793</v>
@@ -10360,13 +10360,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E18" t="s">
         <v>162</v>
       </c>
       <c r="F18" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G18" t="s">
         <v>118</v>
@@ -10374,7 +10374,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B19">
         <v>168287</v>
@@ -10383,21 +10383,21 @@
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E19" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F19" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G19" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B20">
         <v>166567</v>
@@ -10406,21 +10406,21 @@
         <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E20" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F20" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G20" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B21">
         <v>166538</v>
@@ -10429,21 +10429,21 @@
         <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E21" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F21" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G21" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B22">
         <v>166678</v>
@@ -10452,21 +10452,21 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E22" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F22" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G22" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B23">
         <v>167682</v>
@@ -10475,21 +10475,21 @@
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E23" t="s">
         <v>340</v>
       </c>
       <c r="F23" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B24">
         <v>166529</v>
@@ -10498,21 +10498,21 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F24" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G24" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B25">
         <v>166472</v>
@@ -10521,21 +10521,21 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E25" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F25" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G25" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B26">
         <v>166571</v>
@@ -10544,21 +10544,21 @@
         <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E26" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F26" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G26" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B27">
         <v>166575</v>
@@ -10567,13 +10567,13 @@
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F27" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G27" t="s">
         <v>118</v>
@@ -10581,7 +10581,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B28">
         <v>166590</v>
@@ -10590,21 +10590,21 @@
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E28" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F28" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G28" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B29">
         <v>166598</v>
@@ -10613,21 +10613,21 @@
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E29" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F29" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G29" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B30">
         <v>166629</v>
@@ -10636,13 +10636,13 @@
         <v>2</v>
       </c>
       <c r="D30" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E30" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F30" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B31">
         <v>166650</v>
@@ -10659,21 +10659,21 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E31" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F31" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G31" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B32">
         <v>166657</v>
@@ -10682,13 +10682,13 @@
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E32" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F32" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G32" t="s">
         <v>114</v>
@@ -10696,7 +10696,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B33">
         <v>166687</v>
@@ -10705,21 +10705,21 @@
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E33" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F33" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G33" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B34">
         <v>166691</v>
@@ -10728,7 +10728,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E34" t="s">
         <v>336</v>
@@ -10742,7 +10742,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B35">
         <v>166708</v>
@@ -10751,13 +10751,13 @@
         <v>7</v>
       </c>
       <c r="D35" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E35" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F35" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G35" t="s">
         <v>118</v>
@@ -10765,7 +10765,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B36">
         <v>166719</v>
@@ -10774,21 +10774,21 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E36" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F36" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G36" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B37">
         <v>166744</v>
@@ -10797,13 +10797,13 @@
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E37" t="s">
         <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G37" t="s">
         <v>118</v>
@@ -10811,7 +10811,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B38">
         <v>166746</v>
@@ -10820,21 +10820,21 @@
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E38" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F38" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G38" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B39">
         <v>166753</v>
@@ -10843,21 +10843,21 @@
         <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E39" t="s">
         <v>312</v>
       </c>
       <c r="F39" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G39" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B40">
         <v>166779</v>
@@ -10866,13 +10866,13 @@
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E40" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F40" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -10880,7 +10880,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B41">
         <v>166818</v>
@@ -10889,21 +10889,21 @@
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E41" t="s">
         <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G41" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B42">
         <v>167482</v>
@@ -10912,13 +10912,13 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E42" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F42" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G42" t="s">
         <v>118</v>
@@ -10926,7 +10926,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B43">
         <v>167812</v>
@@ -10935,13 +10935,13 @@
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E43" t="s">
         <v>326</v>
       </c>
       <c r="F43" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G43" t="s">
         <v>118</v>
@@ -10949,7 +10949,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B44">
         <v>171332</v>
@@ -10958,16 +10958,16 @@
         <v>7</v>
       </c>
       <c r="D44" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E44" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F44" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G44" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06519633-1D65-684B-9144-B42DF361114C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7216461D-DE59-7B4C-B2FF-C1FF4EBEA6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="1190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="1188">
   <si>
     <t>Session ID</t>
   </si>
@@ -3346,9 +3346,6 @@
     <t>Wu</t>
   </si>
   <si>
-    <t>Cammarata</t>
-  </si>
-  <si>
     <t>Gurgone</t>
   </si>
   <si>
@@ -3470,9 +3467,6 @@
   </si>
   <si>
     <t>Radboud University</t>
-  </si>
-  <si>
-    <t>Dipartimento di Ingegneria dell'Informazione - Università di Pisa</t>
   </si>
   <si>
     <t>Pavia U. &amp; INFN</t>
@@ -4037,10 +4031,10 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -4051,10 +4045,10 @@
         <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -4065,10 +4059,10 @@
         <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -4079,10 +4073,10 @@
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -4093,10 +4087,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -4107,10 +4101,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -4121,10 +4115,10 @@
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -4135,10 +4129,10 @@
         <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -4149,10 +4143,10 @@
         <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
     </row>
   </sheetData>
@@ -4215,7 +4209,7 @@
         <v>1087</v>
       </c>
       <c r="G2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -4238,7 +4232,7 @@
         <v>1088</v>
       </c>
       <c r="G3" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -4261,7 +4255,7 @@
         <v>1089</v>
       </c>
       <c r="G4" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -4284,7 +4278,7 @@
         <v>1090</v>
       </c>
       <c r="G5" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -4330,7 +4324,7 @@
         <v>1092</v>
       </c>
       <c r="G7" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -4376,7 +4370,7 @@
         <v>1094</v>
       </c>
       <c r="G9" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -4445,7 +4439,7 @@
         <v>1096</v>
       </c>
       <c r="G12" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -4468,7 +4462,7 @@
         <v>1097</v>
       </c>
       <c r="G13" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -4560,7 +4554,7 @@
         <v>1099</v>
       </c>
       <c r="G17" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -4583,7 +4577,7 @@
         <v>1100</v>
       </c>
       <c r="G18" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -4652,7 +4646,7 @@
         <v>1103</v>
       </c>
       <c r="G21" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -4675,7 +4669,7 @@
         <v>1104</v>
       </c>
       <c r="G22" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -4692,13 +4686,13 @@
         <v>1023</v>
       </c>
       <c r="E23" t="s">
-        <v>326</v>
+        <v>1078</v>
       </c>
       <c r="F23" t="s">
-        <v>1105</v>
+        <v>1119</v>
       </c>
       <c r="G23" t="s">
-        <v>1147</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -4718,10 +4712,10 @@
         <v>318</v>
       </c>
       <c r="F24" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G24" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -4764,10 +4758,10 @@
         <v>1071</v>
       </c>
       <c r="F26" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G26" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -4810,10 +4804,10 @@
         <v>601</v>
       </c>
       <c r="F28" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G28" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -4833,10 +4827,10 @@
         <v>1072</v>
       </c>
       <c r="F29" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G29" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -4856,7 +4850,7 @@
         <v>326</v>
       </c>
       <c r="F30" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G30" t="s">
         <v>118</v>
@@ -4879,7 +4873,7 @@
         <v>712</v>
       </c>
       <c r="F31" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G31" t="s">
         <v>118</v>
@@ -4902,7 +4896,7 @@
         <v>1073</v>
       </c>
       <c r="F32" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G32" t="s">
         <v>118</v>
@@ -4925,7 +4919,7 @@
         <v>1074</v>
       </c>
       <c r="F33" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G33" t="s">
         <v>118</v>
@@ -4948,7 +4942,7 @@
         <v>719</v>
       </c>
       <c r="F34" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G34" t="s">
         <v>118</v>
@@ -4968,13 +4962,13 @@
         <v>1035</v>
       </c>
       <c r="E35" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="F35" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="G35" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -4994,7 +4988,7 @@
         <v>1073</v>
       </c>
       <c r="F36" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G36" t="s">
         <v>118</v>
@@ -5017,10 +5011,10 @@
         <v>172</v>
       </c>
       <c r="F37" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G37" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -5040,10 +5034,10 @@
         <v>1075</v>
       </c>
       <c r="F38" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G38" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
@@ -5063,10 +5057,10 @@
         <v>1076</v>
       </c>
       <c r="F39" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G39" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -5086,7 +5080,7 @@
         <v>1077</v>
       </c>
       <c r="F40" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G40" t="s">
         <v>118</v>
@@ -5109,7 +5103,7 @@
         <v>1078</v>
       </c>
       <c r="F41" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G41" t="s">
         <v>118</v>
@@ -5132,10 +5126,10 @@
         <v>1079</v>
       </c>
       <c r="F42" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G42" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -5155,10 +5149,10 @@
         <v>712</v>
       </c>
       <c r="F43" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G43" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
@@ -5178,7 +5172,7 @@
         <v>1080</v>
       </c>
       <c r="F44" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G44" t="s">
         <v>480</v>
@@ -5201,7 +5195,7 @@
         <v>1081</v>
       </c>
       <c r="F45" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G45" t="s">
         <v>940</v>
@@ -5247,7 +5241,7 @@
         <v>708</v>
       </c>
       <c r="F47" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G47" t="s">
         <v>118</v>
@@ -5270,7 +5264,7 @@
         <v>706</v>
       </c>
       <c r="F48" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G48" t="s">
         <v>118</v>
@@ -5293,10 +5287,10 @@
         <v>1082</v>
       </c>
       <c r="F49" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G49" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
@@ -5316,10 +5310,10 @@
         <v>1083</v>
       </c>
       <c r="F50" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G50" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -5362,10 +5356,10 @@
         <v>306</v>
       </c>
       <c r="F52" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G52" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
@@ -5385,7 +5379,7 @@
         <v>1084</v>
       </c>
       <c r="F53" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G53" t="s">
         <v>118</v>
@@ -5408,7 +5402,7 @@
         <v>881</v>
       </c>
       <c r="F54" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G54" t="s">
         <v>118</v>
@@ -5431,10 +5425,10 @@
         <v>1085</v>
       </c>
       <c r="F55" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G55" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
@@ -5454,10 +5448,10 @@
         <v>1086</v>
       </c>
       <c r="F56" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G56" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
@@ -5477,7 +5471,7 @@
         <v>341</v>
       </c>
       <c r="F57" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G57" t="s">
         <v>118</v>
@@ -5497,13 +5491,13 @@
         <v>1058</v>
       </c>
       <c r="E58" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="F58" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="G58" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
@@ -5517,7 +5511,7 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="E59" t="s">
         <v>543</v>
@@ -7181,7 +7175,7 @@
         <v>877</v>
       </c>
       <c r="F30" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G30" t="s">
         <v>400</v>
@@ -7612,7 +7606,7 @@
         <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E49" t="s">
         <v>458</v>
@@ -8088,7 +8082,7 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E20" t="s">
         <v>312</v>
@@ -8120,7 +8114,7 @@
         <v>478</v>
       </c>
       <c r="G21" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -8134,16 +8128,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F22" t="s">
         <v>1175</v>
       </c>
-      <c r="E22" t="s">
+      <c r="G22" t="s">
         <v>1176</v>
-      </c>
-      <c r="F22" t="s">
-        <v>1177</v>
-      </c>
-      <c r="G22" t="s">
-        <v>1178</v>
       </c>
     </row>
   </sheetData>
@@ -8619,7 +8613,7 @@
         <v>564</v>
       </c>
       <c r="G20" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -9266,10 +9260,10 @@
         <v>673</v>
       </c>
       <c r="E14" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="F14" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G14" t="s">
         <v>118</v>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10507"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7469A9-31D9-3F4B-BE33-1CA2DDCFE625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -18,7 +24,7 @@
     <sheet name="26959" sheetId="9" r:id="rId9"/>
     <sheet name="26960" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -238,9 +244,6 @@
     <t>Status of the CMS silicon strip detector</t>
   </si>
   <si>
-    <t>BRAND – A DETECTION SYSTEM FOR BETA DECAY CORRELATION MEASUREMENT</t>
-  </si>
-  <si>
     <t>Toward AI-Assisted Design Of Experiments</t>
   </si>
   <si>
@@ -406,9 +409,6 @@
     <t>KIT</t>
   </si>
   <si>
-    <t>Institute of Nuclear Physics, Polish Academy of Science.</t>
-  </si>
-  <si>
     <t>University of California, Los Angeles</t>
   </si>
   <si>
@@ -3482,13 +3482,19 @@
   </si>
   <si>
     <t>Jagiellonian University</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRAND - a detection system for beta decay correlation measurement </t>
+  </si>
+  <si>
+    <t>Institute of Nuclear Physics, Polish Academy of Science</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3551,6 +3557,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -3597,7 +3611,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3629,9 +3643,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3663,6 +3695,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3838,16 +3888,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="100.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3861,7 +3911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3875,7 +3925,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3889,7 +3939,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3903,7 +3953,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -3917,7 +3967,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3931,7 +3981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3945,7 +3995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -3959,7 +4009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -3973,7 +4023,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3993,17 +4043,17 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -4026,9 +4076,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4037,21 +4087,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E2" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="F2" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G2" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4060,21 +4110,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="E3" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="F3" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G3" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4083,21 +4133,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="E4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="F4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G4" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4106,21 +4156,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E5" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="F5" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G5" t="s">
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4129,21 +4179,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E6" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F6" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4152,21 +4202,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E7" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F7" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="G7" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4175,21 +4225,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4198,21 +4248,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="G9" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4221,21 +4271,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E10" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="F10" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4244,21 +4294,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E11" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="F11" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="G11" t="s">
-        <v>1132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4267,21 +4317,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E12" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="F12" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="G12" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4290,21 +4340,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="G13" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4313,21 +4363,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E14" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="F14" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4336,21 +4386,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G15" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4359,21 +4409,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E16" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F16" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="G16" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4382,21 +4432,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E17" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F17" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G17" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4405,21 +4455,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E18" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="F18" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4428,21 +4478,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4451,21 +4501,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E20" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="F20" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="G20" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4474,21 +4524,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E21" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="F21" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="G21" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4497,21 +4547,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F22" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4520,21 +4570,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="G23" t="s">
-        <v>1138</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4543,21 +4593,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="E24" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4566,21 +4616,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G25" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4589,21 +4639,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="E26" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F26" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G26" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4612,21 +4662,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E27" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="F27" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G27" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4635,21 +4685,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E28" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F28" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4658,21 +4708,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E29" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F29" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4681,21 +4731,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E30" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F30" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4704,21 +4754,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E31" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="F31" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4727,21 +4777,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E32" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F32" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="G32" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4750,21 +4800,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E33" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="F33" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="G33" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4773,21 +4823,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E34" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F34" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4796,21 +4846,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G35" t="s">
-        <v>1142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4819,21 +4869,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="E36" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="F36" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G36" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4842,21 +4892,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E37" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="F37" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G37" t="s">
-        <v>1144</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4865,21 +4915,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E38" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="F38" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4888,21 +4938,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E39" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="F39" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="G39" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4911,21 +4961,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E40" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F40" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="G40" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4934,21 +4984,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="E41" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F41" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="G41" t="s">
-        <v>1146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -4957,21 +5007,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E42" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="F42" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="G42" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -4980,21 +5030,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="E43" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F43" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="G43" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5003,21 +5053,21 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="E44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G44" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5026,21 +5076,21 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E45" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F45" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5049,21 +5099,21 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="E46" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F46" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G46" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5072,21 +5122,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="E47" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="F47" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G47" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5095,21 +5145,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="E48" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F48" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="G48" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5118,21 +5168,21 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="E49" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G49" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5141,21 +5191,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="E50" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G50" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5164,21 +5214,21 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E51" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="F51" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="G51" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5187,21 +5237,21 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="E52" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F52" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="G52" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5210,21 +5260,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="E53" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="F53" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="G53" t="s">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5233,21 +5283,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="E54" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="F54" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="G54" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5256,21 +5306,21 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="E55" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="G55" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5279,21 +5329,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="E56" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F56" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="G56" t="s">
-        <v>1152</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5302,21 +5352,21 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="E57" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F57" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G57" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5325,18 +5375,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="E58" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F58" t="s">
-        <v>1117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5345,13 +5395,13 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="E59" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F59" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -5360,17 +5410,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -5393,7 +5443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -5407,16 +5457,16 @@
         <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -5430,16 +5480,16 @@
         <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -5453,16 +5503,16 @@
         <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -5476,16 +5526,16 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -5499,16 +5549,16 @@
         <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -5522,16 +5572,16 @@
         <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -5545,16 +5595,16 @@
         <v>68</v>
       </c>
       <c r="E8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G8" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -5568,16 +5618,16 @@
         <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -5591,16 +5641,16 @@
         <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -5611,19 +5661,19 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>1151</v>
       </c>
       <c r="E11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>53</v>
       </c>
@@ -5634,19 +5684,19 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -5657,19 +5707,19 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>55</v>
       </c>
@@ -5680,19 +5730,19 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -5703,19 +5753,19 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>57</v>
       </c>
@@ -5726,19 +5776,19 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>58</v>
       </c>
@@ -5749,19 +5799,19 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -5772,19 +5822,19 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>60</v>
       </c>
@@ -5795,19 +5845,19 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>61</v>
       </c>
@@ -5818,16 +5868,16 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G20" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -5836,17 +5886,17 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -5869,9 +5919,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B2">
         <v>166492</v>
@@ -5880,21 +5930,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B3">
         <v>166625</v>
@@ -5903,21 +5953,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B4">
         <v>166635</v>
@@ -5926,21 +5976,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5">
         <v>166698</v>
@@ -5949,21 +5999,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B6">
         <v>167674</v>
@@ -5972,21 +6022,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G6" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B7">
         <v>166470</v>
@@ -5995,21 +6045,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B8">
         <v>166666</v>
@@ -6018,21 +6068,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B9">
         <v>166501</v>
@@ -6041,21 +6091,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G9" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B10">
         <v>166533</v>
@@ -6064,21 +6114,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G10" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B11">
         <v>166534</v>
@@ -6087,21 +6137,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B12">
         <v>166683</v>
@@ -6110,21 +6160,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B13">
         <v>166735</v>
@@ -6133,21 +6183,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G13" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B14">
         <v>166741</v>
@@ -6156,21 +6206,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15">
         <v>166793</v>
@@ -6179,21 +6229,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16">
         <v>166822</v>
@@ -6202,21 +6252,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B17">
         <v>167676</v>
@@ -6225,16 +6275,16 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E17" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6243,17 +6293,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -6276,9 +6326,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B2">
         <v>166500</v>
@@ -6287,21 +6337,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G2" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B3">
         <v>166535</v>
@@ -6310,21 +6360,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B4">
         <v>166543</v>
@@ -6333,21 +6383,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B5">
         <v>166549</v>
@@ -6356,21 +6406,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B6">
         <v>166616</v>
@@ -6379,21 +6429,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B7">
         <v>166693</v>
@@ -6402,21 +6452,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G7" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B8">
         <v>166706</v>
@@ -6425,21 +6475,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G8" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B9">
         <v>166721</v>
@@ -6448,21 +6498,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F9" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G9" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B10">
         <v>166724</v>
@@ -6471,21 +6521,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11">
         <v>166768</v>
@@ -6494,21 +6544,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B12">
         <v>166764</v>
@@ -6517,21 +6567,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G12" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B13">
         <v>166805</v>
@@ -6540,21 +6590,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E13" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F13" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G13" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B14">
         <v>167802</v>
@@ -6563,21 +6613,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F14" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G14" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B15">
         <v>167855</v>
@@ -6586,21 +6636,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E15" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F15" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B16">
         <v>166537</v>
@@ -6609,21 +6659,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F16" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B17">
         <v>166548</v>
@@ -6632,21 +6682,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E17" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G17" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B18">
         <v>166588</v>
@@ -6655,21 +6705,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F18" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G18" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19">
         <v>166642</v>
@@ -6678,21 +6728,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E19" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B20">
         <v>166665</v>
@@ -6701,21 +6751,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B21">
         <v>166688</v>
@@ -6724,21 +6774,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B22">
         <v>166722</v>
@@ -6747,21 +6797,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E22" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G22" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B23">
         <v>166769</v>
@@ -6770,21 +6820,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E23" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F23" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B24">
         <v>166471</v>
@@ -6793,21 +6843,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E24" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F24" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G24" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B25">
         <v>166465</v>
@@ -6816,21 +6866,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G25" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B26">
         <v>166491</v>
@@ -6839,21 +6889,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F26" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B27">
         <v>166547</v>
@@ -6862,21 +6912,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E27" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F27" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G27" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B28">
         <v>166554</v>
@@ -6885,21 +6935,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F28" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G28" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B29">
         <v>166787</v>
@@ -6908,21 +6958,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E29" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F29" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G29" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B30">
         <v>166536</v>
@@ -6931,21 +6981,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E30" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F30" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B31">
         <v>166464</v>
@@ -6954,21 +7004,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E31" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F31" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G31" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B32">
         <v>166555</v>
@@ -6977,21 +7027,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G32" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B33">
         <v>166562</v>
@@ -7000,21 +7050,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E33" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F33" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G33" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B34">
         <v>166586</v>
@@ -7023,21 +7073,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E34" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F34" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B35">
         <v>166617</v>
@@ -7046,21 +7096,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F35" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B36">
         <v>166634</v>
@@ -7069,21 +7119,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B37">
         <v>166639</v>
@@ -7092,21 +7142,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E37" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F37" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B38">
         <v>166647</v>
@@ -7115,21 +7165,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E38" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G38" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B39">
         <v>166670</v>
@@ -7138,21 +7188,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F39" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G39" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B40">
         <v>166686</v>
@@ -7161,21 +7211,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E40" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F40" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G40" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B41">
         <v>166689</v>
@@ -7184,21 +7234,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E41" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F41" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G41" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B42">
         <v>166690</v>
@@ -7207,21 +7257,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E42" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F42" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G42" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B43">
         <v>166726</v>
@@ -7230,21 +7280,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E43" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F43" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G43" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B44">
         <v>166812</v>
@@ -7253,21 +7303,21 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E44" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F44" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B45">
         <v>167673</v>
@@ -7276,21 +7326,21 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E45" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F45" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B46">
         <v>171868</v>
@@ -7299,21 +7349,21 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E46" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F46" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G46" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B47">
         <v>172076</v>
@@ -7322,16 +7372,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E47" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F47" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G47" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -7340,17 +7390,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -7373,9 +7423,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B2">
         <v>166631</v>
@@ -7384,21 +7434,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B3">
         <v>166646</v>
@@ -7407,21 +7457,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B4">
         <v>166660</v>
@@ -7430,21 +7480,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G4" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B5">
         <v>166661</v>
@@ -7453,21 +7503,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B6">
         <v>166699</v>
@@ -7476,21 +7526,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G6" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B7">
         <v>166701</v>
@@ -7499,21 +7549,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B8">
         <v>166747</v>
@@ -7522,21 +7572,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F8" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B9">
         <v>166487</v>
@@ -7545,21 +7595,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F9" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G9" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B10">
         <v>166560</v>
@@ -7568,21 +7618,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G10" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B11">
         <v>166597</v>
@@ -7591,21 +7641,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E11" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B12">
         <v>166604</v>
@@ -7614,21 +7664,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F12" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B13">
         <v>166607</v>
@@ -7637,21 +7687,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F13" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B14">
         <v>166612</v>
@@ -7660,21 +7710,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B15">
         <v>166627</v>
@@ -7683,21 +7733,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E15" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F15" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B16">
         <v>166729</v>
@@ -7706,21 +7756,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E16" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F16" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B17">
         <v>166750</v>
@@ -7729,21 +7779,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E17" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F17" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B18">
         <v>166796</v>
@@ -7752,21 +7802,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E18" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B19">
         <v>171014</v>
@@ -7775,21 +7825,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E19" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F19" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G19" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B20">
         <v>171701</v>
@@ -7798,21 +7848,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E20" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="G20" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B21">
         <v>167817</v>
@@ -7821,16 +7871,16 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E21" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F21" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="G21" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -7839,17 +7889,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -7872,9 +7922,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -7883,21 +7933,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="G2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -7906,21 +7956,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="G3" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -7929,21 +7979,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -7952,21 +8002,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="G5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B6">
         <v>166643</v>
@@ -7975,21 +8025,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="G6" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B7">
         <v>166685</v>
@@ -7998,21 +8048,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="G7" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B8">
         <v>166740</v>
@@ -8021,21 +8071,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G8" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B9">
         <v>166754</v>
@@ -8044,21 +8094,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E9" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F9" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B10">
         <v>166475</v>
@@ -8067,21 +8117,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E10" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F10" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="G10" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B11">
         <v>166511</v>
@@ -8090,21 +8140,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E11" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F11" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B12">
         <v>166518</v>
@@ -8113,21 +8163,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E12" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F12" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B13">
         <v>166524</v>
@@ -8136,21 +8186,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F13" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="G13" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B14">
         <v>166525</v>
@@ -8159,21 +8209,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F14" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B15">
         <v>166563</v>
@@ -8182,21 +8232,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E15" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F15" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B16">
         <v>166608</v>
@@ -8205,21 +8255,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E16" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G16" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B17">
         <v>166659</v>
@@ -8228,21 +8278,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E17" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F17" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G17" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B18">
         <v>166664</v>
@@ -8251,21 +8301,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F18" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B19">
         <v>166727</v>
@@ -8274,21 +8324,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E19" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F19" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G19" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B20">
         <v>166738</v>
@@ -8297,16 +8347,16 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E20" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F20" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -8315,17 +8365,17 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -8348,9 +8398,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8359,21 +8409,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8382,21 +8432,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E3" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8405,21 +8455,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8428,21 +8478,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G5" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8451,21 +8501,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G6" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B7">
         <v>167882</v>
@@ -8474,21 +8524,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B8">
         <v>166696</v>
@@ -8497,21 +8547,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E8" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F8" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G8" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B9">
         <v>166700</v>
@@ -8520,21 +8570,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E9" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F9" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G9" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B10">
         <v>166792</v>
@@ -8543,16 +8593,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E10" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F10" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -8561,17 +8611,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G44"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -8594,9 +8644,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8605,21 +8655,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -8628,21 +8678,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G3" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -8651,21 +8701,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -8674,21 +8724,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F5" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="G5" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -8697,21 +8747,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -8720,21 +8770,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E7" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F7" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -8743,21 +8793,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E8" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -8766,21 +8816,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F9" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G9" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -8789,21 +8839,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F10" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -8812,21 +8862,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E11" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F11" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -8835,21 +8885,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E12" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F12" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G12" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -8858,21 +8908,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F13" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -8881,21 +8931,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E14" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F14" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -8904,21 +8954,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E15" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F15" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B16">
         <v>166743</v>
@@ -8927,21 +8977,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F16" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B17">
         <v>166814</v>
@@ -8950,21 +9000,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E17" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F17" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B18">
         <v>166497</v>
@@ -8973,21 +9023,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B19">
         <v>166733</v>
@@ -8996,21 +9046,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E19" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F19" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B20">
         <v>166496</v>
@@ -9019,21 +9069,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E20" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F20" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B21">
         <v>166725</v>
@@ -9042,21 +9092,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E21" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F21" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G21" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9065,21 +9115,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E22" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9088,21 +9138,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9111,21 +9161,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E24" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F24" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G24" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9134,21 +9184,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E25" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F25" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G25" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9157,21 +9207,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E26" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F26" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G26" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9180,21 +9230,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E27" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F27" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9203,21 +9253,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E28" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F28" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G28" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9226,21 +9276,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E29" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9249,21 +9299,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E30" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F30" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G30" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9272,21 +9322,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E31" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F31" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9295,21 +9345,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E32" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F32" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G32" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9318,21 +9368,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F33" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9341,21 +9391,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F34" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9364,21 +9414,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E35" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F35" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G35" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9387,21 +9437,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E36" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9410,21 +9460,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E37" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F37" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9433,21 +9483,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E38" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F38" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9456,21 +9506,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E39" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F39" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G39" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9479,21 +9529,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9502,21 +9552,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9525,21 +9575,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E42" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F42" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G42" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B43">
         <v>172067</v>
@@ -9548,21 +9598,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E43" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F43" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G43" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B44">
         <v>172078</v>
@@ -9571,16 +9621,16 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G44" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>
@@ -9589,17 +9639,17 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" customWidth="1"/>
-    <col min="5" max="6" width="20.7109375" customWidth="1"/>
-    <col min="7" max="7" width="60.7109375" customWidth="1"/>
+    <col min="1" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="100.6640625" customWidth="1"/>
+    <col min="5" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -9622,9 +9672,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9633,21 +9683,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E2" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="F2" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9656,21 +9706,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9679,21 +9729,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E4" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G4" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9702,21 +9752,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E5" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="F5" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G5" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9725,21 +9775,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E6" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="F6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9748,21 +9798,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E7" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="F7" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G7" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9771,21 +9821,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="E8" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F8" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9794,21 +9844,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E9" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="F9" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9817,21 +9867,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E10" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F10" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="G10" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9840,21 +9890,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E11" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="F11" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="G11" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9863,21 +9913,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E12" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="F12" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G12" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9886,21 +9936,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9909,21 +9959,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="E14" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F14" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G14" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B15">
         <v>167481</v>
@@ -9932,21 +9982,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E15" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="F15" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B16">
         <v>168287</v>
@@ -9955,21 +10005,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="E16" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="F16" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G16" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="B17">
         <v>171990</v>
@@ -9978,21 +10028,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E17" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F17" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G17" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B18">
         <v>166567</v>
@@ -10001,21 +10051,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E18" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F18" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G18" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B19">
         <v>166538</v>
@@ -10024,21 +10074,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E19" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="F19" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G19" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B20">
         <v>166678</v>
@@ -10047,21 +10097,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E20" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="F20" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G20" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="B21">
         <v>167682</v>
@@ -10070,21 +10120,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E21" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F21" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G21" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B22">
         <v>166529</v>
@@ -10093,21 +10143,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E22" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="F22" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G22" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="B23">
         <v>166472</v>
@@ -10116,21 +10166,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E23" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F23" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G23" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B24">
         <v>166571</v>
@@ -10139,21 +10189,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E24" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="F24" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="G24" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B25">
         <v>166575</v>
@@ -10162,21 +10212,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E25" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F25" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B26">
         <v>166590</v>
@@ -10185,21 +10235,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E26" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="F26" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G26" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B27">
         <v>166598</v>
@@ -10208,21 +10258,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E27" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F27" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G27" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B28">
         <v>166629</v>
@@ -10231,21 +10281,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E28" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F28" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B29">
         <v>166650</v>
@@ -10254,21 +10304,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E29" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F29" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G29" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B30">
         <v>166657</v>
@@ -10277,21 +10327,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E30" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G30" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B31">
         <v>166687</v>
@@ -10300,21 +10350,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E31" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="F31" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="G31" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B32">
         <v>166691</v>
@@ -10323,21 +10373,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E32" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F32" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G32" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B33">
         <v>166708</v>
@@ -10346,21 +10396,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E33" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="F33" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B34">
         <v>166719</v>
@@ -10369,21 +10419,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="F34" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="G34" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B35">
         <v>166744</v>
@@ -10392,21 +10442,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E35" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F35" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B36">
         <v>166746</v>
@@ -10415,21 +10465,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E36" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="F36" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G36" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B37">
         <v>166753</v>
@@ -10438,21 +10488,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F37" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G37" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B38">
         <v>166779</v>
@@ -10461,21 +10511,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E38" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F38" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B39">
         <v>166818</v>
@@ -10484,21 +10534,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G39" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B40">
         <v>167482</v>
@@ -10507,21 +10557,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E40" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="F40" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B41">
         <v>167812</v>
@@ -10530,21 +10580,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E41" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F41" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G41" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B42">
         <v>171332</v>
@@ -10553,16 +10603,16 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="E42" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="F42" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G42" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7469A9-31D9-3F4B-BE33-1CA2DDCFE625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E3967C-3D38-544E-B557-D2DED63479EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -1831,9 +1831,6 @@
     <t>SRON Leiden</t>
   </si>
   <si>
-    <t>GE</t>
-  </si>
-  <si>
     <t>SRON - Netherlands Institute for Space Research</t>
   </si>
   <si>
@@ -3488,6 +3485,9 @@
   </si>
   <si>
     <t>Institute of Nuclear Physics, Polish Academy of Science</t>
+  </si>
+  <si>
+    <t>University and INFN Genova</t>
   </si>
 </sst>
 </file>
@@ -4078,7 +4078,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4087,21 +4087,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4110,21 +4110,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E3" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F3" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G3" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4133,21 +4133,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G4" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4156,21 +4156,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E5" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F5" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G5" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4179,13 +4179,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E6" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F6" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4202,21 +4202,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F7" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G7" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4225,13 +4225,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E8" t="s">
         <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -4239,7 +4239,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4248,21 +4248,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G9" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4271,13 +4271,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E10" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F10" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4294,21 +4294,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E11" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F11" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G11" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4317,21 +4317,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E12" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F12" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G12" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4340,21 +4340,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G13" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4363,13 +4363,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E14" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F14" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4386,13 +4386,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E15" t="s">
         <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G15" t="s">
         <v>554</v>
@@ -4400,7 +4400,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4409,21 +4409,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E16" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F16" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G16" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4432,21 +4432,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E17" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G17" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4455,13 +4455,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E18" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="F18" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -4469,7 +4469,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4478,13 +4478,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E19" t="s">
         <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4501,21 +4501,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E20" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F20" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G20" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4524,21 +4524,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E21" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F21" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G21" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4547,13 +4547,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E22" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F22" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4570,21 +4570,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E23" t="s">
         <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G23" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4593,13 +4593,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E24" t="s">
         <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4616,21 +4616,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G25" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4639,21 +4639,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E26" t="s">
         <v>585</v>
       </c>
       <c r="F26" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G26" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4662,21 +4662,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E27" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F27" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G27" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4685,13 +4685,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E28" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F28" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4708,13 +4708,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E29" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F29" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4731,13 +4731,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E30" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F30" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G30" t="s">
         <v>121</v>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4754,13 +4754,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E31" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F31" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4777,13 +4777,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E32" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F32" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4800,21 +4800,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E33" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F33" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G33" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4823,13 +4823,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E34" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F34" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4846,21 +4846,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G35" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4869,21 +4869,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E36" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F36" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G36" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4892,21 +4892,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E37" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F37" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G37" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4915,13 +4915,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E38" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="F38" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4938,13 +4938,13 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E39" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="F39" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4961,21 +4961,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E40" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F40" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G40" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4984,21 +4984,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E41" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F41" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G41" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -5007,13 +5007,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E42" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="F42" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G42" t="s">
         <v>475</v>
@@ -5021,7 +5021,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5030,21 +5030,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="E43" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F43" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G43" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5053,21 +5053,21 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5076,13 +5076,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E45" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F45" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G45" t="s">
         <v>121</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5099,13 +5099,13 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E46" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F46" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G46" t="s">
         <v>121</v>
@@ -5113,7 +5113,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5122,21 +5122,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E47" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="F47" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G47" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5145,21 +5145,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="E48" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F48" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G48" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5168,13 +5168,13 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E49" t="s">
         <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G49" t="s">
         <v>121</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5191,21 +5191,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E50" t="s">
         <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G50" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5214,13 +5214,13 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="E51" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F51" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5237,13 +5237,13 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E52" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F52" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G52" t="s">
         <v>121</v>
@@ -5251,7 +5251,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5260,21 +5260,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E53" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F53" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G53" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5283,21 +5283,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E54" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F54" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G54" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5306,13 +5306,13 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E55" t="s">
         <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5329,21 +5329,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E56" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F56" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G56" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5352,7 +5352,7 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E57" t="s">
         <v>531</v>
@@ -5366,7 +5366,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5375,18 +5375,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E58" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F58" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5395,13 +5395,13 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E59" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F59" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
   </sheetData>
@@ -5661,7 +5661,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5670,7 +5670,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -8556,7 +8556,7 @@
         <v>595</v>
       </c>
       <c r="G8" t="s">
-        <v>600</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -8579,7 +8579,7 @@
         <v>596</v>
       </c>
       <c r="G9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -8646,7 +8646,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8655,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E2" t="s">
         <v>588</v>
@@ -8669,7 +8669,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -8678,21 +8678,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -8701,13 +8701,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -8715,7 +8715,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -8724,21 +8724,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -8747,13 +8747,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E6" t="s">
         <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -8761,7 +8761,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -8770,13 +8770,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E7" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G7" t="s">
         <v>121</v>
@@ -8784,7 +8784,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -8793,13 +8793,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E8" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -8807,7 +8807,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -8816,13 +8816,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G9" t="s">
         <v>477</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -8839,7 +8839,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E10" t="s">
         <v>298</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -8862,13 +8862,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G11" t="s">
         <v>121</v>
@@ -8876,7 +8876,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -8885,21 +8885,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E12" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -8908,13 +8908,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E13" t="s">
         <v>450</v>
       </c>
       <c r="F13" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -8922,7 +8922,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -8931,13 +8931,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E14" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F14" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -8945,7 +8945,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -8954,13 +8954,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E15" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="F15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G15" t="s">
         <v>121</v>
@@ -8968,7 +8968,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B16">
         <v>166743</v>
@@ -8977,13 +8977,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E16" t="s">
         <v>298</v>
       </c>
       <c r="F16" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -8991,7 +8991,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B17">
         <v>166814</v>
@@ -9000,13 +9000,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E17" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F17" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G17" t="s">
         <v>125</v>
@@ -9014,7 +9014,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B18">
         <v>166497</v>
@@ -9023,13 +9023,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E18" t="s">
         <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9037,7 +9037,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B19">
         <v>166733</v>
@@ -9046,13 +9046,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E19" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="F19" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -9060,7 +9060,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B20">
         <v>166496</v>
@@ -9069,13 +9069,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E20" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="F20" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G20" t="s">
         <v>121</v>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B21">
         <v>166725</v>
@@ -9092,13 +9092,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E21" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F21" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G21" t="s">
         <v>121</v>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9115,13 +9115,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E22" t="s">
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -9129,7 +9129,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9138,13 +9138,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G23" t="s">
         <v>121</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9161,21 +9161,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E24" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F24" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G24" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9184,21 +9184,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E25" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="F25" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9207,21 +9207,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E26" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="F26" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G26" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9230,13 +9230,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E27" t="s">
         <v>530</v>
       </c>
       <c r="F27" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G27" t="s">
         <v>121</v>
@@ -9244,7 +9244,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9253,21 +9253,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E28" t="s">
         <v>532</v>
       </c>
       <c r="F28" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G28" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9276,13 +9276,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E29" t="s">
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -9290,7 +9290,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9299,21 +9299,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E30" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F30" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G30" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9322,13 +9322,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E31" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="F31" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -9336,7 +9336,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9345,13 +9345,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E32" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F32" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G32" t="s">
         <v>395</v>
@@ -9359,7 +9359,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9368,13 +9368,13 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E33" t="s">
         <v>298</v>
       </c>
       <c r="F33" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G33" t="s">
         <v>121</v>
@@ -9382,7 +9382,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9391,13 +9391,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E34" t="s">
         <v>298</v>
       </c>
       <c r="F34" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -9405,7 +9405,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9414,21 +9414,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E35" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F35" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9437,13 +9437,13 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E36" t="s">
         <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G36" t="s">
         <v>121</v>
@@ -9451,7 +9451,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9460,13 +9460,13 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E37" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F37" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G37" t="s">
         <v>121</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9483,13 +9483,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F38" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9506,21 +9506,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E39" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F39" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G39" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9529,13 +9529,13 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9552,7 +9552,7 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9561,12 +9561,12 @@
         <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B42">
         <v>167825</v>
@@ -9575,21 +9575,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E42" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="F42" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G42" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B43">
         <v>172067</v>
@@ -9598,21 +9598,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E43" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="F43" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G43" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B44">
         <v>172078</v>
@@ -9621,16 +9621,16 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="F44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
   </sheetData>
@@ -9674,7 +9674,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9683,13 +9683,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -9697,7 +9697,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9706,13 +9706,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E3" t="s">
         <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -9720,7 +9720,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9729,21 +9729,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9752,21 +9752,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E5" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F5" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9775,21 +9775,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E6" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F6" t="s">
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9798,21 +9798,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E7" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F7" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9821,13 +9821,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E8" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F8" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9844,13 +9844,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -9858,7 +9858,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9867,21 +9867,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E10" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F10" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G10" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9890,21 +9890,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9913,21 +9913,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F12" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G12" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9936,13 +9936,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E13" t="s">
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9959,21 +9959,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E14" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F14" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G14" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B15">
         <v>167481</v>
@@ -9982,13 +9982,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E15" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F15" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -9996,7 +9996,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B16">
         <v>168287</v>
@@ -10005,21 +10005,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E16" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F16" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G16" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B17">
         <v>171990</v>
@@ -10028,21 +10028,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E17" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F17" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G17" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B18">
         <v>166567</v>
@@ -10051,21 +10051,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F18" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G18" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B19">
         <v>166538</v>
@@ -10074,21 +10074,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E19" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F19" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G19" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B20">
         <v>166678</v>
@@ -10097,21 +10097,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F20" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G20" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B21">
         <v>167682</v>
@@ -10120,13 +10120,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E21" t="s">
         <v>330</v>
       </c>
       <c r="F21" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G21" t="s">
         <v>554</v>
@@ -10134,7 +10134,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B22">
         <v>166529</v>
@@ -10143,21 +10143,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E22" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F22" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G22" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B23">
         <v>166472</v>
@@ -10166,21 +10166,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E23" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F23" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G23" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B24">
         <v>166571</v>
@@ -10189,21 +10189,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E24" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F24" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G24" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B25">
         <v>166575</v>
@@ -10212,13 +10212,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E25" t="s">
         <v>450</v>
       </c>
       <c r="F25" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G25" t="s">
         <v>121</v>
@@ -10226,7 +10226,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B26">
         <v>166590</v>
@@ -10235,21 +10235,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F26" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G26" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B27">
         <v>166598</v>
@@ -10258,21 +10258,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E27" t="s">
         <v>452</v>
       </c>
       <c r="F27" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G27" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B28">
         <v>166629</v>
@@ -10281,13 +10281,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E28" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F28" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -10295,7 +10295,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B29">
         <v>166650</v>
@@ -10304,21 +10304,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E29" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F29" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G29" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B30">
         <v>166657</v>
@@ -10327,13 +10327,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E30" t="s">
         <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G30" t="s">
         <v>119</v>
@@ -10341,7 +10341,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B31">
         <v>166687</v>
@@ -10350,21 +10350,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E31" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F31" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G31" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B32">
         <v>166691</v>
@@ -10373,7 +10373,7 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E32" t="s">
         <v>327</v>
@@ -10387,7 +10387,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B33">
         <v>166708</v>
@@ -10396,13 +10396,13 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E33" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F33" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G33" t="s">
         <v>121</v>
@@ -10410,7 +10410,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B34">
         <v>166719</v>
@@ -10419,21 +10419,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F34" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G34" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B35">
         <v>166744</v>
@@ -10442,13 +10442,13 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E35" t="s">
         <v>314</v>
       </c>
       <c r="F35" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G35" t="s">
         <v>121</v>
@@ -10456,7 +10456,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B36">
         <v>166746</v>
@@ -10465,21 +10465,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E36" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F36" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G36" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B37">
         <v>166753</v>
@@ -10488,21 +10488,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E37" t="s">
         <v>304</v>
       </c>
       <c r="F37" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G37" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B38">
         <v>166779</v>
@@ -10511,13 +10511,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E38" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F38" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -10525,7 +10525,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B39">
         <v>166818</v>
@@ -10534,21 +10534,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E39" t="s">
         <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G39" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B40">
         <v>167482</v>
@@ -10557,13 +10557,13 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E40" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F40" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -10571,7 +10571,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B41">
         <v>167812</v>
@@ -10580,13 +10580,13 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E41" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="F41" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G41" t="s">
         <v>121</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B42">
         <v>171332</v>
@@ -10603,16 +10603,16 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E42" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F42" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G42" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E3967C-3D38-544E-B557-D2DED63479EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1894FB-1AE9-5145-B311-08CA95BE7DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1156">
   <si>
     <t>Session ID</t>
   </si>
@@ -3488,6 +3488,15 @@
   </si>
   <si>
     <t>University and INFN Genova</t>
+  </si>
+  <si>
+    <t>Mahapatra</t>
+  </si>
+  <si>
+    <t>Rupak</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M University</t>
   </si>
 </sst>
 </file>
@@ -9624,13 +9633,13 @@
         <v>686</v>
       </c>
       <c r="E44" t="s">
-        <v>712</v>
+        <v>1154</v>
       </c>
       <c r="F44" t="s">
-        <v>712</v>
+        <v>1153</v>
       </c>
       <c r="G44" t="s">
-        <v>712</v>
+        <v>1155</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA1894FB-1AE9-5145-B311-08CA95BE7DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F6CC2B-B566-F24F-821C-316CF874D11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -2605,9 +2605,6 @@
     <t>Sayak</t>
   </si>
   <si>
-    <t>filomena</t>
-  </si>
-  <si>
     <t>Antonello</t>
   </si>
   <si>
@@ -2647,9 +2644,6 @@
     <t>Bortone</t>
   </si>
   <si>
-    <t>ASILAR</t>
-  </si>
-  <si>
     <t>Kumar</t>
   </si>
   <si>
@@ -2683,9 +2677,6 @@
     <t>Chatterjee</t>
   </si>
   <si>
-    <t>santos</t>
-  </si>
-  <si>
     <t>Pellecchia</t>
   </si>
   <si>
@@ -3497,6 +3488,15 @@
   </si>
   <si>
     <t>Texas A&amp;M University</t>
+  </si>
+  <si>
+    <t>Asilar</t>
+  </si>
+  <si>
+    <t>Filomena</t>
+  </si>
+  <si>
+    <t>Santos</t>
   </si>
 </sst>
 </file>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4096,21 +4096,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="E2" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="F2" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="G2" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4119,21 +4119,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E3" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="F3" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="G3" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4142,21 +4142,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="E4" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="F4" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="G4" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4165,21 +4165,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="E5" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="F5" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="G5" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4188,13 +4188,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E6" t="s">
         <v>690</v>
       </c>
       <c r="F6" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4211,21 +4211,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="E7" t="s">
         <v>855</v>
       </c>
       <c r="F7" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G7" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4234,13 +4234,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="E8" t="s">
         <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4257,21 +4257,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G9" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4280,13 +4280,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="E10" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="F10" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4303,21 +4303,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E11" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="F11" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="G11" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4326,21 +4326,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="E12" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F12" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="G12" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4349,21 +4349,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="G13" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4372,13 +4372,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="E14" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="F14" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -4386,7 +4386,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4395,13 +4395,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E15" t="s">
         <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="G15" t="s">
         <v>554</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4418,21 +4418,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="E16" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="G16" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4441,21 +4441,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="E17" t="s">
         <v>849</v>
       </c>
       <c r="F17" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G17" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4464,13 +4464,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E18" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="F18" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -4478,7 +4478,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4487,13 +4487,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="E19" t="s">
         <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4510,21 +4510,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="E20" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="F20" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="G20" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4533,21 +4533,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="E21" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="F21" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="G21" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4556,13 +4556,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E22" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F22" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -4570,7 +4570,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4579,21 +4579,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="E23" t="s">
         <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="G23" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4602,13 +4602,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="E24" t="s">
         <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4625,21 +4625,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G25" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4648,21 +4648,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E26" t="s">
         <v>585</v>
       </c>
       <c r="F26" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="G26" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4671,21 +4671,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E27" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F27" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="G27" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4694,13 +4694,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="E28" t="s">
         <v>700</v>
       </c>
       <c r="F28" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4717,13 +4717,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="E29" t="s">
         <v>698</v>
       </c>
       <c r="F29" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4740,13 +4740,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="E30" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F30" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="G30" t="s">
         <v>121</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4763,13 +4763,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E31" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="F31" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4786,13 +4786,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E32" t="s">
         <v>706</v>
       </c>
       <c r="F32" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4809,21 +4809,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E33" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F33" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G33" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4832,13 +4832,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E34" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F34" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4855,21 +4855,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G35" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4878,21 +4878,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E36" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F36" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="G36" t="s">
-        <v>1140</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4901,21 +4901,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E37" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="F37" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="G37" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4924,13 +4924,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E38" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F38" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4947,13 +4947,13 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E39" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F39" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -4961,7 +4961,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4970,21 +4970,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E40" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="F40" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G40" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4993,21 +4993,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E41" t="s">
         <v>698</v>
       </c>
       <c r="F41" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="G41" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -5016,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E42" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F42" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="G42" t="s">
         <v>475</v>
@@ -5030,7 +5030,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5039,21 +5039,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E43" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F43" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="G43" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5062,7 +5062,7 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E44" t="s">
         <v>712</v>
@@ -5076,7 +5076,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5085,13 +5085,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E45" t="s">
         <v>694</v>
       </c>
       <c r="F45" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="G45" t="s">
         <v>121</v>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5108,13 +5108,13 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="E46" t="s">
         <v>692</v>
       </c>
       <c r="F46" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G46" t="s">
         <v>121</v>
@@ -5122,7 +5122,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5131,21 +5131,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E47" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="F47" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="G47" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5154,21 +5154,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="E48" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="F48" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="G48" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5177,7 +5177,7 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E49" t="s">
         <v>310</v>
@@ -5191,7 +5191,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5200,21 +5200,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="E50" t="s">
         <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="G50" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5223,13 +5223,13 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="E51" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F51" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
@@ -5237,7 +5237,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5246,13 +5246,13 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E52" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F52" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="G52" t="s">
         <v>121</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5269,21 +5269,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E53" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F53" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="G53" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5292,21 +5292,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E54" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F54" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="G54" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5315,13 +5315,13 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E55" t="s">
         <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -5329,7 +5329,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5338,21 +5338,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E56" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F56" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="G56" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5361,7 +5361,7 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="E57" t="s">
         <v>531</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5384,18 +5384,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E58" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="F58" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5404,13 +5404,13 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E59" t="s">
         <v>709</v>
       </c>
       <c r="F59" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -5670,7 +5670,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5679,7 +5679,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -8565,7 +8565,7 @@
         <v>595</v>
       </c>
       <c r="G8" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -9633,13 +9633,13 @@
         <v>686</v>
       </c>
       <c r="E44" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="F44" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="G44" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>
@@ -9698,7 +9698,7 @@
         <v>845</v>
       </c>
       <c r="F2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -9721,7 +9721,7 @@
         <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -9744,10 +9744,10 @@
         <v>846</v>
       </c>
       <c r="F4" t="s">
-        <v>872</v>
+        <v>1153</v>
       </c>
       <c r="G4" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -9767,10 +9767,10 @@
         <v>847</v>
       </c>
       <c r="F5" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G5" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -9793,7 +9793,7 @@
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9813,10 +9813,10 @@
         <v>849</v>
       </c>
       <c r="F7" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G7" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -9836,7 +9836,7 @@
         <v>850</v>
       </c>
       <c r="F8" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -9859,7 +9859,7 @@
         <v>851</v>
       </c>
       <c r="F9" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -9882,10 +9882,10 @@
         <v>852</v>
       </c>
       <c r="F10" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G10" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -9905,10 +9905,10 @@
         <v>852</v>
       </c>
       <c r="F11" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G11" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -9928,10 +9928,10 @@
         <v>853</v>
       </c>
       <c r="F12" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G12" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -9951,7 +9951,7 @@
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -9974,10 +9974,10 @@
         <v>854</v>
       </c>
       <c r="F14" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="G14" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -9997,7 +9997,7 @@
         <v>855</v>
       </c>
       <c r="F15" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -10020,10 +10020,10 @@
         <v>856</v>
       </c>
       <c r="F16" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G16" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -10043,10 +10043,10 @@
         <v>857</v>
       </c>
       <c r="F17" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G17" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -10063,13 +10063,13 @@
         <v>820</v>
       </c>
       <c r="E18" t="s">
-        <v>858</v>
+        <v>1154</v>
       </c>
       <c r="F18" t="s">
-        <v>884</v>
+        <v>1155</v>
       </c>
       <c r="G18" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -10086,13 +10086,13 @@
         <v>821</v>
       </c>
       <c r="E19" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F19" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="G19" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -10112,10 +10112,10 @@
         <v>857</v>
       </c>
       <c r="F20" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G20" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -10135,7 +10135,7 @@
         <v>330</v>
       </c>
       <c r="F21" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="G21" t="s">
         <v>554</v>
@@ -10155,13 +10155,13 @@
         <v>824</v>
       </c>
       <c r="E22" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F22" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="G22" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -10181,10 +10181,10 @@
         <v>694</v>
       </c>
       <c r="F23" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="G23" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -10201,13 +10201,13 @@
         <v>826</v>
       </c>
       <c r="E24" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F24" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="G24" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -10227,7 +10227,7 @@
         <v>450</v>
       </c>
       <c r="F25" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="G25" t="s">
         <v>121</v>
@@ -10247,13 +10247,13 @@
         <v>828</v>
       </c>
       <c r="E26" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F26" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="G26" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -10273,10 +10273,10 @@
         <v>452</v>
       </c>
       <c r="F27" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="G27" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -10296,7 +10296,7 @@
         <v>850</v>
       </c>
       <c r="F28" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -10319,10 +10319,10 @@
         <v>692</v>
       </c>
       <c r="F29" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="G29" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -10342,7 +10342,7 @@
         <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="G30" t="s">
         <v>119</v>
@@ -10362,13 +10362,13 @@
         <v>833</v>
       </c>
       <c r="E31" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F31" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="G31" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -10408,10 +10408,10 @@
         <v>835</v>
       </c>
       <c r="E33" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F33" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="G33" t="s">
         <v>121</v>
@@ -10431,13 +10431,13 @@
         <v>836</v>
       </c>
       <c r="E34" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F34" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="G34" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
@@ -10457,7 +10457,7 @@
         <v>314</v>
       </c>
       <c r="F35" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="G35" t="s">
         <v>121</v>
@@ -10477,13 +10477,13 @@
         <v>838</v>
       </c>
       <c r="E36" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F36" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="G36" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -10503,10 +10503,10 @@
         <v>304</v>
       </c>
       <c r="F37" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="G37" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -10523,10 +10523,10 @@
         <v>840</v>
       </c>
       <c r="E38" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F38" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -10549,10 +10549,10 @@
         <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G39" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -10569,10 +10569,10 @@
         <v>842</v>
       </c>
       <c r="E40" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F40" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -10595,7 +10595,7 @@
         <v>700</v>
       </c>
       <c r="F41" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="G41" t="s">
         <v>121</v>
@@ -10615,13 +10615,13 @@
         <v>844</v>
       </c>
       <c r="E42" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F42" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="G42" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F6CC2B-B566-F24F-821C-316CF874D11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6946F761-3652-F94F-BE7E-40EC02842956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="1151">
   <si>
     <t>Session ID</t>
   </si>
@@ -1954,9 +1954,6 @@
     <t>181</t>
   </si>
   <si>
-    <t>375</t>
-  </si>
-  <si>
     <t>230</t>
   </si>
   <si>
@@ -2083,9 +2080,6 @@
     <t>A tile prototype of the Plastic Scintillation Detector for HERD based on long Printed Circuit Boards: design and test with ion beams at CNAO</t>
   </si>
   <si>
-    <t>BINGO: Bi-Isotope 0ν2β Next Generation Observatory</t>
-  </si>
-  <si>
     <t>Baikal-CVD Neutrino Telescope</t>
   </si>
   <si>
@@ -2161,15 +2155,9 @@
     <t>Thomas</t>
   </si>
   <si>
-    <t>Antoine</t>
-  </si>
-  <si>
     <t>Yury</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Bonesini</t>
   </si>
   <si>
@@ -2275,9 +2263,6 @@
     <t>Boschi</t>
   </si>
   <si>
-    <t>Armatol</t>
-  </si>
-  <si>
     <t>Malyshkin</t>
   </si>
   <si>
@@ -2314,9 +2299,6 @@
     <t>INFN Pavia</t>
   </si>
   <si>
-    <t>CEA Saclay</t>
-  </si>
-  <si>
     <t>Joint Institute for Nuclear Research, Dubna, Russia</t>
   </si>
   <si>
@@ -2359,9 +2341,6 @@
     <t>371</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>86</t>
   </si>
   <si>
@@ -2482,9 +2461,6 @@
     <t>Dual-Polarity Ion Drift Chamber: Experimental results with Xe-SF6 mixtures</t>
   </si>
   <si>
-    <t>Full characterization of the random electrode sectorization in the GEM-foils</t>
-  </si>
-  <si>
     <t>Effects of hydrocarbon admixtures to the electroluminescence yield of He-CF4</t>
   </si>
   <si>
@@ -2587,9 +2563,6 @@
     <t>Brunella</t>
   </si>
   <si>
-    <t>ARINDAM</t>
-  </si>
-  <si>
     <t>Matt</t>
   </si>
   <si>
@@ -2656,9 +2629,6 @@
     <t>D'Anzi</t>
   </si>
   <si>
-    <t>SEN</t>
-  </si>
-  <si>
     <t>Posik</t>
   </si>
   <si>
@@ -2668,9 +2638,6 @@
     <t>I. G. M. Borges</t>
   </si>
   <si>
-    <t>Fallavollita</t>
-  </si>
-  <si>
     <t>Roque</t>
   </si>
   <si>
@@ -3497,6 +3464,24 @@
   </si>
   <si>
     <t>Santos</t>
+  </si>
+  <si>
+    <t>Arindam</t>
+  </si>
+  <si>
+    <t>Sen</t>
+  </si>
+  <si>
+    <t>The ITk interlock hardware protection system</t>
+  </si>
+  <si>
+    <t>Susanne</t>
+  </si>
+  <si>
+    <t>Kersten</t>
+  </si>
+  <si>
+    <t>Wuppertal University</t>
   </si>
 </sst>
 </file>
@@ -3555,11 +3540,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4087,7 +4073,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>925</v>
+        <v>914</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4096,21 +4082,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>983</v>
+        <v>972</v>
       </c>
       <c r="E2" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="F2" t="s">
-        <v>1070</v>
+        <v>1059</v>
       </c>
       <c r="G2" t="s">
-        <v>1120</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>926</v>
+        <v>915</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4119,21 +4105,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="E3" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="F3" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="G3" t="s">
-        <v>1121</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>927</v>
+        <v>916</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4142,21 +4128,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>985</v>
+        <v>974</v>
       </c>
       <c r="E4" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="F4" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="G4" t="s">
-        <v>1122</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>928</v>
+        <v>917</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4165,21 +4151,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>986</v>
+        <v>975</v>
       </c>
       <c r="E5" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="F5" t="s">
-        <v>1073</v>
+        <v>1062</v>
       </c>
       <c r="G5" t="s">
-        <v>1123</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4188,13 +4174,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>987</v>
+        <v>976</v>
       </c>
       <c r="E6" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F6" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -4202,7 +4188,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4211,21 +4197,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>988</v>
+        <v>977</v>
       </c>
       <c r="E7" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="F7" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
       <c r="G7" t="s">
-        <v>1124</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4234,13 +4220,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>989</v>
+        <v>978</v>
       </c>
       <c r="E8" t="s">
         <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1076</v>
+        <v>1065</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -4248,7 +4234,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4257,21 +4243,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>990</v>
+        <v>979</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
       <c r="G9" t="s">
-        <v>1125</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4280,13 +4266,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>991</v>
+        <v>980</v>
       </c>
       <c r="E10" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
       <c r="F10" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -4294,7 +4280,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>934</v>
+        <v>923</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4303,21 +4289,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>992</v>
+        <v>981</v>
       </c>
       <c r="E11" t="s">
-        <v>1046</v>
+        <v>1035</v>
       </c>
       <c r="F11" t="s">
-        <v>1079</v>
+        <v>1068</v>
       </c>
       <c r="G11" t="s">
-        <v>1126</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4326,21 +4312,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="E12" t="s">
-        <v>1047</v>
+        <v>1036</v>
       </c>
       <c r="F12" t="s">
-        <v>1080</v>
+        <v>1069</v>
       </c>
       <c r="G12" t="s">
-        <v>1127</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4349,21 +4335,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="G13" t="s">
-        <v>1128</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>937</v>
+        <v>926</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4372,13 +4358,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>995</v>
+        <v>984</v>
       </c>
       <c r="E14" t="s">
-        <v>1048</v>
+        <v>1037</v>
       </c>
       <c r="F14" t="s">
-        <v>1082</v>
+        <v>1071</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -4386,7 +4372,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4395,13 +4381,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="E15" t="s">
         <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>883</v>
+        <v>872</v>
       </c>
       <c r="G15" t="s">
         <v>554</v>
@@ -4409,7 +4395,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4418,21 +4404,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="E16" t="s">
-        <v>1049</v>
+        <v>1038</v>
       </c>
       <c r="F16" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="G16" t="s">
-        <v>1129</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>940</v>
+        <v>929</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4441,21 +4427,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="E17" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="F17" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="G17" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>941</v>
+        <v>930</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4464,13 +4450,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="E18" t="s">
-        <v>1050</v>
+        <v>1039</v>
       </c>
       <c r="F18" t="s">
-        <v>1084</v>
+        <v>1073</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -4478,7 +4464,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>942</v>
+        <v>931</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4487,13 +4473,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="E19" t="s">
         <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1085</v>
+        <v>1074</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -4501,7 +4487,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>943</v>
+        <v>932</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4510,21 +4496,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>1001</v>
+        <v>990</v>
       </c>
       <c r="E20" t="s">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="F20" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
       <c r="G20" t="s">
-        <v>1130</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>944</v>
+        <v>933</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4533,21 +4519,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
       <c r="E21" t="s">
-        <v>1052</v>
+        <v>1041</v>
       </c>
       <c r="F21" t="s">
-        <v>1087</v>
+        <v>1076</v>
       </c>
       <c r="G21" t="s">
-        <v>1131</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>945</v>
+        <v>934</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4556,13 +4542,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="E22" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
       <c r="F22" t="s">
-        <v>1088</v>
+        <v>1077</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -4570,7 +4556,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>946</v>
+        <v>935</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4579,21 +4565,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="E23" t="s">
         <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1089</v>
+        <v>1078</v>
       </c>
       <c r="G23" t="s">
-        <v>1132</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4602,13 +4588,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="E24" t="s">
         <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1090</v>
+        <v>1079</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -4616,7 +4602,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4625,21 +4611,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="G25" t="s">
-        <v>923</v>
+        <v>912</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>949</v>
+        <v>938</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4648,21 +4634,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="E26" t="s">
         <v>585</v>
       </c>
       <c r="F26" t="s">
-        <v>1091</v>
+        <v>1080</v>
       </c>
       <c r="G26" t="s">
-        <v>1133</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4671,21 +4657,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="E27" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
       <c r="F27" t="s">
-        <v>1092</v>
+        <v>1081</v>
       </c>
       <c r="G27" t="s">
-        <v>1134</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>951</v>
+        <v>940</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4694,13 +4680,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="E28" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F28" t="s">
-        <v>1093</v>
+        <v>1082</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -4708,7 +4694,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>952</v>
+        <v>941</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4717,13 +4703,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="E29" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F29" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -4731,7 +4717,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4740,13 +4726,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>1011</v>
+        <v>1000</v>
       </c>
       <c r="E30" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="F30" t="s">
-        <v>1095</v>
+        <v>1084</v>
       </c>
       <c r="G30" t="s">
         <v>121</v>
@@ -4754,7 +4740,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>954</v>
+        <v>943</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4763,13 +4749,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="E31" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="F31" t="s">
-        <v>1096</v>
+        <v>1085</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -4777,7 +4763,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>955</v>
+        <v>944</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4786,13 +4772,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="E32" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F32" t="s">
-        <v>1097</v>
+        <v>1086</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -4800,7 +4786,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>956</v>
+        <v>945</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4809,21 +4795,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>1014</v>
+        <v>1003</v>
       </c>
       <c r="E33" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
       <c r="F33" t="s">
-        <v>1098</v>
+        <v>1087</v>
       </c>
       <c r="G33" t="s">
-        <v>1135</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>957</v>
+        <v>946</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4832,13 +4818,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="E34" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="F34" t="s">
-        <v>1099</v>
+        <v>1088</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -4846,7 +4832,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>958</v>
+        <v>947</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4855,21 +4841,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1016</v>
+        <v>1005</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1100</v>
+        <v>1089</v>
       </c>
       <c r="G35" t="s">
-        <v>1136</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>959</v>
+        <v>948</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4878,21 +4864,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1017</v>
+        <v>1006</v>
       </c>
       <c r="E36" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="F36" t="s">
-        <v>1101</v>
+        <v>1090</v>
       </c>
       <c r="G36" t="s">
-        <v>1137</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4901,21 +4887,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1018</v>
+        <v>1007</v>
       </c>
       <c r="E37" t="s">
-        <v>1059</v>
+        <v>1048</v>
       </c>
       <c r="F37" t="s">
-        <v>1102</v>
+        <v>1091</v>
       </c>
       <c r="G37" t="s">
-        <v>1138</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>961</v>
+        <v>950</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4924,13 +4910,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1019</v>
+        <v>1008</v>
       </c>
       <c r="E38" t="s">
-        <v>1060</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="s">
-        <v>1103</v>
+        <v>1092</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -4938,7 +4924,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4947,13 +4933,13 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1020</v>
+        <v>1009</v>
       </c>
       <c r="E39" t="s">
-        <v>1053</v>
+        <v>1042</v>
       </c>
       <c r="F39" t="s">
-        <v>1088</v>
+        <v>1077</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -4961,7 +4947,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4970,21 +4956,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1021</v>
+        <v>1010</v>
       </c>
       <c r="E40" t="s">
-        <v>1061</v>
+        <v>1050</v>
       </c>
       <c r="F40" t="s">
-        <v>1104</v>
+        <v>1093</v>
       </c>
       <c r="G40" t="s">
-        <v>1139</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>964</v>
+        <v>953</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4993,21 +4979,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="E41" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F41" t="s">
-        <v>1105</v>
+        <v>1094</v>
       </c>
       <c r="G41" t="s">
-        <v>1140</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -5016,13 +5002,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
       <c r="E42" t="s">
-        <v>1062</v>
+        <v>1051</v>
       </c>
       <c r="F42" t="s">
-        <v>1106</v>
+        <v>1095</v>
       </c>
       <c r="G42" t="s">
         <v>475</v>
@@ -5030,7 +5016,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5039,21 +5025,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1024</v>
+        <v>1013</v>
       </c>
       <c r="E43" t="s">
-        <v>1063</v>
+        <v>1052</v>
       </c>
       <c r="F43" t="s">
-        <v>1107</v>
+        <v>1096</v>
       </c>
       <c r="G43" t="s">
-        <v>920</v>
+        <v>909</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>967</v>
+        <v>956</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5062,21 +5048,21 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
       <c r="E44" t="s">
-        <v>712</v>
+        <v>168</v>
       </c>
       <c r="F44" t="s">
-        <v>712</v>
+        <v>184</v>
       </c>
       <c r="G44" t="s">
-        <v>712</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5085,13 +5071,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1026</v>
+        <v>1015</v>
       </c>
       <c r="E45" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F45" t="s">
-        <v>1108</v>
+        <v>1097</v>
       </c>
       <c r="G45" t="s">
         <v>121</v>
@@ -5099,7 +5085,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5108,13 +5094,13 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="E46" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F46" t="s">
-        <v>1109</v>
+        <v>1098</v>
       </c>
       <c r="G46" t="s">
         <v>121</v>
@@ -5122,7 +5108,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>970</v>
+        <v>959</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5131,21 +5117,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="E47" t="s">
-        <v>1064</v>
+        <v>1053</v>
       </c>
       <c r="F47" t="s">
-        <v>1110</v>
+        <v>1099</v>
       </c>
       <c r="G47" t="s">
-        <v>1141</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5154,21 +5140,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="E48" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="F48" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
       <c r="G48" t="s">
-        <v>1142</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5177,13 +5163,13 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="E49" t="s">
         <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G49" t="s">
         <v>121</v>
@@ -5191,7 +5177,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>973</v>
+        <v>962</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5200,21 +5186,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="E50" t="s">
         <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1112</v>
+        <v>1101</v>
       </c>
       <c r="G50" t="s">
-        <v>1143</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5223,13 +5209,13 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="E51" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="F51" t="s">
-        <v>1113</v>
+        <v>1102</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
@@ -5237,7 +5223,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5246,13 +5232,13 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
       <c r="E52" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="F52" t="s">
-        <v>1114</v>
+        <v>1103</v>
       </c>
       <c r="G52" t="s">
         <v>121</v>
@@ -5260,7 +5246,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>976</v>
+        <v>965</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5269,21 +5255,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="E53" t="s">
-        <v>1067</v>
+        <v>1056</v>
       </c>
       <c r="F53" t="s">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="G53" t="s">
-        <v>1144</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5292,21 +5278,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="E54" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
       <c r="F54" t="s">
-        <v>1116</v>
+        <v>1105</v>
       </c>
       <c r="G54" t="s">
-        <v>1145</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5315,13 +5301,13 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
       <c r="E55" t="s">
         <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1117</v>
+        <v>1106</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -5329,7 +5315,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5338,21 +5324,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
       <c r="E56" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
       <c r="F56" t="s">
-        <v>1118</v>
+        <v>1107</v>
       </c>
       <c r="G56" t="s">
-        <v>1146</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5361,7 +5347,7 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="E57" t="s">
         <v>531</v>
@@ -5375,7 +5361,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5384,18 +5370,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="E58" t="s">
-        <v>1065</v>
+        <v>1054</v>
       </c>
       <c r="F58" t="s">
-        <v>1111</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5404,13 +5390,13 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="E59" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F59" t="s">
-        <v>1119</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>
@@ -5670,7 +5656,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1147</v>
+        <v>1136</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5679,7 +5665,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1148</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6303,7 +6289,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7391,6 +7377,29 @@
       </c>
       <c r="G47" t="s">
         <v>401</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>449</v>
+      </c>
+      <c r="B48">
+        <v>169409</v>
+      </c>
+      <c r="C48">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1150</v>
       </c>
     </row>
   </sheetData>
@@ -8565,7 +8574,7 @@
         <v>595</v>
       </c>
       <c r="G8" t="s">
-        <v>1149</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -8621,7 +8630,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -8664,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E2" t="s">
         <v>588</v>
@@ -8687,16 +8696,16 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="G3" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -8710,13 +8719,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F4" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -8733,16 +8742,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F5" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G5" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -8756,13 +8765,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E6" t="s">
         <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -8779,13 +8788,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E7" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F7" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="G7" t="s">
         <v>121</v>
@@ -8802,13 +8811,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E8" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F8" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -8825,13 +8834,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E9" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F9" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G9" t="s">
         <v>477</v>
@@ -8848,7 +8857,7 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E10" t="s">
         <v>298</v>
@@ -8871,13 +8880,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E11" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F11" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="G11" t="s">
         <v>121</v>
@@ -8894,16 +8903,16 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E12" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F12" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="G12" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -8917,13 +8926,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E13" t="s">
         <v>450</v>
       </c>
       <c r="F13" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -8940,13 +8949,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E14" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F14" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -8963,13 +8972,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E15" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F15" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G15" t="s">
         <v>121</v>
@@ -8986,13 +8995,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E16" t="s">
         <v>298</v>
       </c>
       <c r="F16" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -9009,13 +9018,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E17" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F17" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G17" t="s">
         <v>125</v>
@@ -9032,13 +9041,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E18" t="s">
         <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9055,13 +9064,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E19" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F19" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -9078,13 +9087,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E20" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F20" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G20" t="s">
         <v>121</v>
@@ -9101,13 +9110,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E21" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F21" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G21" t="s">
         <v>121</v>
@@ -9124,13 +9133,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E22" t="s">
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -9147,13 +9156,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G23" t="s">
         <v>121</v>
@@ -9170,16 +9179,16 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E24" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F24" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G24" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -9193,16 +9202,16 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E25" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F25" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G25" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -9216,16 +9225,16 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="E26" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F26" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G26" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -9239,13 +9248,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E27" t="s">
         <v>530</v>
       </c>
       <c r="F27" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="G27" t="s">
         <v>121</v>
@@ -9262,16 +9271,16 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E28" t="s">
         <v>532</v>
       </c>
       <c r="F28" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="G28" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -9285,13 +9294,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E29" t="s">
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -9308,16 +9317,16 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E30" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="F30" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G30" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -9331,13 +9340,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E31" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F31" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -9354,13 +9363,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E32" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F32" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="G32" t="s">
         <v>395</v>
@@ -9377,13 +9386,13 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E33" t="s">
         <v>298</v>
       </c>
       <c r="F33" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G33" t="s">
         <v>121</v>
@@ -9400,13 +9409,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E34" t="s">
         <v>298</v>
       </c>
       <c r="F34" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -9423,16 +9432,16 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E35" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F35" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G35" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -9446,13 +9455,13 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E36" t="s">
         <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G36" t="s">
         <v>121</v>
@@ -9469,13 +9478,13 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E37" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F37" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G37" t="s">
         <v>121</v>
@@ -9492,13 +9501,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E38" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F38" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -9515,16 +9524,16 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E39" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F39" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G39" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -9538,13 +9547,13 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -9561,7 +9570,7 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9570,7 +9579,7 @@
         <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -9578,22 +9587,22 @@
         <v>641</v>
       </c>
       <c r="B42">
-        <v>167825</v>
+        <v>172067</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E42" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F42" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="G42" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
@@ -9601,45 +9610,22 @@
         <v>642</v>
       </c>
       <c r="B43">
-        <v>172067</v>
+        <v>172078</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E43" t="s">
-        <v>711</v>
+        <v>1140</v>
       </c>
       <c r="F43" t="s">
-        <v>749</v>
+        <v>1139</v>
       </c>
       <c r="G43" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>643</v>
-      </c>
-      <c r="B44">
-        <v>172078</v>
-      </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
-      <c r="D44" t="s">
-        <v>686</v>
-      </c>
-      <c r="E44" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F44" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G44" t="s">
-        <v>1152</v>
+        <v>1141</v>
       </c>
     </row>
   </sheetData>
@@ -9649,7 +9635,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -9683,7 +9669,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9692,13 +9678,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>804</v>
+        <v>797</v>
       </c>
       <c r="E2" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
       <c r="F2" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -9706,7 +9692,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9715,13 +9701,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="E3" t="s">
         <v>452</v>
       </c>
       <c r="F3" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -9729,7 +9715,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9738,21 +9724,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>806</v>
+        <v>799</v>
       </c>
       <c r="E4" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
       <c r="F4" t="s">
-        <v>1153</v>
+        <v>1142</v>
       </c>
       <c r="G4" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9761,21 +9747,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="E5" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
       <c r="F5" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9784,21 +9770,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
       <c r="E6" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="F6" t="s">
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9807,21 +9793,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
       <c r="E7" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="F7" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="G7" t="s">
-        <v>906</v>
+        <v>895</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9830,13 +9816,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="E8" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="F8" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -9844,7 +9830,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9853,13 +9839,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
       <c r="E9" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="F9" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -9867,7 +9853,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9876,21 +9862,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="E10" t="s">
-        <v>852</v>
+        <v>1145</v>
       </c>
       <c r="F10" t="s">
-        <v>875</v>
+        <v>1146</v>
       </c>
       <c r="G10" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9899,21 +9885,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="E11" t="s">
-        <v>852</v>
+        <v>1145</v>
       </c>
       <c r="F11" t="s">
-        <v>875</v>
+        <v>1146</v>
       </c>
       <c r="G11" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9922,21 +9908,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
       <c r="E12" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="F12" t="s">
-        <v>876</v>
+        <v>866</v>
       </c>
       <c r="G12" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9945,13 +9931,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="E13" t="s">
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>877</v>
+        <v>867</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -9959,7 +9945,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9968,611 +9954,611 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="E14" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="F14" t="s">
-        <v>878</v>
+        <v>868</v>
       </c>
       <c r="G14" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B15">
-        <v>167481</v>
+        <v>168287</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
       <c r="E15" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
       <c r="F15" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>899</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B16">
-        <v>168287</v>
+        <v>171990</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E16" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="F16" t="s">
-        <v>880</v>
+        <v>870</v>
       </c>
       <c r="G16" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B17">
-        <v>171990</v>
+        <v>166567</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="E17" t="s">
-        <v>857</v>
+        <v>1143</v>
       </c>
       <c r="F17" t="s">
-        <v>881</v>
+        <v>1144</v>
       </c>
       <c r="G17" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B18">
-        <v>166567</v>
+        <v>166538</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
       <c r="E18" t="s">
-        <v>1154</v>
+        <v>849</v>
       </c>
       <c r="F18" t="s">
-        <v>1155</v>
+        <v>871</v>
       </c>
       <c r="G18" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B19">
-        <v>166538</v>
+        <v>166678</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
       <c r="E19" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
       <c r="F19" t="s">
-        <v>882</v>
+        <v>870</v>
       </c>
       <c r="G19" t="s">
-        <v>913</v>
+        <v>900</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="B20">
-        <v>166678</v>
+        <v>167682</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
       <c r="E20" t="s">
-        <v>857</v>
+        <v>330</v>
       </c>
       <c r="F20" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="G20" t="s">
-        <v>911</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="B21">
-        <v>167682</v>
+        <v>166529</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
       <c r="E21" t="s">
-        <v>330</v>
+        <v>850</v>
       </c>
       <c r="F21" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="G21" t="s">
-        <v>554</v>
+        <v>903</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="B22">
-        <v>166529</v>
+        <v>166472</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
       <c r="E22" t="s">
-        <v>859</v>
+        <v>692</v>
       </c>
       <c r="F22" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="G22" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B23">
-        <v>166472</v>
+        <v>166571</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
       <c r="E23" t="s">
-        <v>694</v>
+        <v>851</v>
       </c>
       <c r="F23" t="s">
-        <v>885</v>
+        <v>875</v>
       </c>
       <c r="G23" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="B24">
-        <v>166571</v>
+        <v>166575</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
       <c r="E24" t="s">
-        <v>860</v>
+        <v>450</v>
       </c>
       <c r="F24" t="s">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="G24" t="s">
-        <v>916</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="B25">
-        <v>166575</v>
+        <v>166590</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="E25" t="s">
-        <v>450</v>
+        <v>852</v>
       </c>
       <c r="F25" t="s">
-        <v>887</v>
+        <v>877</v>
       </c>
       <c r="G25" t="s">
-        <v>121</v>
+        <v>906</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="B26">
-        <v>166590</v>
+        <v>166598</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="E26" t="s">
-        <v>861</v>
+        <v>452</v>
       </c>
       <c r="F26" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="G26" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="B27">
-        <v>166598</v>
+        <v>166629</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="E27" t="s">
-        <v>452</v>
+        <v>842</v>
       </c>
       <c r="F27" t="s">
-        <v>889</v>
+        <v>864</v>
       </c>
       <c r="G27" t="s">
-        <v>910</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="B28">
-        <v>166629</v>
+        <v>166650</v>
       </c>
       <c r="C28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="E28" t="s">
-        <v>850</v>
+        <v>690</v>
       </c>
       <c r="F28" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="G28" t="s">
-        <v>121</v>
+        <v>907</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="B29">
-        <v>166650</v>
+        <v>166657</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="E29" t="s">
-        <v>692</v>
+        <v>316</v>
       </c>
       <c r="F29" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="G29" t="s">
-        <v>918</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="B30">
-        <v>166657</v>
+        <v>166687</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="E30" t="s">
-        <v>316</v>
+        <v>853</v>
       </c>
       <c r="F30" t="s">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>908</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="B31">
-        <v>166687</v>
+        <v>166691</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E31" t="s">
-        <v>862</v>
+        <v>327</v>
       </c>
       <c r="F31" t="s">
-        <v>892</v>
+        <v>371</v>
       </c>
       <c r="G31" t="s">
-        <v>919</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="B32">
-        <v>166691</v>
+        <v>166708</v>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="E32" t="s">
-        <v>327</v>
+        <v>854</v>
       </c>
       <c r="F32" t="s">
-        <v>371</v>
+        <v>882</v>
       </c>
       <c r="G32" t="s">
-        <v>398</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="B33">
-        <v>166708</v>
+        <v>166719</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="E33" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F33" t="s">
-        <v>893</v>
+        <v>883</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>909</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="B34">
-        <v>166719</v>
+        <v>166744</v>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>836</v>
+        <v>829</v>
       </c>
       <c r="E34" t="s">
-        <v>864</v>
+        <v>314</v>
       </c>
       <c r="F34" t="s">
-        <v>894</v>
+        <v>884</v>
       </c>
       <c r="G34" t="s">
-        <v>920</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="B35">
-        <v>166744</v>
+        <v>166746</v>
       </c>
       <c r="C35">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>837</v>
+        <v>830</v>
       </c>
       <c r="E35" t="s">
-        <v>314</v>
+        <v>856</v>
       </c>
       <c r="F35" t="s">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>910</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="B36">
-        <v>166746</v>
+        <v>166753</v>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>838</v>
+        <v>831</v>
       </c>
       <c r="E36" t="s">
-        <v>865</v>
+        <v>304</v>
       </c>
       <c r="F36" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="G36" t="s">
-        <v>921</v>
+        <v>911</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="B37">
-        <v>166753</v>
+        <v>166779</v>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="E37" t="s">
-        <v>304</v>
+        <v>857</v>
       </c>
       <c r="F37" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="G37" t="s">
-        <v>922</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="B38">
-        <v>166779</v>
+        <v>166818</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="E38" t="s">
-        <v>866</v>
+        <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>912</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="B39">
-        <v>166818</v>
+        <v>167482</v>
       </c>
       <c r="C39">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>841</v>
+        <v>834</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>858</v>
       </c>
       <c r="F39" t="s">
-        <v>899</v>
+        <v>889</v>
       </c>
       <c r="G39" t="s">
-        <v>923</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="B40">
-        <v>167482</v>
+        <v>167812</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
       <c r="E40" t="s">
-        <v>867</v>
+        <v>698</v>
       </c>
       <c r="F40" t="s">
-        <v>900</v>
+        <v>890</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -10580,48 +10566,25 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="B41">
-        <v>167812</v>
+        <v>171332</v>
       </c>
       <c r="C41">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>843</v>
+        <v>836</v>
       </c>
       <c r="E41" t="s">
-        <v>700</v>
+        <v>859</v>
       </c>
       <c r="F41" t="s">
-        <v>901</v>
+        <v>891</v>
       </c>
       <c r="G41" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>803</v>
-      </c>
-      <c r="B42">
-        <v>171332</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42" t="s">
-        <v>844</v>
-      </c>
-      <c r="E42" t="s">
-        <v>868</v>
-      </c>
-      <c r="F42" t="s">
-        <v>902</v>
-      </c>
-      <c r="G42" t="s">
-        <v>924</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6946F761-3652-F94F-BE7E-40EC02842956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C2CE92-099F-7B49-A1B7-DFF0916F00B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="25300" windowHeight="18580" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="1151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="1145">
   <si>
     <t>Session ID</t>
   </si>
@@ -1285,9 +1285,6 @@
     <t>361</t>
   </si>
   <si>
-    <t>425</t>
-  </si>
-  <si>
     <t>465</t>
   </si>
   <si>
@@ -1345,9 +1342,6 @@
     <t>Open-sky muon tomography for Glacier monitoring</t>
   </si>
   <si>
-    <t>Detection of inter-fraction morphological changes in particle therapy exploiting charged secondary fragments</t>
-  </si>
-  <si>
     <t>The use of Low-Temperature Cofired Ceramics technology in Gas Electron Multiplier detectors</t>
   </si>
   <si>
@@ -1441,9 +1435,6 @@
     <t>Cervelli</t>
   </si>
   <si>
-    <t>Traini</t>
-  </si>
-  <si>
     <t>Bielowka</t>
   </si>
   <si>
@@ -1648,9 +1639,6 @@
     <t>Mihule</t>
   </si>
   <si>
-    <t>GHIMOUZ</t>
-  </si>
-  <si>
     <t>Tsuji</t>
   </si>
   <si>
@@ -1660,9 +1648,6 @@
     <t>Zhang</t>
   </si>
   <si>
-    <t>de LA TAILLE</t>
-  </si>
-  <si>
     <t>Gargiulo</t>
   </si>
   <si>
@@ -3424,18 +3409,9 @@
     <t>AGH-UST</t>
   </si>
   <si>
-    <t>HSE University</t>
-  </si>
-  <si>
     <t>University of Frankfurt</t>
   </si>
   <si>
-    <t>HSE, JINR</t>
-  </si>
-  <si>
-    <t>JINR</t>
-  </si>
-  <si>
     <t>Jagiellonian University</t>
   </si>
   <si>
@@ -3482,6 +3458,12 @@
   </si>
   <si>
     <t>Wuppertal University</t>
+  </si>
+  <si>
+    <t>De La Taille</t>
+  </si>
+  <si>
+    <t>Ghimouz</t>
   </si>
 </sst>
 </file>
@@ -4073,7 +4055,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4082,21 +4064,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="E2" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="F2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="G2" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4105,21 +4087,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="E3" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="F3" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="G3" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4128,21 +4110,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="E4" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="F4" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="G4" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4151,21 +4133,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E5" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="F5" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="G5" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4174,13 +4156,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="E6" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="F6" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -4188,7 +4170,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4197,21 +4179,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E7" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="F7" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G7" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4220,13 +4202,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="E8" t="s">
         <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -4234,7 +4216,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4243,21 +4225,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="G9" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4266,13 +4248,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="E10" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="F10" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -4280,7 +4262,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4289,21 +4271,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="E11" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="F11" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="G11" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4312,21 +4294,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="E12" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="F12" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="G12" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4335,21 +4317,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="G13" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4358,13 +4340,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E14" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="F14" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -4372,7 +4354,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4381,21 +4363,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E15" t="s">
         <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="G15" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4404,21 +4386,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="E16" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="F16" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="G16" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4427,21 +4409,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="E17" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="F17" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G17" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4450,13 +4432,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E18" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="F18" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -4464,7 +4446,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4473,13 +4455,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="E19" t="s">
         <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -4487,7 +4469,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4496,21 +4478,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="E20" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="F20" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="G20" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4519,21 +4501,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="E21" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F21" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="G21" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4542,13 +4524,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="E22" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="F22" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -4556,7 +4538,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4565,21 +4547,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="E23" t="s">
         <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="G23" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4588,13 +4570,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="E24" t="s">
         <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -4602,7 +4584,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4611,21 +4593,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="G25" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4634,21 +4616,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E26" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F26" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="G26" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4657,21 +4639,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="E27" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="F27" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="G27" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4680,13 +4662,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="E28" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F28" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -4694,7 +4676,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4703,13 +4685,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="E29" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F29" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -4717,7 +4699,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4726,13 +4708,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E30" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="F30" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="G30" t="s">
         <v>121</v>
@@ -4740,7 +4722,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4749,13 +4731,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="E31" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="F31" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -4763,7 +4745,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4772,13 +4754,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="E32" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F32" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -4786,7 +4768,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4795,21 +4777,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="E33" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="F33" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="G33" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4818,13 +4800,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="E34" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="F34" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -4832,7 +4814,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4841,21 +4823,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="G35" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4864,21 +4846,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E36" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="F36" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G36" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4887,21 +4869,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="E37" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="F37" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="G37" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4910,13 +4892,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="E38" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="F38" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -4924,7 +4906,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4933,13 +4915,13 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="E39" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="F39" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -4947,7 +4929,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4956,21 +4938,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="E40" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="F40" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="G40" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4979,21 +4961,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="E41" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F41" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="G41" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -5002,21 +4984,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="E42" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="F42" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="G42" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5025,21 +5007,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="E43" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="F43" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="G43" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5048,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="E44" t="s">
         <v>168</v>
@@ -5062,7 +5044,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5071,13 +5053,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="E45" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="G45" t="s">
         <v>121</v>
@@ -5085,7 +5067,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5094,13 +5076,13 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="E46" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F46" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="G46" t="s">
         <v>121</v>
@@ -5108,7 +5090,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5117,21 +5099,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="E47" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="F47" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="G47" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5140,21 +5122,18 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="E48" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="F48" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1131</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5163,13 +5142,13 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="E49" t="s">
         <v>310</v>
       </c>
       <c r="F49" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="G49" t="s">
         <v>121</v>
@@ -5177,7 +5156,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5186,21 +5165,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="E50" t="s">
         <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="G50" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5209,13 +5188,13 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="E51" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="F51" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
@@ -5223,7 +5202,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5232,13 +5211,13 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="E52" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F52" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="G52" t="s">
         <v>121</v>
@@ -5246,7 +5225,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5255,21 +5234,18 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="E53" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="F53" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G53" t="s">
-        <v>1133</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5278,21 +5254,18 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="E54" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="F54" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G54" t="s">
-        <v>1134</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5301,13 +5274,13 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="E55" t="s">
         <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -5315,7 +5288,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5324,21 +5297,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="E56" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="F56" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="G56" t="s">
-        <v>1135</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5347,21 +5320,21 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="E57" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F57" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G57" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5370,18 +5343,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="E58" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5390,13 +5363,16 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E59" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="F59" t="s">
-        <v>1108</v>
+        <v>1103</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -5656,7 +5632,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1136</v>
+        <v>1128</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5665,7 +5641,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1137</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7390,16 +7366,16 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1147</v>
+        <v>1139</v>
       </c>
       <c r="E48" t="s">
-        <v>1148</v>
+        <v>1140</v>
       </c>
       <c r="F48" t="s">
-        <v>1149</v>
+        <v>1141</v>
       </c>
       <c r="G48" t="s">
-        <v>1150</v>
+        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -7409,7 +7385,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7452,13 +7428,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -7475,13 +7451,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -7498,16 +7474,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F4" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -7521,16 +7497,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
         <v>295</v>
       </c>
       <c r="F5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -7544,16 +7520,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -7567,16 +7543,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -7590,13 +7566,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E8" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F8" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -7613,16 +7589,16 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E9" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F9" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G9" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -7636,16 +7612,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E10" t="s">
         <v>164</v>
       </c>
       <c r="F10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G10" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -7659,13 +7635,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E11" t="s">
         <v>298</v>
       </c>
       <c r="F11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G11" t="s">
         <v>121</v>
@@ -7682,13 +7658,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F12" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G12" t="s">
         <v>119</v>
@@ -7705,13 +7681,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -7728,13 +7704,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E14" t="s">
         <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -7751,7 +7727,7 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E15" t="s">
         <v>332</v>
@@ -7774,13 +7750,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E16" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -7797,13 +7773,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E17" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F17" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G17" t="s">
         <v>121</v>
@@ -7814,22 +7790,22 @@
         <v>418</v>
       </c>
       <c r="B18">
-        <v>166796</v>
+        <v>171014</v>
       </c>
       <c r="C18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E18" t="s">
-        <v>302</v>
+        <v>451</v>
       </c>
       <c r="F18" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -7837,22 +7813,22 @@
         <v>419</v>
       </c>
       <c r="B19">
-        <v>171014</v>
+        <v>171701</v>
       </c>
       <c r="C19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E19" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F19" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -7860,45 +7836,22 @@
         <v>420</v>
       </c>
       <c r="B20">
-        <v>171701</v>
+        <v>167817</v>
       </c>
       <c r="C20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E20" t="s">
-        <v>454</v>
+        <v>304</v>
       </c>
       <c r="F20" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G20" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>421</v>
-      </c>
-      <c r="B21">
-        <v>167817</v>
-      </c>
-      <c r="C21">
-        <v>20</v>
-      </c>
-      <c r="D21" t="s">
-        <v>441</v>
-      </c>
-      <c r="E21" t="s">
-        <v>304</v>
-      </c>
-      <c r="F21" t="s">
-        <v>473</v>
-      </c>
-      <c r="G21" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -7942,7 +7895,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -7951,21 +7904,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E2" t="s">
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -7974,21 +7927,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -7997,13 +7950,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E4" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F4" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -8011,7 +7964,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8020,21 +7973,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G5" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B6">
         <v>166643</v>
@@ -8043,21 +7996,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F6" t="s">
-        <v>539</v>
+        <v>1144</v>
       </c>
       <c r="G6" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B7">
         <v>166685</v>
@@ -8066,21 +8019,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E7" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F7" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="G7" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B8">
         <v>166740</v>
@@ -8089,7 +8042,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E8" t="s">
         <v>173</v>
@@ -8098,12 +8051,12 @@
         <v>189</v>
       </c>
       <c r="G8" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B9">
         <v>166754</v>
@@ -8112,13 +8065,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E9" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F9" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -8126,7 +8079,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B10">
         <v>166475</v>
@@ -8135,21 +8088,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E10" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F10" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="G10" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B11">
         <v>166511</v>
@@ -8158,21 +8111,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F11" t="s">
-        <v>543</v>
+        <v>1143</v>
       </c>
       <c r="G11" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B12">
         <v>166518</v>
@@ -8181,13 +8134,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E12" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F12" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="G12" t="s">
         <v>121</v>
@@ -8195,7 +8148,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B13">
         <v>166524</v>
@@ -8204,21 +8157,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E13" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F13" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G13" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B14">
         <v>166525</v>
@@ -8227,13 +8180,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E14" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F14" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -8241,7 +8194,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B15">
         <v>166563</v>
@@ -8250,13 +8203,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F15" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -8264,7 +8217,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B16">
         <v>166608</v>
@@ -8273,21 +8226,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E16" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F16" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="G16" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B17">
         <v>166659</v>
@@ -8296,21 +8249,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F17" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="G17" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B18">
         <v>166664</v>
@@ -8319,13 +8272,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E18" t="s">
         <v>304</v>
       </c>
       <c r="F18" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -8333,7 +8286,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B19">
         <v>166727</v>
@@ -8342,21 +8295,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E19" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F19" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G19" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B20">
         <v>166738</v>
@@ -8365,13 +8318,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E20" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F20" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="G20" t="s">
         <v>121</v>
@@ -8418,7 +8371,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8427,13 +8380,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="E2" t="s">
         <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -8441,7 +8394,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8450,13 +8403,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E3" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="F3" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -8464,7 +8417,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8473,13 +8426,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="E4" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="F4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -8487,7 +8440,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8496,21 +8449,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="E5" t="s">
         <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="G5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8519,21 +8472,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E6" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F6" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="G6" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B7">
         <v>167882</v>
@@ -8542,13 +8495,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="E7" t="s">
         <v>298</v>
       </c>
       <c r="F7" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G7" t="s">
         <v>121</v>
@@ -8556,7 +8509,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="B8">
         <v>166696</v>
@@ -8565,21 +8518,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E8" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F8" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="G8" t="s">
-        <v>1138</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="B9">
         <v>166700</v>
@@ -8588,21 +8541,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="E9" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F9" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G9" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B10">
         <v>166792</v>
@@ -8611,13 +8564,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="E10" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="F10" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -8664,7 +8617,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8673,13 +8626,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="E2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="F2" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -8687,7 +8640,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -8696,21 +8649,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="F3" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="G3" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -8719,13 +8672,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="E4" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="F4" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="G4" t="s">
         <v>121</v>
@@ -8733,7 +8686,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -8742,21 +8695,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="E5" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="F5" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="G5" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -8765,13 +8718,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="E6" t="s">
         <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -8779,7 +8732,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -8788,13 +8741,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="F7" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="G7" t="s">
         <v>121</v>
@@ -8802,7 +8755,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -8811,13 +8764,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="E8" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="F8" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -8825,7 +8778,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -8834,21 +8787,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="E9" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F9" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="G9" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -8857,13 +8810,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="E10" t="s">
         <v>298</v>
       </c>
       <c r="F10" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -8871,7 +8824,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -8880,13 +8833,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="E11" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="F11" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="G11" t="s">
         <v>121</v>
@@ -8894,7 +8847,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -8903,21 +8856,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="E12" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="G12" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -8926,13 +8879,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F13" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -8940,7 +8893,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -8949,13 +8902,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="E14" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="F14" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -8963,7 +8916,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -8972,13 +8925,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E15" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="F15" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="G15" t="s">
         <v>121</v>
@@ -8986,7 +8939,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B16">
         <v>166743</v>
@@ -8995,13 +8948,13 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="E16" t="s">
         <v>298</v>
       </c>
       <c r="F16" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="G16" t="s">
         <v>121</v>
@@ -9009,7 +8962,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B17">
         <v>166814</v>
@@ -9018,13 +8971,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E17" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="F17" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="G17" t="s">
         <v>125</v>
@@ -9032,7 +8985,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B18">
         <v>166497</v>
@@ -9041,13 +8994,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E18" t="s">
         <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -9055,7 +9008,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B19">
         <v>166733</v>
@@ -9064,13 +9017,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E19" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="F19" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -9078,7 +9031,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B20">
         <v>166496</v>
@@ -9087,13 +9040,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E20" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="F20" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="G20" t="s">
         <v>121</v>
@@ -9101,7 +9054,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B21">
         <v>166725</v>
@@ -9110,13 +9063,13 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E21" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F21" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="G21" t="s">
         <v>121</v>
@@ -9124,7 +9077,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9133,13 +9086,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="E22" t="s">
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -9147,7 +9100,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9156,13 +9109,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="G23" t="s">
         <v>121</v>
@@ -9170,7 +9123,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9179,21 +9132,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="E24" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="F24" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="G24" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9202,21 +9155,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="E25" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="F25" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G25" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9225,21 +9178,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="E26" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="F26" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="G26" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9248,13 +9201,13 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="E27" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F27" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="G27" t="s">
         <v>121</v>
@@ -9262,7 +9215,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9271,21 +9224,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E28" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F28" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="G28" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9294,13 +9247,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E29" t="s">
         <v>298</v>
       </c>
       <c r="F29" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -9308,7 +9261,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9317,21 +9270,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="E30" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="F30" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="G30" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9340,13 +9293,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E31" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="F31" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -9354,7 +9307,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9363,13 +9316,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="E32" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="F32" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="G32" t="s">
         <v>395</v>
@@ -9377,7 +9330,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9386,13 +9339,13 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E33" t="s">
         <v>298</v>
       </c>
       <c r="F33" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="G33" t="s">
         <v>121</v>
@@ -9400,7 +9353,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9409,13 +9362,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="E34" t="s">
         <v>298</v>
       </c>
       <c r="F34" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -9423,7 +9376,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9432,21 +9385,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="E35" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="F35" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="G35" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9455,13 +9408,13 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="E36" t="s">
         <v>310</v>
       </c>
       <c r="F36" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="G36" t="s">
         <v>121</v>
@@ -9469,7 +9422,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9478,13 +9431,13 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="E37" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F37" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="G37" t="s">
         <v>121</v>
@@ -9492,7 +9445,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9501,13 +9454,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="E38" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="F38" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -9515,7 +9468,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9524,21 +9477,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="E39" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="F39" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="G39" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9547,13 +9500,13 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -9561,7 +9514,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9570,7 +9523,7 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9579,12 +9532,12 @@
         <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="B42">
         <v>172067</v>
@@ -9593,21 +9546,21 @@
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E42" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="F42" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="G42" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="B43">
         <v>172078</v>
@@ -9616,16 +9569,16 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E43" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="F43" t="s">
-        <v>1139</v>
+        <v>1131</v>
       </c>
       <c r="G43" t="s">
-        <v>1141</v>
+        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -9669,7 +9622,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9678,13 +9631,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="E2" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="F2" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -9692,7 +9645,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9701,13 +9654,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="E3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F3" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -9715,7 +9668,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9724,21 +9677,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="E4" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="F4" t="s">
-        <v>1142</v>
+        <v>1134</v>
       </c>
       <c r="G4" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9747,21 +9700,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="E5" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="F5" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G5" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9770,21 +9723,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="E6" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="F6" t="s">
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9793,21 +9746,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="E7" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="F7" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="G7" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9816,13 +9769,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="E8" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F8" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -9830,7 +9783,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9839,13 +9792,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="E9" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="F9" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -9853,7 +9806,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9862,21 +9815,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E10" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
       <c r="F10" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="G10" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9885,21 +9838,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="E11" t="s">
-        <v>1145</v>
+        <v>1137</v>
       </c>
       <c r="F11" t="s">
-        <v>1146</v>
+        <v>1138</v>
       </c>
       <c r="G11" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9908,21 +9861,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="E12" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="F12" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="G12" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9931,13 +9884,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="E13" t="s">
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -9945,7 +9898,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9954,21 +9907,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="E14" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="F14" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="G14" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B15">
         <v>168287</v>
@@ -9977,21 +9930,21 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="E15" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="F15" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="G15" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="B16">
         <v>171990</v>
@@ -10000,21 +9953,21 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="E16" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="F16" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G16" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="B17">
         <v>166567</v>
@@ -10023,21 +9976,21 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="E17" t="s">
-        <v>1143</v>
+        <v>1135</v>
       </c>
       <c r="F17" t="s">
-        <v>1144</v>
+        <v>1136</v>
       </c>
       <c r="G17" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B18">
         <v>166538</v>
@@ -10046,21 +9999,21 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="E18" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="F18" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="G18" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="B19">
         <v>166678</v>
@@ -10069,21 +10022,21 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="E19" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="F19" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="G19" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B20">
         <v>167682</v>
@@ -10092,21 +10045,21 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="E20" t="s">
         <v>330</v>
       </c>
       <c r="F20" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="G20" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="B21">
         <v>166529</v>
@@ -10115,21 +10068,21 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="E21" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="F21" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G21" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B22">
         <v>166472</v>
@@ -10138,21 +10091,21 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="E22" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="G22" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="B23">
         <v>166571</v>
@@ -10161,21 +10114,21 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="E23" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="F23" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="G23" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="B24">
         <v>166575</v>
@@ -10184,13 +10137,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="E24" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F24" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -10198,7 +10151,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="B25">
         <v>166590</v>
@@ -10207,21 +10160,21 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="E25" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="F25" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="G25" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="B26">
         <v>166598</v>
@@ -10230,21 +10183,21 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="E26" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F26" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="G26" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="B27">
         <v>166629</v>
@@ -10253,13 +10206,13 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="E27" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="F27" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="G27" t="s">
         <v>121</v>
@@ -10267,7 +10220,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B28">
         <v>166650</v>
@@ -10276,21 +10229,21 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="E28" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F28" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G28" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B29">
         <v>166657</v>
@@ -10299,13 +10252,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="E29" t="s">
         <v>316</v>
       </c>
       <c r="F29" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="G29" t="s">
         <v>119</v>
@@ -10313,7 +10266,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B30">
         <v>166687</v>
@@ -10322,21 +10275,21 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="E30" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="F30" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="G30" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B31">
         <v>166691</v>
@@ -10345,7 +10298,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="E31" t="s">
         <v>327</v>
@@ -10359,7 +10312,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B32">
         <v>166708</v>
@@ -10368,13 +10321,13 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="E32" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F32" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -10382,7 +10335,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="B33">
         <v>166719</v>
@@ -10391,21 +10344,21 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="E33" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="F33" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G33" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B34">
         <v>166744</v>
@@ -10414,13 +10367,13 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E34" t="s">
         <v>314</v>
       </c>
       <c r="F34" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -10428,7 +10381,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B35">
         <v>166746</v>
@@ -10437,21 +10390,21 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="E35" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="F35" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="G35" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="B36">
         <v>166753</v>
@@ -10460,21 +10413,21 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="E36" t="s">
         <v>304</v>
       </c>
       <c r="F36" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="G36" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="B37">
         <v>166779</v>
@@ -10483,13 +10436,13 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="E37" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="F37" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="G37" t="s">
         <v>121</v>
@@ -10497,7 +10450,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="B38">
         <v>166818</v>
@@ -10506,21 +10459,21 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="E38" t="s">
         <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="G38" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="B39">
         <v>167482</v>
@@ -10529,13 +10482,13 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="E39" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F39" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -10543,7 +10496,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="B40">
         <v>167812</v>
@@ -10552,13 +10505,13 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="E40" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="F40" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -10566,7 +10519,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="B41">
         <v>171332</v>
@@ -10575,16 +10528,16 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="E41" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F41" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="G41" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C2CE92-099F-7B49-A1B7-DFF0916F00B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C474A-29EC-8346-9EF3-0BFA66E14289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1144">
   <si>
     <t>Session ID</t>
   </si>
@@ -2282,9 +2282,6 @@
   </si>
   <si>
     <t>INFN Pavia</t>
-  </si>
-  <si>
-    <t>Joint Institute for Nuclear Research, Dubna, Russia</t>
   </si>
   <si>
     <t>82</t>
@@ -4055,7 +4052,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4064,21 +4061,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="F2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4087,21 +4084,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E3" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4110,21 +4107,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G4" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4133,21 +4130,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E5" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G5" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4156,13 +4153,13 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E6" t="s">
         <v>683</v>
       </c>
       <c r="F6" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G6" t="s">
         <v>121</v>
@@ -4170,7 +4167,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4179,21 +4176,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G7" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4202,13 +4199,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E8" t="s">
         <v>304</v>
       </c>
       <c r="F8" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -4216,7 +4213,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4225,21 +4222,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E9" t="s">
         <v>331</v>
       </c>
       <c r="F9" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G9" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4248,13 +4245,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E10" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F10" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -4262,7 +4259,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4271,21 +4268,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E11" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F11" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G11" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4294,21 +4291,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E12" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F12" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G12" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4317,21 +4314,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G13" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4340,13 +4337,13 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E14" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F14" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G14" t="s">
         <v>121</v>
@@ -4354,7 +4351,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4363,13 +4360,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E15" t="s">
         <v>330</v>
       </c>
       <c r="F15" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G15" t="s">
         <v>549</v>
@@ -4377,7 +4374,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4386,21 +4383,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E16" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F16" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G16" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4409,21 +4406,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E17" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F17" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G17" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4432,13 +4429,13 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E18" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F18" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G18" t="s">
         <v>121</v>
@@ -4446,7 +4443,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4455,13 +4452,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E19" t="s">
         <v>298</v>
       </c>
       <c r="F19" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G19" t="s">
         <v>121</v>
@@ -4469,7 +4466,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4478,21 +4475,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E20" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F20" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G20" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4501,21 +4498,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E21" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F21" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G21" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4524,13 +4521,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E22" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F22" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G22" t="s">
         <v>121</v>
@@ -4538,7 +4535,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4547,21 +4544,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E23" t="s">
         <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G23" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4570,13 +4567,13 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E24" t="s">
         <v>298</v>
       </c>
       <c r="F24" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -4584,7 +4581,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4593,21 +4590,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G25" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4616,21 +4613,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E26" t="s">
         <v>580</v>
       </c>
       <c r="F26" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G26" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4639,21 +4636,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E27" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F27" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G27" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4662,13 +4659,13 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E28" t="s">
         <v>693</v>
       </c>
       <c r="F28" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G28" t="s">
         <v>121</v>
@@ -4676,7 +4673,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4685,13 +4682,13 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E29" t="s">
         <v>691</v>
       </c>
       <c r="F29" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G29" t="s">
         <v>121</v>
@@ -4699,7 +4696,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4708,13 +4705,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E30" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F30" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G30" t="s">
         <v>121</v>
@@ -4722,7 +4719,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4731,13 +4728,13 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E31" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F31" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G31" t="s">
         <v>121</v>
@@ -4745,7 +4742,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4754,13 +4751,13 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E32" t="s">
         <v>699</v>
       </c>
       <c r="F32" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -4768,7 +4765,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4777,21 +4774,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E33" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F33" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G33" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4800,13 +4797,13 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E34" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F34" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -4814,7 +4811,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4823,21 +4820,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G35" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4846,21 +4843,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E36" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F36" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G36" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4869,21 +4866,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E37" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F37" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G37" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4892,13 +4889,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E38" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F38" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G38" t="s">
         <v>121</v>
@@ -4906,7 +4903,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4915,13 +4912,13 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E39" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F39" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -4929,7 +4926,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4938,21 +4935,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E40" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F40" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G40" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4961,21 +4958,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E41" t="s">
         <v>691</v>
       </c>
       <c r="F41" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G41" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -4984,13 +4981,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E42" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F42" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G42" t="s">
         <v>472</v>
@@ -4998,7 +4995,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5007,21 +5004,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E43" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F43" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G43" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5030,7 +5027,7 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E44" t="s">
         <v>168</v>
@@ -5044,7 +5041,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5053,13 +5050,13 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E45" t="s">
         <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G45" t="s">
         <v>121</v>
@@ -5067,7 +5064,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5076,13 +5073,13 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E46" t="s">
         <v>685</v>
       </c>
       <c r="F46" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G46" t="s">
         <v>121</v>
@@ -5090,7 +5087,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5099,21 +5096,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E47" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="F47" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G47" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5122,18 +5119,18 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E48" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F48" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5142,7 +5139,7 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E49" t="s">
         <v>310</v>
@@ -5156,7 +5153,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5165,21 +5162,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E50" t="s">
         <v>299</v>
       </c>
       <c r="F50" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G50" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5188,13 +5185,13 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E51" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G51" t="s">
         <v>121</v>
@@ -5202,7 +5199,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5211,13 +5208,13 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E52" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F52" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G52" t="s">
         <v>121</v>
@@ -5225,7 +5222,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5234,18 +5231,18 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E53" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="F53" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5254,18 +5251,18 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E54" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F54" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5274,13 +5271,13 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E55" t="s">
         <v>331</v>
       </c>
       <c r="F55" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -5288,7 +5285,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5297,21 +5294,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E56" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F56" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G56" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5320,7 +5317,7 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E57" t="s">
         <v>528</v>
@@ -5334,7 +5331,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5343,18 +5340,18 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E58" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F58" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5363,16 +5360,16 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E59" t="s">
         <v>702</v>
       </c>
       <c r="F59" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G59" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
   </sheetData>
@@ -5632,7 +5629,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5641,7 +5638,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7366,16 +7363,16 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E48" t="s">
         <v>1139</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>1140</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>1141</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1142</v>
       </c>
     </row>
   </sheetData>
@@ -8002,7 +7999,7 @@
         <v>520</v>
       </c>
       <c r="F6" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G6" t="s">
         <v>551</v>
@@ -8117,7 +8114,7 @@
         <v>524</v>
       </c>
       <c r="F11" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G11" t="s">
         <v>555</v>
@@ -8527,7 +8524,7 @@
         <v>590</v>
       </c>
       <c r="G8" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -9554,9 +9551,6 @@
       <c r="F42" t="s">
         <v>739</v>
       </c>
-      <c r="G42" t="s">
-        <v>751</v>
-      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -9572,13 +9566,13 @@
         <v>679</v>
       </c>
       <c r="E43" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G43" t="s">
         <v>1132</v>
-      </c>
-      <c r="F43" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G43" t="s">
-        <v>1133</v>
       </c>
     </row>
   </sheetData>
@@ -9622,7 +9616,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9631,13 +9625,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G2" t="s">
         <v>121</v>
@@ -9645,7 +9639,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9654,13 +9648,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E3" t="s">
         <v>450</v>
       </c>
       <c r="F3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G3" t="s">
         <v>121</v>
@@ -9668,7 +9662,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9677,21 +9671,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F4" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9700,21 +9694,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="F5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9723,21 +9717,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E6" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F6" t="s">
         <v>360</v>
       </c>
       <c r="G6" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9746,21 +9740,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F7" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9769,13 +9763,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E8" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F8" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G8" t="s">
         <v>121</v>
@@ -9783,7 +9777,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9792,13 +9786,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G9" t="s">
         <v>121</v>
@@ -9806,7 +9800,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9815,21 +9809,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E10" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F10" t="s">
         <v>1137</v>
       </c>
-      <c r="F10" t="s">
-        <v>1138</v>
-      </c>
       <c r="G10" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9838,21 +9832,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E11" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F11" t="s">
         <v>1137</v>
       </c>
-      <c r="F11" t="s">
-        <v>1138</v>
-      </c>
       <c r="G11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9861,21 +9855,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F12" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G12" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9884,13 +9878,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E13" t="s">
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G13" t="s">
         <v>121</v>
@@ -9898,7 +9892,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9907,21 +9901,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E14" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G14" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B15">
         <v>168287</v>
@@ -9930,21 +9924,21 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E15" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F15" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G15" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B16">
         <v>171990</v>
@@ -9953,21 +9947,21 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E16" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F16" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G16" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B17">
         <v>166567</v>
@@ -9976,21 +9970,21 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E17" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F17" t="s">
         <v>1135</v>
       </c>
-      <c r="F17" t="s">
-        <v>1136</v>
-      </c>
       <c r="G17" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B18">
         <v>166538</v>
@@ -9999,21 +9993,21 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E18" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F18" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G18" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B19">
         <v>166678</v>
@@ -10022,21 +10016,21 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E19" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F19" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G19" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B20">
         <v>167682</v>
@@ -10045,13 +10039,13 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E20" t="s">
         <v>330</v>
       </c>
       <c r="F20" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G20" t="s">
         <v>549</v>
@@ -10059,7 +10053,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B21">
         <v>166529</v>
@@ -10068,21 +10062,21 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E21" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F21" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G21" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B22">
         <v>166472</v>
@@ -10091,21 +10085,21 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E22" t="s">
         <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G22" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B23">
         <v>166571</v>
@@ -10114,21 +10108,21 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E23" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F23" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G23" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B24">
         <v>166575</v>
@@ -10137,13 +10131,13 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E24" t="s">
         <v>448</v>
       </c>
       <c r="F24" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G24" t="s">
         <v>121</v>
@@ -10151,7 +10145,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B25">
         <v>166590</v>
@@ -10160,21 +10154,21 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F25" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G25" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B26">
         <v>166598</v>
@@ -10183,21 +10177,21 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E26" t="s">
         <v>450</v>
       </c>
       <c r="F26" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G26" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B27">
         <v>166629</v>
@@ -10206,13 +10200,13 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E27" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F27" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G27" t="s">
         <v>121</v>
@@ -10220,7 +10214,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B28">
         <v>166650</v>
@@ -10229,21 +10223,21 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E28" t="s">
         <v>685</v>
       </c>
       <c r="F28" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G28" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B29">
         <v>166657</v>
@@ -10252,13 +10246,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E29" t="s">
         <v>316</v>
       </c>
       <c r="F29" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G29" t="s">
         <v>119</v>
@@ -10266,7 +10260,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B30">
         <v>166687</v>
@@ -10275,21 +10269,21 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E30" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F30" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G30" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B31">
         <v>166691</v>
@@ -10298,7 +10292,7 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E31" t="s">
         <v>327</v>
@@ -10312,7 +10306,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B32">
         <v>166708</v>
@@ -10321,13 +10315,13 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E32" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F32" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G32" t="s">
         <v>121</v>
@@ -10335,7 +10329,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B33">
         <v>166719</v>
@@ -10344,21 +10338,21 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E33" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F33" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G33" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B34">
         <v>166744</v>
@@ -10367,13 +10361,13 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E34" t="s">
         <v>314</v>
       </c>
       <c r="F34" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G34" t="s">
         <v>121</v>
@@ -10381,7 +10375,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B35">
         <v>166746</v>
@@ -10390,21 +10384,21 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E35" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F35" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G35" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B36">
         <v>166753</v>
@@ -10413,21 +10407,21 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E36" t="s">
         <v>304</v>
       </c>
       <c r="F36" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G36" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B37">
         <v>166779</v>
@@ -10436,13 +10430,13 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E37" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F37" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G37" t="s">
         <v>121</v>
@@ -10450,7 +10444,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B38">
         <v>166818</v>
@@ -10459,21 +10453,21 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E38" t="s">
         <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G38" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B39">
         <v>167482</v>
@@ -10482,13 +10476,13 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E39" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F39" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G39" t="s">
         <v>121</v>
@@ -10496,7 +10490,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B40">
         <v>167812</v>
@@ -10505,13 +10499,13 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E40" t="s">
         <v>693</v>
       </c>
       <c r="F40" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G40" t="s">
         <v>121</v>
@@ -10519,7 +10513,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B41">
         <v>171332</v>
@@ -10528,16 +10522,16 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E41" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F41" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G41" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E2C474A-29EC-8346-9EF3-0BFA66E14289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D036B6-B3E0-F74B-8582-A2A51657EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="1145">
   <si>
     <t>Session ID</t>
   </si>
@@ -3461,6 +3461,9 @@
   </si>
   <si>
     <t>Ghimouz</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -5127,6 +5130,9 @@
       <c r="F48" t="s">
         <v>1094</v>
       </c>
+      <c r="G48" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -5239,6 +5245,9 @@
       <c r="F53" t="s">
         <v>1098</v>
       </c>
+      <c r="G53" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
@@ -5259,6 +5268,9 @@
       <c r="F54" t="s">
         <v>1099</v>
       </c>
+      <c r="G54" t="s">
+        <v>1144</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
@@ -5347,6 +5359,9 @@
       </c>
       <c r="F58" t="s">
         <v>1094</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D036B6-B3E0-F74B-8582-A2A51657EA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF3E890-575E-254C-AD1D-991D3F846272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="1145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="1162">
   <si>
     <t>Session ID</t>
   </si>
@@ -619,9 +619,6 @@
     <t>University of Sherbrooke</t>
   </si>
   <si>
-    <t>INFN Pisa/University of Siena</t>
-  </si>
-  <si>
     <t>University of Trieste</t>
   </si>
   <si>
@@ -1222,12 +1219,6 @@
     <t>University of Torino</t>
   </si>
   <si>
-    <t>INFN Pisa / Belle II</t>
-  </si>
-  <si>
-    <t>University of Pisa-INFN Pisa</t>
-  </si>
-  <si>
     <t>Ghent University (BE)</t>
   </si>
   <si>
@@ -1678,9 +1669,6 @@
     <t>INFN-LNF</t>
   </si>
   <si>
-    <t>INFN</t>
-  </si>
-  <si>
     <t>Charles University</t>
   </si>
   <si>
@@ -2719,9 +2707,6 @@
     <t>Departamento de Física Universidade de Coimbra and LIP</t>
   </si>
   <si>
-    <t>INFN Bari</t>
-  </si>
-  <si>
     <t>Johannes Gutenberg-University Mainz</t>
   </si>
   <si>
@@ -2746,12 +2731,6 @@
     <t>Max Planck Institut für Physik - Werner Heisenberg Institute</t>
   </si>
   <si>
-    <t>LNF</t>
-  </si>
-  <si>
-    <t>INFN Pisa</t>
-  </si>
-  <si>
     <t>University of Michigan</t>
   </si>
   <si>
@@ -3364,9 +3343,6 @@
     <t>University of West Bohemia</t>
   </si>
   <si>
-    <t>Instituto Nazionale di Fisica Nucleare</t>
-  </si>
-  <si>
     <t>University of Torino and Istituto Nazionale di Fisica Nucleare</t>
   </si>
   <si>
@@ -3400,9 +3376,6 @@
     <t>University of Zürich</t>
   </si>
   <si>
-    <t>University of Pisa and INFN-Pisa</t>
-  </si>
-  <si>
     <t>AGH-UST</t>
   </si>
   <si>
@@ -3464,6 +3437,84 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>INFN - Pisa</t>
+  </si>
+  <si>
+    <t>INFN - Catania</t>
+  </si>
+  <si>
+    <t>INFN - Padova</t>
+  </si>
+  <si>
+    <t>INFN - Bologna</t>
+  </si>
+  <si>
+    <t>INFN - Torino</t>
+  </si>
+  <si>
+    <t>INFN - Roma1</t>
+  </si>
+  <si>
+    <t>INFN - Ferrara</t>
+  </si>
+  <si>
+    <t>INFN - Pavia</t>
+  </si>
+  <si>
+    <t>INFN - LNGS</t>
+  </si>
+  <si>
+    <t>INFN - Pisa/University of Siena</t>
+  </si>
+  <si>
+    <t>INFN - Trieste</t>
+  </si>
+  <si>
+    <t>INFN - Firenze</t>
+  </si>
+  <si>
+    <t>INFN - LNF</t>
+  </si>
+  <si>
+    <t>INFN - Cosenza</t>
+  </si>
+  <si>
+    <t>INFN - Perugia</t>
+  </si>
+  <si>
+    <t>INFN - TIFPA</t>
+  </si>
+  <si>
+    <t>INFN - Pisa / Belle II</t>
+  </si>
+  <si>
+    <t>University of Pisa-INFN - Pisa</t>
+  </si>
+  <si>
+    <t>INFN - Bari</t>
+  </si>
+  <si>
+    <t>INFN - Roma</t>
+  </si>
+  <si>
+    <t>INFN - Milano</t>
+  </si>
+  <si>
+    <t>INFN - Genova</t>
+  </si>
+  <si>
+    <t>INFN - Napoli</t>
+  </si>
+  <si>
+    <t>INFN - Roma3</t>
+  </si>
+  <si>
+    <t>INFN - Cagliari</t>
+  </si>
+  <si>
+    <t>University of Pisa and INFN - Pisa</t>
   </si>
 </sst>
 </file>
@@ -4055,7 +4106,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4064,21 +4115,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>966</v>
+        <v>959</v>
       </c>
       <c r="E2" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="F2" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="G2" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4087,21 +4138,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="E3" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="F3" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="G3" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4110,21 +4161,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="E4" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="F4" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="G4" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4133,21 +4184,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="E5" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="F5" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="G5" t="s">
-        <v>1106</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4156,21 +4207,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="E6" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="F6" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4179,21 +4230,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>971</v>
+        <v>964</v>
       </c>
       <c r="E7" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="F7" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="G7" t="s">
-        <v>1107</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4202,21 +4253,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>972</v>
+        <v>965</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F8" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4225,21 +4276,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>973</v>
+        <v>966</v>
       </c>
       <c r="E9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F9" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="G9" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4248,21 +4299,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="E10" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="F10" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4271,21 +4322,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>975</v>
+        <v>968</v>
       </c>
       <c r="E11" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="F11" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G11" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>918</v>
+        <v>911</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4294,21 +4345,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>976</v>
+        <v>969</v>
       </c>
       <c r="E12" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
       <c r="F12" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="G12" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>919</v>
+        <v>912</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4317,21 +4368,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="G13" t="s">
-        <v>1111</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4340,21 +4391,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="E14" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="F14" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4363,21 +4414,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="E15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F15" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="G15" t="s">
-        <v>549</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4386,21 +4437,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>980</v>
+        <v>973</v>
       </c>
       <c r="E16" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="F16" t="s">
-        <v>1066</v>
+        <v>1059</v>
       </c>
       <c r="G16" t="s">
-        <v>1112</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4409,21 +4460,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>981</v>
+        <v>974</v>
       </c>
       <c r="E17" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="F17" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G17" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>924</v>
+        <v>917</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4432,21 +4483,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>982</v>
+        <v>975</v>
       </c>
       <c r="E18" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="F18" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4455,21 +4506,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>983</v>
+        <v>976</v>
       </c>
       <c r="E19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F19" t="s">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4478,21 +4529,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="E20" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="F20" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="G20" t="s">
-        <v>1113</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4501,21 +4552,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>985</v>
+        <v>978</v>
       </c>
       <c r="E21" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="F21" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="G21" t="s">
-        <v>1114</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4524,21 +4575,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="E22" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="F22" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>929</v>
+        <v>922</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4547,21 +4598,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="E23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F23" t="s">
-        <v>1072</v>
+        <v>1065</v>
       </c>
       <c r="G23" t="s">
-        <v>1115</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>930</v>
+        <v>923</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4570,21 +4621,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>988</v>
+        <v>981</v>
       </c>
       <c r="E24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F24" t="s">
-        <v>1073</v>
+        <v>1066</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>931</v>
+        <v>924</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4593,21 +4644,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="G25" t="s">
-        <v>906</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>932</v>
+        <v>925</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4616,21 +4667,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="E26" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F26" t="s">
-        <v>1074</v>
+        <v>1067</v>
       </c>
       <c r="G26" t="s">
-        <v>1116</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4639,21 +4690,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="E27" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="F27" t="s">
-        <v>1075</v>
+        <v>1068</v>
       </c>
       <c r="G27" t="s">
-        <v>1117</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>934</v>
+        <v>927</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4662,21 +4713,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="E28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F28" t="s">
-        <v>1076</v>
+        <v>1069</v>
       </c>
       <c r="G28" t="s">
-        <v>121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>935</v>
+        <v>928</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4685,21 +4736,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="E29" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F29" t="s">
-        <v>1077</v>
+        <v>1070</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4708,21 +4759,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="E30" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="F30" t="s">
-        <v>1078</v>
+        <v>1071</v>
       </c>
       <c r="G30" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>937</v>
+        <v>930</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4731,21 +4782,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="E31" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="F31" t="s">
-        <v>1079</v>
+        <v>1072</v>
       </c>
       <c r="G31" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4754,21 +4805,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="E32" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F32" t="s">
-        <v>1080</v>
+        <v>1073</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>939</v>
+        <v>932</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4777,21 +4828,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="E33" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="F33" t="s">
-        <v>1081</v>
+        <v>1074</v>
       </c>
       <c r="G33" t="s">
-        <v>1118</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>940</v>
+        <v>933</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4800,21 +4851,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="E34" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="F34" t="s">
-        <v>1082</v>
+        <v>1075</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>941</v>
+        <v>934</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4823,21 +4874,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1083</v>
+        <v>1076</v>
       </c>
       <c r="G35" t="s">
-        <v>1119</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4846,21 +4897,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>1000</v>
+        <v>993</v>
       </c>
       <c r="E36" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="F36" t="s">
-        <v>1084</v>
+        <v>1077</v>
       </c>
       <c r="G36" t="s">
-        <v>1120</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>943</v>
+        <v>936</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4869,21 +4920,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>1001</v>
+        <v>994</v>
       </c>
       <c r="E37" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="F37" t="s">
-        <v>1085</v>
+        <v>1078</v>
       </c>
       <c r="G37" t="s">
-        <v>1121</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4892,21 +4943,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>1002</v>
+        <v>995</v>
       </c>
       <c r="E38" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="F38" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4915,21 +4966,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="E39" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="F39" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>946</v>
+        <v>939</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4938,21 +4989,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="E40" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="F40" t="s">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="G40" t="s">
-        <v>1122</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -4961,21 +5012,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E41" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F41" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="G41" t="s">
-        <v>1123</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -4984,21 +5035,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="E42" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="F42" t="s">
-        <v>1089</v>
+        <v>1082</v>
       </c>
       <c r="G42" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>949</v>
+        <v>942</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5007,21 +5058,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1007</v>
+        <v>1000</v>
       </c>
       <c r="E43" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="F43" t="s">
-        <v>1090</v>
+        <v>1083</v>
       </c>
       <c r="G43" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>950</v>
+        <v>943</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5030,7 +5081,7 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="E44" t="s">
         <v>168</v>
@@ -5039,12 +5090,12 @@
         <v>184</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>951</v>
+        <v>944</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5053,21 +5104,21 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F45" t="s">
-        <v>1091</v>
+        <v>1084</v>
       </c>
       <c r="G45" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>952</v>
+        <v>945</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5076,21 +5127,21 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="E46" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F46" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>953</v>
+        <v>946</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5099,21 +5150,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="E47" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="F47" t="s">
-        <v>1093</v>
+        <v>1086</v>
       </c>
       <c r="G47" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>954</v>
+        <v>947</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5122,21 +5173,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="E48" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="F48" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="G48" t="s">
-        <v>1144</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>955</v>
+        <v>948</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5145,21 +5196,21 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="E49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F49" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G49" t="s">
-        <v>121</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>956</v>
+        <v>949</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5168,21 +5219,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1014</v>
+        <v>1007</v>
       </c>
       <c r="E50" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F50" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="G50" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>957</v>
+        <v>950</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5191,21 +5242,21 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="E51" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="F51" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="G51" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>958</v>
+        <v>951</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5214,21 +5265,21 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="E52" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="F52" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="G52" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>959</v>
+        <v>952</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5237,21 +5288,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="E53" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="F53" t="s">
-        <v>1098</v>
+        <v>1091</v>
       </c>
       <c r="G53" t="s">
-        <v>1144</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5260,21 +5311,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="E54" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="F54" t="s">
-        <v>1099</v>
+        <v>1092</v>
       </c>
       <c r="G54" t="s">
-        <v>1144</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5283,21 +5334,21 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="E55" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F55" t="s">
-        <v>1100</v>
+        <v>1093</v>
       </c>
       <c r="G55" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5306,21 +5357,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1020</v>
+        <v>1013</v>
       </c>
       <c r="E56" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="F56" t="s">
-        <v>1101</v>
+        <v>1094</v>
       </c>
       <c r="G56" t="s">
-        <v>1126</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>963</v>
+        <v>956</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5329,21 +5380,21 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1021</v>
+        <v>1014</v>
       </c>
       <c r="E57" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F57" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="G57" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="B58">
         <v>171955</v>
@@ -5352,21 +5403,21 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1022</v>
+        <v>1015</v>
       </c>
       <c r="E58" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="F58" t="s">
-        <v>1094</v>
+        <v>1087</v>
       </c>
       <c r="G58" t="s">
-        <v>1144</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="B59">
         <v>171965</v>
@@ -5375,16 +5426,16 @@
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>1023</v>
+        <v>1016</v>
       </c>
       <c r="E59" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F59" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="G59" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -5515,7 +5566,7 @@
         <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -5561,7 +5612,7 @@
         <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -5644,7 +5695,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5653,7 +5704,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -5676,7 +5727,7 @@
         <v>109</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -5722,7 +5773,7 @@
         <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -5745,7 +5796,7 @@
         <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -5814,7 +5865,7 @@
         <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -5945,7 +5996,7 @@
         <v>179</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -5968,7 +6019,7 @@
         <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -6037,7 +6088,7 @@
         <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -6083,7 +6134,7 @@
         <v>185</v>
       </c>
       <c r="G9" t="s">
-        <v>196</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -6106,7 +6157,7 @@
         <v>186</v>
       </c>
       <c r="G10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -6129,7 +6180,7 @@
         <v>187</v>
       </c>
       <c r="G11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -6152,7 +6203,7 @@
         <v>188</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -6175,7 +6226,7 @@
         <v>189</v>
       </c>
       <c r="G13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -6221,7 +6272,7 @@
         <v>191</v>
       </c>
       <c r="G15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -6244,7 +6295,7 @@
         <v>192</v>
       </c>
       <c r="G16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -6267,7 +6318,7 @@
         <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6311,7 +6362,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B2">
         <v>166500</v>
@@ -6320,21 +6371,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B3">
         <v>166535</v>
@@ -6343,13 +6394,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E3" t="s">
         <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G3" t="s">
         <v>119</v>
@@ -6357,7 +6408,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B4">
         <v>166543</v>
@@ -6366,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G4" t="s">
         <v>125</v>
@@ -6380,7 +6431,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B5">
         <v>166549</v>
@@ -6389,21 +6440,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G5" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B6">
         <v>166616</v>
@@ -6412,21 +6463,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B7">
         <v>166693</v>
@@ -6435,21 +6486,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B8">
         <v>166706</v>
@@ -6458,21 +6509,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F8" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B9">
         <v>166721</v>
@@ -6481,21 +6532,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B10">
         <v>166724</v>
@@ -6504,13 +6555,13 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F10" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G10" t="s">
         <v>121</v>
@@ -6518,7 +6569,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B11">
         <v>166768</v>
@@ -6527,13 +6578,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E11" t="s">
         <v>82</v>
       </c>
       <c r="F11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G11" t="s">
         <v>121</v>
@@ -6541,7 +6592,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B12">
         <v>166764</v>
@@ -6550,21 +6601,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
         <v>83</v>
       </c>
       <c r="F12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B13">
         <v>166805</v>
@@ -6573,21 +6624,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B14">
         <v>167802</v>
@@ -6596,21 +6647,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B15">
         <v>167855</v>
@@ -6619,13 +6670,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F15" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -6633,7 +6684,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B16">
         <v>166537</v>
@@ -6642,21 +6693,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G16" t="s">
-        <v>121</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B17">
         <v>166548</v>
@@ -6665,21 +6716,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F17" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18">
         <v>166588</v>
@@ -6688,21 +6739,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B19">
         <v>166642</v>
@@ -6711,13 +6762,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G19" t="s">
         <v>119</v>
@@ -6725,7 +6776,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B20">
         <v>166665</v>
@@ -6734,7 +6785,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
         <v>168</v>
@@ -6743,12 +6794,12 @@
         <v>184</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B21">
         <v>166688</v>
@@ -6757,21 +6808,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F21" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22">
         <v>166722</v>
@@ -6780,21 +6831,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F22" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G22" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B23">
         <v>166769</v>
@@ -6803,13 +6854,13 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F23" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G23" t="s">
         <v>121</v>
@@ -6817,7 +6868,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B24">
         <v>166471</v>
@@ -6826,21 +6877,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B25">
         <v>166465</v>
@@ -6849,13 +6900,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E25" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F25" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G25" t="s">
         <v>119</v>
@@ -6863,7 +6914,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B26">
         <v>166491</v>
@@ -6872,21 +6923,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G26" t="s">
-        <v>121</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B27">
         <v>166547</v>
@@ -6895,21 +6946,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B28">
         <v>166554</v>
@@ -6918,21 +6969,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E28" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F28" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G28" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B29">
         <v>166787</v>
@@ -6941,21 +6992,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F29" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G29" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B30">
         <v>166536</v>
@@ -6964,13 +7015,13 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E30" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F30" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G30" t="s">
         <v>119</v>
@@ -6978,7 +7029,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B31">
         <v>166464</v>
@@ -6987,21 +7038,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E31" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G31" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B32">
         <v>166555</v>
@@ -7010,21 +7061,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E32" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F32" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B33">
         <v>166562</v>
@@ -7033,21 +7084,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F33" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B34">
         <v>166586</v>
@@ -7056,21 +7107,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E34" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G34" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B35">
         <v>166617</v>
@@ -7079,21 +7130,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F35" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B36">
         <v>166634</v>
@@ -7102,21 +7153,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E36" t="s">
         <v>90</v>
       </c>
       <c r="F36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B37">
         <v>166639</v>
@@ -7125,21 +7176,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E37" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F37" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B38">
         <v>166647</v>
@@ -7148,21 +7199,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E38" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G38" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B39">
         <v>166670</v>
@@ -7171,21 +7222,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E39" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F39" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G39" t="s">
-        <v>397</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B40">
         <v>166686</v>
@@ -7194,21 +7245,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E40" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F40" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G40" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B41">
         <v>166689</v>
@@ -7217,21 +7268,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E41" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F41" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G41" t="s">
-        <v>398</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B42">
         <v>166690</v>
@@ -7240,21 +7291,21 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E42" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F42" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G42" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B43">
         <v>166726</v>
@@ -7263,21 +7314,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E43" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F43" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G43" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B44">
         <v>166812</v>
@@ -7286,21 +7337,21 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E44" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F44" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G44" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B45">
         <v>167673</v>
@@ -7309,21 +7360,21 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E45" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F45" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G45" t="s">
-        <v>121</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B46">
         <v>171868</v>
@@ -7332,21 +7383,21 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E46" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F46" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G46" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B47">
         <v>172076</v>
@@ -7355,16 +7406,16 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E47" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G47" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
@@ -7378,16 +7429,16 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1138</v>
+        <v>1129</v>
       </c>
       <c r="E48" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="F48" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="G48" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -7431,7 +7482,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B2">
         <v>166631</v>
@@ -7440,21 +7491,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B3">
         <v>166646</v>
@@ -7463,21 +7514,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F3" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B4">
         <v>166660</v>
@@ -7486,21 +7537,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E4" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B5">
         <v>166661</v>
@@ -7509,21 +7560,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F5" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="G5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B6">
         <v>166699</v>
@@ -7532,21 +7583,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F6" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G6" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B7">
         <v>166701</v>
@@ -7555,21 +7606,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="G7" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B8">
         <v>166747</v>
@@ -7578,21 +7629,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E8" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F8" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B9">
         <v>166487</v>
@@ -7601,21 +7652,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G9" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B10">
         <v>166560</v>
@@ -7624,21 +7675,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E10" t="s">
         <v>164</v>
       </c>
       <c r="F10" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="G10" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B11">
         <v>166597</v>
@@ -7647,21 +7698,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B12">
         <v>166604</v>
@@ -7670,13 +7721,13 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E12" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F12" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="G12" t="s">
         <v>119</v>
@@ -7684,7 +7735,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B13">
         <v>166607</v>
@@ -7693,21 +7744,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F13" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B14">
         <v>166612</v>
@@ -7716,21 +7767,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E14" t="s">
         <v>162</v>
       </c>
       <c r="F14" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B15">
         <v>166627</v>
@@ -7739,21 +7790,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F15" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B16">
         <v>166729</v>
@@ -7762,21 +7813,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E16" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G16" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B17">
         <v>166750</v>
@@ -7785,21 +7836,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E17" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G17" t="s">
-        <v>121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B18">
         <v>171014</v>
@@ -7808,21 +7859,21 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E18" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F18" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G18" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B19">
         <v>171701</v>
@@ -7831,21 +7882,21 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E19" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F19" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="G19" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B20">
         <v>167817</v>
@@ -7854,16 +7905,16 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -7907,7 +7958,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -7916,21 +7967,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E2" t="s">
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -7939,21 +7990,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="G3" t="s">
-        <v>549</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -7962,21 +8013,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -7985,21 +8036,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F5" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B6">
         <v>166643</v>
@@ -8008,21 +8059,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E6" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F6" t="s">
-        <v>1143</v>
+        <v>1134</v>
       </c>
       <c r="G6" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B7">
         <v>166685</v>
@@ -8031,21 +8082,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E7" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F7" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="G7" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B8">
         <v>166740</v>
@@ -8054,7 +8105,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E8" t="s">
         <v>173</v>
@@ -8063,12 +8114,12 @@
         <v>189</v>
       </c>
       <c r="G8" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B9">
         <v>166754</v>
@@ -8077,21 +8128,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E9" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F9" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B10">
         <v>166475</v>
@@ -8100,21 +8151,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E10" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F10" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="G10" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B11">
         <v>166511</v>
@@ -8123,21 +8174,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F11" t="s">
-        <v>1142</v>
+        <v>1133</v>
       </c>
       <c r="G11" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B12">
         <v>166518</v>
@@ -8146,21 +8197,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F12" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B13">
         <v>166524</v>
@@ -8169,21 +8220,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E13" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F13" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G13" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B14">
         <v>166525</v>
@@ -8192,21 +8243,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F14" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B15">
         <v>166563</v>
@@ -8215,13 +8266,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F15" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -8229,7 +8280,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B16">
         <v>166608</v>
@@ -8238,21 +8289,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E16" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F16" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="G16" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B17">
         <v>166659</v>
@@ -8261,21 +8312,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E17" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F17" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G17" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B18">
         <v>166664</v>
@@ -8284,21 +8335,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F18" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B19">
         <v>166727</v>
@@ -8307,21 +8358,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E19" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F19" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G19" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B20">
         <v>166738</v>
@@ -8330,16 +8381,16 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E20" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F20" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
   </sheetData>
@@ -8383,7 +8434,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8392,21 +8443,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E2" t="s">
         <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8415,21 +8466,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="E3" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="F3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8438,21 +8489,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E4" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F4" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8461,21 +8512,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E5" t="s">
         <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="G5" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8484,21 +8535,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="E6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="F6" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="G6" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B7">
         <v>167882</v>
@@ -8507,21 +8558,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F7" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B8">
         <v>166696</v>
@@ -8530,21 +8581,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="E8" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="F8" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="G8" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B9">
         <v>166700</v>
@@ -8553,21 +8604,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E9" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="F9" t="s">
+        <v>587</v>
+      </c>
+      <c r="G9" t="s">
         <v>591</v>
-      </c>
-      <c r="G9" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B10">
         <v>166792</v>
@@ -8576,16 +8627,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="E10" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F10" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
   </sheetData>
@@ -8629,7 +8680,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8638,21 +8689,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -8661,21 +8712,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="E3" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F3" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G3" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -8684,21 +8735,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E4" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="F4" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="G4" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -8707,21 +8758,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="E5" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="F5" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="G5" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -8730,21 +8781,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E6" t="s">
         <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="G6" t="s">
-        <v>121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -8753,21 +8804,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="E7" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="F7" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -8776,21 +8827,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E8" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F8" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -8799,21 +8850,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="E9" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F9" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="G9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -8822,21 +8873,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="E10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F10" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -8845,21 +8896,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E11" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F11" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -8868,21 +8919,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E12" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F12" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="G12" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -8891,21 +8942,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F13" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -8914,21 +8965,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="E14" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="F14" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B15">
         <v>166705</v>
@@ -8937,21 +8988,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="E15" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="F15" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G15" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B16">
         <v>166743</v>
@@ -8960,21 +9011,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F16" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G16" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B17">
         <v>166814</v>
@@ -8983,13 +9034,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="E17" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="F17" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="G17" t="s">
         <v>125</v>
@@ -8997,7 +9048,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B18">
         <v>166497</v>
@@ -9006,21 +9057,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="E18" t="s">
         <v>165</v>
       </c>
       <c r="F18" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="G18" t="s">
-        <v>121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B19">
         <v>166733</v>
@@ -9029,21 +9080,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="E19" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F19" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="G19" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B20">
         <v>166496</v>
@@ -9052,21 +9103,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="E20" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="F20" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B21">
         <v>166725</v>
@@ -9075,21 +9126,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E21" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F21" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="G21" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B22">
         <v>166783</v>
@@ -9098,21 +9149,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="E22" t="s">
         <v>93</v>
       </c>
       <c r="F22" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B23">
         <v>166468</v>
@@ -9121,21 +9172,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E23" t="s">
         <v>162</v>
       </c>
       <c r="F23" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="G23" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B24">
         <v>166494</v>
@@ -9144,21 +9195,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E24" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F24" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="G24" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B25">
         <v>166509</v>
@@ -9167,21 +9218,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="E25" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="F25" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="G25" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B26">
         <v>166531</v>
@@ -9190,21 +9241,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="E26" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="F26" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G26" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B27">
         <v>166532</v>
@@ -9213,21 +9264,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="E27" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F27" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G27" t="s">
-        <v>121</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B28">
         <v>166559</v>
@@ -9236,21 +9287,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="E28" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F28" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="G28" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B29">
         <v>166564</v>
@@ -9259,21 +9310,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="E29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F29" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B30">
         <v>166565</v>
@@ -9282,21 +9333,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="E30" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F30" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G30" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B31">
         <v>166606</v>
@@ -9305,21 +9356,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="E31" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="F31" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G31" t="s">
-        <v>121</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B32">
         <v>166658</v>
@@ -9328,21 +9379,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="E32" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F32" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G32" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B33">
         <v>166667</v>
@@ -9351,21 +9402,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="E33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F33" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B34">
         <v>166671</v>
@@ -9374,21 +9425,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F34" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B35">
         <v>166684</v>
@@ -9397,21 +9448,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E35" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F35" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="G35" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B36">
         <v>166730</v>
@@ -9420,21 +9471,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="E36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F36" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G36" t="s">
-        <v>121</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B37">
         <v>166736</v>
@@ -9443,21 +9494,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="E37" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="F37" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B38">
         <v>166739</v>
@@ -9466,21 +9517,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="E38" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="F38" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="G38" t="s">
-        <v>121</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B39">
         <v>166749</v>
@@ -9489,21 +9540,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="E39" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F39" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="G39" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B40">
         <v>166766</v>
@@ -9512,21 +9563,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="E40" t="s">
         <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B41">
         <v>167683</v>
@@ -9535,7 +9586,7 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="E41" t="s">
         <v>164</v>
@@ -9544,12 +9595,12 @@
         <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B42">
         <v>172067</v>
@@ -9558,18 +9609,18 @@
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="E42" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="F42" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B43">
         <v>172078</v>
@@ -9578,16 +9629,16 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E43" t="s">
-        <v>1131</v>
+        <v>1122</v>
       </c>
       <c r="F43" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="G43" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
     </row>
   </sheetData>
@@ -9631,7 +9682,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B2">
         <v>166521</v>
@@ -9640,21 +9691,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="E2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="F2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B3">
         <v>166508</v>
@@ -9663,21 +9714,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F3" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B4">
         <v>166540</v>
@@ -9686,21 +9737,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="E4" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="F4" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="G4" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B5">
         <v>166541</v>
@@ -9709,21 +9760,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="E5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="F5" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="G5" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B6">
         <v>166561</v>
@@ -9732,21 +9783,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="E6" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="F6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G6" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B7">
         <v>166619</v>
@@ -9755,21 +9806,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E7" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="F7" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="G7" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B8">
         <v>166623</v>
@@ -9778,21 +9829,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="E8" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="F8" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B9">
         <v>166630</v>
@@ -9801,21 +9852,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F9" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B10">
         <v>166673</v>
@@ -9824,21 +9875,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E10" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
       <c r="F10" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="G10" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B11">
         <v>166675</v>
@@ -9847,21 +9898,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="E11" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
       <c r="F11" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="G11" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B12">
         <v>166711</v>
@@ -9870,21 +9921,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="E12" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F12" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="G12" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B13">
         <v>166755</v>
@@ -9893,21 +9944,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="E13" t="s">
         <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="G13" t="s">
-        <v>121</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B14">
         <v>166757</v>
@@ -9916,21 +9967,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="E14" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="F14" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G14" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B15">
         <v>168287</v>
@@ -9939,21 +9990,21 @@
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E15" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="F15" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="G15" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B16">
         <v>171990</v>
@@ -9962,21 +10013,21 @@
         <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E16" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F16" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="G16" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B17">
         <v>166567</v>
@@ -9985,21 +10036,21 @@
         <v>17</v>
       </c>
       <c r="D17" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E17" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
       <c r="F17" t="s">
-        <v>1135</v>
+        <v>1126</v>
       </c>
       <c r="G17" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B18">
         <v>166538</v>
@@ -10008,21 +10059,21 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E18" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="F18" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="G18" t="s">
-        <v>896</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B19">
         <v>166678</v>
@@ -10031,21 +10082,21 @@
         <v>19</v>
       </c>
       <c r="D19" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E19" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F19" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="G19" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B20">
         <v>167682</v>
@@ -10054,21 +10105,21 @@
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E20" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F20" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="G20" t="s">
-        <v>549</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B21">
         <v>166529</v>
@@ -10077,21 +10128,21 @@
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="E21" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="F21" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="G21" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B22">
         <v>166472</v>
@@ -10100,21 +10151,21 @@
         <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E22" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="F22" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="G22" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B23">
         <v>166571</v>
@@ -10123,21 +10174,21 @@
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E23" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F23" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="G23" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B24">
         <v>166575</v>
@@ -10146,21 +10197,21 @@
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="E24" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F24" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B25">
         <v>166590</v>
@@ -10169,21 +10220,21 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="E25" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="F25" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="G25" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B26">
         <v>166598</v>
@@ -10192,21 +10243,21 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="E26" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F26" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="G26" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B27">
         <v>166629</v>
@@ -10215,21 +10266,21 @@
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="E27" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="F27" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="G27" t="s">
-        <v>121</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B28">
         <v>166650</v>
@@ -10238,21 +10289,21 @@
         <v>8</v>
       </c>
       <c r="D28" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="E28" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="F28" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="G28" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B29">
         <v>166657</v>
@@ -10261,13 +10312,13 @@
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="E29" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F29" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G29" t="s">
         <v>119</v>
@@ -10275,7 +10326,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B30">
         <v>166687</v>
@@ -10284,21 +10335,21 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="E30" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="F30" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="G30" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B31">
         <v>166691</v>
@@ -10307,21 +10358,21 @@
         <v>11</v>
       </c>
       <c r="D31" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="E31" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G31" t="s">
-        <v>398</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B32">
         <v>166708</v>
@@ -10330,21 +10381,21 @@
         <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="E32" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F32" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="G32" t="s">
-        <v>121</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B33">
         <v>166719</v>
@@ -10353,21 +10404,21 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="E33" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F33" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="G33" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B34">
         <v>166744</v>
@@ -10376,21 +10427,21 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E34" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F34" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="G34" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B35">
         <v>166746</v>
@@ -10399,21 +10450,21 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="E35" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="F35" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="G35" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B36">
         <v>166753</v>
@@ -10422,21 +10473,21 @@
         <v>16</v>
       </c>
       <c r="D36" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="E36" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F36" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="G36" t="s">
-        <v>905</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B37">
         <v>166779</v>
@@ -10445,21 +10496,21 @@
         <v>17</v>
       </c>
       <c r="D37" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="E37" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="F37" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B38">
         <v>166818</v>
@@ -10468,21 +10519,21 @@
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E38" t="s">
         <v>92</v>
       </c>
       <c r="F38" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="G38" t="s">
-        <v>906</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B39">
         <v>167482</v>
@@ -10491,21 +10542,21 @@
         <v>19</v>
       </c>
       <c r="D39" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E39" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="F39" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="G39" t="s">
-        <v>121</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B40">
         <v>167812</v>
@@ -10514,21 +10565,21 @@
         <v>20</v>
       </c>
       <c r="D40" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E40" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="F40" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B41">
         <v>171332</v>
@@ -10537,16 +10588,16 @@
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="E41" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="F41" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="G41" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF3E890-575E-254C-AD1D-991D3F846272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755A24DD-3FDE-B842-BA11-0379498D879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4072,7 +4072,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -5394,47 +5394,24 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B58">
-        <v>171955</v>
+        <v>171965</v>
       </c>
       <c r="C58">
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E58" t="s">
-        <v>1041</v>
+        <v>698</v>
       </c>
       <c r="F58" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="G58" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>958</v>
-      </c>
-      <c r="B59">
-        <v>171965</v>
-      </c>
-      <c r="C59">
-        <v>18</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E59" t="s">
-        <v>698</v>
-      </c>
-      <c r="F59" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G59" t="s">
         <v>1116</v>
       </c>
     </row>
@@ -9648,7 +9625,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -10600,6 +10577,29 @@
         <v>900</v>
       </c>
     </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B42">
+        <v>171955</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1087</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755A24DD-3FDE-B842-BA11-0379498D879B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC768A8D-7575-F24D-A427-DDD3BBB4E33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Program" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1163">
   <si>
     <t>Session ID</t>
   </si>
@@ -3515,6 +3515,9 @@
   </si>
   <si>
     <t>University of Pisa and INFN - Pisa</t>
+  </si>
+  <si>
+    <t>Test beam results and future R&amp;D of the fibre-sampling Dual-Readout Calorimeter</t>
   </si>
 </sst>
 </file>
@@ -7425,7 +7428,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7894,6 +7897,29 @@
         <v>476</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>252</v>
+      </c>
+      <c r="B21">
+        <v>172148</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E21" t="s">
+        <v>439</v>
+      </c>
+      <c r="F21" t="s">
+        <v>452</v>
+      </c>
+      <c r="G21" t="s">
+        <v>468</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7901,7 +7927,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -8368,6 +8394,29 @@
       </c>
       <c r="G20" t="s">
         <v>1136</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>399</v>
+      </c>
+      <c r="B21">
+        <v>172147</v>
+      </c>
+      <c r="C21">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E21" t="s">
+        <v>449</v>
+      </c>
+      <c r="F21" t="s">
+        <v>466</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1156</v>
       </c>
     </row>
   </sheetData>

--- a/pm2022/pm2022.xlsx
+++ b/pm2022/pm2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/galli/Documents/OrgConferenze/21PisaMeeting/pisameet/pm2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC768A8D-7575-F24D-A427-DDD3BBB4E33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5365E2-5A49-AB4D-80D4-96D69DF4ACA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="220" yWindow="500" windowWidth="31720" windowHeight="18600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1454" uniqueCount="1163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1450" uniqueCount="1162">
   <si>
     <t>Session ID</t>
   </si>
@@ -1454,9 +1454,6 @@
   </si>
   <si>
     <t>Wroclaw University of Science and Technology</t>
-  </si>
-  <si>
-    <t>Università degli studi dell'Insubria</t>
   </si>
   <si>
     <t>Paul Scherrer Institut - ETH Zürich</t>
@@ -4109,7 +4106,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B2">
         <v>166461</v>
@@ -4118,21 +4115,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="G2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B3">
         <v>166479</v>
@@ -4141,21 +4138,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B4">
         <v>166522</v>
@@ -4164,21 +4161,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B5">
         <v>166488</v>
@@ -4187,21 +4184,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E5" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="F5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G5" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B6">
         <v>166495</v>
@@ -4210,21 +4207,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F6" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G6" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B7">
         <v>166520</v>
@@ -4233,21 +4230,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F7" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G7" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B8">
         <v>166528</v>
@@ -4256,21 +4253,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E8" t="s">
         <v>303</v>
       </c>
       <c r="F8" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G8" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B9">
         <v>166523</v>
@@ -4279,21 +4276,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E9" t="s">
         <v>330</v>
       </c>
       <c r="F9" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G9" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B10">
         <v>166570</v>
@@ -4302,21 +4299,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="E10" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="F10" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G10" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B11">
         <v>166578</v>
@@ -4325,21 +4322,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E11" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F11" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B12">
         <v>166569</v>
@@ -4348,21 +4345,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E12" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F12" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G12" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B13">
         <v>166734</v>
@@ -4371,21 +4368,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E13" t="s">
         <v>83</v>
       </c>
       <c r="F13" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G13" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B14">
         <v>166637</v>
@@ -4394,21 +4391,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E14" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="F14" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G14" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B15">
         <v>166648</v>
@@ -4417,21 +4414,21 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E15" t="s">
         <v>329</v>
       </c>
       <c r="F15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G15" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B16">
         <v>166676</v>
@@ -4440,21 +4437,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="E16" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="F16" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G16" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B17">
         <v>166715</v>
@@ -4463,21 +4460,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="E17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F17" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G17" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B18">
         <v>166692</v>
@@ -4486,21 +4483,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E18" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F18" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G18" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B19">
         <v>166694</v>
@@ -4509,21 +4506,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E19" t="s">
         <v>297</v>
       </c>
       <c r="F19" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G19" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B20">
         <v>166709</v>
@@ -4532,21 +4529,21 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E20" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="F20" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G20" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B21">
         <v>166717</v>
@@ -4555,21 +4552,21 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E21" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F21" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G21" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B22">
         <v>166751</v>
@@ -4578,21 +4575,21 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E22" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F22" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G22" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B23">
         <v>166777</v>
@@ -4601,21 +4598,21 @@
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E23" t="s">
         <v>309</v>
       </c>
       <c r="F23" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G23" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B24">
         <v>166789</v>
@@ -4624,21 +4621,21 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E24" t="s">
         <v>297</v>
       </c>
       <c r="F24" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G24" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B25">
         <v>166819</v>
@@ -4647,21 +4644,21 @@
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E25" t="s">
         <v>92</v>
       </c>
       <c r="F25" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G25" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B26">
         <v>166527</v>
@@ -4670,21 +4667,21 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E26" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F26" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G26" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B27">
         <v>166610</v>
@@ -4693,21 +4690,21 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E27" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="F27" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G27" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B28">
         <v>166512</v>
@@ -4716,21 +4713,21 @@
         <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="E28" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F28" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G28" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B29">
         <v>166526</v>
@@ -4739,21 +4736,21 @@
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E29" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F29" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G29" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B30">
         <v>166530</v>
@@ -4762,21 +4759,21 @@
         <v>9</v>
       </c>
       <c r="D30" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E30" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F30" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G30" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B31">
         <v>166602</v>
@@ -4785,21 +4782,21 @@
         <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E31" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="F31" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G31" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B32">
         <v>166605</v>
@@ -4808,21 +4805,21 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E32" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F32" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G32" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B33">
         <v>166614</v>
@@ -4831,21 +4828,21 @@
         <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E33" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F33" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G33" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B34">
         <v>166618</v>
@@ -4854,21 +4851,21 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E34" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F34" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G34" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B35">
         <v>166620</v>
@@ -4877,21 +4874,21 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E35" t="s">
         <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G35" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B36">
         <v>166621</v>
@@ -4900,21 +4897,21 @@
         <v>15</v>
       </c>
       <c r="D36" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E36" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F36" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G36" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B37">
         <v>166632</v>
@@ -4923,21 +4920,21 @@
         <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E37" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F37" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G37" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B38">
         <v>166649</v>
@@ -4946,21 +4943,21 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="E38" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F38" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G38" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B39">
         <v>166652</v>
@@ -4969,21 +4966,21 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E39" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F39" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G39" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B40">
         <v>166672</v>
@@ -4992,21 +4989,21 @@
         <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E40" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F40" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G40" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B41">
         <v>166677</v>
@@ -5015,21 +5012,21 @@
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F41" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G41" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B42">
         <v>166680</v>
@@ -5038,13 +5035,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E42" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F42" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G42" t="s">
         <v>469</v>
@@ -5052,7 +5049,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B43">
         <v>166718</v>
@@ -5061,21 +5058,21 @@
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E43" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F43" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G43" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B44">
         <v>166720</v>
@@ -5084,7 +5081,7 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E44" t="s">
         <v>168</v>
@@ -5093,12 +5090,12 @@
         <v>184</v>
       </c>
       <c r="G44" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B45">
         <v>166742</v>
@@ -5107,21 +5104,21 @@
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E45" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F45" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G45" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B46">
         <v>166752</v>
@@ -5130,21 +5127,21 @@
         <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E46" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F46" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G46" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B47">
         <v>166761</v>
@@ -5153,21 +5150,21 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E47" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F47" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G47" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B48">
         <v>166772</v>
@@ -5176,21 +5173,21 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E48" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F48" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G48" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B49">
         <v>166786</v>
@@ -5199,21 +5196,21 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E49" t="s">
         <v>309</v>
       </c>
       <c r="F49" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G49" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B50">
         <v>166815</v>
@@ -5222,21 +5219,21 @@
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="E50" t="s">
         <v>298</v>
       </c>
       <c r="F50" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G50" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B51">
         <v>166816</v>
@@ -5245,21 +5242,21 @@
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E51" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F51" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G51" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B52">
         <v>166817</v>
@@ -5268,21 +5265,21 @@
         <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E52" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F52" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G52" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B53">
         <v>167826</v>
@@ -5291,21 +5288,21 @@
         <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E53" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="F53" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G53" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B54">
         <v>167837</v>
@@ -5314,21 +5311,21 @@
         <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E54" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F54" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G54" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B55">
         <v>170164</v>
@@ -5337,21 +5334,21 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E55" t="s">
         <v>330</v>
       </c>
       <c r="F55" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G55" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B56">
         <v>170518</v>
@@ -5360,21 +5357,21 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E56" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F56" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G56" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B57">
         <v>171826</v>
@@ -5383,21 +5380,21 @@
         <v>16</v>
       </c>
       <c r="D57" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E57" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F57" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G57" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B58">
         <v>171965</v>
@@ -5406,16 +5403,16 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E58" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="F58" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G58" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
   </sheetData>
@@ -5546,7 +5543,7 @@
         <v>102</v>
       </c>
       <c r="G5" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -5592,7 +5589,7 @@
         <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -5675,7 +5672,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="E11" t="s">
         <v>89</v>
@@ -5684,7 +5681,7 @@
         <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -5707,7 +5704,7 @@
         <v>109</v>
       </c>
       <c r="G12" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -5753,7 +5750,7 @@
         <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -5776,7 +5773,7 @@
         <v>112</v>
       </c>
       <c r="G15" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -5845,7 +5842,7 @@
         <v>115</v>
       </c>
       <c r="G18" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -5976,7 +5973,7 @@
         <v>179</v>
       </c>
       <c r="G3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -5999,7 +5996,7 @@
         <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -6068,7 +6065,7 @@
         <v>183</v>
       </c>
       <c r="G7" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -6114,7 +6111,7 @@
         <v>185</v>
       </c>
       <c r="G9" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -6183,7 +6180,7 @@
         <v>188</v>
       </c>
       <c r="G12" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -6682,7 +6679,7 @@
         <v>347</v>
       </c>
       <c r="G16" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -6774,7 +6771,7 @@
         <v>184</v>
       </c>
       <c r="G20" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -6797,7 +6794,7 @@
         <v>351</v>
       </c>
       <c r="G21" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -6912,7 +6909,7 @@
         <v>356</v>
       </c>
       <c r="G26" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -7119,7 +7116,7 @@
         <v>364</v>
       </c>
       <c r="G35" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -7142,7 +7139,7 @@
         <v>365</v>
       </c>
       <c r="G36" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
@@ -7165,7 +7162,7 @@
         <v>366</v>
       </c>
       <c r="G37" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -7211,7 +7208,7 @@
         <v>368</v>
       </c>
       <c r="G39" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
@@ -7257,7 +7254,7 @@
         <v>370</v>
       </c>
       <c r="G41" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
@@ -7326,7 +7323,7 @@
         <v>373</v>
       </c>
       <c r="G44" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
@@ -7349,7 +7346,7 @@
         <v>374</v>
       </c>
       <c r="G45" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
@@ -7372,7 +7369,7 @@
         <v>375</v>
       </c>
       <c r="G46" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -7409,16 +7406,16 @@
         <v>7</v>
       </c>
       <c r="D48" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E48" t="s">
         <v>1129</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>1130</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>1131</v>
-      </c>
-      <c r="G48" t="s">
-        <v>1132</v>
       </c>
     </row>
   </sheetData>
@@ -7428,7 +7425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="12.6640625" customWidth="1"/>
@@ -7480,7 +7477,7 @@
         <v>450</v>
       </c>
       <c r="G2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -7503,7 +7500,7 @@
         <v>451</v>
       </c>
       <c r="G3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -7618,7 +7615,7 @@
         <v>456</v>
       </c>
       <c r="G8" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -7687,7 +7684,7 @@
         <v>459</v>
       </c>
       <c r="G11" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -7733,7 +7730,7 @@
         <v>461</v>
       </c>
       <c r="G13" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -7756,7 +7753,7 @@
         <v>462</v>
       </c>
       <c r="G14" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -7779,7 +7776,7 @@
         <v>375</v>
       </c>
       <c r="G15" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -7802,7 +7799,7 @@
         <v>463</v>
       </c>
       <c r="G16" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -7825,7 +7822,7 @@
         <v>464</v>
       </c>
       <c r="G17" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -7871,7 +7868,7 @@
         <v>466</v>
       </c>
       <c r="G19" t="s">
-        <v>475</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -7894,30 +7891,7 @@
         <v>467</v>
       </c>
       <c r="G20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="2">
-        <v>252</v>
-      </c>
-      <c r="B21">
-        <v>172148</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>420</v>
-      </c>
-      <c r="E21" t="s">
-        <v>439</v>
-      </c>
-      <c r="F21" t="s">
-        <v>452</v>
-      </c>
-      <c r="G21" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -7961,7 +7935,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B2">
         <v>166466</v>
@@ -7970,21 +7944,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E2" t="s">
         <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B3">
         <v>166467</v>
@@ -7993,21 +7967,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E3" t="s">
         <v>83</v>
       </c>
       <c r="F3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G3" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B4">
         <v>166519</v>
@@ -8016,21 +7990,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G4" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B5">
         <v>166550</v>
@@ -8039,21 +8013,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E5" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B6">
         <v>166643</v>
@@ -8062,21 +8036,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F6" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7">
         <v>166685</v>
@@ -8085,21 +8059,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="E7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G7" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B8">
         <v>166740</v>
@@ -8108,7 +8082,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
         <v>173</v>
@@ -8117,12 +8091,12 @@
         <v>189</v>
       </c>
       <c r="G8" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B9">
         <v>166754</v>
@@ -8131,21 +8105,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G9" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B10">
         <v>166475</v>
@@ -8154,21 +8128,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F10" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="G10" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B11">
         <v>166511</v>
@@ -8177,21 +8151,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F11" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G11" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B12">
         <v>166518</v>
@@ -8200,21 +8174,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F12" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G12" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B13">
         <v>166524</v>
@@ -8223,21 +8197,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E13" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F13" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G13" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B14">
         <v>166525</v>
@@ -8246,21 +8220,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F14" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G14" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B15">
         <v>166563</v>
@@ -8269,13 +8243,13 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E15" t="s">
         <v>439</v>
       </c>
       <c r="F15" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G15" t="s">
         <v>119</v>
@@ -8283,7 +8257,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B16">
         <v>166608</v>
@@ -8292,21 +8266,21 @@
         <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E16" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F16" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B17">
         <v>166659</v>
@@ -8315,21 +8289,21 @@
         <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E17" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F17" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="G17" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B18">
         <v>166664</v>
@@ -8338,21 +8312,21 @@
         <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E18" t="s">
         <v>303</v>
       </c>
       <c r="F18" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="G18" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B19">
         <v>166727</v>
@@ -8361,21 +8335,21 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E19" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G19" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B20">
         <v>166738</v>
@@ -8384,16 +8358,16 @@
         <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E20" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F20" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G20" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -8407,7 +8381,7 @@
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E21" t="s">
         <v>449</v>
@@ -8416,7 +8390,7 @@
         <v>466</v>
       </c>
       <c r="G21" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -8460,7 +8434,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B2">
         <v>166656</v>
@@ -8469,21 +8443,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E2" t="s">
         <v>170</v>
       </c>
       <c r="F2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="G2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B3">
         <v>166795</v>
@@ -8492,21 +8466,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="F3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="G3" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B4">
         <v>166674</v>
@@ -8515,21 +8489,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="G4" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B5">
         <v>166582</v>
@@ -8538,21 +8512,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E5" t="s">
         <v>170</v>
       </c>
       <c r="F5" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="G5" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B6">
         <v>166679</v>
@@ -8561,21 +8535,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="E6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B7">
         <v>167882</v>
@@ -8584,21 +8558,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E7" t="s">
         <v>297</v>
       </c>
       <c r="F7" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B8">
         <v>166696</v>
@@ -8607,21 +8581,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G8" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B9">
         <v>166700</v>
@@ -8630,21 +8604,21 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="F9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="G9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B10">
         <v>166792</v>
@@ -8653,16 +8627,16 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E10" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G10" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
   </sheetData>
@@ -8706,7 +8680,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B2">
         <v>166462</v>
@@ -8715,21 +8689,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B3">
         <v>166486</v>
@@ -8738,21 +8712,21 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="F3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B4">
         <v>166545</v>
@@ -8761,21 +8735,21 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="F4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B5">
         <v>166557</v>
@@ -8784,21 +8758,21 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E5" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="F5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B6">
         <v>166566</v>
@@ -8807,21 +8781,21 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E6" t="s">
         <v>170</v>
       </c>
       <c r="F6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G6" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B7">
         <v>166600</v>
@@ -8830,21 +8804,21 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G7" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B8">
         <v>166603</v>
@@ -8853,21 +8827,21 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E8" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G8" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B9">
         <v>166624</v>
@@ -8876,13 +8850,13 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="F9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G9" t="s">
         <v>471</v>
@@ -8890,7 +8864,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B10">
         <v>166628</v>
@@ -8899,21 +8873,21 @@
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E10" t="s">
         <v>297</v>
       </c>
       <c r="F10" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G10" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B11">
         <v>166636</v>
@@ -8922,21 +8896,21 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="F11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G11" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B12">
         <v>166640</v>
@@ -8945,21 +8919,21 @@
         <v>11</v>
       </c>
       <c r="D12" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="F12" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G12" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B13">
         <v>166668</v>
@@ -8968,21 +8942,21 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E13" t="s">
         <v>445</v>
       </c>
       <c r="F13" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G13" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B14">
         <v>166682</v>
@@ -8991,21 +8965,21 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F14" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
    